--- a/first_stage_optimization/lshp_operation.xlsx
+++ b/first_stage_optimization/lshp_operation.xlsx
@@ -439,10 +439,10 @@
         <v>288</v>
       </c>
       <c r="B2" t="n">
-        <v>8901.854124982217</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C2" t="n">
-        <v>24552.1504509887</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="3">
@@ -450,10 +450,10 @@
         <v>289</v>
       </c>
       <c r="B3" t="n">
-        <v>16134.66738214708</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C3" t="n">
-        <v>44500.92929869557</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>290</v>
       </c>
       <c r="B4" t="n">
-        <v>16134.66738214708</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C4" t="n">
-        <v>44500.92929869557</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="5">
@@ -472,10 +472,10 @@
         <v>291</v>
       </c>
       <c r="B5" t="n">
-        <v>16134.66738214708</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C5" t="n">
-        <v>44500.92929869557</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="6">
@@ -483,10 +483,10 @@
         <v>292</v>
       </c>
       <c r="B6" t="n">
-        <v>16134.66738214708</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C6" t="n">
-        <v>44500.92929869557</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="7">
@@ -494,10 +494,10 @@
         <v>293</v>
       </c>
       <c r="B7" t="n">
-        <v>13340.72596546899</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C7" t="n">
-        <v>36794.97624100422</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="8">
@@ -505,10 +505,10 @@
         <v>294</v>
       </c>
       <c r="B8" t="n">
-        <v>13699.21297290814</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>37783.71710530011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -516,10 +516,10 @@
         <v>295</v>
       </c>
       <c r="B9" t="n">
-        <v>2420.200107322061</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>6675.139394804333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>297</v>
       </c>
       <c r="B11" t="n">
-        <v>5243.835375634333</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14462.9908865248</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -549,10 +549,10 @@
         <v>298</v>
       </c>
       <c r="B12" t="n">
-        <v>2420.200107322061</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>6675.139394804333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -560,10 +560,10 @@
         <v>299</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>7571.621973941301</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>20883.24513659566</v>
       </c>
     </row>
     <row r="14">
@@ -571,10 +571,10 @@
         <v>300</v>
       </c>
       <c r="B14" t="n">
-        <v>2420.200107322061</v>
+        <v>4157.129133592324</v>
       </c>
       <c r="C14" t="n">
-        <v>6675.139394804333</v>
+        <v>11465.75292058619</v>
       </c>
     </row>
     <row r="15">
@@ -582,10 +582,10 @@
         <v>301</v>
       </c>
       <c r="B15" t="n">
-        <v>2420.200107322061</v>
+        <v>7859.845117504699</v>
       </c>
       <c r="C15" t="n">
-        <v>6675.139394804333</v>
+        <v>21678.19165951901</v>
       </c>
     </row>
     <row r="16">
@@ -593,10 +593,10 @@
         <v>302</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3244.59692381376</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8948.903307989189</v>
       </c>
     </row>
     <row r="17">
@@ -648,10 +648,10 @@
         <v>307</v>
       </c>
       <c r="B21" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C21" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="22">
@@ -659,10 +659,10 @@
         <v>308</v>
       </c>
       <c r="B22" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C22" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="23">
@@ -670,10 +670,10 @@
         <v>309</v>
       </c>
       <c r="B23" t="n">
-        <v>5985.027132146482</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C23" t="n">
-        <v>16507.26742301042</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="24">
@@ -681,10 +681,10 @@
         <v>310</v>
       </c>
       <c r="B24" t="n">
-        <v>9943.607275116043</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C24" t="n">
-        <v>27425.40356385391</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="25">
@@ -692,10 +692,10 @@
         <v>311</v>
       </c>
       <c r="B25" t="n">
-        <v>10910.10897839308</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C25" t="n">
-        <v>30091.10611265208</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="26">
@@ -703,10 +703,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="n">
-        <v>11744.29309637522</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C26" t="n">
-        <v>32391.86432335392</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="27">
@@ -714,10 +714,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="n">
-        <v>12276.64674128739</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C27" t="n">
-        <v>33860.1457172643</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="28">
@@ -725,10 +725,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="n">
-        <v>12578.03317065227</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C28" t="n">
-        <v>34691.39781977699</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="29">
@@ -736,10 +736,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="n">
-        <v>13227.00910138741</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C29" t="n">
-        <v>36481.33444048199</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="30">
@@ -747,10 +747,10 @@
         <v>316</v>
       </c>
       <c r="B30" t="n">
-        <v>13178.33134409655</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C30" t="n">
-        <v>36347.07661016463</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="31">
@@ -758,10 +758,10 @@
         <v>317</v>
       </c>
       <c r="B31" t="n">
-        <v>13340.72596546899</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C31" t="n">
-        <v>36794.97624100422</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="32">
@@ -769,10 +769,10 @@
         <v>318</v>
       </c>
       <c r="B32" t="n">
-        <v>13699.21297290814</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C32" t="n">
-        <v>37783.71710530011</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="33">
@@ -780,10 +780,10 @@
         <v>319</v>
       </c>
       <c r="B33" t="n">
-        <v>2420.200107322061</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>6675.139394804333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -813,10 +813,10 @@
         <v>322</v>
       </c>
       <c r="B36" t="n">
-        <v>2839.036305900561</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C36" t="n">
-        <v>7830.329001086502</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="37">
@@ -824,10 +824,10 @@
         <v>323</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="38">
@@ -835,10 +835,10 @@
         <v>324</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="39">
@@ -901,10 +901,10 @@
         <v>330</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>1649.647793852731</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>4549.883682338455</v>
       </c>
     </row>
     <row r="45">
@@ -912,10 +912,10 @@
         <v>331</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>2423.783616176349</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>6685.023049074291</v>
       </c>
     </row>
     <row r="46">
@@ -923,10 +923,10 @@
         <v>332</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2606.87476649653</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>7190.005652225482</v>
       </c>
     </row>
     <row r="47">
@@ -934,10 +934,10 @@
         <v>333</v>
       </c>
       <c r="B47" t="n">
-        <v>3488.436715026574</v>
+        <v>3759.547892638409</v>
       </c>
       <c r="C47" t="n">
-        <v>9621.436373094504</v>
+        <v>10369.18648539864</v>
       </c>
     </row>
     <row r="48">
@@ -945,10 +945,10 @@
         <v>334</v>
       </c>
       <c r="B48" t="n">
-        <v>9943.607275116043</v>
+        <v>3913.606187237279</v>
       </c>
       <c r="C48" t="n">
-        <v>27425.40356385391</v>
+        <v>10794.09374338201</v>
       </c>
     </row>
     <row r="49">
@@ -956,10 +956,10 @@
         <v>335</v>
       </c>
       <c r="B49" t="n">
-        <v>10910.10897839308</v>
+        <v>2083.727200419131</v>
       </c>
       <c r="C49" t="n">
-        <v>30091.10611265208</v>
+        <v>5747.115489112803</v>
       </c>
     </row>
     <row r="50">
@@ -967,10 +967,10 @@
         <v>336</v>
       </c>
       <c r="B50" t="n">
-        <v>8901.854124982217</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C50" t="n">
-        <v>24552.1504509887</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="51">
@@ -978,10 +978,10 @@
         <v>337</v>
       </c>
       <c r="B51" t="n">
-        <v>9312.950706695086</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C51" t="n">
-        <v>25685.99346643148</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="52">
@@ -989,10 +989,10 @@
         <v>338</v>
       </c>
       <c r="B52" t="n">
-        <v>14573.37670624126</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C52" t="n">
-        <v>40194.74285322378</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="53">
@@ -1000,10 +1000,10 @@
         <v>339</v>
       </c>
       <c r="B53" t="n">
-        <v>16134.66738214708</v>
+        <v>6321.080014189263</v>
       </c>
       <c r="C53" t="n">
-        <v>44500.92929869557</v>
+        <v>17434.13286065532</v>
       </c>
     </row>
     <row r="54">
@@ -1011,10 +1011,10 @@
         <v>340</v>
       </c>
       <c r="B54" t="n">
-        <v>10221.76780871828</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C54" t="n">
-        <v>28192.59646261903</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="55">
@@ -1022,10 +1022,10 @@
         <v>341</v>
       </c>
       <c r="B55" t="n">
-        <v>10481.82013139813</v>
+        <v>5420.552036878907</v>
       </c>
       <c r="C55" t="n">
-        <v>28909.84521348838</v>
+        <v>14950.39204960349</v>
       </c>
     </row>
     <row r="56">
@@ -1033,10 +1033,10 @@
         <v>342</v>
       </c>
       <c r="B56" t="n">
-        <v>8143.656771676204</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>22460.97088001951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1220,10 +1220,10 @@
         <v>359</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>6228.763502302742</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>17179.51524312018</v>
       </c>
     </row>
     <row r="74">
@@ -1231,10 +1231,10 @@
         <v>360</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>5821.15015514865</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>16055.27931601456</v>
       </c>
     </row>
     <row r="75">
@@ -1242,10 +1242,10 @@
         <v>361</v>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>5809.795287589211</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>16023.96152392808</v>
       </c>
     </row>
     <row r="76">
@@ -1253,10 +1253,10 @@
         <v>362</v>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>5911.932054259483</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>16305.66432726075</v>
       </c>
     </row>
     <row r="77">
@@ -1264,10 +1264,10 @@
         <v>363</v>
       </c>
       <c r="B77" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C77" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="78">
@@ -1275,10 +1275,10 @@
         <v>364</v>
       </c>
       <c r="B78" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C78" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="79">
@@ -1286,10 +1286,10 @@
         <v>365</v>
       </c>
       <c r="B79" t="n">
-        <v>2420.200107322061</v>
+        <v>7754.904030281272</v>
       </c>
       <c r="C79" t="n">
-        <v>6675.139394804333</v>
+        <v>21388.75427649459</v>
       </c>
     </row>
     <row r="80">
@@ -1297,10 +1297,10 @@
         <v>366</v>
       </c>
       <c r="B80" t="n">
-        <v>2420.200107322061</v>
+        <v>9198.907302094618</v>
       </c>
       <c r="C80" t="n">
-        <v>6675.139394804333</v>
+        <v>25371.45103646335</v>
       </c>
     </row>
     <row r="81">
@@ -1374,10 +1374,10 @@
         <v>373</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>5684.661918074331</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>15678.8319282693</v>
       </c>
     </row>
     <row r="88">
@@ -1484,10 +1484,10 @@
         <v>383</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="98">
@@ -1495,10 +1495,10 @@
         <v>384</v>
       </c>
       <c r="B98" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C98" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="99">
@@ -1506,10 +1506,10 @@
         <v>385</v>
       </c>
       <c r="B99" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C99" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="100">
@@ -1517,10 +1517,10 @@
         <v>386</v>
       </c>
       <c r="B100" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C100" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="101">
@@ -1528,10 +1528,10 @@
         <v>387</v>
       </c>
       <c r="B101" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C101" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="102">
@@ -1539,10 +1539,10 @@
         <v>388</v>
       </c>
       <c r="B102" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C102" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="103">
@@ -1550,10 +1550,10 @@
         <v>389</v>
       </c>
       <c r="B103" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C103" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="104">
@@ -1561,10 +1561,10 @@
         <v>390</v>
       </c>
       <c r="B104" t="n">
-        <v>3041.751087047618</v>
+        <v>3801.67068790515</v>
       </c>
       <c r="C104" t="n">
-        <v>8389.435422679511</v>
+        <v>10485.36511428707</v>
       </c>
     </row>
     <row r="105">
@@ -1627,10 +1627,10 @@
         <v>396</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>10361.8771713293</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>28579.03125498031</v>
       </c>
     </row>
     <row r="111">
@@ -1638,10 +1638,10 @@
         <v>397</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>9692.899210867357</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>26733.92715609799</v>
       </c>
     </row>
     <row r="112">
@@ -1737,10 +1737,10 @@
         <v>406</v>
       </c>
       <c r="B120" t="n">
-        <v>2420.200107322061</v>
+        <v>2140.480629651258</v>
       </c>
       <c r="C120" t="n">
-        <v>6675.139394804333</v>
+        <v>5903.646781757358</v>
       </c>
     </row>
     <row r="121">
@@ -1748,10 +1748,10 @@
         <v>407</v>
       </c>
       <c r="B121" t="n">
-        <v>2864.773100341647</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C121" t="n">
-        <v>7901.313499413693</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="122">
@@ -1759,10 +1759,10 @@
         <v>408</v>
       </c>
       <c r="B122" t="n">
-        <v>4805.136610000351</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C122" t="n">
-        <v>13253.01845322231</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="123">
@@ -1770,10 +1770,10 @@
         <v>409</v>
       </c>
       <c r="B123" t="n">
-        <v>4945.285151706286</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C123" t="n">
-        <v>13639.5613052102</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="124">
@@ -1781,10 +1781,10 @@
         <v>410</v>
       </c>
       <c r="B124" t="n">
-        <v>5199.695434453103</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C124" t="n">
-        <v>14341.2487795925</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="125">
@@ -1792,10 +1792,10 @@
         <v>411</v>
       </c>
       <c r="B125" t="n">
-        <v>5551.512530101291</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C125" t="n">
-        <v>15311.59340019719</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="126">
@@ -1803,10 +1803,10 @@
         <v>412</v>
       </c>
       <c r="B126" t="n">
-        <v>2803.745187687189</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C126" t="n">
-        <v>7732.99277968891</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="127">
@@ -1814,10 +1814,10 @@
         <v>413</v>
       </c>
       <c r="B127" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C127" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="128">
@@ -1825,10 +1825,10 @@
         <v>414</v>
       </c>
       <c r="B128" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C128" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="129">
@@ -1836,10 +1836,10 @@
         <v>415</v>
       </c>
       <c r="B129" t="n">
-        <v>2420.200107322061</v>
+        <v>8426.964116154217</v>
       </c>
       <c r="C129" t="n">
-        <v>6675.139394804333</v>
+        <v>23242.35916698025</v>
       </c>
     </row>
     <row r="130">
@@ -1847,10 +1847,10 @@
         <v>416</v>
       </c>
       <c r="B130" t="n">
-        <v>2420.200107322061</v>
+        <v>8593.836862446151</v>
       </c>
       <c r="C130" t="n">
-        <v>6675.139394804333</v>
+        <v>23702.60988729155</v>
       </c>
     </row>
     <row r="131">
@@ -1858,10 +1858,10 @@
         <v>417</v>
       </c>
       <c r="B131" t="n">
-        <v>2420.200107322061</v>
+        <v>8604.394097444776</v>
       </c>
       <c r="C131" t="n">
-        <v>6675.139394804333</v>
+        <v>23731.72773379785</v>
       </c>
     </row>
     <row r="132">
@@ -1869,10 +1869,10 @@
         <v>418</v>
       </c>
       <c r="B132" t="n">
-        <v>2420.200107322061</v>
+        <v>6674.542034261469</v>
       </c>
       <c r="C132" t="n">
-        <v>6675.139394804333</v>
+        <v>18409.01433744435</v>
       </c>
     </row>
     <row r="133">
@@ -1880,10 +1880,10 @@
         <v>419</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="134">
@@ -1891,10 +1891,10 @@
         <v>420</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="135">
@@ -1902,10 +1902,10 @@
         <v>421</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="136">
@@ -1913,10 +1913,10 @@
         <v>422</v>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="137">
@@ -1979,10 +1979,10 @@
         <v>428</v>
       </c>
       <c r="B142" t="n">
-        <v>2420.200107322061</v>
+        <v>2029.366833690533</v>
       </c>
       <c r="C142" t="n">
-        <v>6675.139394804333</v>
+        <v>5597.184487800856</v>
       </c>
     </row>
     <row r="143">
@@ -1990,10 +1990,10 @@
         <v>429</v>
       </c>
       <c r="B143" t="n">
-        <v>2420.200107322061</v>
+        <v>2514.057212889899</v>
       </c>
       <c r="C143" t="n">
-        <v>6675.139394804333</v>
+        <v>6934.006114528354</v>
       </c>
     </row>
     <row r="144">
@@ -2001,10 +2001,10 @@
         <v>430</v>
       </c>
       <c r="B144" t="n">
-        <v>2420.200107322061</v>
+        <v>1719.1410707326</v>
       </c>
       <c r="C144" t="n">
-        <v>6675.139394804333</v>
+        <v>4741.55267234116</v>
       </c>
     </row>
     <row r="145">
@@ -2012,10 +2012,10 @@
         <v>431</v>
       </c>
       <c r="B145" t="n">
-        <v>3239.061000251517</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C145" t="n">
-        <v>8933.634710427708</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="146">
@@ -2023,10 +2023,10 @@
         <v>432</v>
       </c>
       <c r="B146" t="n">
-        <v>5021.63289104411</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C146" t="n">
-        <v>13850.13554699141</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="147">
@@ -2034,10 +2034,10 @@
         <v>433</v>
       </c>
       <c r="B147" t="n">
-        <v>5794.123187294271</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C147" t="n">
-        <v>15980.7363981372</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="148">
@@ -2045,10 +2045,10 @@
         <v>434</v>
       </c>
       <c r="B148" t="n">
-        <v>6036.082042597282</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C148" t="n">
-        <v>16648.08166519531</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="149">
@@ -2056,10 +2056,10 @@
         <v>435</v>
       </c>
       <c r="B149" t="n">
-        <v>6096.602337579903</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C149" t="n">
-        <v>16815.0023276651</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="150">
@@ -2067,10 +2067,10 @@
         <v>436</v>
       </c>
       <c r="B150" t="n">
-        <v>5760.59695567439</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C150" t="n">
-        <v>15888.2678998638</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="151">
@@ -2078,10 +2078,10 @@
         <v>437</v>
       </c>
       <c r="B151" t="n">
-        <v>7624.718279109347</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C151" t="n">
-        <v>21029.68973730181</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="152">
@@ -2089,10 +2089,10 @@
         <v>438</v>
       </c>
       <c r="B152" t="n">
-        <v>3710.410509788099</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C152" t="n">
-        <v>10233.6609645835</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="153">
@@ -2100,10 +2100,10 @@
         <v>439</v>
       </c>
       <c r="B153" t="n">
-        <v>3445.882467185456</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C153" t="n">
-        <v>9504.067757449404</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="154">
@@ -2111,10 +2111,10 @@
         <v>440</v>
       </c>
       <c r="B154" t="n">
-        <v>3655.963053483239</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C154" t="n">
-        <v>10083.4897620338</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="155">
@@ -2122,10 +2122,10 @@
         <v>441</v>
       </c>
       <c r="B155" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C155" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="156">
@@ -2133,10 +2133,10 @@
         <v>442</v>
       </c>
       <c r="B156" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C156" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="157">
@@ -2144,10 +2144,10 @@
         <v>443</v>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="158">
@@ -2155,10 +2155,10 @@
         <v>444</v>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="159">
@@ -2166,10 +2166,10 @@
         <v>445</v>
       </c>
       <c r="B159" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C159" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="160">
@@ -2177,10 +2177,10 @@
         <v>446</v>
       </c>
       <c r="B160" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C160" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="161">
@@ -2188,10 +2188,10 @@
         <v>447</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="162">
@@ -2243,10 +2243,10 @@
         <v>452</v>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>1649.647793852731</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>4549.883682338455</v>
       </c>
     </row>
     <row r="167">
@@ -2254,10 +2254,10 @@
         <v>453</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>3191.012512059943</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>8801.112463437457</v>
       </c>
     </row>
     <row r="168">
@@ -2265,10 +2265,10 @@
         <v>454</v>
       </c>
       <c r="B168" t="n">
-        <v>2420.200107322061</v>
+        <v>5125.049000201142</v>
       </c>
       <c r="C168" t="n">
-        <v>6675.139394804333</v>
+        <v>14135.36689716077</v>
       </c>
     </row>
     <row r="169">
@@ -2276,10 +2276,10 @@
         <v>455</v>
       </c>
       <c r="B169" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C169" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="170">
@@ -2287,10 +2287,10 @@
         <v>456</v>
       </c>
       <c r="B170" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C170" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="171">
@@ -2298,10 +2298,10 @@
         <v>457</v>
       </c>
       <c r="B171" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C171" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="172">
@@ -2309,10 +2309,10 @@
         <v>458</v>
       </c>
       <c r="B172" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C172" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="173">
@@ -2320,10 +2320,10 @@
         <v>459</v>
       </c>
       <c r="B173" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C173" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="174">
@@ -2331,10 +2331,10 @@
         <v>460</v>
       </c>
       <c r="B174" t="n">
-        <v>7335.74867471428</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C174" t="n">
-        <v>20232.68440523741</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="175">
@@ -2342,10 +2342,10 @@
         <v>461</v>
       </c>
       <c r="B175" t="n">
-        <v>7628.07829297733</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C175" t="n">
-        <v>21038.95697139102</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="176">
@@ -2353,10 +2353,10 @@
         <v>462</v>
       </c>
       <c r="B176" t="n">
-        <v>8143.656771676204</v>
+        <v>6293.008293438715</v>
       </c>
       <c r="C176" t="n">
-        <v>22460.97088001951</v>
+        <v>17356.70841608356</v>
       </c>
     </row>
     <row r="177">
@@ -2529,10 +2529,10 @@
         <v>478</v>
       </c>
       <c r="B192" t="n">
-        <v>2420.200107322061</v>
+        <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>6675.139394804333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -2540,10 +2540,10 @@
         <v>479</v>
       </c>
       <c r="B193" t="n">
-        <v>2420.200107322061</v>
+        <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>6675.139394804333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -2551,10 +2551,10 @@
         <v>480</v>
       </c>
       <c r="B194" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C194" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="195">
@@ -2562,10 +2562,10 @@
         <v>481</v>
       </c>
       <c r="B195" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C195" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="196">
@@ -2573,10 +2573,10 @@
         <v>482</v>
       </c>
       <c r="B196" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C196" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="197">
@@ -2584,10 +2584,10 @@
         <v>483</v>
       </c>
       <c r="B197" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C197" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="198">
@@ -2595,10 +2595,10 @@
         <v>484</v>
       </c>
       <c r="B198" t="n">
-        <v>4508.192055797882</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C198" t="n">
-        <v>12434.0174599438</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="199">
@@ -2606,10 +2606,10 @@
         <v>485</v>
       </c>
       <c r="B199" t="n">
-        <v>4867.561120571379</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C199" t="n">
-        <v>13425.1911212812</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="200">
@@ -2617,10 +2617,10 @@
         <v>486</v>
       </c>
       <c r="B200" t="n">
-        <v>5453.106985922411</v>
+        <v>6293.008293438715</v>
       </c>
       <c r="C200" t="n">
-        <v>15040.18165923069</v>
+        <v>17356.70841608356</v>
       </c>
     </row>
     <row r="201">
@@ -2793,10 +2793,10 @@
         <v>502</v>
       </c>
       <c r="B216" t="n">
-        <v>2420.200107322061</v>
+        <v>2140.480629651258</v>
       </c>
       <c r="C216" t="n">
-        <v>6675.139394804333</v>
+        <v>5903.646781757358</v>
       </c>
     </row>
     <row r="217">
@@ -2804,10 +2804,10 @@
         <v>503</v>
       </c>
       <c r="B217" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C217" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="218">
@@ -2815,10 +2815,10 @@
         <v>504</v>
       </c>
       <c r="B218" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C218" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="219">
@@ -2826,10 +2826,10 @@
         <v>505</v>
       </c>
       <c r="B219" t="n">
-        <v>2420.200107322061</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C219" t="n">
-        <v>6675.139394804333</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="220">
@@ -2837,10 +2837,10 @@
         <v>506</v>
       </c>
       <c r="B220" t="n">
-        <v>3925.948090342247</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C220" t="n">
-        <v>10828.13387228441</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="221">
@@ -2848,10 +2848,10 @@
         <v>507</v>
       </c>
       <c r="B221" t="n">
-        <v>4430.940683692036</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C221" t="n">
-        <v>12220.9509140469</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="222">
@@ -2859,10 +2859,10 @@
         <v>508</v>
       </c>
       <c r="B222" t="n">
-        <v>4508.192055797882</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C222" t="n">
-        <v>12434.0174599438</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="223">
@@ -2870,10 +2870,10 @@
         <v>509</v>
       </c>
       <c r="B223" t="n">
-        <v>4867.561120571379</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C223" t="n">
-        <v>13425.1911212812</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="224">
@@ -2881,10 +2881,10 @@
         <v>510</v>
       </c>
       <c r="B224" t="n">
-        <v>3041.751087047618</v>
+        <v>6293.008293438715</v>
       </c>
       <c r="C224" t="n">
-        <v>8389.435422679511</v>
+        <v>17356.70841608356</v>
       </c>
     </row>
     <row r="225">
@@ -3046,10 +3046,10 @@
         <v>525</v>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>9686.003634797733</v>
       </c>
       <c r="C239" t="n">
-        <v>0</v>
+        <v>26714.90850911382</v>
       </c>
     </row>
     <row r="240">
@@ -3057,10 +3057,10 @@
         <v>526</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>10231.81959613874</v>
       </c>
       <c r="C240" t="n">
-        <v>0</v>
+        <v>28220.3202371927</v>
       </c>
     </row>
     <row r="241">
@@ -3068,10 +3068,10 @@
         <v>527</v>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>10649.67939851187</v>
       </c>
       <c r="C241" t="n">
-        <v>0</v>
+        <v>29372.8168509592</v>
       </c>
     </row>
     <row r="242">
@@ -3079,10 +3079,10 @@
         <v>528</v>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>8070.687362726562</v>
       </c>
       <c r="C242" t="n">
-        <v>0</v>
+        <v>22259.71439101196</v>
       </c>
     </row>
     <row r="243">
@@ -3090,10 +3090,10 @@
         <v>529</v>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>8167.710632158042</v>
       </c>
       <c r="C243" t="n">
-        <v>0</v>
+        <v>22527.3136882913</v>
       </c>
     </row>
     <row r="244">
@@ -3101,10 +3101,10 @@
         <v>530</v>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>8274.935142536411</v>
       </c>
       <c r="C244" t="n">
-        <v>0</v>
+        <v>22823.04896701882</v>
       </c>
     </row>
     <row r="245">
@@ -3112,10 +3112,10 @@
         <v>531</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>9996.023861394573</v>
       </c>
       <c r="C245" t="n">
-        <v>0</v>
+        <v>27569.9734359692</v>
       </c>
     </row>
     <row r="246">
@@ -3123,10 +3123,10 @@
         <v>532</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C246" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="247">
@@ -3134,10 +3134,10 @@
         <v>533</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>10672.37460599518</v>
       </c>
       <c r="C247" t="n">
-        <v>0</v>
+        <v>29435.41236654767</v>
       </c>
     </row>
     <row r="248">
@@ -3145,10 +3145,10 @@
         <v>534</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C248" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="249">
@@ -3189,10 +3189,10 @@
         <v>538</v>
       </c>
       <c r="B252" t="n">
-        <v>0</v>
+        <v>2666.633644515992</v>
       </c>
       <c r="C252" t="n">
-        <v>0</v>
+        <v>7354.82625513769</v>
       </c>
     </row>
     <row r="253">
@@ -3266,10 +3266,10 @@
         <v>545</v>
       </c>
       <c r="B259" t="n">
-        <v>0</v>
+        <v>2487.300163474301</v>
       </c>
       <c r="C259" t="n">
-        <v>0</v>
+        <v>6860.207657077488</v>
       </c>
     </row>
     <row r="260">
@@ -3277,10 +3277,10 @@
         <v>546</v>
       </c>
       <c r="B260" t="n">
-        <v>0</v>
+        <v>3901.193284849212</v>
       </c>
       <c r="C260" t="n">
-        <v>0</v>
+        <v>10759.8577917829</v>
       </c>
     </row>
     <row r="261">
@@ -3288,10 +3288,10 @@
         <v>547</v>
       </c>
       <c r="B261" t="n">
-        <v>0</v>
+        <v>5746.620025821905</v>
       </c>
       <c r="C261" t="n">
-        <v>0</v>
+        <v>15849.71821349924</v>
       </c>
     </row>
     <row r="262">
@@ -3299,10 +3299,10 @@
         <v>548</v>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>4342.898865330611</v>
       </c>
       <c r="C262" t="n">
-        <v>0</v>
+        <v>11978.12330307517</v>
       </c>
     </row>
     <row r="263">
@@ -3310,10 +3310,10 @@
         <v>549</v>
       </c>
       <c r="B263" t="n">
-        <v>0</v>
+        <v>5709.740530550902</v>
       </c>
       <c r="C263" t="n">
-        <v>0</v>
+        <v>15748.00109886926</v>
       </c>
     </row>
     <row r="264">
@@ -3321,10 +3321,10 @@
         <v>550</v>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>3913.606187237279</v>
       </c>
       <c r="C264" t="n">
-        <v>0</v>
+        <v>10794.09374338201</v>
       </c>
     </row>
     <row r="265">
@@ -3332,10 +3332,10 @@
         <v>551</v>
       </c>
       <c r="B265" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C265" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="266">
@@ -3343,10 +3343,10 @@
         <v>552</v>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C266" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="267">
@@ -3354,10 +3354,10 @@
         <v>553</v>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C267" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="268">
@@ -3365,10 +3365,10 @@
         <v>554</v>
       </c>
       <c r="B268" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C268" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="269">
@@ -3376,10 +3376,10 @@
         <v>555</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C269" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="270">
@@ -3387,10 +3387,10 @@
         <v>556</v>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C270" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="271">
@@ -3398,10 +3398,10 @@
         <v>557</v>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C271" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="272">
@@ -3409,10 +3409,10 @@
         <v>558</v>
       </c>
       <c r="B272" t="n">
-        <v>0</v>
+        <v>6997.352910028611</v>
       </c>
       <c r="C272" t="n">
-        <v>0</v>
+        <v>19299.35707703245</v>
       </c>
     </row>
     <row r="273">
@@ -3442,10 +3442,10 @@
         <v>561</v>
       </c>
       <c r="B275" t="n">
-        <v>0</v>
+        <v>1649.647793852841</v>
       </c>
       <c r="C275" t="n">
-        <v>0</v>
+        <v>4549.883682338757</v>
       </c>
     </row>
     <row r="276">
@@ -3453,10 +3453,10 @@
         <v>562</v>
       </c>
       <c r="B276" t="n">
-        <v>0</v>
+        <v>1649.647793852841</v>
       </c>
       <c r="C276" t="n">
-        <v>0</v>
+        <v>4549.883682338757</v>
       </c>
     </row>
     <row r="277">
@@ -3475,10 +3475,10 @@
         <v>564</v>
       </c>
       <c r="B278" t="n">
-        <v>0</v>
+        <v>1649.647793852841</v>
       </c>
       <c r="C278" t="n">
-        <v>0</v>
+        <v>4549.883682338757</v>
       </c>
     </row>
     <row r="279">
@@ -3486,10 +3486,10 @@
         <v>565</v>
       </c>
       <c r="B279" t="n">
-        <v>0</v>
+        <v>10654.43087058984</v>
       </c>
       <c r="C279" t="n">
-        <v>0</v>
+        <v>29385.92185758862</v>
       </c>
     </row>
     <row r="280">
@@ -3497,10 +3497,10 @@
         <v>566</v>
       </c>
       <c r="B280" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C280" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="281">
@@ -3552,10 +3552,10 @@
         <v>571</v>
       </c>
       <c r="B285" t="n">
-        <v>0</v>
+        <v>1649.647793852841</v>
       </c>
       <c r="C285" t="n">
-        <v>0</v>
+        <v>4549.883682338757</v>
       </c>
     </row>
     <row r="286">
@@ -3563,10 +3563,10 @@
         <v>572</v>
       </c>
       <c r="B286" t="n">
-        <v>0</v>
+        <v>1649.647793852841</v>
       </c>
       <c r="C286" t="n">
-        <v>0</v>
+        <v>4549.883682338757</v>
       </c>
     </row>
     <row r="287">
@@ -3574,10 +3574,10 @@
         <v>573</v>
       </c>
       <c r="B287" t="n">
-        <v>0</v>
+        <v>1938.961669997816</v>
       </c>
       <c r="C287" t="n">
-        <v>0</v>
+        <v>5347.838548250955</v>
       </c>
     </row>
     <row r="288">
@@ -3585,10 +3585,10 @@
         <v>574</v>
       </c>
       <c r="B288" t="n">
-        <v>0</v>
+        <v>3913.606187237279</v>
       </c>
       <c r="C288" t="n">
-        <v>0</v>
+        <v>10794.09374338201</v>
       </c>
     </row>
     <row r="289">
@@ -3596,10 +3596,10 @@
         <v>575</v>
       </c>
       <c r="B289" t="n">
-        <v>0</v>
+        <v>4089.402655993988</v>
       </c>
       <c r="C289" t="n">
-        <v>0</v>
+        <v>11278.95692908108</v>
       </c>
     </row>
     <row r="290">
@@ -3607,10 +3607,10 @@
         <v>576</v>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C290" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="291">
@@ -3618,10 +3618,10 @@
         <v>577</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>6956.998276113732</v>
       </c>
       <c r="C291" t="n">
-        <v>0</v>
+        <v>19188.05520335963</v>
       </c>
     </row>
     <row r="292">
@@ -3629,10 +3629,10 @@
         <v>578</v>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>7025.505483901085</v>
       </c>
       <c r="C292" t="n">
-        <v>0</v>
+        <v>19377.00452211468</v>
       </c>
     </row>
     <row r="293">
@@ -3651,10 +3651,10 @@
         <v>580</v>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C294" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="295">
@@ -3662,10 +3662,10 @@
         <v>581</v>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C295" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="296">
@@ -3673,10 +3673,10 @@
         <v>582</v>
       </c>
       <c r="B296" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C296" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="297">
@@ -3684,10 +3684,10 @@
         <v>583</v>
       </c>
       <c r="B297" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C297" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="298">
@@ -3695,10 +3695,10 @@
         <v>584</v>
       </c>
       <c r="B298" t="n">
-        <v>0</v>
+        <v>9583.095508839462</v>
       </c>
       <c r="C298" t="n">
-        <v>0</v>
+        <v>26431.07822435706</v>
       </c>
     </row>
     <row r="299">
@@ -3706,10 +3706,10 @@
         <v>585</v>
       </c>
       <c r="B299" t="n">
-        <v>0</v>
+        <v>7914.075982679272</v>
       </c>
       <c r="C299" t="n">
-        <v>0</v>
+        <v>21827.7654833718</v>
       </c>
     </row>
     <row r="300">
@@ -3717,10 +3717,10 @@
         <v>586</v>
       </c>
       <c r="B300" t="n">
-        <v>0</v>
+        <v>4306.182319570999</v>
       </c>
       <c r="C300" t="n">
-        <v>0</v>
+        <v>11876.85561851486</v>
       </c>
     </row>
     <row r="301">
@@ -3728,10 +3728,10 @@
         <v>587</v>
       </c>
       <c r="B301" t="n">
-        <v>0</v>
+        <v>2102.322267714388</v>
       </c>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>5798.402432649447</v>
       </c>
     </row>
     <row r="302">
@@ -3739,10 +3739,10 @@
         <v>588</v>
       </c>
       <c r="B302" t="n">
-        <v>0</v>
+        <v>2748.333252112464</v>
       </c>
       <c r="C302" t="n">
-        <v>0</v>
+        <v>7580.161452651875</v>
       </c>
     </row>
     <row r="303">
@@ -3750,10 +3750,10 @@
         <v>589</v>
       </c>
       <c r="B303" t="n">
-        <v>0</v>
+        <v>1649.647793852841</v>
       </c>
       <c r="C303" t="n">
-        <v>0</v>
+        <v>4549.883682338757</v>
       </c>
     </row>
     <row r="304">
@@ -3761,10 +3761,10 @@
         <v>590</v>
       </c>
       <c r="B304" t="n">
-        <v>0</v>
+        <v>2650.593490323663</v>
       </c>
       <c r="C304" t="n">
-        <v>0</v>
+        <v>7310.586002100751</v>
       </c>
     </row>
     <row r="305">
@@ -3772,10 +3772,10 @@
         <v>591</v>
       </c>
       <c r="B305" t="n">
-        <v>0</v>
+        <v>4811.138560992982</v>
       </c>
       <c r="C305" t="n">
-        <v>0</v>
+        <v>13269.57239824338</v>
       </c>
     </row>
     <row r="306">
@@ -3783,10 +3783,10 @@
         <v>592</v>
       </c>
       <c r="B306" t="n">
-        <v>0</v>
+        <v>5880.356316974166</v>
       </c>
       <c r="C306" t="n">
-        <v>0</v>
+        <v>16218.57547570855</v>
       </c>
     </row>
     <row r="307">
@@ -3838,10 +3838,10 @@
         <v>597</v>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C311" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="312">
@@ -3849,10 +3849,10 @@
         <v>598</v>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C312" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="313">
@@ -3860,10 +3860,10 @@
         <v>599</v>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C313" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="314">
@@ -3871,10 +3871,10 @@
         <v>600</v>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="315">
@@ -3882,10 +3882,10 @@
         <v>601</v>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C315" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="316">
@@ -3893,10 +3893,10 @@
         <v>602</v>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C316" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="317">
@@ -3904,10 +3904,10 @@
         <v>603</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C317" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="318">
@@ -3915,10 +3915,10 @@
         <v>604</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="319">
@@ -3926,10 +3926,10 @@
         <v>605</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C319" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="320">
@@ -3937,10 +3937,10 @@
         <v>606</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C320" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="321">
@@ -3948,10 +3948,10 @@
         <v>607</v>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C321" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="322">
@@ -3959,10 +3959,10 @@
         <v>608</v>
       </c>
       <c r="B322" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C322" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="323">
@@ -3970,10 +3970,10 @@
         <v>609</v>
       </c>
       <c r="B323" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C323" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="324">
@@ -3981,10 +3981,10 @@
         <v>610</v>
       </c>
       <c r="B324" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C324" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="325">
@@ -3992,10 +3992,10 @@
         <v>611</v>
       </c>
       <c r="B325" t="n">
-        <v>0</v>
+        <v>8978.88728521926</v>
       </c>
       <c r="C325" t="n">
-        <v>0</v>
+        <v>24764.61514803953</v>
       </c>
     </row>
     <row r="326">
@@ -4003,10 +4003,10 @@
         <v>612</v>
       </c>
       <c r="B326" t="n">
-        <v>0</v>
+        <v>6442.740912541312</v>
       </c>
       <c r="C326" t="n">
-        <v>0</v>
+        <v>17769.68505443472</v>
       </c>
     </row>
     <row r="327">
@@ -4014,10 +4014,10 @@
         <v>613</v>
       </c>
       <c r="B327" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C327" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="328">
@@ -4025,10 +4025,10 @@
         <v>614</v>
       </c>
       <c r="B328" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C328" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="329">
@@ -4036,10 +4036,10 @@
         <v>615</v>
       </c>
       <c r="B329" t="n">
-        <v>0</v>
+        <v>5221.288087981926</v>
       </c>
       <c r="C329" t="n">
-        <v>0</v>
+        <v>14400.80334773442</v>
       </c>
     </row>
     <row r="330">
@@ -4047,10 +4047,10 @@
         <v>616</v>
       </c>
       <c r="B330" t="n">
-        <v>0</v>
+        <v>4202.236440499842</v>
       </c>
       <c r="C330" t="n">
-        <v>0</v>
+        <v>11590.16311312397</v>
       </c>
     </row>
     <row r="331">
@@ -4069,10 +4069,10 @@
         <v>618</v>
       </c>
       <c r="B332" t="n">
-        <v>0</v>
+        <v>1649.647793852738</v>
       </c>
       <c r="C332" t="n">
-        <v>0</v>
+        <v>4549.883682338474</v>
       </c>
     </row>
     <row r="333">
@@ -4080,10 +4080,10 @@
         <v>619</v>
       </c>
       <c r="B333" t="n">
-        <v>0</v>
+        <v>6795.685774307415</v>
       </c>
       <c r="C333" t="n">
-        <v>0</v>
+        <v>18743.14016000264</v>
       </c>
     </row>
     <row r="334">
@@ -4091,10 +4091,10 @@
         <v>620</v>
       </c>
       <c r="B334" t="n">
-        <v>0</v>
+        <v>8032.944710977689</v>
       </c>
       <c r="C334" t="n">
-        <v>0</v>
+        <v>22155.6166096793</v>
       </c>
     </row>
     <row r="335">
@@ -4102,10 +4102,10 @@
         <v>621</v>
       </c>
       <c r="B335" t="n">
-        <v>0</v>
+        <v>9618.476955091568</v>
       </c>
       <c r="C335" t="n">
-        <v>0</v>
+        <v>26528.66357897632</v>
       </c>
     </row>
     <row r="336">
@@ -4113,10 +4113,10 @@
         <v>622</v>
       </c>
       <c r="B336" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C336" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="337">
@@ -4124,10 +4124,10 @@
         <v>623</v>
       </c>
       <c r="B337" t="n">
-        <v>0</v>
+        <v>10997.65195901894</v>
       </c>
       <c r="C337" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
   </sheetData>
@@ -4166,10 +4166,10 @@
         <v>5160</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2104.096865820094</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7563.756914925292</v>
       </c>
     </row>
     <row r="3">
@@ -4177,10 +4177,10 @@
         <v>5161</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1605.307122677738</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5770.719517230988</v>
       </c>
     </row>
     <row r="4">
@@ -4188,10 +4188,10 @@
         <v>5162</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1512.48805673732</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5437.055766645957</v>
       </c>
     </row>
     <row r="5">
@@ -4199,10 +4199,10 @@
         <v>5163</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3358.454019954424</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>12072.88990803568</v>
       </c>
     </row>
     <row r="6">
@@ -4210,10 +4210,10 @@
         <v>5164</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3699.457645448454</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>13298.72155687461</v>
       </c>
     </row>
     <row r="7">
@@ -4221,10 +4221,10 @@
         <v>5165</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>4519.393840387589</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>16246.20851197313</v>
       </c>
     </row>
     <row r="8">
@@ -4254,7 +4254,7 @@
         <v>5168</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>690.3397879591588</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         <v>5169</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>716.9192426275441</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>5170</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1088.230744064651</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>5171</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1844.754962767621</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>5172</v>
       </c>
       <c r="B14" t="n">
-        <v>6819.799704428286</v>
+        <v>1490.176574563599</v>
       </c>
       <c r="C14" t="n">
-        <v>24515.65230228589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4309,7 +4309,7 @@
         <v>5173</v>
       </c>
       <c r="B15" t="n">
-        <v>1327.989828441336</v>
+        <v>1497.163797044169</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>5174</v>
       </c>
       <c r="B16" t="n">
-        <v>2000.852027642381</v>
+        <v>1879.512102603256</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
         <v>5175</v>
       </c>
       <c r="B17" t="n">
-        <v>1988.594826220712</v>
+        <v>1494.335245363373</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>5176</v>
       </c>
       <c r="B18" t="n">
-        <v>3261.799678452492</v>
+        <v>1468.315675708288</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -4353,7 +4353,7 @@
         <v>5177</v>
       </c>
       <c r="B19" t="n">
-        <v>2324.552178485387</v>
+        <v>957.805625470408</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>5178</v>
       </c>
       <c r="B20" t="n">
-        <v>1517.479418776307</v>
+        <v>572.270525798585</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -4375,10 +4375,10 @@
         <v>5179</v>
       </c>
       <c r="B21" t="n">
-        <v>847.3816435518777</v>
+        <v>4486.089307824661</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>16126.4861776247</v>
       </c>
     </row>
     <row r="22">
@@ -4386,10 +4386,10 @@
         <v>5180</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>4606.276735769084</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>16558.53305910104</v>
       </c>
     </row>
     <row r="23">
@@ -4397,10 +4397,10 @@
         <v>5181</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>4266.134100467688</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>15335.79647714283</v>
       </c>
     </row>
     <row r="24">
@@ -4408,10 +4408,10 @@
         <v>5182</v>
       </c>
       <c r="B24" t="n">
-        <v>2501.43523481772</v>
+        <v>3757.906203318487</v>
       </c>
       <c r="C24" t="n">
-        <v>8992.099347677104</v>
+        <v>13508.83102994041</v>
       </c>
     </row>
     <row r="25">
@@ -4419,10 +4419,10 @@
         <v>5183</v>
       </c>
       <c r="B25" t="n">
-        <v>1918.217499919684</v>
+        <v>2955.930541755406</v>
       </c>
       <c r="C25" t="n">
-        <v>6895.562231491281</v>
+        <v>10625.90816916933</v>
       </c>
     </row>
     <row r="26">
@@ -4430,10 +4430,10 @@
         <v>5184</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="27">
@@ -4441,10 +4441,10 @@
         <v>5185</v>
       </c>
       <c r="B27" t="n">
-        <v>2500.256199090198</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C27" t="n">
-        <v>8987.860978340665</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="28">
@@ -4452,10 +4452,10 @@
         <v>5186</v>
       </c>
       <c r="B28" t="n">
-        <v>12379.33303735631</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C28" t="n">
-        <v>44500.92929869557</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="29">
@@ -4463,10 +4463,10 @@
         <v>5187</v>
       </c>
       <c r="B29" t="n">
-        <v>2500.902948877261</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C29" t="n">
-        <v>8990.185898953203</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="30">
@@ -4474,10 +4474,10 @@
         <v>5188</v>
       </c>
       <c r="B30" t="n">
-        <v>5395.462077106334</v>
+        <v>3699.457645448506</v>
       </c>
       <c r="C30" t="n">
-        <v>19395.47758369199</v>
+        <v>13298.7215568748</v>
       </c>
     </row>
     <row r="31">
@@ -4496,10 +4496,10 @@
         <v>5190</v>
       </c>
       <c r="B32" t="n">
-        <v>2743.153846930154</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>9861.02361325219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4518,10 +4518,10 @@
         <v>5192</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>5492.033204206517</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>19742.62915368468</v>
       </c>
     </row>
     <row r="35">
@@ -4529,10 +4529,10 @@
         <v>5193</v>
       </c>
       <c r="B35" t="n">
-        <v>1916.339354268994</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="36">
@@ -4540,10 +4540,10 @@
         <v>5194</v>
       </c>
       <c r="B36" t="n">
-        <v>3227.117824545722</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="37">
@@ -4551,10 +4551,10 @@
         <v>5195</v>
       </c>
       <c r="B37" t="n">
-        <v>3929.157135457161</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="38">
@@ -4562,10 +4562,10 @@
         <v>5196</v>
       </c>
       <c r="B38" t="n">
-        <v>3964.028805785842</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="39">
@@ -4573,10 +4573,10 @@
         <v>5197</v>
       </c>
       <c r="B39" t="n">
-        <v>3983.964669036627</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="40">
@@ -4584,10 +4584,10 @@
         <v>5198</v>
       </c>
       <c r="B40" t="n">
-        <v>4001.704055284764</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="41">
@@ -4595,10 +4595,10 @@
         <v>5199</v>
       </c>
       <c r="B41" t="n">
-        <v>3314.316683222221</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="42">
@@ -4606,10 +4606,10 @@
         <v>5200</v>
       </c>
       <c r="B42" t="n">
-        <v>4566.527817300436</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="43">
@@ -4617,10 +4617,10 @@
         <v>5201</v>
       </c>
       <c r="B43" t="n">
-        <v>3486.833551854741</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="44">
@@ -4628,10 +4628,10 @@
         <v>5202</v>
       </c>
       <c r="B44" t="n">
-        <v>2023.307809023724</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="45">
@@ -4639,10 +4639,10 @@
         <v>5203</v>
       </c>
       <c r="B45" t="n">
-        <v>1271.067649040437</v>
+        <v>4486.089307824611</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>16126.48617762452</v>
       </c>
     </row>
     <row r="46">
@@ -4672,10 +4672,10 @@
         <v>5206</v>
       </c>
       <c r="B48" t="n">
-        <v>2501.43523481772</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8992.099347677104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4683,10 +4683,10 @@
         <v>5207</v>
       </c>
       <c r="B49" t="n">
-        <v>12379.33303735631</v>
+        <v>6440.735782742589</v>
       </c>
       <c r="C49" t="n">
-        <v>44500.92929869557</v>
+        <v>23153.00241414427</v>
       </c>
     </row>
     <row r="50">
@@ -4694,10 +4694,10 @@
         <v>5208</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>7871.815531435896</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>28297.413548833</v>
       </c>
     </row>
     <row r="51">
@@ -4705,10 +4705,10 @@
         <v>5209</v>
       </c>
       <c r="B51" t="n">
-        <v>8155.479791560351</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C51" t="n">
-        <v>29317.12302318615</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="52">
@@ -4716,10 +4716,10 @@
         <v>5210</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="53">
@@ -4727,10 +4727,10 @@
         <v>5211</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="54">
@@ -4738,10 +4738,10 @@
         <v>5212</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>8180.260414725609</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>29406.20381260566</v>
       </c>
     </row>
     <row r="55">
@@ -4793,10 +4793,10 @@
         <v>5217</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="60">
@@ -4804,10 +4804,10 @@
         <v>5218</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="61">
@@ -4815,10 +4815,10 @@
         <v>5219</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="62">
@@ -4826,10 +4826,10 @@
         <v>5220</v>
       </c>
       <c r="B62" t="n">
-        <v>1376.52520246953</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="63">
@@ -4837,10 +4837,10 @@
         <v>5221</v>
       </c>
       <c r="B63" t="n">
-        <v>1991.984742662004</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="64">
@@ -4848,10 +4848,10 @@
         <v>5222</v>
       </c>
       <c r="B64" t="n">
-        <v>2667.799804557779</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="65">
@@ -4859,10 +4859,10 @@
         <v>5223</v>
       </c>
       <c r="B65" t="n">
-        <v>2054.426363079256</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="66">
@@ -4870,10 +4870,10 @@
         <v>5224</v>
       </c>
       <c r="B66" t="n">
-        <v>2609.440893155184</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="67">
@@ -4881,10 +4881,10 @@
         <v>5225</v>
       </c>
       <c r="B67" t="n">
-        <v>1743.416775927372</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="68">
@@ -4892,7 +4892,7 @@
         <v>5226</v>
       </c>
       <c r="B68" t="n">
-        <v>1011.655844816268</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -4991,10 +4991,10 @@
         <v>5235</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>7873.231468214149</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>28302.50352438098</v>
       </c>
     </row>
     <row r="78">
@@ -5002,10 +5002,10 @@
         <v>5236</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>8180.260414725557</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>29406.20381260548</v>
       </c>
     </row>
     <row r="79">
@@ -5013,10 +5013,10 @@
         <v>5237</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="80">
@@ -5057,10 +5057,10 @@
         <v>5241</v>
       </c>
       <c r="B83" t="n">
-        <v>12379.33303735631</v>
+        <v>1075.375719707645</v>
       </c>
       <c r="C83" t="n">
-        <v>44500.92929869557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5068,7 +5068,7 @@
         <v>5242</v>
       </c>
       <c r="B84" t="n">
-        <v>1936.272246970959</v>
+        <v>1474.736780830645</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>5243</v>
       </c>
       <c r="B85" t="n">
-        <v>3274.289585735333</v>
+        <v>1475.804549839725</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>5244</v>
       </c>
       <c r="B86" t="n">
-        <v>3964.028805785842</v>
+        <v>1490.176574563599</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>5245</v>
       </c>
       <c r="B87" t="n">
-        <v>4647.959583257298</v>
+        <v>1497.163797044169</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         <v>5246</v>
       </c>
       <c r="B88" t="n">
-        <v>4732.546514427365</v>
+        <v>1127.709109819074</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>5247</v>
       </c>
       <c r="B89" t="n">
-        <v>5302.906693155553</v>
+        <v>1159.230484233877</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>5248</v>
       </c>
       <c r="B90" t="n">
-        <v>5218.886602597744</v>
+        <v>1835.390835249886</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>5249</v>
       </c>
       <c r="B91" t="n">
-        <v>4067.968954412758</v>
+        <v>1277.071086865342</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
         <v>5250</v>
       </c>
       <c r="B92" t="n">
-        <v>3034.963653839994</v>
+        <v>572.270525798585</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>5251</v>
       </c>
       <c r="B93" t="n">
-        <v>2118.444476304936</v>
+        <v>441.9208053756686</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>5252</v>
       </c>
       <c r="B94" t="n">
-        <v>1221.663651469608</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
         <v>5253</v>
       </c>
       <c r="B95" t="n">
-        <v>710.6220486422399</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -5200,10 +5200,10 @@
         <v>5254</v>
       </c>
       <c r="B96" t="n">
-        <v>2501.435234817748</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>8992.099347677204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5211,10 +5211,10 @@
         <v>5255</v>
       </c>
       <c r="B97" t="n">
-        <v>1918.217499919684</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>6895.562231491281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5222,10 +5222,10 @@
         <v>5256</v>
       </c>
       <c r="B98" t="n">
-        <v>1856.899955603446</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>6675.139394804331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5233,10 +5233,10 @@
         <v>5257</v>
       </c>
       <c r="B99" t="n">
-        <v>1856.899955603447</v>
+        <v>1605.307122677687</v>
       </c>
       <c r="C99" t="n">
-        <v>6675.139394804334</v>
+        <v>5770.719517230804</v>
       </c>
     </row>
     <row r="100">
@@ -5244,10 +5244,10 @@
         <v>5258</v>
       </c>
       <c r="B100" t="n">
-        <v>4937.848056348181</v>
+        <v>1512.488056737244</v>
       </c>
       <c r="C100" t="n">
-        <v>17750.45768460708</v>
+        <v>5437.055766645681</v>
       </c>
     </row>
     <row r="101">
@@ -5255,10 +5255,10 @@
         <v>5259</v>
       </c>
       <c r="B101" t="n">
-        <v>1856.899955603446</v>
+        <v>1528.632894778551</v>
       </c>
       <c r="C101" t="n">
-        <v>6675.139394804332</v>
+        <v>5495.092842960461</v>
       </c>
     </row>
     <row r="102">
@@ -5266,10 +5266,10 @@
         <v>5260</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>1845.333289930335</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>6633.559822642609</v>
       </c>
     </row>
     <row r="103">
@@ -5277,10 +5277,10 @@
         <v>5261</v>
       </c>
       <c r="B103" t="n">
-        <v>1856.89995560344</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>6675.139394804311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5299,7 +5299,7 @@
         <v>5263</v>
       </c>
       <c r="B105" t="n">
-        <v>1188.29535412091</v>
+        <v>656.9809114963647</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>5264</v>
       </c>
       <c r="B106" t="n">
-        <v>2475.334940521342</v>
+        <v>690.3397879591588</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -5321,7 +5321,7 @@
         <v>5265</v>
       </c>
       <c r="B107" t="n">
-        <v>3832.674827929175</v>
+        <v>1075.375719707645</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
         <v>5266</v>
       </c>
       <c r="B108" t="n">
-        <v>4558.632946774895</v>
+        <v>1450.970643549065</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>5267</v>
       </c>
       <c r="B109" t="n">
-        <v>5893.755904013819</v>
+        <v>1844.754962767621</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
         <v>5268</v>
       </c>
       <c r="B110" t="n">
-        <v>6606.714988202591</v>
+        <v>1862.716685368439</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>5269</v>
       </c>
       <c r="B111" t="n">
-        <v>7303.93442385259</v>
+        <v>1871.455470837247</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>5270</v>
       </c>
       <c r="B112" t="n">
-        <v>7336.46514994151</v>
+        <v>1879.512102603256</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -5387,7 +5387,7 @@
         <v>5271</v>
       </c>
       <c r="B113" t="n">
-        <v>7357.323423660053</v>
+        <v>1867.915434044036</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
         <v>5272</v>
       </c>
       <c r="B114" t="n">
-        <v>7828.327495752929</v>
+        <v>1468.315675708288</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
         <v>5273</v>
       </c>
       <c r="B115" t="n">
-        <v>5811.404995489645</v>
+        <v>1277.071086865342</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>5274</v>
       </c>
       <c r="B116" t="n">
-        <v>4552.443072616299</v>
+        <v>804.9293551367629</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -5431,7 +5431,7 @@
         <v>5275</v>
       </c>
       <c r="B117" t="n">
-        <v>2965.826119856812</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -5442,7 +5442,7 @@
         <v>5276</v>
       </c>
       <c r="B118" t="n">
-        <v>2348.451367717662</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
         <v>5277</v>
       </c>
       <c r="B119" t="n">
-        <v>1776.547663254889</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -5464,7 +5464,7 @@
         <v>5278</v>
       </c>
       <c r="B120" t="n">
-        <v>1017.839082958451</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>5279</v>
       </c>
       <c r="B121" t="n">
-        <v>915.7336334687392</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
         <v>5280</v>
       </c>
       <c r="B122" t="n">
-        <v>531.9509231328631</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -5552,10 +5552,10 @@
         <v>5286</v>
       </c>
       <c r="B128" t="n">
-        <v>1856.899955603446</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>6675.139394804333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5563,7 +5563,7 @@
         <v>5287</v>
       </c>
       <c r="B129" t="n">
-        <v>1535.001450798823</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>5288</v>
       </c>
       <c r="B130" t="n">
-        <v>2672.182900350447</v>
+        <v>5181.365160847776</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>18625.84712745172</v>
       </c>
     </row>
     <row r="131">
@@ -5585,7 +5585,7 @@
         <v>5289</v>
       </c>
       <c r="B131" t="n">
-        <v>3876.708943975496</v>
+        <v>960.499716303184</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
         <v>5290</v>
       </c>
       <c r="B132" t="n">
-        <v>5047.89724987357</v>
+        <v>1298.404483621192</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>5291</v>
       </c>
       <c r="B133" t="n">
-        <v>6283.156280782693</v>
+        <v>1655.295631556161</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>5292</v>
       </c>
       <c r="B134" t="n">
-        <v>6932.897048177049</v>
+        <v>1674.616576256903</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -5629,7 +5629,7 @@
         <v>5293</v>
       </c>
       <c r="B135" t="n">
-        <v>7552.574985514701</v>
+        <v>1683.387241135303</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>5294</v>
       </c>
       <c r="B136" t="n">
-        <v>8169.584221112982</v>
+        <v>1352.735777506381</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>5295</v>
       </c>
       <c r="B137" t="n">
-        <v>8133.212161511111</v>
+        <v>1009.921942040277</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
         <v>5296</v>
       </c>
       <c r="B138" t="n">
-        <v>8027.969999425504</v>
+        <v>995.2646642949775</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
         <v>5297</v>
       </c>
       <c r="B139" t="n">
-        <v>6666.308259455172</v>
+        <v>619.7128942235997</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -5684,10 +5684,10 @@
         <v>5298</v>
       </c>
       <c r="B140" t="n">
-        <v>4926.0660631894</v>
+        <v>6217.958231119063</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>22352.16701822926</v>
       </c>
     </row>
     <row r="141">
@@ -5695,7 +5695,7 @@
         <v>5299</v>
       </c>
       <c r="B141" t="n">
-        <v>3450.709893829663</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
         <v>5300</v>
       </c>
       <c r="B142" t="n">
-        <v>2910.390652124738</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
         <v>5301</v>
       </c>
       <c r="B143" t="n">
-        <v>2390.762180999916</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>5302</v>
       </c>
       <c r="B144" t="n">
-        <v>1649.9029689193</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>5303</v>
       </c>
       <c r="B145" t="n">
-        <v>1498.858027043226</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -5750,10 +5750,10 @@
         <v>5304</v>
       </c>
       <c r="B146" t="n">
-        <v>1059.263761519767</v>
+        <v>6005.178953988655</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>21587.27317950352</v>
       </c>
     </row>
     <row r="147">
@@ -5761,10 +5761,10 @@
         <v>5305</v>
       </c>
       <c r="B147" t="n">
-        <v>731.8419023983838</v>
+        <v>8004.922191931879</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>28775.90217742411</v>
       </c>
     </row>
     <row r="148">
@@ -5772,7 +5772,7 @@
         <v>5306</v>
       </c>
       <c r="B148" t="n">
-        <v>504.1155444438644</v>
+        <v>0</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -5783,10 +5783,10 @@
         <v>5307</v>
       </c>
       <c r="B149" t="n">
-        <v>12379.33303735631</v>
+        <v>7954.247763642288</v>
       </c>
       <c r="C149" t="n">
-        <v>44500.92929869557</v>
+        <v>28593.73895879497</v>
       </c>
     </row>
     <row r="150">
@@ -5794,10 +5794,10 @@
         <v>5308</v>
       </c>
       <c r="B150" t="n">
-        <v>12379.33303735631</v>
+        <v>8022.344547721922</v>
       </c>
       <c r="C150" t="n">
-        <v>44500.92929869557</v>
+        <v>28838.53164388162</v>
       </c>
     </row>
     <row r="151">
@@ -5805,10 +5805,10 @@
         <v>5309</v>
       </c>
       <c r="B151" t="n">
-        <v>12379.33303735631</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>44500.92929869557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -5816,7 +5816,7 @@
         <v>5310</v>
       </c>
       <c r="B152" t="n">
-        <v>687.0446550929947</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -5827,10 +5827,10 @@
         <v>5311</v>
       </c>
       <c r="B153" t="n">
-        <v>1134.99433511229</v>
+        <v>3045.80832514813</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>10948.99866784269</v>
       </c>
     </row>
     <row r="154">
@@ -5838,7 +5838,7 @@
         <v>5312</v>
       </c>
       <c r="B154" t="n">
-        <v>1972.246304425233</v>
+        <v>642.022129331799</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>5313</v>
       </c>
       <c r="B155" t="n">
-        <v>2458.496529245611</v>
+        <v>692.7235785653447</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>5314</v>
       </c>
       <c r="B156" t="n">
-        <v>3331.587411231836</v>
+        <v>912.7042013393901</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
         <v>5315</v>
       </c>
       <c r="B157" t="n">
-        <v>3832.384905809829</v>
+        <v>1169.722955275643</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -5882,7 +5882,7 @@
         <v>5316</v>
       </c>
       <c r="B158" t="n">
-        <v>4330.922875886352</v>
+        <v>1191.452244464731</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -5893,7 +5893,7 @@
         <v>5317</v>
       </c>
       <c r="B159" t="n">
-        <v>4796.941252195735</v>
+        <v>1439.334293949124</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>5318</v>
       </c>
       <c r="B160" t="n">
-        <v>4794.655036821998</v>
+        <v>1197.411560566057</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
         <v>5319</v>
       </c>
       <c r="B161" t="n">
-        <v>4568.257044403148</v>
+        <v>1127.884208519988</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>5320</v>
       </c>
       <c r="B162" t="n">
-        <v>3992.248631752863</v>
+        <v>1050.699455014127</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>5321</v>
       </c>
       <c r="B163" t="n">
-        <v>3331.06299077794</v>
+        <v>781.656367405008</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>5322</v>
       </c>
       <c r="B164" t="n">
-        <v>2926.876029629524</v>
+        <v>578.857971071766</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -5959,7 +5959,7 @@
         <v>5323</v>
       </c>
       <c r="B165" t="n">
-        <v>2452.169070888459</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>5324</v>
       </c>
       <c r="B166" t="n">
-        <v>1645.560970092511</v>
+        <v>0</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
         <v>5325</v>
       </c>
       <c r="B167" t="n">
-        <v>1223.241893982893</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -5992,7 +5992,7 @@
         <v>5326</v>
       </c>
       <c r="B168" t="n">
-        <v>1213.878510018219</v>
+        <v>0</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>5327</v>
       </c>
       <c r="B169" t="n">
-        <v>863.2746313368747</v>
+        <v>0</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         <v>5328</v>
       </c>
       <c r="B170" t="n">
-        <v>1856.899955603446</v>
+        <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>6675.139394804332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -6025,10 +6025,10 @@
         <v>5329</v>
       </c>
       <c r="B171" t="n">
-        <v>12379.33303735631</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>44500.92929869557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -6036,10 +6036,10 @@
         <v>5330</v>
       </c>
       <c r="B172" t="n">
-        <v>12379.33303735631</v>
+        <v>5423.07054654082</v>
       </c>
       <c r="C172" t="n">
-        <v>44500.92929869557</v>
+        <v>19494.72384701182</v>
       </c>
     </row>
     <row r="173">
@@ -6047,10 +6047,10 @@
         <v>5331</v>
       </c>
       <c r="B173" t="n">
-        <v>12379.33303735631</v>
+        <v>5538.003146077993</v>
       </c>
       <c r="C173" t="n">
-        <v>44500.92929869557</v>
+        <v>19907.88079744566</v>
       </c>
     </row>
     <row r="174">
@@ -6058,10 +6058,10 @@
         <v>5332</v>
       </c>
       <c r="B174" t="n">
-        <v>12379.33303735631</v>
+        <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>44500.92929869557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -6069,10 +6069,10 @@
         <v>5333</v>
       </c>
       <c r="B175" t="n">
-        <v>1856.89995560344</v>
+        <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>6675.139394804311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -6102,7 +6102,7 @@
         <v>5336</v>
       </c>
       <c r="B178" t="n">
-        <v>1856.503613534696</v>
+        <v>1380.676677790173</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>5337</v>
       </c>
       <c r="B179" t="n">
-        <v>2555.113652987385</v>
+        <v>1792.292447037863</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
         <v>5338</v>
       </c>
       <c r="B180" t="n">
-        <v>3872.550245907864</v>
+        <v>2539.201387613717</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>5339</v>
       </c>
       <c r="B181" t="n">
-        <v>4584.010236316848</v>
+        <v>2951.606201551307</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>5340</v>
       </c>
       <c r="B182" t="n">
-        <v>5946.028759816625</v>
+        <v>2980.349704097881</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -6157,7 +6157,7 @@
         <v>5341</v>
       </c>
       <c r="B183" t="n">
-        <v>6639.949142206677</v>
+        <v>2994.330492216481</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
         <v>5342</v>
       </c>
       <c r="B184" t="n">
-        <v>6669.522189313492</v>
+        <v>3044.567999579099</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>5343</v>
       </c>
       <c r="B185" t="n">
-        <v>6694.464903302984</v>
+        <v>3362.241985022975</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -6190,7 +6190,7 @@
         <v>5344</v>
       </c>
       <c r="B186" t="n">
-        <v>6523.590660008794</v>
+        <v>2976.238864391453</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>5345</v>
       </c>
       <c r="B187" t="n">
-        <v>5230.250327782114</v>
+        <v>2554.142173730684</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>5346</v>
       </c>
       <c r="B188" t="n">
-        <v>4046.609866081502</v>
+        <v>1609.861608401671</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>5347</v>
       </c>
       <c r="B189" t="n">
-        <v>2596.349449865642</v>
+        <v>1104.797666246954</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>5348</v>
       </c>
       <c r="B190" t="n">
-        <v>1957.039907465989</v>
+        <v>839.6310055495454</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>5349</v>
       </c>
       <c r="B191" t="n">
-        <v>1459.963461259691</v>
+        <v>585.6417030346713</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>5350</v>
       </c>
       <c r="B192" t="n">
-        <v>1357.119712956501</v>
+        <v>563.1645323076219</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>5351</v>
       </c>
       <c r="B193" t="n">
-        <v>915.7336334687392</v>
+        <v>503.2959857066625</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -6278,7 +6278,7 @@
         <v>5352</v>
       </c>
       <c r="B194" t="n">
-        <v>811.8213270037274</v>
+        <v>0</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -6289,10 +6289,10 @@
         <v>5353</v>
       </c>
       <c r="B195" t="n">
-        <v>497.999270684367</v>
+        <v>1605.307122677656</v>
       </c>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>5770.719517230693</v>
       </c>
     </row>
     <row r="196">
@@ -6300,10 +6300,10 @@
         <v>5354</v>
       </c>
       <c r="B196" t="n">
-        <v>12379.33303735631</v>
+        <v>1512.48805673732</v>
       </c>
       <c r="C196" t="n">
-        <v>44500.92929869557</v>
+        <v>5437.055766645957</v>
       </c>
     </row>
     <row r="197">
@@ -6311,10 +6311,10 @@
         <v>5355</v>
       </c>
       <c r="B197" t="n">
-        <v>12379.33303735631</v>
+        <v>1528.632894778576</v>
       </c>
       <c r="C197" t="n">
-        <v>44500.92929869557</v>
+        <v>5495.092842960549</v>
       </c>
     </row>
     <row r="198">
@@ -6322,10 +6322,10 @@
         <v>5356</v>
       </c>
       <c r="B198" t="n">
-        <v>2158.946681107802</v>
+        <v>1845.333289930281</v>
       </c>
       <c r="C198" t="n">
-        <v>7760.929714525979</v>
+        <v>6633.559822642414</v>
       </c>
     </row>
     <row r="199">
@@ -6333,10 +6333,10 @@
         <v>5357</v>
       </c>
       <c r="B199" t="n">
-        <v>1856.89995560344</v>
+        <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>6675.139394804311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -6344,10 +6344,10 @@
         <v>5358</v>
       </c>
       <c r="B200" t="n">
-        <v>2775.528645210656</v>
+        <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>9977.40376111578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -6355,7 +6355,7 @@
         <v>5359</v>
       </c>
       <c r="B201" t="n">
-        <v>1782.438214893986</v>
+        <v>0</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
         <v>5360</v>
       </c>
       <c r="B202" t="n">
-        <v>3094.166735347271</v>
+        <v>1380.676677790173</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -6377,7 +6377,7 @@
         <v>5361</v>
       </c>
       <c r="B203" t="n">
-        <v>4471.453007256381</v>
+        <v>1792.292447037863</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -6388,7 +6388,7 @@
         <v>5362</v>
       </c>
       <c r="B204" t="n">
-        <v>5808.83212545358</v>
+        <v>2539.201387613717</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>5363</v>
       </c>
       <c r="B205" t="n">
-        <v>6596.985566397112</v>
+        <v>3320.565855764806</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -6410,7 +6410,7 @@
         <v>5364</v>
       </c>
       <c r="B206" t="n">
-        <v>7928.038346422167</v>
+        <v>3725.43391763805</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -6421,7 +6421,7 @@
         <v>5365</v>
       </c>
       <c r="B207" t="n">
-        <v>8631.904987144411</v>
+        <v>4117.196819211281</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>5366</v>
       </c>
       <c r="B208" t="n">
-        <v>9337.341259020788</v>
+        <v>4134.936118497692</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>5367</v>
       </c>
       <c r="B209" t="n">
-        <v>9942.921289836935</v>
+        <v>4147.898076832479</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>5368</v>
       </c>
       <c r="B210" t="n">
-        <v>9133.067138532761</v>
+        <v>4404.949925253007</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
         <v>5369</v>
       </c>
       <c r="B211" t="n">
-        <v>7554.81695512964</v>
+        <v>3511.94779920109</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -6476,7 +6476,7 @@
         <v>5370</v>
       </c>
       <c r="B212" t="n">
-        <v>6069.927307679985</v>
+        <v>2683.098998798981</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -6487,7 +6487,7 @@
         <v>5371</v>
       </c>
       <c r="B213" t="n">
-        <v>4236.893768897251</v>
+        <v>1799.365425988101</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
         <v>5372</v>
       </c>
       <c r="B214" t="n">
-        <v>3522.67798725506</v>
+        <v>1469.352537197047</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>5373</v>
       </c>
       <c r="B215" t="n">
-        <v>2842.478936265626</v>
+        <v>1171.283952970514</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
         <v>5374</v>
       </c>
       <c r="B216" t="n">
-        <v>2035.683917882848</v>
+        <v>750.8846578925702</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -6531,7 +6531,7 @@
         <v>5375</v>
       </c>
       <c r="B217" t="n">
-        <v>1831.472083224858</v>
+        <v>671.0582338470149</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -6542,7 +6542,7 @@
         <v>5376</v>
       </c>
       <c r="B218" t="n">
-        <v>1353.034251469941</v>
+        <v>306.3151758225118</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -6553,10 +6553,10 @@
         <v>5377</v>
       </c>
       <c r="B219" t="n">
-        <v>1015.358798552934</v>
+        <v>1605.307122677698</v>
       </c>
       <c r="C219" t="n">
-        <v>0</v>
+        <v>5770.719517230842</v>
       </c>
     </row>
     <row r="220">
@@ -6564,10 +6564,10 @@
         <v>5378</v>
       </c>
       <c r="B220" t="n">
-        <v>993.7423838404452</v>
+        <v>1512.488056737244</v>
       </c>
       <c r="C220" t="n">
-        <v>0</v>
+        <v>5437.055766645681</v>
       </c>
     </row>
     <row r="221">
@@ -6575,10 +6575,10 @@
         <v>5379</v>
       </c>
       <c r="B221" t="n">
-        <v>786.3762244749153</v>
+        <v>1528.632894778632</v>
       </c>
       <c r="C221" t="n">
-        <v>0</v>
+        <v>5495.092842960752</v>
       </c>
     </row>
     <row r="222">
@@ -6586,10 +6586,10 @@
         <v>5380</v>
       </c>
       <c r="B222" t="n">
-        <v>632.572247008873</v>
+        <v>1845.333289930281</v>
       </c>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>6633.559822642414</v>
       </c>
     </row>
     <row r="223">
@@ -6597,7 +6597,7 @@
         <v>5381</v>
       </c>
       <c r="B223" t="n">
-        <v>844.3397324731509</v>
+        <v>0</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
         <v>5382</v>
       </c>
       <c r="B224" t="n">
-        <v>1585.606203008711</v>
+        <v>842.1372331707084</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>5383</v>
       </c>
       <c r="B225" t="n">
-        <v>2970.72393644014</v>
+        <v>1642.443584356478</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -6630,7 +6630,7 @@
         <v>5384</v>
       </c>
       <c r="B226" t="n">
-        <v>4331.834205607942</v>
+        <v>2761.353355580345</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -6641,7 +6641,7 @@
         <v>5385</v>
       </c>
       <c r="B227" t="n">
-        <v>5749.014182198166</v>
+        <v>3584.595939687137</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -6652,7 +6652,7 @@
         <v>5386</v>
       </c>
       <c r="B228" t="n">
-        <v>6454.226016516687</v>
+        <v>3990.157540522056</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
         <v>5387</v>
       </c>
       <c r="B229" t="n">
-        <v>7858.324839167642</v>
+        <v>3689.50467618012</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
         <v>5388</v>
       </c>
       <c r="B230" t="n">
-        <v>8588.72457480813</v>
+        <v>4470.53787117406</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
         <v>5389</v>
       </c>
       <c r="B231" t="n">
-        <v>9355.961275985765</v>
+        <v>4117.196819211281</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
         <v>5390</v>
       </c>
       <c r="B232" t="n">
-        <v>10004.23137838218</v>
+        <v>4134.936118497692</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -6707,7 +6707,7 @@
         <v>5391</v>
       </c>
       <c r="B233" t="n">
-        <v>10008.75563373118</v>
+        <v>2988.667592598601</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>5392</v>
       </c>
       <c r="B234" t="n">
-        <v>9133.067138532761</v>
+        <v>2936.628453288431</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
         <v>5393</v>
       </c>
       <c r="B235" t="n">
-        <v>7554.81695512964</v>
+        <v>2234.87671233575</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>5394</v>
       </c>
       <c r="B236" t="n">
-        <v>5564.103733719947</v>
+        <v>1609.861608401671</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
         <v>5395</v>
       </c>
       <c r="B237" t="n">
-        <v>3813.207763408692</v>
+        <v>1325.759517998861</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -6762,7 +6762,7 @@
         <v>5396</v>
       </c>
       <c r="B238" t="n">
-        <v>3131.265591324821</v>
+        <v>1049.537034422274</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -6773,7 +6773,7 @@
         <v>5397</v>
       </c>
       <c r="B239" t="n">
-        <v>2487.169805464986</v>
+        <v>780.856934689724</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -6784,7 +6784,7 @@
         <v>5398</v>
       </c>
       <c r="B240" t="n">
-        <v>1696.399407275985</v>
+        <v>563.1645323076219</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>5399</v>
       </c>
       <c r="B241" t="n">
-        <v>1220.981076923717</v>
+        <v>671.0582338470149</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
         <v>5400</v>
       </c>
       <c r="B242" t="n">
-        <v>1082.430103812667</v>
+        <v>600.1805185620557</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>5401</v>
       </c>
       <c r="B243" t="n">
-        <v>746.998758780038</v>
+        <v>661.63948185294</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         <v>5402</v>
       </c>
       <c r="B244" t="n">
-        <v>745.3079919521787</v>
+        <v>791.4783456982442</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         <v>5403</v>
       </c>
       <c r="B245" t="n">
-        <v>524.2540895534338</v>
+        <v>692.2032510547143</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>5404</v>
       </c>
       <c r="B246" t="n">
-        <v>1265.134955010845</v>
+        <v>652.5337281047515</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
         <v>5405</v>
       </c>
       <c r="B247" t="n">
-        <v>1281.996881384645</v>
+        <v>886.006898556305</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>5406</v>
       </c>
       <c r="B248" t="n">
-        <v>2092.1977583921</v>
+        <v>842.1372331707084</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -6883,7 +6883,7 @@
         <v>5407</v>
       </c>
       <c r="B249" t="n">
-        <v>2970.72393644014</v>
+        <v>1642.443584356478</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>5408</v>
       </c>
       <c r="B250" t="n">
-        <v>4331.834205607942</v>
+        <v>2086.860739570775</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -6905,7 +6905,7 @@
         <v>5409</v>
       </c>
       <c r="B251" t="n">
-        <v>5145.581536485603</v>
+        <v>2867.668166745508</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -6916,7 +6916,7 @@
         <v>5410</v>
       </c>
       <c r="B252" t="n">
-        <v>5849.492973211798</v>
+        <v>3627.426882323249</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -6927,7 +6927,7 @@
         <v>5411</v>
       </c>
       <c r="B253" t="n">
-        <v>7203.452473158436</v>
+        <v>4427.411298292202</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
         <v>5412</v>
       </c>
       <c r="B254" t="n">
-        <v>7928.038346422167</v>
+        <v>4470.53787117406</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>5413</v>
       </c>
       <c r="B255" t="n">
-        <v>8631.904987144411</v>
+        <v>2994.330492216481</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         <v>5414</v>
       </c>
       <c r="B256" t="n">
-        <v>9337.341259020788</v>
+        <v>2631.320891643725</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         <v>5415</v>
       </c>
       <c r="B257" t="n">
-        <v>9280.114675067925</v>
+        <v>2615.084505789795</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -6982,7 +6982,7 @@
         <v>5416</v>
       </c>
       <c r="B258" t="n">
-        <v>8480.69684930356</v>
+        <v>2202.475236077089</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -6993,7 +6993,7 @@
         <v>5417</v>
       </c>
       <c r="B259" t="n">
-        <v>6392.525949185526</v>
+        <v>1277.071086865342</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
         <v>5418</v>
       </c>
       <c r="B260" t="n">
-        <v>4552.443072616299</v>
+        <v>1073.240288525456</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>5419</v>
       </c>
       <c r="B261" t="n">
-        <v>3389.512125345373</v>
+        <v>662.8797589994305</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>5420</v>
       </c>
       <c r="B262" t="n">
-        <v>2739.858947360526</v>
+        <v>0</v>
       </c>
       <c r="C262" t="n">
         <v>0</v>
@@ -7037,7 +7037,7 @@
         <v>5421</v>
       </c>
       <c r="B263" t="n">
-        <v>2131.861610342909</v>
+        <v>0</v>
       </c>
       <c r="C263" t="n">
         <v>0</v>
@@ -7048,7 +7048,7 @@
         <v>5422</v>
       </c>
       <c r="B264" t="n">
-        <v>1696.399407275985</v>
+        <v>0</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
@@ -7059,7 +7059,7 @@
         <v>5423</v>
       </c>
       <c r="B265" t="n">
-        <v>1220.981076923717</v>
+        <v>0</v>
       </c>
       <c r="C265" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>5424</v>
       </c>
       <c r="B266" t="n">
-        <v>1082.430103812667</v>
+        <v>2104.096865820102</v>
       </c>
       <c r="C266" t="n">
-        <v>0</v>
+        <v>7563.756914925321</v>
       </c>
     </row>
     <row r="267">
@@ -7081,10 +7081,10 @@
         <v>5425</v>
       </c>
       <c r="B267" t="n">
-        <v>746.998758780038</v>
+        <v>1605.30712267771</v>
       </c>
       <c r="C267" t="n">
-        <v>0</v>
+        <v>5770.719517230886</v>
       </c>
     </row>
     <row r="268">
@@ -7092,7 +7092,7 @@
         <v>5426</v>
       </c>
       <c r="B268" t="n">
-        <v>745.3079919521787</v>
+        <v>0</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
@@ -7103,7 +7103,7 @@
         <v>5427</v>
       </c>
       <c r="B269" t="n">
-        <v>524.2540895534338</v>
+        <v>0</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>5428</v>
       </c>
       <c r="B270" t="n">
-        <v>632.572247008873</v>
+        <v>0</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -7125,7 +7125,7 @@
         <v>5429</v>
       </c>
       <c r="B271" t="n">
-        <v>844.3397324731509</v>
+        <v>0</v>
       </c>
       <c r="C271" t="n">
         <v>0</v>
@@ -7136,7 +7136,7 @@
         <v>5430</v>
       </c>
       <c r="B272" t="n">
-        <v>1569.148272010146</v>
+        <v>0</v>
       </c>
       <c r="C272" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
         <v>5431</v>
       </c>
       <c r="B273" t="n">
-        <v>2398.847605634659</v>
+        <v>1313.95602673644</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>5432</v>
       </c>
       <c r="B274" t="n">
-        <v>3713.002410782014</v>
+        <v>2071.016465749331</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
         <v>5433</v>
       </c>
       <c r="B275" t="n">
-        <v>5110.24563544572</v>
+        <v>2509.211525595056</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -7180,7 +7180,7 @@
         <v>5434</v>
       </c>
       <c r="B276" t="n">
-        <v>5808.83212545358</v>
+        <v>2901.941287098131</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>5435</v>
       </c>
       <c r="B277" t="n">
-        <v>6548.580107149232</v>
+        <v>2951.606201551307</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
         <v>5436</v>
       </c>
       <c r="B278" t="n">
-        <v>7267.353053714765</v>
+        <v>2980.349704097881</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>5437</v>
       </c>
       <c r="B279" t="n">
-        <v>7967.919705498499</v>
+        <v>3029.413655426994</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
@@ -7224,7 +7224,7 @@
         <v>5438</v>
       </c>
       <c r="B280" t="n">
-        <v>8003.408110569526</v>
+        <v>3383.124431329076</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
@@ -7235,7 +7235,7 @@
         <v>5439</v>
       </c>
       <c r="B281" t="n">
-        <v>7291.491886801509</v>
+        <v>2988.667592598601</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
@@ -7246,7 +7246,7 @@
         <v>5440</v>
       </c>
       <c r="B282" t="n">
-        <v>5218.886602597744</v>
+        <v>2202.475236077089</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
@@ -7257,7 +7257,7 @@
         <v>5441</v>
       </c>
       <c r="B283" t="n">
-        <v>4067.968954412758</v>
+        <v>1277.071086865342</v>
       </c>
       <c r="C283" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>5442</v>
       </c>
       <c r="B284" t="n">
-        <v>3540.787227800031</v>
+        <v>536.621319876215</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
         <v>5443</v>
       </c>
       <c r="B285" t="n">
-        <v>2542.135298080876</v>
+        <v>0</v>
       </c>
       <c r="C285" t="n">
         <v>0</v>
@@ -7290,7 +7290,7 @@
         <v>5444</v>
       </c>
       <c r="B286" t="n">
-        <v>1957.039907465989</v>
+        <v>0</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>5445</v>
       </c>
       <c r="B287" t="n">
-        <v>1776.547663254889</v>
+        <v>0</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
         <v>5446</v>
       </c>
       <c r="B288" t="n">
-        <v>1357.119712956501</v>
+        <v>0</v>
       </c>
       <c r="C288" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
         <v>5447</v>
       </c>
       <c r="B289" t="n">
-        <v>915.7336334687392</v>
+        <v>0</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
@@ -7334,10 +7334,10 @@
         <v>5448</v>
       </c>
       <c r="B290" t="n">
-        <v>797.926337915366</v>
+        <v>2298.04108081247</v>
       </c>
       <c r="C290" t="n">
-        <v>0</v>
+        <v>8260.942924318728</v>
       </c>
     </row>
     <row r="291">
@@ -7345,10 +7345,10 @@
         <v>5449</v>
       </c>
       <c r="B291" t="n">
-        <v>509.3212378009041</v>
+        <v>1690.60284730891</v>
       </c>
       <c r="C291" t="n">
-        <v>0</v>
+        <v>6077.338541037733</v>
       </c>
     </row>
     <row r="292">
@@ -7356,10 +7356,10 @@
         <v>5450</v>
       </c>
       <c r="B292" t="n">
-        <v>488.7701965487762</v>
+        <v>1566.603360959052</v>
       </c>
       <c r="C292" t="n">
-        <v>0</v>
+        <v>5631.588163494937</v>
       </c>
     </row>
     <row r="293">
@@ -7367,10 +7367,10 @@
         <v>5451</v>
       </c>
       <c r="B293" t="n">
-        <v>9425.507838494923</v>
+        <v>1392.403727304189</v>
       </c>
       <c r="C293" t="n">
-        <v>33882.58936563342</v>
+        <v>5005.379501223644</v>
       </c>
     </row>
     <row r="294">
@@ -7378,10 +7378,10 @@
         <v>5452</v>
       </c>
       <c r="B294" t="n">
-        <v>1856.899955603445</v>
+        <v>1516.479755457432</v>
       </c>
       <c r="C294" t="n">
-        <v>6675.13939480433</v>
+        <v>5451.405029404246</v>
       </c>
     </row>
     <row r="295">
@@ -7389,10 +7389,10 @@
         <v>5453</v>
       </c>
       <c r="B295" t="n">
-        <v>1856.899955603445</v>
+        <v>1899.108708620582</v>
       </c>
       <c r="C295" t="n">
-        <v>6675.13939480433</v>
+        <v>6826.870407140262</v>
       </c>
     </row>
     <row r="296">
@@ -7400,7 +7400,7 @@
         <v>5454</v>
       </c>
       <c r="B296" t="n">
-        <v>902.6553921878502</v>
+        <v>0</v>
       </c>
       <c r="C296" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
         <v>5455</v>
       </c>
       <c r="B297" t="n">
-        <v>1535.001450798823</v>
+        <v>0</v>
       </c>
       <c r="C297" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>5456</v>
       </c>
       <c r="B298" t="n">
-        <v>2137.746909266406</v>
+        <v>5181.365160847776</v>
       </c>
       <c r="C298" t="n">
-        <v>0</v>
+        <v>18625.84712745172</v>
       </c>
     </row>
     <row r="299">
@@ -7433,10 +7433,10 @@
         <v>5457</v>
       </c>
       <c r="B299" t="n">
-        <v>2769.076020338925</v>
+        <v>5887.19176508303</v>
       </c>
       <c r="C299" t="n">
-        <v>0</v>
+        <v>21163.13566451811</v>
       </c>
     </row>
     <row r="300">
@@ -7444,10 +7444,10 @@
         <v>5458</v>
       </c>
       <c r="B300" t="n">
-        <v>3926.141889600081</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C300" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="301">
@@ -7455,10 +7455,10 @@
         <v>5459</v>
       </c>
       <c r="B301" t="n">
-        <v>4569.577594131159</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="302">
@@ -7466,7 +7466,7 @@
         <v>5460</v>
       </c>
       <c r="B302" t="n">
-        <v>4621.947107849776</v>
+        <v>1004.771214385633</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>5461</v>
       </c>
       <c r="B303" t="n">
-        <v>4647.749937617412</v>
+        <v>1010.033503932439</v>
       </c>
       <c r="C303" t="n">
         <v>0</v>
@@ -7488,7 +7488,7 @@
         <v>5462</v>
       </c>
       <c r="B304" t="n">
-        <v>4668.335771090785</v>
+        <v>1352.735777506381</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -7499,7 +7499,7 @@
         <v>5463</v>
       </c>
       <c r="B305" t="n">
-        <v>4066.606548594838</v>
+        <v>1048.400267719588</v>
       </c>
       <c r="C305" t="n">
         <v>0</v>
@@ -7510,7 +7510,7 @@
         <v>5464</v>
       </c>
       <c r="B306" t="n">
-        <v>4081.751519845503</v>
+        <v>995.2646642949775</v>
       </c>
       <c r="C306" t="n">
         <v>0</v>
@@ -7521,10 +7521,10 @@
         <v>5465</v>
       </c>
       <c r="B307" t="n">
-        <v>2563.962358929924</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C307" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="308">
@@ -7532,10 +7532,10 @@
         <v>5466</v>
       </c>
       <c r="B308" t="n">
-        <v>1404.463043698418</v>
+        <v>6217.958231119064</v>
       </c>
       <c r="C308" t="n">
-        <v>0</v>
+        <v>22352.16701822926</v>
       </c>
     </row>
     <row r="309">
@@ -7543,7 +7543,7 @@
         <v>5467</v>
       </c>
       <c r="B309" t="n">
-        <v>766.8244208510366</v>
+        <v>0</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
         <v>5470</v>
       </c>
       <c r="B312" t="n">
-        <v>989.9431464593922</v>
+        <v>0</v>
       </c>
       <c r="C312" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>5471</v>
       </c>
       <c r="B313" t="n">
-        <v>599.5481206725257</v>
+        <v>0</v>
       </c>
       <c r="C313" t="n">
         <v>0</v>
@@ -7598,10 +7598,10 @@
         <v>5472</v>
       </c>
       <c r="B314" t="n">
-        <v>1856.899955603446</v>
+        <v>0</v>
       </c>
       <c r="C314" t="n">
-        <v>6675.139394804332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -7609,10 +7609,10 @@
         <v>5473</v>
       </c>
       <c r="B315" t="n">
-        <v>1856.899955603446</v>
+        <v>0</v>
       </c>
       <c r="C315" t="n">
-        <v>6675.139394804331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -7620,10 +7620,10 @@
         <v>5474</v>
       </c>
       <c r="B316" t="n">
-        <v>12273.62644746081</v>
+        <v>0</v>
       </c>
       <c r="C316" t="n">
-        <v>44120.93778629739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -7631,10 +7631,10 @@
         <v>5475</v>
       </c>
       <c r="B317" t="n">
-        <v>12379.33303735631</v>
+        <v>0</v>
       </c>
       <c r="C317" t="n">
-        <v>44500.92929869557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -7642,10 +7642,10 @@
         <v>5476</v>
       </c>
       <c r="B318" t="n">
-        <v>12379.33303735631</v>
+        <v>0</v>
       </c>
       <c r="C318" t="n">
-        <v>44500.92929869557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -7653,10 +7653,10 @@
         <v>5477</v>
       </c>
       <c r="B319" t="n">
-        <v>1856.899955603446</v>
+        <v>0</v>
       </c>
       <c r="C319" t="n">
-        <v>6675.139394804332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -7664,10 +7664,10 @@
         <v>5478</v>
       </c>
       <c r="B320" t="n">
-        <v>1856.899955603446</v>
+        <v>0</v>
       </c>
       <c r="C320" t="n">
-        <v>6675.139394804331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -7675,10 +7675,10 @@
         <v>5479</v>
       </c>
       <c r="B321" t="n">
-        <v>12379.33303735631</v>
+        <v>4739.905750759392</v>
       </c>
       <c r="C321" t="n">
-        <v>44500.92929869557</v>
+        <v>17038.89943509184</v>
       </c>
     </row>
     <row r="322">
@@ -7686,10 +7686,10 @@
         <v>5480</v>
       </c>
       <c r="B322" t="n">
-        <v>12379.33303735631</v>
+        <v>4660.746443195231</v>
       </c>
       <c r="C322" t="n">
-        <v>44500.92929869557</v>
+        <v>16754.33945608358</v>
       </c>
     </row>
     <row r="323">
@@ -7697,10 +7697,10 @@
         <v>5481</v>
       </c>
       <c r="B323" t="n">
-        <v>854.8344322288972</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C323" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="324">
@@ -7708,10 +7708,10 @@
         <v>5482</v>
       </c>
       <c r="B324" t="n">
-        <v>1290.005291014592</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C324" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="325">
@@ -7719,10 +7719,10 @@
         <v>5483</v>
       </c>
       <c r="B325" t="n">
-        <v>1703.277483358446</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C325" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="326">
@@ -7730,10 +7730,10 @@
         <v>5484</v>
       </c>
       <c r="B326" t="n">
-        <v>2165.460970103893</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C326" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="327">
@@ -7741,10 +7741,10 @@
         <v>5485</v>
       </c>
       <c r="B327" t="n">
-        <v>2616.514723821504</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C327" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="328">
@@ -7752,10 +7752,10 @@
         <v>5486</v>
       </c>
       <c r="B328" t="n">
-        <v>2615.268305221695</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C328" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="329">
@@ -7763,10 +7763,10 @@
         <v>5487</v>
       </c>
       <c r="B329" t="n">
-        <v>2557.610733598832</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C329" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="330">
@@ -7774,10 +7774,10 @@
         <v>5488</v>
       </c>
       <c r="B330" t="n">
-        <v>2354.688892700638</v>
+        <v>8437.954933007895</v>
       </c>
       <c r="C330" t="n">
-        <v>0</v>
+        <v>30332.55788225838</v>
       </c>
     </row>
     <row r="331">
@@ -7785,10 +7785,10 @@
         <v>5489</v>
       </c>
       <c r="B331" t="n">
-        <v>1915.452366438793</v>
+        <v>3384.8070443907</v>
       </c>
       <c r="C331" t="n">
-        <v>0</v>
+        <v>12167.62312780662</v>
       </c>
     </row>
     <row r="332">
@@ -7796,7 +7796,7 @@
         <v>5490</v>
       </c>
       <c r="B332" t="n">
-        <v>1463.438482654044</v>
+        <v>0</v>
       </c>
       <c r="C332" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
         <v>5491</v>
       </c>
       <c r="B333" t="n">
-        <v>1050.92960180934</v>
+        <v>0</v>
       </c>
       <c r="C333" t="n">
         <v>0</v>
@@ -7818,7 +7818,7 @@
         <v>5492</v>
       </c>
       <c r="B334" t="n">
-        <v>658.2265016876692</v>
+        <v>0</v>
       </c>
       <c r="C334" t="n">
         <v>0</v>
@@ -7829,10 +7829,10 @@
         <v>5493</v>
       </c>
       <c r="B335" t="n">
-        <v>2513.502425989741</v>
+        <v>0</v>
       </c>
       <c r="C335" t="n">
-        <v>9035.478196889697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -7840,10 +7840,10 @@
         <v>5494</v>
       </c>
       <c r="B336" t="n">
-        <v>2095.497891518153</v>
+        <v>0</v>
       </c>
       <c r="C336" t="n">
-        <v>7532.845528480058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -7851,10 +7851,10 @@
         <v>5495</v>
       </c>
       <c r="B337" t="n">
-        <v>1856.899955603446</v>
+        <v>0</v>
       </c>
       <c r="C337" t="n">
-        <v>6675.139394804333</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/first_stage_optimization/lshp_operation.xlsx
+++ b/first_stage_optimization/lshp_operation.xlsx
@@ -439,10 +439,10 @@
         <v>288</v>
       </c>
       <c r="B2" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C2" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="3">
@@ -450,10 +450,10 @@
         <v>289</v>
       </c>
       <c r="B3" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C3" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>290</v>
       </c>
       <c r="B4" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C4" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="5">
@@ -472,10 +472,10 @@
         <v>291</v>
       </c>
       <c r="B5" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C5" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="6">
@@ -483,10 +483,10 @@
         <v>292</v>
       </c>
       <c r="B6" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C6" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="7">
@@ -494,10 +494,10 @@
         <v>293</v>
       </c>
       <c r="B7" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C7" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="8">
@@ -505,10 +505,10 @@
         <v>294</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="9">
@@ -560,10 +560,10 @@
         <v>299</v>
       </c>
       <c r="B13" t="n">
-        <v>7571.621973941301</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C13" t="n">
-        <v>20883.24513659566</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="14">
@@ -571,10 +571,10 @@
         <v>300</v>
       </c>
       <c r="B14" t="n">
-        <v>4157.129133592324</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C14" t="n">
-        <v>11465.75292058619</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="15">
@@ -582,10 +582,10 @@
         <v>301</v>
       </c>
       <c r="B15" t="n">
-        <v>7859.845117504699</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C15" t="n">
-        <v>21678.19165951901</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="16">
@@ -593,10 +593,10 @@
         <v>302</v>
       </c>
       <c r="B16" t="n">
-        <v>3244.59692381376</v>
+        <v>7715.679075472789</v>
       </c>
       <c r="C16" t="n">
-        <v>8948.903307989189</v>
+        <v>21280.56816398705</v>
       </c>
     </row>
     <row r="17">
@@ -648,10 +648,10 @@
         <v>307</v>
       </c>
       <c r="B21" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C21" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="22">
@@ -659,10 +659,10 @@
         <v>308</v>
       </c>
       <c r="B22" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C22" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="23">
@@ -670,10 +670,10 @@
         <v>309</v>
       </c>
       <c r="B23" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C23" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="24">
@@ -681,10 +681,10 @@
         <v>310</v>
       </c>
       <c r="B24" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C24" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="25">
@@ -692,10 +692,10 @@
         <v>311</v>
       </c>
       <c r="B25" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C25" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="26">
@@ -703,10 +703,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C26" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="27">
@@ -714,10 +714,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C27" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="28">
@@ -725,10 +725,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C28" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="29">
@@ -736,10 +736,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C29" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="30">
@@ -747,10 +747,10 @@
         <v>316</v>
       </c>
       <c r="B30" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C30" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="31">
@@ -758,10 +758,10 @@
         <v>317</v>
       </c>
       <c r="B31" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C31" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="32">
@@ -769,10 +769,10 @@
         <v>318</v>
       </c>
       <c r="B32" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C32" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="33">
@@ -780,10 +780,10 @@
         <v>319</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>5061.248487878984</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>13959.3990869281</v>
       </c>
     </row>
     <row r="34">
@@ -813,10 +813,10 @@
         <v>322</v>
       </c>
       <c r="B36" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C36" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="37">
@@ -824,10 +824,10 @@
         <v>323</v>
       </c>
       <c r="B37" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C37" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="38">
@@ -835,10 +835,10 @@
         <v>324</v>
       </c>
       <c r="B38" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C38" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="39">
@@ -846,10 +846,10 @@
         <v>325</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="40">
@@ -857,10 +857,10 @@
         <v>326</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="41">
@@ -868,10 +868,10 @@
         <v>327</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>10522.31423963353</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>29021.53177044781</v>
       </c>
     </row>
     <row r="42">
@@ -901,10 +901,10 @@
         <v>330</v>
       </c>
       <c r="B44" t="n">
-        <v>1649.647793852731</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>4549.883682338455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -912,10 +912,10 @@
         <v>331</v>
       </c>
       <c r="B45" t="n">
-        <v>2423.783616176349</v>
+        <v>6894.865767835377</v>
       </c>
       <c r="C45" t="n">
-        <v>6685.023049074291</v>
+        <v>19016.68790507215</v>
       </c>
     </row>
     <row r="46">
@@ -923,10 +923,10 @@
         <v>332</v>
       </c>
       <c r="B46" t="n">
-        <v>2606.87476649653</v>
+        <v>7077.956918155559</v>
       </c>
       <c r="C46" t="n">
-        <v>7190.005652225482</v>
+        <v>19521.67050822334</v>
       </c>
     </row>
     <row r="47">
@@ -934,10 +934,10 @@
         <v>333</v>
       </c>
       <c r="B47" t="n">
-        <v>3759.547892638409</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C47" t="n">
-        <v>10369.18648539864</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="48">
@@ -945,10 +945,10 @@
         <v>334</v>
       </c>
       <c r="B48" t="n">
-        <v>3913.606187237279</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C48" t="n">
-        <v>10794.09374338201</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="49">
@@ -956,10 +956,10 @@
         <v>335</v>
       </c>
       <c r="B49" t="n">
-        <v>2083.727200419131</v>
+        <v>6554.809352078159</v>
       </c>
       <c r="C49" t="n">
-        <v>5747.115489112803</v>
+        <v>18078.78034511066</v>
       </c>
     </row>
     <row r="50">
@@ -967,10 +967,10 @@
         <v>336</v>
       </c>
       <c r="B50" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C50" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="51">
@@ -978,10 +978,10 @@
         <v>337</v>
       </c>
       <c r="B51" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C51" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="52">
@@ -989,10 +989,10 @@
         <v>338</v>
       </c>
       <c r="B52" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C52" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="53">
@@ -1000,10 +1000,10 @@
         <v>339</v>
       </c>
       <c r="B53" t="n">
-        <v>6321.080014189263</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C53" t="n">
-        <v>17434.13286065532</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="54">
@@ -1011,10 +1011,10 @@
         <v>340</v>
       </c>
       <c r="B54" t="n">
-        <v>10997.65195901894</v>
+        <v>9400.398830393617</v>
       </c>
       <c r="C54" t="n">
-        <v>30332.55788225838</v>
+        <v>25927.18361171565</v>
       </c>
     </row>
     <row r="55">
@@ -1022,10 +1022,10 @@
         <v>341</v>
       </c>
       <c r="B55" t="n">
-        <v>5420.552036878907</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C55" t="n">
-        <v>14950.39204960349</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="56">
@@ -1220,10 +1220,10 @@
         <v>359</v>
       </c>
       <c r="B73" t="n">
-        <v>6228.763502302742</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C73" t="n">
-        <v>17179.51524312018</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="74">
@@ -1231,10 +1231,10 @@
         <v>360</v>
       </c>
       <c r="B74" t="n">
-        <v>5821.15015514865</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C74" t="n">
-        <v>16055.27931601456</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="75">
@@ -1242,10 +1242,10 @@
         <v>361</v>
       </c>
       <c r="B75" t="n">
-        <v>5809.795287589211</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C75" t="n">
-        <v>16023.96152392808</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="76">
@@ -1253,10 +1253,10 @@
         <v>362</v>
       </c>
       <c r="B76" t="n">
-        <v>5911.932054259483</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C76" t="n">
-        <v>16305.66432726075</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="77">
@@ -1264,10 +1264,10 @@
         <v>363</v>
       </c>
       <c r="B77" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C77" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="78">
@@ -1275,10 +1275,10 @@
         <v>364</v>
       </c>
       <c r="B78" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C78" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="79">
@@ -1286,10 +1286,10 @@
         <v>365</v>
       </c>
       <c r="B79" t="n">
-        <v>7754.904030281272</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C79" t="n">
-        <v>21388.75427649459</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="80">
@@ -1297,10 +1297,10 @@
         <v>366</v>
       </c>
       <c r="B80" t="n">
-        <v>9198.907302094618</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C80" t="n">
-        <v>25371.45103646335</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="81">
@@ -1374,10 +1374,10 @@
         <v>373</v>
       </c>
       <c r="B87" t="n">
-        <v>5684.661918074331</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C87" t="n">
-        <v>15678.8319282693</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="88">
@@ -1462,10 +1462,10 @@
         <v>381</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>1622.479896434131</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>4474.952067475599</v>
       </c>
     </row>
     <row r="96">
@@ -1473,10 +1473,10 @@
         <v>382</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>3756.082560895171</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>10359.62877470961</v>
       </c>
     </row>
     <row r="97">
@@ -1484,10 +1484,10 @@
         <v>383</v>
       </c>
       <c r="B97" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C97" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="98">
@@ -1495,10 +1495,10 @@
         <v>384</v>
       </c>
       <c r="B98" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C98" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="99">
@@ -1506,10 +1506,10 @@
         <v>385</v>
       </c>
       <c r="B99" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C99" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="100">
@@ -1517,10 +1517,10 @@
         <v>386</v>
       </c>
       <c r="B100" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C100" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="101">
@@ -1528,10 +1528,10 @@
         <v>387</v>
       </c>
       <c r="B101" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C101" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="102">
@@ -1539,10 +1539,10 @@
         <v>388</v>
       </c>
       <c r="B102" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C102" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="103">
@@ -1550,10 +1550,10 @@
         <v>389</v>
       </c>
       <c r="B103" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C103" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="104">
@@ -1561,10 +1561,10 @@
         <v>390</v>
       </c>
       <c r="B104" t="n">
-        <v>3801.67068790515</v>
+        <v>7837.206172529511</v>
       </c>
       <c r="C104" t="n">
-        <v>10485.36511428707</v>
+        <v>21615.75132121661</v>
       </c>
     </row>
     <row r="105">
@@ -1605,10 +1605,10 @@
         <v>394</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>2345.250100787285</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>6468.420231480806</v>
       </c>
     </row>
     <row r="109">
@@ -1627,10 +1627,10 @@
         <v>396</v>
       </c>
       <c r="B110" t="n">
-        <v>10361.8771713293</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C110" t="n">
-        <v>28579.03125498031</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="111">
@@ -1638,10 +1638,10 @@
         <v>397</v>
       </c>
       <c r="B111" t="n">
-        <v>9692.899210867357</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C111" t="n">
-        <v>26733.92715609799</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="112">
@@ -1715,10 +1715,10 @@
         <v>404</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>2696.459230950215</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>7437.088026128404</v>
       </c>
     </row>
     <row r="119">
@@ -1726,10 +1726,10 @@
         <v>405</v>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>4950.369843695064</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>13653.58536367629</v>
       </c>
     </row>
     <row r="120">
@@ -1737,10 +1737,10 @@
         <v>406</v>
       </c>
       <c r="B120" t="n">
-        <v>2140.480629651258</v>
+        <v>6176.01611427562</v>
       </c>
       <c r="C120" t="n">
-        <v>5903.646781757358</v>
+        <v>17034.0329886869</v>
       </c>
     </row>
     <row r="121">
@@ -1748,10 +1748,10 @@
         <v>407</v>
       </c>
       <c r="B121" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C121" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="122">
@@ -1759,10 +1759,10 @@
         <v>408</v>
       </c>
       <c r="B122" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C122" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="123">
@@ -1770,10 +1770,10 @@
         <v>409</v>
       </c>
       <c r="B123" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C123" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="124">
@@ -1781,10 +1781,10 @@
         <v>410</v>
       </c>
       <c r="B124" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C124" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="125">
@@ -1792,10 +1792,10 @@
         <v>411</v>
       </c>
       <c r="B125" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C125" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="126">
@@ -1803,10 +1803,10 @@
         <v>412</v>
       </c>
       <c r="B126" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C126" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="127">
@@ -1814,10 +1814,10 @@
         <v>413</v>
       </c>
       <c r="B127" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C127" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="128">
@@ -1825,10 +1825,10 @@
         <v>414</v>
       </c>
       <c r="B128" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C128" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="129">
@@ -1836,10 +1836,10 @@
         <v>415</v>
       </c>
       <c r="B129" t="n">
-        <v>8426.964116154217</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C129" t="n">
-        <v>23242.35916698025</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="130">
@@ -1847,10 +1847,10 @@
         <v>416</v>
       </c>
       <c r="B130" t="n">
-        <v>8593.836862446151</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C130" t="n">
-        <v>23702.60988729155</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="131">
@@ -1858,10 +1858,10 @@
         <v>417</v>
       </c>
       <c r="B131" t="n">
-        <v>8604.394097444776</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C131" t="n">
-        <v>23731.72773379785</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="132">
@@ -1869,10 +1869,10 @@
         <v>418</v>
       </c>
       <c r="B132" t="n">
-        <v>6674.542034261469</v>
+        <v>10710.07751888583</v>
       </c>
       <c r="C132" t="n">
-        <v>18409.01433744435</v>
+        <v>29539.40054437389</v>
       </c>
     </row>
     <row r="133">
@@ -1880,10 +1880,10 @@
         <v>419</v>
       </c>
       <c r="B133" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C133" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="134">
@@ -1891,10 +1891,10 @@
         <v>420</v>
       </c>
       <c r="B134" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C134" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="135">
@@ -1902,10 +1902,10 @@
         <v>421</v>
       </c>
       <c r="B135" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C135" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="136">
@@ -1913,10 +1913,10 @@
         <v>422</v>
       </c>
       <c r="B136" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C136" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="137">
@@ -1924,10 +1924,10 @@
         <v>423</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="138">
@@ -1935,10 +1935,10 @@
         <v>424</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>4081.108700781916</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>11256.0814209744</v>
       </c>
     </row>
     <row r="139">
@@ -1946,10 +1946,10 @@
         <v>425</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>5535.111192715002</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>15266.35696996009</v>
       </c>
     </row>
     <row r="140">
@@ -1957,10 +1957,10 @@
         <v>426</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>6538.550852195971</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>18033.93787413659</v>
       </c>
     </row>
     <row r="141">
@@ -1968,10 +1968,10 @@
         <v>427</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>6437.462881180372</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>17755.1277478063</v>
       </c>
     </row>
     <row r="142">
@@ -1979,10 +1979,10 @@
         <v>428</v>
       </c>
       <c r="B142" t="n">
-        <v>2029.366833690533</v>
+        <v>6064.902318314894</v>
       </c>
       <c r="C142" t="n">
-        <v>5597.184487800856</v>
+        <v>16727.5706947304</v>
       </c>
     </row>
     <row r="143">
@@ -1990,10 +1990,10 @@
         <v>429</v>
       </c>
       <c r="B143" t="n">
-        <v>2514.057212889899</v>
+        <v>6549.592697514261</v>
       </c>
       <c r="C143" t="n">
-        <v>6934.006114528354</v>
+        <v>18064.3923214579</v>
       </c>
     </row>
     <row r="144">
@@ -2001,10 +2001,10 @@
         <v>430</v>
       </c>
       <c r="B144" t="n">
-        <v>1719.1410707326</v>
+        <v>5754.676555356961</v>
       </c>
       <c r="C144" t="n">
-        <v>4741.55267234116</v>
+        <v>15871.9388792707</v>
       </c>
     </row>
     <row r="145">
@@ -2012,10 +2012,10 @@
         <v>431</v>
       </c>
       <c r="B145" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C145" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="146">
@@ -2023,10 +2023,10 @@
         <v>432</v>
       </c>
       <c r="B146" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C146" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="147">
@@ -2034,10 +2034,10 @@
         <v>433</v>
       </c>
       <c r="B147" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C147" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="148">
@@ -2045,10 +2045,10 @@
         <v>434</v>
       </c>
       <c r="B148" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C148" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="149">
@@ -2056,10 +2056,10 @@
         <v>435</v>
       </c>
       <c r="B149" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C149" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="150">
@@ -2067,10 +2067,10 @@
         <v>436</v>
       </c>
       <c r="B150" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C150" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="151">
@@ -2078,10 +2078,10 @@
         <v>437</v>
       </c>
       <c r="B151" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C151" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="152">
@@ -2089,10 +2089,10 @@
         <v>438</v>
       </c>
       <c r="B152" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C152" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="153">
@@ -2100,10 +2100,10 @@
         <v>439</v>
       </c>
       <c r="B153" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C153" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="154">
@@ -2111,10 +2111,10 @@
         <v>440</v>
       </c>
       <c r="B154" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C154" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="155">
@@ -2122,10 +2122,10 @@
         <v>441</v>
       </c>
       <c r="B155" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C155" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="156">
@@ -2133,10 +2133,10 @@
         <v>442</v>
       </c>
       <c r="B156" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C156" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="157">
@@ -2144,10 +2144,10 @@
         <v>443</v>
       </c>
       <c r="B157" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C157" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="158">
@@ -2155,10 +2155,10 @@
         <v>444</v>
       </c>
       <c r="B158" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C158" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="159">
@@ -2166,10 +2166,10 @@
         <v>445</v>
       </c>
       <c r="B159" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C159" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="160">
@@ -2177,10 +2177,10 @@
         <v>446</v>
       </c>
       <c r="B160" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C160" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="161">
@@ -2188,10 +2188,10 @@
         <v>447</v>
       </c>
       <c r="B161" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C161" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="162">
@@ -2221,10 +2221,10 @@
         <v>450</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>1644.834349911096</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>4536.607751483694</v>
       </c>
     </row>
     <row r="165">
@@ -2232,10 +2232,10 @@
         <v>451</v>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>3205.01860376423</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>8839.742580930499</v>
       </c>
     </row>
     <row r="166">
@@ -2243,10 +2243,10 @@
         <v>452</v>
       </c>
       <c r="B166" t="n">
-        <v>1649.647793852731</v>
+        <v>4927.983410894259</v>
       </c>
       <c r="C166" t="n">
-        <v>4549.883682338455</v>
+        <v>13591.84147768699</v>
       </c>
     </row>
     <row r="167">
@@ -2254,10 +2254,10 @@
         <v>453</v>
       </c>
       <c r="B167" t="n">
-        <v>3191.012512059943</v>
+        <v>7226.547996684305</v>
       </c>
       <c r="C167" t="n">
-        <v>8801.112463437457</v>
+        <v>19931.498670367</v>
       </c>
     </row>
     <row r="168">
@@ -2265,10 +2265,10 @@
         <v>454</v>
       </c>
       <c r="B168" t="n">
-        <v>5125.049000201142</v>
+        <v>9160.584484825504</v>
       </c>
       <c r="C168" t="n">
-        <v>14135.36689716077</v>
+        <v>25265.75310409031</v>
       </c>
     </row>
     <row r="169">
@@ -2276,10 +2276,10 @@
         <v>455</v>
       </c>
       <c r="B169" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C169" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="170">
@@ -2287,10 +2287,10 @@
         <v>456</v>
       </c>
       <c r="B170" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C170" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="171">
@@ -2298,10 +2298,10 @@
         <v>457</v>
       </c>
       <c r="B171" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C171" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="172">
@@ -2309,10 +2309,10 @@
         <v>458</v>
       </c>
       <c r="B172" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C172" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="173">
@@ -2320,10 +2320,10 @@
         <v>459</v>
       </c>
       <c r="B173" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C173" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="174">
@@ -2331,10 +2331,10 @@
         <v>460</v>
       </c>
       <c r="B174" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C174" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="175">
@@ -2342,10 +2342,10 @@
         <v>461</v>
       </c>
       <c r="B175" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C175" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="176">
@@ -2353,10 +2353,10 @@
         <v>462</v>
       </c>
       <c r="B176" t="n">
-        <v>6293.008293438715</v>
+        <v>10328.54377806308</v>
       </c>
       <c r="C176" t="n">
-        <v>17356.70841608356</v>
+        <v>28487.09462301311</v>
       </c>
     </row>
     <row r="177">
@@ -2518,10 +2518,10 @@
         <v>477</v>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>2695.174524152985</v>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>7433.544684019202</v>
       </c>
     </row>
     <row r="192">
@@ -2529,10 +2529,10 @@
         <v>478</v>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>3756.082560895171</v>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>10359.62877470961</v>
       </c>
     </row>
     <row r="193">
@@ -2540,10 +2540,10 @@
         <v>479</v>
       </c>
       <c r="B193" t="n">
-        <v>0</v>
+        <v>4403.242377510923</v>
       </c>
       <c r="C193" t="n">
-        <v>0</v>
+        <v>12144.55638195861</v>
       </c>
     </row>
     <row r="194">
@@ -2551,10 +2551,10 @@
         <v>480</v>
       </c>
       <c r="B194" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C194" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="195">
@@ -2562,10 +2562,10 @@
         <v>481</v>
       </c>
       <c r="B195" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C195" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="196">
@@ -2573,10 +2573,10 @@
         <v>482</v>
       </c>
       <c r="B196" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C196" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="197">
@@ -2584,10 +2584,10 @@
         <v>483</v>
       </c>
       <c r="B197" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C197" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="198">
@@ -2595,10 +2595,10 @@
         <v>484</v>
       </c>
       <c r="B198" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C198" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="199">
@@ -2606,10 +2606,10 @@
         <v>485</v>
       </c>
       <c r="B199" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C199" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="200">
@@ -2617,10 +2617,10 @@
         <v>486</v>
       </c>
       <c r="B200" t="n">
-        <v>6293.008293438715</v>
+        <v>10328.54377806308</v>
       </c>
       <c r="C200" t="n">
-        <v>17356.70841608356</v>
+        <v>28487.09462301311</v>
       </c>
     </row>
     <row r="201">
@@ -2628,10 +2628,10 @@
         <v>487</v>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>10026.99388425181</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>27655.3916701916</v>
       </c>
     </row>
     <row r="202">
@@ -2771,10 +2771,10 @@
         <v>500</v>
       </c>
       <c r="B214" t="n">
-        <v>0</v>
+        <v>2696.459230950215</v>
       </c>
       <c r="C214" t="n">
-        <v>0</v>
+        <v>7437.088026128404</v>
       </c>
     </row>
     <row r="215">
@@ -2782,10 +2782,10 @@
         <v>501</v>
       </c>
       <c r="B215" t="n">
-        <v>0</v>
+        <v>4950.369843695064</v>
       </c>
       <c r="C215" t="n">
-        <v>0</v>
+        <v>13653.58536367629</v>
       </c>
     </row>
     <row r="216">
@@ -2793,10 +2793,10 @@
         <v>502</v>
       </c>
       <c r="B216" t="n">
-        <v>2140.480629651258</v>
+        <v>6176.01611427562</v>
       </c>
       <c r="C216" t="n">
-        <v>5903.646781757358</v>
+        <v>17034.0329886869</v>
       </c>
     </row>
     <row r="217">
@@ -2804,10 +2804,10 @@
         <v>503</v>
       </c>
       <c r="B217" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C217" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="218">
@@ -2815,10 +2815,10 @@
         <v>504</v>
       </c>
       <c r="B218" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C218" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="219">
@@ -2826,10 +2826,10 @@
         <v>505</v>
       </c>
       <c r="B219" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C219" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="220">
@@ -2837,10 +2837,10 @@
         <v>506</v>
       </c>
       <c r="B220" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C220" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="221">
@@ -2848,10 +2848,10 @@
         <v>507</v>
       </c>
       <c r="B221" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C221" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="222">
@@ -2859,10 +2859,10 @@
         <v>508</v>
       </c>
       <c r="B222" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C222" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="223">
@@ -2870,10 +2870,10 @@
         <v>509</v>
       </c>
       <c r="B223" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C223" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="224">
@@ -2881,10 +2881,10 @@
         <v>510</v>
       </c>
       <c r="B224" t="n">
-        <v>6293.008293438715</v>
+        <v>10328.54377806308</v>
       </c>
       <c r="C224" t="n">
-        <v>17356.70841608356</v>
+        <v>28487.09462301311</v>
       </c>
     </row>
     <row r="225">
@@ -3046,10 +3046,10 @@
         <v>525</v>
       </c>
       <c r="B239" t="n">
-        <v>9686.003634797733</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C239" t="n">
-        <v>26714.90850911382</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="240">
@@ -3057,10 +3057,10 @@
         <v>526</v>
       </c>
       <c r="B240" t="n">
-        <v>10231.81959613874</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C240" t="n">
-        <v>28220.3202371927</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="241">
@@ -3068,10 +3068,10 @@
         <v>527</v>
       </c>
       <c r="B241" t="n">
-        <v>10649.67939851187</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C241" t="n">
-        <v>29372.8168509592</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="242">
@@ -3079,10 +3079,10 @@
         <v>528</v>
       </c>
       <c r="B242" t="n">
-        <v>8070.687362726562</v>
+        <v>10728.92339674058</v>
       </c>
       <c r="C242" t="n">
-        <v>22259.71439101196</v>
+        <v>29591.37924700981</v>
       </c>
     </row>
     <row r="243">
@@ -3090,10 +3090,10 @@
         <v>529</v>
       </c>
       <c r="B243" t="n">
-        <v>8167.710632158042</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C243" t="n">
-        <v>22527.3136882913</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="244">
@@ -3101,10 +3101,10 @@
         <v>530</v>
       </c>
       <c r="B244" t="n">
-        <v>8274.935142536411</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C244" t="n">
-        <v>22823.04896701882</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="245">
@@ -3112,10 +3112,10 @@
         <v>531</v>
       </c>
       <c r="B245" t="n">
-        <v>9996.023861394573</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C245" t="n">
-        <v>27569.9734359692</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="246">
@@ -3123,10 +3123,10 @@
         <v>532</v>
       </c>
       <c r="B246" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C246" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="247">
@@ -3134,10 +3134,10 @@
         <v>533</v>
       </c>
       <c r="B247" t="n">
-        <v>10672.37460599518</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C247" t="n">
-        <v>29435.41236654767</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="248">
@@ -3145,10 +3145,10 @@
         <v>534</v>
       </c>
       <c r="B248" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C248" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="249">
@@ -3189,10 +3189,10 @@
         <v>538</v>
       </c>
       <c r="B252" t="n">
-        <v>2666.633644515992</v>
+        <v>7137.715796175021</v>
       </c>
       <c r="C252" t="n">
-        <v>7354.82625513769</v>
+        <v>19686.49111113555</v>
       </c>
     </row>
     <row r="253">
@@ -3200,10 +3200,10 @@
         <v>539</v>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>3680.085914273101</v>
       </c>
       <c r="C253" t="n">
-        <v>0</v>
+        <v>10150.02287964115</v>
       </c>
     </row>
     <row r="254">
@@ -3211,10 +3211,10 @@
         <v>540</v>
       </c>
       <c r="B254" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C254" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="255">
@@ -3222,10 +3222,10 @@
         <v>541</v>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C255" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="256">
@@ -3233,10 +3233,10 @@
         <v>542</v>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C256" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="257">
@@ -3244,10 +3244,10 @@
         <v>543</v>
       </c>
       <c r="B257" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C257" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="258">
@@ -3255,10 +3255,10 @@
         <v>544</v>
       </c>
       <c r="B258" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C258" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="259">
@@ -3266,10 +3266,10 @@
         <v>545</v>
       </c>
       <c r="B259" t="n">
-        <v>2487.300163474301</v>
+        <v>6958.382315133329</v>
       </c>
       <c r="C259" t="n">
-        <v>6860.207657077488</v>
+        <v>19191.87251307534</v>
       </c>
     </row>
     <row r="260">
@@ -3277,10 +3277,10 @@
         <v>546</v>
       </c>
       <c r="B260" t="n">
-        <v>3901.193284849212</v>
+        <v>8372.27543650824</v>
       </c>
       <c r="C260" t="n">
-        <v>10759.8577917829</v>
+        <v>23091.52264778076</v>
       </c>
     </row>
     <row r="261">
@@ -3288,10 +3288,10 @@
         <v>547</v>
       </c>
       <c r="B261" t="n">
-        <v>5746.620025821905</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C261" t="n">
-        <v>15849.71821349924</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="262">
@@ -3299,10 +3299,10 @@
         <v>548</v>
       </c>
       <c r="B262" t="n">
-        <v>4342.898865330611</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C262" t="n">
-        <v>11978.12330307517</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="263">
@@ -3310,10 +3310,10 @@
         <v>549</v>
       </c>
       <c r="B263" t="n">
-        <v>5709.740530550902</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C263" t="n">
-        <v>15748.00109886926</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="264">
@@ -3321,10 +3321,10 @@
         <v>550</v>
       </c>
       <c r="B264" t="n">
-        <v>3913.606187237279</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C264" t="n">
-        <v>10794.09374338201</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="265">
@@ -3332,10 +3332,10 @@
         <v>551</v>
       </c>
       <c r="B265" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C265" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="266">
@@ -3343,10 +3343,10 @@
         <v>552</v>
       </c>
       <c r="B266" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C266" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="267">
@@ -3354,10 +3354,10 @@
         <v>553</v>
       </c>
       <c r="B267" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C267" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="268">
@@ -3365,10 +3365,10 @@
         <v>554</v>
       </c>
       <c r="B268" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C268" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="269">
@@ -3376,10 +3376,10 @@
         <v>555</v>
       </c>
       <c r="B269" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C269" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="270">
@@ -3387,10 +3387,10 @@
         <v>556</v>
       </c>
       <c r="B270" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C270" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="271">
@@ -3398,10 +3398,10 @@
         <v>557</v>
       </c>
       <c r="B271" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C271" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="272">
@@ -3409,10 +3409,10 @@
         <v>558</v>
       </c>
       <c r="B272" t="n">
-        <v>6997.352910028611</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C272" t="n">
-        <v>19299.35707703245</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="273">
@@ -3420,10 +3420,10 @@
         <v>559</v>
       </c>
       <c r="B273" t="n">
-        <v>0</v>
+        <v>9779.305357044783</v>
       </c>
       <c r="C273" t="n">
-        <v>0</v>
+        <v>26972.24342943307</v>
       </c>
     </row>
     <row r="274">
@@ -3431,10 +3431,10 @@
         <v>560</v>
       </c>
       <c r="B274" t="n">
-        <v>0</v>
+        <v>9996.65096565463</v>
       </c>
       <c r="C274" t="n">
-        <v>0</v>
+        <v>27571.70304846624</v>
       </c>
     </row>
     <row r="275">
@@ -3442,10 +3442,10 @@
         <v>561</v>
       </c>
       <c r="B275" t="n">
-        <v>1649.647793852841</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C275" t="n">
-        <v>4549.883682338757</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="276">
@@ -3453,10 +3453,10 @@
         <v>562</v>
       </c>
       <c r="B276" t="n">
-        <v>1649.647793852841</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C276" t="n">
-        <v>4549.883682338757</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="277">
@@ -3464,10 +3464,10 @@
         <v>563</v>
       </c>
       <c r="B277" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C277" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="278">
@@ -3475,10 +3475,10 @@
         <v>564</v>
       </c>
       <c r="B278" t="n">
-        <v>1649.647793852841</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C278" t="n">
-        <v>4549.883682338757</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="279">
@@ -3486,10 +3486,10 @@
         <v>565</v>
       </c>
       <c r="B279" t="n">
-        <v>10654.43087058984</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C279" t="n">
-        <v>29385.92185758862</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="280">
@@ -3497,10 +3497,10 @@
         <v>566</v>
       </c>
       <c r="B280" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C280" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="281">
@@ -3508,10 +3508,10 @@
         <v>567</v>
       </c>
       <c r="B281" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C281" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="282">
@@ -3519,10 +3519,10 @@
         <v>568</v>
       </c>
       <c r="B282" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C282" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="283">
@@ -3530,10 +3530,10 @@
         <v>569</v>
       </c>
       <c r="B283" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C283" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="284">
@@ -3541,10 +3541,10 @@
         <v>570</v>
       </c>
       <c r="B284" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C284" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="285">
@@ -3552,10 +3552,10 @@
         <v>571</v>
       </c>
       <c r="B285" t="n">
-        <v>1649.647793852841</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C285" t="n">
-        <v>4549.883682338757</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="286">
@@ -3563,10 +3563,10 @@
         <v>572</v>
       </c>
       <c r="B286" t="n">
-        <v>1649.647793852841</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C286" t="n">
-        <v>4549.883682338757</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="287">
@@ -3574,10 +3574,10 @@
         <v>573</v>
       </c>
       <c r="B287" t="n">
-        <v>1938.961669997816</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C287" t="n">
-        <v>5347.838548250955</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="288">
@@ -3585,10 +3585,10 @@
         <v>574</v>
       </c>
       <c r="B288" t="n">
-        <v>3913.606187237279</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C288" t="n">
-        <v>10794.09374338201</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="289">
@@ -3596,10 +3596,10 @@
         <v>575</v>
       </c>
       <c r="B289" t="n">
-        <v>4089.402655993988</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C289" t="n">
-        <v>11278.95692908108</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="290">
@@ -3607,10 +3607,10 @@
         <v>576</v>
       </c>
       <c r="B290" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C290" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="291">
@@ -3618,10 +3618,10 @@
         <v>577</v>
       </c>
       <c r="B291" t="n">
-        <v>6956.998276113732</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C291" t="n">
-        <v>19188.05520335963</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="292">
@@ -3629,10 +3629,10 @@
         <v>578</v>
       </c>
       <c r="B292" t="n">
-        <v>7025.505483901085</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C292" t="n">
-        <v>19377.00452211468</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="293">
@@ -3640,10 +3640,10 @@
         <v>579</v>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C293" t="n">
-        <v>0</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="294">
@@ -3651,10 +3651,10 @@
         <v>580</v>
       </c>
       <c r="B294" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C294" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="295">
@@ -3662,10 +3662,10 @@
         <v>581</v>
       </c>
       <c r="B295" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C295" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="296">
@@ -3673,10 +3673,10 @@
         <v>582</v>
       </c>
       <c r="B296" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C296" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="297">
@@ -3684,10 +3684,10 @@
         <v>583</v>
       </c>
       <c r="B297" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C297" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="298">
@@ -3695,10 +3695,10 @@
         <v>584</v>
       </c>
       <c r="B298" t="n">
-        <v>9583.095508839462</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C298" t="n">
-        <v>26431.07822435706</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="299">
@@ -3706,10 +3706,10 @@
         <v>585</v>
       </c>
       <c r="B299" t="n">
-        <v>7914.075982679272</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C299" t="n">
-        <v>21827.7654833718</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="300">
@@ -3717,10 +3717,10 @@
         <v>586</v>
       </c>
       <c r="B300" t="n">
-        <v>4306.182319570999</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C300" t="n">
-        <v>11876.85561851486</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="301">
@@ -3728,10 +3728,10 @@
         <v>587</v>
       </c>
       <c r="B301" t="n">
-        <v>2102.322267714388</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C301" t="n">
-        <v>5798.402432649447</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="302">
@@ -3739,10 +3739,10 @@
         <v>588</v>
       </c>
       <c r="B302" t="n">
-        <v>2748.333252112464</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C302" t="n">
-        <v>7580.161452651875</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="303">
@@ -3750,10 +3750,10 @@
         <v>589</v>
       </c>
       <c r="B303" t="n">
-        <v>1649.647793852841</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C303" t="n">
-        <v>4549.883682338757</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="304">
@@ -3761,10 +3761,10 @@
         <v>590</v>
       </c>
       <c r="B304" t="n">
-        <v>2650.593490323663</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C304" t="n">
-        <v>7310.586002100751</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="305">
@@ -3772,10 +3772,10 @@
         <v>591</v>
       </c>
       <c r="B305" t="n">
-        <v>4811.138560992982</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C305" t="n">
-        <v>13269.57239824338</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="306">
@@ -3783,10 +3783,10 @@
         <v>592</v>
       </c>
       <c r="B306" t="n">
-        <v>5880.356316974166</v>
+        <v>10351.43846863319</v>
       </c>
       <c r="C306" t="n">
-        <v>16218.57547570855</v>
+        <v>28550.2403317064</v>
       </c>
     </row>
     <row r="307">
@@ -3838,10 +3838,10 @@
         <v>597</v>
       </c>
       <c r="B311" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C311" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="312">
@@ -3849,10 +3849,10 @@
         <v>598</v>
       </c>
       <c r="B312" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C312" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="313">
@@ -3860,10 +3860,10 @@
         <v>599</v>
       </c>
       <c r="B313" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C313" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="314">
@@ -3871,10 +3871,10 @@
         <v>600</v>
       </c>
       <c r="B314" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C314" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="315">
@@ -3882,10 +3882,10 @@
         <v>601</v>
       </c>
       <c r="B315" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C315" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="316">
@@ -3893,10 +3893,10 @@
         <v>602</v>
       </c>
       <c r="B316" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C316" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="317">
@@ -3904,10 +3904,10 @@
         <v>603</v>
       </c>
       <c r="B317" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C317" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="318">
@@ -3915,10 +3915,10 @@
         <v>604</v>
       </c>
       <c r="B318" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C318" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="319">
@@ -3926,10 +3926,10 @@
         <v>605</v>
       </c>
       <c r="B319" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C319" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="320">
@@ -3937,10 +3937,10 @@
         <v>606</v>
       </c>
       <c r="B320" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C320" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="321">
@@ -3948,10 +3948,10 @@
         <v>607</v>
       </c>
       <c r="B321" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C321" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="322">
@@ -3959,10 +3959,10 @@
         <v>608</v>
       </c>
       <c r="B322" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C322" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="323">
@@ -3970,10 +3970,10 @@
         <v>609</v>
       </c>
       <c r="B323" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C323" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="324">
@@ -3981,10 +3981,10 @@
         <v>610</v>
       </c>
       <c r="B324" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C324" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="325">
@@ -3992,10 +3992,10 @@
         <v>611</v>
       </c>
       <c r="B325" t="n">
-        <v>8978.88728521926</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C325" t="n">
-        <v>24764.61514803953</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="326">
@@ -4003,10 +4003,10 @@
         <v>612</v>
       </c>
       <c r="B326" t="n">
-        <v>6442.740912541312</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C326" t="n">
-        <v>17769.68505443472</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="327">
@@ -4014,10 +4014,10 @@
         <v>613</v>
       </c>
       <c r="B327" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C327" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="328">
@@ -4025,10 +4025,10 @@
         <v>614</v>
       </c>
       <c r="B328" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C328" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="329">
@@ -4036,10 +4036,10 @@
         <v>615</v>
       </c>
       <c r="B329" t="n">
-        <v>5221.288087981926</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C329" t="n">
-        <v>14400.80334773442</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="330">
@@ -4047,10 +4047,10 @@
         <v>616</v>
       </c>
       <c r="B330" t="n">
-        <v>4202.236440499842</v>
+        <v>9167.688534285411</v>
       </c>
       <c r="C330" t="n">
-        <v>11590.16311312397</v>
+        <v>25285.34674028138</v>
       </c>
     </row>
     <row r="331">
@@ -4058,10 +4058,10 @@
         <v>617</v>
       </c>
       <c r="B331" t="n">
-        <v>0</v>
+        <v>9975.68237012327</v>
       </c>
       <c r="C331" t="n">
-        <v>0</v>
+        <v>27513.86969094277</v>
       </c>
     </row>
     <row r="332">
@@ -4069,10 +4069,10 @@
         <v>618</v>
       </c>
       <c r="B332" t="n">
-        <v>1649.647793852738</v>
+        <v>9966.717478079683</v>
       </c>
       <c r="C332" t="n">
-        <v>4549.883682338474</v>
+        <v>27489.14367598671</v>
       </c>
     </row>
     <row r="333">
@@ -4080,10 +4080,10 @@
         <v>619</v>
       </c>
       <c r="B333" t="n">
-        <v>6795.685774307415</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C333" t="n">
-        <v>18743.14016000264</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="334">
@@ -4091,10 +4091,10 @@
         <v>620</v>
       </c>
       <c r="B334" t="n">
-        <v>8032.944710977689</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C334" t="n">
-        <v>22155.6166096793</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="335">
@@ -4102,10 +4102,10 @@
         <v>621</v>
       </c>
       <c r="B335" t="n">
-        <v>9618.476955091568</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C335" t="n">
-        <v>26528.66357897632</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="336">
@@ -4113,10 +4113,10 @@
         <v>622</v>
       </c>
       <c r="B336" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C336" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="337">
@@ -4124,10 +4124,10 @@
         <v>623</v>
       </c>
       <c r="B337" t="n">
-        <v>10997.65195901894</v>
+        <v>10816.53264289492</v>
       </c>
       <c r="C337" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
   </sheetData>
@@ -4166,10 +4166,10 @@
         <v>5160</v>
       </c>
       <c r="B2" t="n">
-        <v>2104.096865820094</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7563.756914925292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4177,10 +4177,10 @@
         <v>5161</v>
       </c>
       <c r="B3" t="n">
-        <v>1605.307122677738</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>5770.719517230988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -4188,10 +4188,10 @@
         <v>5162</v>
       </c>
       <c r="B4" t="n">
-        <v>1512.48805673732</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5437.055766645957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4199,10 +4199,10 @@
         <v>5163</v>
       </c>
       <c r="B5" t="n">
-        <v>3358.454019954424</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>12072.88990803568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4210,10 +4210,10 @@
         <v>5164</v>
       </c>
       <c r="B6" t="n">
-        <v>3699.457645448454</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>13298.72155687461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4221,10 +4221,10 @@
         <v>5165</v>
       </c>
       <c r="B7" t="n">
-        <v>4519.393840387589</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>16246.20851197313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4375,10 +4375,10 @@
         <v>5179</v>
       </c>
       <c r="B21" t="n">
-        <v>4486.089307824661</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>16126.4861776247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -4386,10 +4386,10 @@
         <v>5180</v>
       </c>
       <c r="B22" t="n">
-        <v>4606.276735769084</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>16558.53305910104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4397,10 +4397,10 @@
         <v>5181</v>
       </c>
       <c r="B23" t="n">
-        <v>4266.134100467688</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>15335.79647714283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4408,10 +4408,10 @@
         <v>5182</v>
       </c>
       <c r="B24" t="n">
-        <v>3757.906203318487</v>
+        <v>3757.906203318435</v>
       </c>
       <c r="C24" t="n">
-        <v>13508.83102994041</v>
+        <v>13508.83102994023</v>
       </c>
     </row>
     <row r="25">
@@ -4419,10 +4419,10 @@
         <v>5183</v>
       </c>
       <c r="B25" t="n">
-        <v>2955.930541755406</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C25" t="n">
-        <v>10625.90816916933</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="26">
@@ -4430,10 +4430,10 @@
         <v>5184</v>
       </c>
       <c r="B26" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C26" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="27">
@@ -4441,10 +4441,10 @@
         <v>5185</v>
       </c>
       <c r="B27" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C27" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="28">
@@ -4452,10 +4452,10 @@
         <v>5186</v>
       </c>
       <c r="B28" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C28" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="29">
@@ -4463,10 +4463,10 @@
         <v>5187</v>
       </c>
       <c r="B29" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C29" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="30">
@@ -4474,10 +4474,10 @@
         <v>5188</v>
       </c>
       <c r="B30" t="n">
-        <v>3699.457645448506</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C30" t="n">
-        <v>13298.7215568748</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="31">
@@ -4518,10 +4518,10 @@
         <v>5192</v>
       </c>
       <c r="B34" t="n">
-        <v>5492.033204206517</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C34" t="n">
-        <v>19742.62915368468</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="35">
@@ -4529,10 +4529,10 @@
         <v>5193</v>
       </c>
       <c r="B35" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C35" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="36">
@@ -4540,10 +4540,10 @@
         <v>5194</v>
       </c>
       <c r="B36" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C36" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="37">
@@ -4551,10 +4551,10 @@
         <v>5195</v>
       </c>
       <c r="B37" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C37" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="38">
@@ -4562,10 +4562,10 @@
         <v>5196</v>
       </c>
       <c r="B38" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C38" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="39">
@@ -4573,10 +4573,10 @@
         <v>5197</v>
       </c>
       <c r="B39" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C39" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="40">
@@ -4584,10 +4584,10 @@
         <v>5198</v>
       </c>
       <c r="B40" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C40" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="41">
@@ -4595,10 +4595,10 @@
         <v>5199</v>
       </c>
       <c r="B41" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C41" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="42">
@@ -4606,10 +4606,10 @@
         <v>5200</v>
       </c>
       <c r="B42" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C42" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="43">
@@ -4617,10 +4617,10 @@
         <v>5201</v>
       </c>
       <c r="B43" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C43" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="44">
@@ -4628,10 +4628,10 @@
         <v>5202</v>
       </c>
       <c r="B44" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C44" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="45">
@@ -4639,10 +4639,10 @@
         <v>5203</v>
       </c>
       <c r="B45" t="n">
-        <v>4486.089307824611</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>16126.48617762452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4683,10 +4683,10 @@
         <v>5207</v>
       </c>
       <c r="B49" t="n">
-        <v>6440.735782742589</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>23153.00241414427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4694,10 +4694,10 @@
         <v>5208</v>
       </c>
       <c r="B50" t="n">
-        <v>7871.815531435896</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>28297.413548833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4705,10 +4705,10 @@
         <v>5209</v>
       </c>
       <c r="B51" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C51" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="52">
@@ -4716,10 +4716,10 @@
         <v>5210</v>
       </c>
       <c r="B52" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C52" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="53">
@@ -4727,10 +4727,10 @@
         <v>5211</v>
       </c>
       <c r="B53" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C53" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="54">
@@ -4738,10 +4738,10 @@
         <v>5212</v>
       </c>
       <c r="B54" t="n">
-        <v>8180.260414725609</v>
+        <v>8180.260414725616</v>
       </c>
       <c r="C54" t="n">
-        <v>29406.20381260566</v>
+        <v>29406.20381260569</v>
       </c>
     </row>
     <row r="55">
@@ -4793,10 +4793,10 @@
         <v>5217</v>
       </c>
       <c r="B59" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C59" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="60">
@@ -4804,10 +4804,10 @@
         <v>5218</v>
       </c>
       <c r="B60" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C60" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="61">
@@ -4815,10 +4815,10 @@
         <v>5219</v>
       </c>
       <c r="B61" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C61" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="62">
@@ -4826,10 +4826,10 @@
         <v>5220</v>
       </c>
       <c r="B62" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C62" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="63">
@@ -4837,10 +4837,10 @@
         <v>5221</v>
       </c>
       <c r="B63" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C63" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="64">
@@ -4848,10 +4848,10 @@
         <v>5222</v>
       </c>
       <c r="B64" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C64" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="65">
@@ -4859,10 +4859,10 @@
         <v>5223</v>
       </c>
       <c r="B65" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C65" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="66">
@@ -4870,10 +4870,10 @@
         <v>5224</v>
       </c>
       <c r="B66" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C66" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="67">
@@ -4881,10 +4881,10 @@
         <v>5225</v>
       </c>
       <c r="B67" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C67" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="68">
@@ -4991,10 +4991,10 @@
         <v>5235</v>
       </c>
       <c r="B77" t="n">
-        <v>7873.231468214149</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>28302.50352438098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5002,10 +5002,10 @@
         <v>5236</v>
       </c>
       <c r="B78" t="n">
-        <v>8180.260414725557</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>29406.20381260548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -5013,10 +5013,10 @@
         <v>5237</v>
       </c>
       <c r="B79" t="n">
-        <v>8437.954933007895</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>30332.55788225838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5233,10 +5233,10 @@
         <v>5257</v>
       </c>
       <c r="B99" t="n">
-        <v>1605.307122677687</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>5770.719517230804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5244,10 +5244,10 @@
         <v>5258</v>
       </c>
       <c r="B100" t="n">
-        <v>1512.488056737244</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>5437.055766645681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5255,10 +5255,10 @@
         <v>5259</v>
       </c>
       <c r="B101" t="n">
-        <v>1528.632894778551</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>5495.092842960461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -5266,10 +5266,10 @@
         <v>5260</v>
       </c>
       <c r="B102" t="n">
-        <v>1845.333289930335</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>6633.559822642609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5574,10 +5574,10 @@
         <v>5288</v>
       </c>
       <c r="B130" t="n">
-        <v>5181.365160847776</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>18625.84712745172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5684,10 +5684,10 @@
         <v>5298</v>
       </c>
       <c r="B140" t="n">
-        <v>6217.958231119063</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>22352.16701822926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -5750,10 +5750,10 @@
         <v>5304</v>
       </c>
       <c r="B146" t="n">
-        <v>6005.178953988655</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>21587.27317950352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -5761,10 +5761,10 @@
         <v>5305</v>
       </c>
       <c r="B147" t="n">
-        <v>8004.922191931879</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>28775.90217742411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -5783,10 +5783,10 @@
         <v>5307</v>
       </c>
       <c r="B149" t="n">
-        <v>7954.247763642288</v>
+        <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>28593.73895879497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -5794,10 +5794,10 @@
         <v>5308</v>
       </c>
       <c r="B150" t="n">
-        <v>8022.344547721922</v>
+        <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>28838.53164388162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -5827,10 +5827,10 @@
         <v>5311</v>
       </c>
       <c r="B153" t="n">
-        <v>3045.80832514813</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>10948.99866784269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -6036,10 +6036,10 @@
         <v>5330</v>
       </c>
       <c r="B172" t="n">
-        <v>5423.07054654082</v>
+        <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>19494.72384701182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -6047,10 +6047,10 @@
         <v>5331</v>
       </c>
       <c r="B173" t="n">
-        <v>5538.003146077993</v>
+        <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>19907.88079744566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -6289,10 +6289,10 @@
         <v>5353</v>
       </c>
       <c r="B195" t="n">
-        <v>1605.307122677656</v>
+        <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>5770.719517230693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -6300,10 +6300,10 @@
         <v>5354</v>
       </c>
       <c r="B196" t="n">
-        <v>1512.48805673732</v>
+        <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>5437.055766645957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -6311,10 +6311,10 @@
         <v>5355</v>
       </c>
       <c r="B197" t="n">
-        <v>1528.632894778576</v>
+        <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>5495.092842960549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -6322,10 +6322,10 @@
         <v>5356</v>
       </c>
       <c r="B198" t="n">
-        <v>1845.333289930281</v>
+        <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>6633.559822642414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -6553,10 +6553,10 @@
         <v>5377</v>
       </c>
       <c r="B219" t="n">
-        <v>1605.307122677698</v>
+        <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>5770.719517230842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -6564,10 +6564,10 @@
         <v>5378</v>
       </c>
       <c r="B220" t="n">
-        <v>1512.488056737244</v>
+        <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>5437.055766645681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -6575,10 +6575,10 @@
         <v>5379</v>
       </c>
       <c r="B221" t="n">
-        <v>1528.632894778632</v>
+        <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>5495.092842960752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -6586,10 +6586,10 @@
         <v>5380</v>
       </c>
       <c r="B222" t="n">
-        <v>1845.333289930281</v>
+        <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>6633.559822642414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -7070,10 +7070,10 @@
         <v>5424</v>
       </c>
       <c r="B266" t="n">
-        <v>2104.096865820102</v>
+        <v>0</v>
       </c>
       <c r="C266" t="n">
-        <v>7563.756914925321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -7081,10 +7081,10 @@
         <v>5425</v>
       </c>
       <c r="B267" t="n">
-        <v>1605.30712267771</v>
+        <v>0</v>
       </c>
       <c r="C267" t="n">
-        <v>5770.719517230886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -7334,10 +7334,10 @@
         <v>5448</v>
       </c>
       <c r="B290" t="n">
-        <v>2298.04108081247</v>
+        <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>8260.942924318728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -7345,10 +7345,10 @@
         <v>5449</v>
       </c>
       <c r="B291" t="n">
-        <v>1690.60284730891</v>
+        <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>6077.338541037733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -7356,10 +7356,10 @@
         <v>5450</v>
       </c>
       <c r="B292" t="n">
-        <v>1566.603360959052</v>
+        <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>5631.588163494937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -7367,10 +7367,10 @@
         <v>5451</v>
       </c>
       <c r="B293" t="n">
-        <v>1392.403727304189</v>
+        <v>0</v>
       </c>
       <c r="C293" t="n">
-        <v>5005.379501223644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -7378,10 +7378,10 @@
         <v>5452</v>
       </c>
       <c r="B294" t="n">
-        <v>1516.479755457432</v>
+        <v>0</v>
       </c>
       <c r="C294" t="n">
-        <v>5451.405029404246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -7389,10 +7389,10 @@
         <v>5453</v>
       </c>
       <c r="B295" t="n">
-        <v>1899.108708620582</v>
+        <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>6826.870407140262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -7422,10 +7422,10 @@
         <v>5456</v>
       </c>
       <c r="B298" t="n">
-        <v>5181.365160847776</v>
+        <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>18625.84712745172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -7433,10 +7433,10 @@
         <v>5457</v>
       </c>
       <c r="B299" t="n">
-        <v>5887.19176508303</v>
+        <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>21163.13566451811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -7444,10 +7444,10 @@
         <v>5458</v>
       </c>
       <c r="B300" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C300" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="301">
@@ -7455,10 +7455,10 @@
         <v>5459</v>
       </c>
       <c r="B301" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C301" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="302">
@@ -7521,10 +7521,10 @@
         <v>5465</v>
       </c>
       <c r="B307" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C307" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="308">
@@ -7532,10 +7532,10 @@
         <v>5466</v>
       </c>
       <c r="B308" t="n">
-        <v>6217.958231119064</v>
+        <v>0</v>
       </c>
       <c r="C308" t="n">
-        <v>22352.16701822926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -7675,10 +7675,10 @@
         <v>5479</v>
       </c>
       <c r="B321" t="n">
-        <v>4739.905750759392</v>
+        <v>0</v>
       </c>
       <c r="C321" t="n">
-        <v>17038.89943509184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -7686,10 +7686,10 @@
         <v>5480</v>
       </c>
       <c r="B322" t="n">
-        <v>4660.746443195231</v>
+        <v>0</v>
       </c>
       <c r="C322" t="n">
-        <v>16754.33945608358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -7697,10 +7697,10 @@
         <v>5481</v>
       </c>
       <c r="B323" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C323" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="324">
@@ -7708,10 +7708,10 @@
         <v>5482</v>
       </c>
       <c r="B324" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C324" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="325">
@@ -7719,10 +7719,10 @@
         <v>5483</v>
       </c>
       <c r="B325" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C325" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="326">
@@ -7730,10 +7730,10 @@
         <v>5484</v>
       </c>
       <c r="B326" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C326" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="327">
@@ -7741,10 +7741,10 @@
         <v>5485</v>
       </c>
       <c r="B327" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C327" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="328">
@@ -7752,10 +7752,10 @@
         <v>5486</v>
       </c>
       <c r="B328" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C328" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="329">
@@ -7763,10 +7763,10 @@
         <v>5487</v>
       </c>
       <c r="B329" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C329" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="330">
@@ -7774,10 +7774,10 @@
         <v>5488</v>
       </c>
       <c r="B330" t="n">
-        <v>8437.954933007895</v>
+        <v>8298.991031199892</v>
       </c>
       <c r="C330" t="n">
-        <v>30332.55788225838</v>
+        <v>29833.01378317262</v>
       </c>
     </row>
     <row r="331">
@@ -7785,10 +7785,10 @@
         <v>5489</v>
       </c>
       <c r="B331" t="n">
-        <v>3384.8070443907</v>
+        <v>0</v>
       </c>
       <c r="C331" t="n">
-        <v>12167.62312780662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">

--- a/first_stage_optimization/lshp_operation.xlsx
+++ b/first_stage_optimization/lshp_operation.xlsx
@@ -439,10 +439,10 @@
         <v>288</v>
       </c>
       <c r="B2" t="n">
-        <v>10816.53264289492</v>
+        <v>13118.95506015835</v>
       </c>
       <c r="C2" t="n">
-        <v>29833.01378317262</v>
+        <v>36183.3112376924</v>
       </c>
     </row>
     <row r="3">
@@ -450,10 +450,10 @@
         <v>289</v>
       </c>
       <c r="B3" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C3" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>290</v>
       </c>
       <c r="B4" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C4" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="5">
@@ -472,10 +472,10 @@
         <v>291</v>
       </c>
       <c r="B5" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C5" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="6">
@@ -483,10 +483,10 @@
         <v>292</v>
       </c>
       <c r="B6" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C6" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="7">
@@ -494,10 +494,10 @@
         <v>293</v>
       </c>
       <c r="B7" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C7" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="8">
@@ -505,10 +505,10 @@
         <v>294</v>
       </c>
       <c r="B8" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C8" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="9">
@@ -516,10 +516,10 @@
         <v>295</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2429.926916918618</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>6701.966849991739</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>297</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>8695.088195568311</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>23981.87058166778</v>
       </c>
     </row>
     <row r="12">
@@ -549,10 +549,10 @@
         <v>298</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4801.571070258774</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>13243.1843594543</v>
       </c>
     </row>
     <row r="13">
@@ -560,10 +560,10 @@
         <v>299</v>
       </c>
       <c r="B13" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -571,10 +571,10 @@
         <v>300</v>
       </c>
       <c r="B14" t="n">
-        <v>10816.53264289492</v>
+        <v>2429.926916918618</v>
       </c>
       <c r="C14" t="n">
-        <v>29833.01378317262</v>
+        <v>6701.966849991739</v>
       </c>
     </row>
     <row r="15">
@@ -582,10 +582,10 @@
         <v>301</v>
       </c>
       <c r="B15" t="n">
-        <v>10816.53264289492</v>
+        <v>2429.926916918618</v>
       </c>
       <c r="C15" t="n">
-        <v>29833.01378317262</v>
+        <v>6701.966849991739</v>
       </c>
     </row>
     <row r="16">
@@ -593,10 +593,10 @@
         <v>302</v>
       </c>
       <c r="B16" t="n">
-        <v>7715.679075472789</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21280.56816398705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -648,10 +648,10 @@
         <v>307</v>
       </c>
       <c r="B21" t="n">
-        <v>10816.53264289492</v>
+        <v>2429.926916918602</v>
       </c>
       <c r="C21" t="n">
-        <v>29833.01378317262</v>
+        <v>6701.966849991695</v>
       </c>
     </row>
     <row r="22">
@@ -659,10 +659,10 @@
         <v>308</v>
       </c>
       <c r="B22" t="n">
-        <v>10816.53264289492</v>
+        <v>5537.230684303509</v>
       </c>
       <c r="C22" t="n">
-        <v>29833.01378317262</v>
+        <v>15272.2027269934</v>
       </c>
     </row>
     <row r="23">
@@ -670,10 +670,10 @@
         <v>309</v>
       </c>
       <c r="B23" t="n">
-        <v>10816.53264289492</v>
+        <v>10202.12806732262</v>
       </c>
       <c r="C23" t="n">
-        <v>29833.01378317262</v>
+        <v>28138.42820971411</v>
       </c>
     </row>
     <row r="24">
@@ -681,10 +681,10 @@
         <v>310</v>
       </c>
       <c r="B24" t="n">
-        <v>10816.53264289492</v>
+        <v>14160.70821029218</v>
       </c>
       <c r="C24" t="n">
-        <v>29833.01378317262</v>
+        <v>39056.5643505576</v>
       </c>
     </row>
     <row r="25">
@@ -692,10 +692,10 @@
         <v>311</v>
       </c>
       <c r="B25" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C25" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="26">
@@ -703,10 +703,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="n">
-        <v>10816.53264289492</v>
+        <v>15961.39403155136</v>
       </c>
       <c r="C26" t="n">
-        <v>29833.01378317262</v>
+        <v>44023.02511005761</v>
       </c>
     </row>
     <row r="27">
@@ -714,10 +714,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C27" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="28">
@@ -725,10 +725,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C28" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="29">
@@ -736,10 +736,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C29" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="30">
@@ -747,10 +747,10 @@
         <v>316</v>
       </c>
       <c r="B30" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C30" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="31">
@@ -758,10 +758,10 @@
         <v>317</v>
       </c>
       <c r="B31" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C31" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="32">
@@ -769,10 +769,10 @@
         <v>318</v>
       </c>
       <c r="B32" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C32" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="33">
@@ -780,10 +780,10 @@
         <v>319</v>
       </c>
       <c r="B33" t="n">
-        <v>5061.248487878984</v>
+        <v>2429.926916918618</v>
       </c>
       <c r="C33" t="n">
-        <v>13959.3990869281</v>
+        <v>6701.966849991739</v>
       </c>
     </row>
     <row r="34">
@@ -813,10 +813,10 @@
         <v>322</v>
       </c>
       <c r="B36" t="n">
-        <v>10816.53264289492</v>
+        <v>7056.137241076699</v>
       </c>
       <c r="C36" t="n">
-        <v>29833.01378317262</v>
+        <v>19461.4897877902</v>
       </c>
     </row>
     <row r="37">
@@ -824,10 +824,10 @@
         <v>323</v>
       </c>
       <c r="B37" t="n">
-        <v>10816.53264289492</v>
+        <v>2898.191571504383</v>
       </c>
       <c r="C37" t="n">
-        <v>29833.01378317262</v>
+        <v>7993.484784216809</v>
       </c>
     </row>
     <row r="38">
@@ -835,10 +835,10 @@
         <v>324</v>
       </c>
       <c r="B38" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -846,10 +846,10 @@
         <v>325</v>
       </c>
       <c r="B39" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -857,10 +857,10 @@
         <v>326</v>
       </c>
       <c r="B40" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -868,10 +868,10 @@
         <v>327</v>
       </c>
       <c r="B41" t="n">
-        <v>10522.31423963353</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>29021.53177044781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -912,10 +912,10 @@
         <v>331</v>
       </c>
       <c r="B45" t="n">
-        <v>6894.865767835377</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>19016.68790507215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -923,10 +923,10 @@
         <v>332</v>
       </c>
       <c r="B46" t="n">
-        <v>7077.956918155559</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>19521.67050822334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -934,10 +934,10 @@
         <v>333</v>
       </c>
       <c r="B47" t="n">
-        <v>10816.53264289492</v>
+        <v>7705.537650202712</v>
       </c>
       <c r="C47" t="n">
-        <v>29833.01378317262</v>
+        <v>21252.5971597982</v>
       </c>
     </row>
     <row r="48">
@@ -945,10 +945,10 @@
         <v>334</v>
       </c>
       <c r="B48" t="n">
-        <v>10816.53264289492</v>
+        <v>14160.70821029218</v>
       </c>
       <c r="C48" t="n">
-        <v>29833.01378317262</v>
+        <v>39056.5643505576</v>
       </c>
     </row>
     <row r="49">
@@ -956,10 +956,10 @@
         <v>335</v>
       </c>
       <c r="B49" t="n">
-        <v>6554.809352078159</v>
+        <v>15127.20991356922</v>
       </c>
       <c r="C49" t="n">
-        <v>18078.78034511066</v>
+        <v>41722.26689935577</v>
       </c>
     </row>
     <row r="50">
@@ -967,10 +967,10 @@
         <v>336</v>
       </c>
       <c r="B50" t="n">
-        <v>10816.53264289492</v>
+        <v>13118.95506015835</v>
       </c>
       <c r="C50" t="n">
-        <v>29833.01378317262</v>
+        <v>36183.3112376924</v>
       </c>
     </row>
     <row r="51">
@@ -978,10 +978,10 @@
         <v>337</v>
       </c>
       <c r="B51" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C51" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="52">
@@ -989,10 +989,10 @@
         <v>338</v>
       </c>
       <c r="B52" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C52" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="53">
@@ -1000,10 +1000,10 @@
         <v>339</v>
       </c>
       <c r="B53" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C53" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="54">
@@ -1011,10 +1011,10 @@
         <v>340</v>
       </c>
       <c r="B54" t="n">
-        <v>9400.398830393617</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C54" t="n">
-        <v>25927.18361171565</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="55">
@@ -1022,10 +1022,10 @@
         <v>341</v>
       </c>
       <c r="B55" t="n">
-        <v>10816.53264289492</v>
+        <v>14698.92106657426</v>
       </c>
       <c r="C55" t="n">
-        <v>29833.01378317262</v>
+        <v>40541.00600019208</v>
       </c>
     </row>
     <row r="56">
@@ -1033,10 +1033,10 @@
         <v>342</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>12360.75770685234</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>34092.1316667232</v>
       </c>
     </row>
     <row r="57">
@@ -1220,10 +1220,10 @@
         <v>359</v>
       </c>
       <c r="B73" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1231,10 +1231,10 @@
         <v>360</v>
       </c>
       <c r="B74" t="n">
-        <v>10816.53264289492</v>
+        <v>2638.281499484566</v>
       </c>
       <c r="C74" t="n">
-        <v>29833.01378317262</v>
+        <v>7276.628374039385</v>
       </c>
     </row>
     <row r="75">
@@ -1242,10 +1242,10 @@
         <v>361</v>
       </c>
       <c r="B75" t="n">
-        <v>10816.53264289492</v>
+        <v>2843.180045531988</v>
       </c>
       <c r="C75" t="n">
-        <v>29833.01378317262</v>
+        <v>7841.757824501503</v>
       </c>
     </row>
     <row r="76">
@@ -1253,10 +1253,10 @@
         <v>362</v>
       </c>
       <c r="B76" t="n">
-        <v>10816.53264289492</v>
+        <v>3081.266129689524</v>
       </c>
       <c r="C76" t="n">
-        <v>29833.01378317262</v>
+        <v>8498.421624699899</v>
       </c>
     </row>
     <row r="77">
@@ -1264,10 +1264,10 @@
         <v>363</v>
       </c>
       <c r="B77" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C77" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="78">
@@ -1275,10 +1275,10 @@
         <v>364</v>
       </c>
       <c r="B78" t="n">
-        <v>10816.53264289492</v>
+        <v>6877.03455153217</v>
       </c>
       <c r="C78" t="n">
-        <v>29833.01378317262</v>
+        <v>18967.50773437357</v>
       </c>
     </row>
     <row r="79">
@@ -1286,10 +1286,10 @@
         <v>365</v>
       </c>
       <c r="B79" t="n">
-        <v>10816.53264289492</v>
+        <v>4173.492512380869</v>
       </c>
       <c r="C79" t="n">
-        <v>29833.01378317262</v>
+        <v>11510.8846574426</v>
       </c>
     </row>
     <row r="80">
@@ -1297,10 +1297,10 @@
         <v>366</v>
       </c>
       <c r="B80" t="n">
-        <v>10816.53264289492</v>
+        <v>4917.184139769854</v>
       </c>
       <c r="C80" t="n">
-        <v>29833.01378317262</v>
+        <v>13562.0560727944</v>
       </c>
     </row>
     <row r="81">
@@ -1374,10 +1374,10 @@
         <v>373</v>
       </c>
       <c r="B87" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -1462,10 +1462,10 @@
         <v>381</v>
       </c>
       <c r="B95" t="n">
-        <v>1622.479896434131</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>4474.952067475599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1473,10 +1473,10 @@
         <v>382</v>
       </c>
       <c r="B96" t="n">
-        <v>3756.082560895171</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>10359.62877470961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1484,10 +1484,10 @@
         <v>383</v>
       </c>
       <c r="B97" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1495,10 +1495,10 @@
         <v>384</v>
       </c>
       <c r="B98" t="n">
-        <v>10816.53264289492</v>
+        <v>5064.45420342849</v>
       </c>
       <c r="C98" t="n">
-        <v>29833.01378317262</v>
+        <v>13968.2407517509</v>
       </c>
     </row>
     <row r="99">
@@ -1506,10 +1506,10 @@
         <v>385</v>
       </c>
       <c r="B99" t="n">
-        <v>10816.53264289492</v>
+        <v>5315.822562258178</v>
       </c>
       <c r="C99" t="n">
-        <v>29833.01378317262</v>
+        <v>14661.53831402891</v>
       </c>
     </row>
     <row r="100">
@@ -1517,10 +1517,10 @@
         <v>386</v>
       </c>
       <c r="B100" t="n">
-        <v>10816.53264289492</v>
+        <v>5568.829288862742</v>
       </c>
       <c r="C100" t="n">
-        <v>29833.01378317262</v>
+        <v>15359.3546486366</v>
       </c>
     </row>
     <row r="101">
@@ -1528,10 +1528,10 @@
         <v>387</v>
       </c>
       <c r="B101" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C101" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="102">
@@ -1539,10 +1539,10 @@
         <v>388</v>
       </c>
       <c r="B102" t="n">
-        <v>10816.53264289492</v>
+        <v>10731.33559033422</v>
       </c>
       <c r="C102" t="n">
-        <v>29833.01378317262</v>
+        <v>29598.03230368727</v>
       </c>
     </row>
     <row r="103">
@@ -1550,10 +1550,10 @@
         <v>389</v>
       </c>
       <c r="B103" t="n">
-        <v>10816.53264289492</v>
+        <v>4173.492512380869</v>
       </c>
       <c r="C103" t="n">
-        <v>29833.01378317262</v>
+        <v>11510.8846574426</v>
       </c>
     </row>
     <row r="104">
@@ -1561,10 +1561,10 @@
         <v>390</v>
       </c>
       <c r="B104" t="n">
-        <v>7837.206172529511</v>
+        <v>7258.852022223756</v>
       </c>
       <c r="C104" t="n">
-        <v>21615.75132121661</v>
+        <v>20020.59620938321</v>
       </c>
     </row>
     <row r="105">
@@ -1605,10 +1605,10 @@
         <v>394</v>
       </c>
       <c r="B108" t="n">
-        <v>2345.250100787285</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>6468.420231480806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1627,10 +1627,10 @@
         <v>396</v>
       </c>
       <c r="B110" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -1638,10 +1638,10 @@
         <v>397</v>
       </c>
       <c r="B111" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1715,10 +1715,10 @@
         <v>404</v>
       </c>
       <c r="B118" t="n">
-        <v>2696.459230950215</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>7437.088026128404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -1726,10 +1726,10 @@
         <v>405</v>
       </c>
       <c r="B119" t="n">
-        <v>4950.369843695064</v>
+        <v>3052.562834927492</v>
       </c>
       <c r="C119" t="n">
-        <v>13653.58536367629</v>
+        <v>8419.255239636506</v>
       </c>
     </row>
     <row r="120">
@@ -1737,10 +1737,10 @@
         <v>406</v>
       </c>
       <c r="B120" t="n">
-        <v>6176.01611427562</v>
+        <v>6394.335385638709</v>
       </c>
       <c r="C120" t="n">
-        <v>17034.0329886869</v>
+        <v>17636.17806111781</v>
       </c>
     </row>
     <row r="121">
@@ -1748,10 +1748,10 @@
         <v>407</v>
       </c>
       <c r="B121" t="n">
-        <v>10816.53264289492</v>
+        <v>7081.874035517784</v>
       </c>
       <c r="C121" t="n">
-        <v>29833.01378317262</v>
+        <v>19532.47428611739</v>
       </c>
     </row>
     <row r="122">
@@ -1759,10 +1759,10 @@
         <v>408</v>
       </c>
       <c r="B122" t="n">
-        <v>10816.53264289492</v>
+        <v>9022.237545176489</v>
       </c>
       <c r="C122" t="n">
-        <v>29833.01378317262</v>
+        <v>24884.179239926</v>
       </c>
     </row>
     <row r="123">
@@ -1770,10 +1770,10 @@
         <v>409</v>
       </c>
       <c r="B123" t="n">
-        <v>10816.53264289492</v>
+        <v>9162.386086882425</v>
       </c>
       <c r="C123" t="n">
-        <v>29833.01378317262</v>
+        <v>25270.72209191389</v>
       </c>
     </row>
     <row r="124">
@@ -1781,10 +1781,10 @@
         <v>410</v>
       </c>
       <c r="B124" t="n">
-        <v>10816.53264289492</v>
+        <v>9416.796369629241</v>
       </c>
       <c r="C124" t="n">
-        <v>29833.01378317262</v>
+        <v>25972.40956629619</v>
       </c>
     </row>
     <row r="125">
@@ -1792,10 +1792,10 @@
         <v>411</v>
       </c>
       <c r="B125" t="n">
-        <v>10816.53264289492</v>
+        <v>11667.69471951104</v>
       </c>
       <c r="C125" t="n">
-        <v>29833.01378317262</v>
+        <v>32180.5987997151</v>
       </c>
     </row>
     <row r="126">
@@ -1803,10 +1803,10 @@
         <v>412</v>
       </c>
       <c r="B126" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C126" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="127">
@@ -1814,10 +1814,10 @@
         <v>413</v>
       </c>
       <c r="B127" t="n">
-        <v>10816.53264289492</v>
+        <v>6370.840815083351</v>
       </c>
       <c r="C127" t="n">
-        <v>29833.01378317262</v>
+        <v>17571.3778270365</v>
       </c>
     </row>
     <row r="128">
@@ -1825,10 +1825,10 @@
         <v>414</v>
       </c>
       <c r="B128" t="n">
-        <v>10816.53264289492</v>
+        <v>5351.549131298641</v>
       </c>
       <c r="C128" t="n">
-        <v>29833.01378317262</v>
+        <v>14760.07554974</v>
       </c>
     </row>
     <row r="129">
@@ -1836,10 +1836,10 @@
         <v>415</v>
       </c>
       <c r="B129" t="n">
-        <v>10816.53264289492</v>
+        <v>5056.985611796154</v>
       </c>
       <c r="C129" t="n">
-        <v>29833.01378317262</v>
+        <v>13947.6416739813</v>
       </c>
     </row>
     <row r="130">
@@ -1847,10 +1847,10 @@
         <v>416</v>
       </c>
       <c r="B130" t="n">
-        <v>10816.53264289492</v>
+        <v>5287.524291730701</v>
       </c>
       <c r="C130" t="n">
-        <v>29833.01378317262</v>
+        <v>14583.4890238767</v>
       </c>
     </row>
     <row r="131">
@@ -1858,10 +1858,10 @@
         <v>417</v>
       </c>
       <c r="B131" t="n">
-        <v>10816.53264289492</v>
+        <v>5383.29470299504</v>
       </c>
       <c r="C131" t="n">
-        <v>29833.01378317262</v>
+        <v>14847.6328205624</v>
       </c>
     </row>
     <row r="132">
@@ -1869,10 +1869,10 @@
         <v>418</v>
       </c>
       <c r="B132" t="n">
-        <v>10710.07751888583</v>
+        <v>3762.636051725938</v>
       </c>
       <c r="C132" t="n">
-        <v>29539.40054437389</v>
+        <v>10377.703918449</v>
       </c>
     </row>
     <row r="133">
@@ -1880,10 +1880,10 @@
         <v>419</v>
       </c>
       <c r="B133" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -1891,10 +1891,10 @@
         <v>420</v>
       </c>
       <c r="B134" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -1902,10 +1902,10 @@
         <v>421</v>
       </c>
       <c r="B135" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -1913,10 +1913,10 @@
         <v>422</v>
       </c>
       <c r="B136" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -1924,10 +1924,10 @@
         <v>423</v>
       </c>
       <c r="B137" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -1935,10 +1935,10 @@
         <v>424</v>
       </c>
       <c r="B138" t="n">
-        <v>4081.108700781916</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>11256.0814209744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -1946,10 +1946,10 @@
         <v>425</v>
       </c>
       <c r="B139" t="n">
-        <v>5535.111192715002</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>15266.35696996009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -1957,10 +1957,10 @@
         <v>426</v>
       </c>
       <c r="B140" t="n">
-        <v>6538.550852195971</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>18033.93787413659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -1968,10 +1968,10 @@
         <v>427</v>
       </c>
       <c r="B141" t="n">
-        <v>6437.462881180372</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>17755.1277478063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -1979,10 +1979,10 @@
         <v>428</v>
       </c>
       <c r="B142" t="n">
-        <v>6064.902318314894</v>
+        <v>4315.482029573499</v>
       </c>
       <c r="C142" t="n">
-        <v>16727.5706947304</v>
+        <v>11902.50509287449</v>
       </c>
     </row>
     <row r="143">
@@ -1990,10 +1990,10 @@
         <v>429</v>
       </c>
       <c r="B143" t="n">
-        <v>6549.592697514261</v>
+        <v>4810.551126905028</v>
       </c>
       <c r="C143" t="n">
-        <v>18064.3923214579</v>
+        <v>13267.95219981</v>
       </c>
     </row>
     <row r="144">
@@ -2001,10 +2001,10 @@
         <v>430</v>
       </c>
       <c r="B144" t="n">
-        <v>5754.676555356961</v>
+        <v>6123.780274270564</v>
       </c>
       <c r="C144" t="n">
-        <v>15871.9388792707</v>
+        <v>16889.961631784</v>
       </c>
     </row>
     <row r="145">
@@ -2012,10 +2012,10 @@
         <v>431</v>
       </c>
       <c r="B145" t="n">
-        <v>10816.53264289492</v>
+        <v>7456.161935427655</v>
       </c>
       <c r="C145" t="n">
-        <v>29833.01378317262</v>
+        <v>20564.7954971314</v>
       </c>
     </row>
     <row r="146">
@@ -2023,10 +2023,10 @@
         <v>432</v>
       </c>
       <c r="B146" t="n">
-        <v>10816.53264289492</v>
+        <v>9238.733826220248</v>
       </c>
       <c r="C146" t="n">
-        <v>29833.01378317262</v>
+        <v>25481.29633369511</v>
       </c>
     </row>
     <row r="147">
@@ -2034,10 +2034,10 @@
         <v>433</v>
       </c>
       <c r="B147" t="n">
-        <v>10816.53264289492</v>
+        <v>10011.22412247041</v>
       </c>
       <c r="C147" t="n">
-        <v>29833.01378317262</v>
+        <v>27611.8971848409</v>
       </c>
     </row>
     <row r="148">
@@ -2045,10 +2045,10 @@
         <v>434</v>
       </c>
       <c r="B148" t="n">
-        <v>10816.53264289492</v>
+        <v>10253.18297777342</v>
       </c>
       <c r="C148" t="n">
-        <v>29833.01378317262</v>
+        <v>28279.242451899</v>
       </c>
     </row>
     <row r="149">
@@ -2056,10 +2056,10 @@
         <v>435</v>
       </c>
       <c r="B149" t="n">
-        <v>10816.53264289492</v>
+        <v>10313.70327275604</v>
       </c>
       <c r="C149" t="n">
-        <v>29833.01378317262</v>
+        <v>28446.1631143688</v>
       </c>
     </row>
     <row r="150">
@@ -2067,10 +2067,10 @@
         <v>436</v>
       </c>
       <c r="B150" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C150" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="151">
@@ -2078,10 +2078,10 @@
         <v>437</v>
       </c>
       <c r="B151" t="n">
-        <v>10816.53264289492</v>
+        <v>11841.81921428548</v>
       </c>
       <c r="C151" t="n">
-        <v>29833.01378317262</v>
+        <v>32660.85052400551</v>
       </c>
     </row>
     <row r="152">
@@ -2089,10 +2089,10 @@
         <v>438</v>
       </c>
       <c r="B152" t="n">
-        <v>10816.53264289492</v>
+        <v>7927.511444964237</v>
       </c>
       <c r="C152" t="n">
-        <v>29833.01378317262</v>
+        <v>21864.82175128719</v>
       </c>
     </row>
     <row r="153">
@@ -2100,10 +2100,10 @@
         <v>439</v>
       </c>
       <c r="B153" t="n">
-        <v>10816.53264289492</v>
+        <v>7662.983402361594</v>
       </c>
       <c r="C153" t="n">
-        <v>29833.01378317262</v>
+        <v>21135.2285441531</v>
       </c>
     </row>
     <row r="154">
@@ -2111,10 +2111,10 @@
         <v>440</v>
       </c>
       <c r="B154" t="n">
-        <v>10816.53264289492</v>
+        <v>7873.063988659377</v>
       </c>
       <c r="C154" t="n">
-        <v>29833.01378317262</v>
+        <v>21714.6505487375</v>
       </c>
     </row>
     <row r="155">
@@ -2122,10 +2122,10 @@
         <v>441</v>
       </c>
       <c r="B155" t="n">
-        <v>10816.53264289492</v>
+        <v>6572.88908759745</v>
       </c>
       <c r="C155" t="n">
-        <v>29833.01378317262</v>
+        <v>18128.645955168</v>
       </c>
     </row>
     <row r="156">
@@ -2133,10 +2133,10 @@
         <v>442</v>
       </c>
       <c r="B156" t="n">
-        <v>10816.53264289492</v>
+        <v>5550.704995034321</v>
       </c>
       <c r="C156" t="n">
-        <v>29833.01378317262</v>
+        <v>15309.36614257419</v>
       </c>
     </row>
     <row r="157">
@@ -2144,10 +2144,10 @@
         <v>443</v>
       </c>
       <c r="B157" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -2155,10 +2155,10 @@
         <v>444</v>
       </c>
       <c r="B158" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -2166,10 +2166,10 @@
         <v>445</v>
       </c>
       <c r="B159" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C159" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="160">
@@ -2177,10 +2177,10 @@
         <v>446</v>
       </c>
       <c r="B160" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C160" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="161">
@@ -2188,10 +2188,10 @@
         <v>447</v>
       </c>
       <c r="B161" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -2221,10 +2221,10 @@
         <v>450</v>
       </c>
       <c r="B164" t="n">
-        <v>1644.834349911096</v>
+        <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>4536.607751483694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -2232,10 +2232,10 @@
         <v>451</v>
       </c>
       <c r="B165" t="n">
-        <v>3205.01860376423</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>8839.742580930499</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -2243,10 +2243,10 @@
         <v>452</v>
       </c>
       <c r="B166" t="n">
-        <v>4927.983410894259</v>
+        <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>13591.84147768699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -2254,10 +2254,10 @@
         <v>453</v>
       </c>
       <c r="B167" t="n">
-        <v>7226.547996684305</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>19931.498670367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -2265,10 +2265,10 @@
         <v>454</v>
       </c>
       <c r="B168" t="n">
-        <v>9160.584484825504</v>
+        <v>4590.808653745414</v>
       </c>
       <c r="C168" t="n">
-        <v>25265.75310409031</v>
+        <v>12661.8818030433</v>
       </c>
     </row>
     <row r="169">
@@ -2276,10 +2276,10 @@
         <v>455</v>
       </c>
       <c r="B169" t="n">
-        <v>10816.53264289492</v>
+        <v>5388.367454674169</v>
       </c>
       <c r="C169" t="n">
-        <v>29833.01378317262</v>
+        <v>14861.6239465321</v>
       </c>
     </row>
     <row r="170">
@@ -2287,10 +2287,10 @@
         <v>456</v>
       </c>
       <c r="B170" t="n">
-        <v>10816.53264289492</v>
+        <v>5064.45420342849</v>
       </c>
       <c r="C170" t="n">
-        <v>29833.01378317262</v>
+        <v>13968.2407517509</v>
       </c>
     </row>
     <row r="171">
@@ -2298,10 +2298,10 @@
         <v>457</v>
       </c>
       <c r="B171" t="n">
-        <v>10816.53264289492</v>
+        <v>5315.822562258178</v>
       </c>
       <c r="C171" t="n">
-        <v>29833.01378317262</v>
+        <v>14661.53831402891</v>
       </c>
     </row>
     <row r="172">
@@ -2309,10 +2309,10 @@
         <v>458</v>
       </c>
       <c r="B172" t="n">
-        <v>10816.53264289492</v>
+        <v>5568.829288862742</v>
       </c>
       <c r="C172" t="n">
-        <v>29833.01378317262</v>
+        <v>15359.3546486366</v>
       </c>
     </row>
     <row r="173">
@@ -2320,10 +2320,10 @@
         <v>459</v>
       </c>
       <c r="B173" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C173" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="174">
@@ -2331,10 +2331,10 @@
         <v>460</v>
       </c>
       <c r="B174" t="n">
-        <v>10816.53264289492</v>
+        <v>14337.74605321794</v>
       </c>
       <c r="C174" t="n">
-        <v>29833.01378317262</v>
+        <v>39544.85136290408</v>
       </c>
     </row>
     <row r="175">
@@ -2342,10 +2342,10 @@
         <v>461</v>
       </c>
       <c r="B175" t="n">
-        <v>10816.53264289492</v>
+        <v>11845.17922815347</v>
       </c>
       <c r="C175" t="n">
-        <v>29833.01378317262</v>
+        <v>32670.11775809471</v>
       </c>
     </row>
     <row r="176">
@@ -2353,10 +2353,10 @@
         <v>462</v>
       </c>
       <c r="B176" t="n">
-        <v>10328.54377806308</v>
+        <v>12360.75770685234</v>
       </c>
       <c r="C176" t="n">
-        <v>28487.09462301311</v>
+        <v>34092.1316667232</v>
       </c>
     </row>
     <row r="177">
@@ -2518,10 +2518,10 @@
         <v>477</v>
       </c>
       <c r="B191" t="n">
-        <v>2695.174524152985</v>
+        <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>7433.544684019202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -2529,10 +2529,10 @@
         <v>478</v>
       </c>
       <c r="B192" t="n">
-        <v>3756.082560895171</v>
+        <v>4079.838630950432</v>
       </c>
       <c r="C192" t="n">
-        <v>10359.62877470961</v>
+        <v>11252.5784489926</v>
       </c>
     </row>
     <row r="193">
@@ -2540,10 +2540,10 @@
         <v>479</v>
       </c>
       <c r="B193" t="n">
-        <v>4403.242377510923</v>
+        <v>4635.133747201618</v>
       </c>
       <c r="C193" t="n">
-        <v>12144.55638195861</v>
+        <v>12784.1345773543</v>
       </c>
     </row>
     <row r="194">
@@ -2551,10 +2551,10 @@
         <v>480</v>
       </c>
       <c r="B194" t="n">
-        <v>10816.53264289492</v>
+        <v>5064.45420342849</v>
       </c>
       <c r="C194" t="n">
-        <v>29833.01378317262</v>
+        <v>13968.2407517509</v>
       </c>
     </row>
     <row r="195">
@@ -2562,10 +2562,10 @@
         <v>481</v>
       </c>
       <c r="B195" t="n">
-        <v>10816.53264289492</v>
+        <v>5315.822562258178</v>
       </c>
       <c r="C195" t="n">
-        <v>29833.01378317262</v>
+        <v>14661.53831402891</v>
       </c>
     </row>
     <row r="196">
@@ -2573,10 +2573,10 @@
         <v>482</v>
       </c>
       <c r="B196" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C196" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="197">
@@ -2584,10 +2584,10 @@
         <v>483</v>
       </c>
       <c r="B197" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C197" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="198">
@@ -2595,10 +2595,10 @@
         <v>484</v>
       </c>
       <c r="B198" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C198" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="199">
@@ -2606,10 +2606,10 @@
         <v>485</v>
       </c>
       <c r="B199" t="n">
-        <v>10816.53264289492</v>
+        <v>9084.662055747518</v>
       </c>
       <c r="C199" t="n">
-        <v>29833.01378317262</v>
+        <v>25056.35190798489</v>
       </c>
     </row>
     <row r="200">
@@ -2617,10 +2617,10 @@
         <v>486</v>
       </c>
       <c r="B200" t="n">
-        <v>10328.54377806308</v>
+        <v>9670.207921098548</v>
       </c>
       <c r="C200" t="n">
-        <v>28487.09462301311</v>
+        <v>26671.34244593438</v>
       </c>
     </row>
     <row r="201">
@@ -2628,10 +2628,10 @@
         <v>487</v>
       </c>
       <c r="B201" t="n">
-        <v>10026.99388425181</v>
+        <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>27655.3916701916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -2771,10 +2771,10 @@
         <v>500</v>
       </c>
       <c r="B214" t="n">
-        <v>2696.459230950215</v>
+        <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>7437.088026128404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -2782,10 +2782,10 @@
         <v>501</v>
       </c>
       <c r="B215" t="n">
-        <v>4950.369843695064</v>
+        <v>3052.562834927492</v>
       </c>
       <c r="C215" t="n">
-        <v>13653.58536367629</v>
+        <v>8419.255239636506</v>
       </c>
     </row>
     <row r="216">
@@ -2793,10 +2793,10 @@
         <v>502</v>
       </c>
       <c r="B216" t="n">
-        <v>6176.01611427562</v>
+        <v>4079.838630950432</v>
       </c>
       <c r="C216" t="n">
-        <v>17034.0329886869</v>
+        <v>11252.5784489926</v>
       </c>
     </row>
     <row r="217">
@@ -2804,10 +2804,10 @@
         <v>503</v>
       </c>
       <c r="B217" t="n">
-        <v>10816.53264289492</v>
+        <v>4635.133747201618</v>
       </c>
       <c r="C217" t="n">
-        <v>29833.01378317262</v>
+        <v>12784.1345773543</v>
       </c>
     </row>
     <row r="218">
@@ -2815,10 +2815,10 @@
         <v>504</v>
       </c>
       <c r="B218" t="n">
-        <v>10816.53264289492</v>
+        <v>5064.45420342849</v>
       </c>
       <c r="C218" t="n">
-        <v>29833.01378317262</v>
+        <v>13968.2407517509</v>
       </c>
     </row>
     <row r="219">
@@ -2826,10 +2826,10 @@
         <v>505</v>
       </c>
       <c r="B219" t="n">
-        <v>10816.53264289492</v>
+        <v>5315.822562258178</v>
       </c>
       <c r="C219" t="n">
-        <v>29833.01378317262</v>
+        <v>14661.53831402891</v>
       </c>
     </row>
     <row r="220">
@@ -2837,10 +2837,10 @@
         <v>506</v>
       </c>
       <c r="B220" t="n">
-        <v>10816.53264289492</v>
+        <v>8143.049025518385</v>
       </c>
       <c r="C220" t="n">
-        <v>29833.01378317262</v>
+        <v>22459.2946589881</v>
       </c>
     </row>
     <row r="221">
@@ -2848,10 +2848,10 @@
         <v>507</v>
       </c>
       <c r="B221" t="n">
-        <v>10816.53264289492</v>
+        <v>8648.041618868174</v>
       </c>
       <c r="C221" t="n">
-        <v>29833.01378317262</v>
+        <v>23852.1117007506</v>
       </c>
     </row>
     <row r="222">
@@ -2859,10 +2859,10 @@
         <v>508</v>
       </c>
       <c r="B222" t="n">
-        <v>10816.53264289492</v>
+        <v>8725.29299097402</v>
       </c>
       <c r="C222" t="n">
-        <v>29833.01378317262</v>
+        <v>24065.1782466475</v>
       </c>
     </row>
     <row r="223">
@@ -2870,10 +2870,10 @@
         <v>509</v>
       </c>
       <c r="B223" t="n">
-        <v>10816.53264289492</v>
+        <v>9084.662055747518</v>
       </c>
       <c r="C223" t="n">
-        <v>29833.01378317262</v>
+        <v>25056.35190798489</v>
       </c>
     </row>
     <row r="224">
@@ -2881,10 +2881,10 @@
         <v>510</v>
       </c>
       <c r="B224" t="n">
-        <v>10328.54377806308</v>
+        <v>7258.852022223756</v>
       </c>
       <c r="C224" t="n">
-        <v>28487.09462301311</v>
+        <v>20020.59620938321</v>
       </c>
     </row>
     <row r="225">
@@ -3046,10 +3046,10 @@
         <v>525</v>
       </c>
       <c r="B239" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -3057,10 +3057,10 @@
         <v>526</v>
       </c>
       <c r="B240" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -3068,10 +3068,10 @@
         <v>527</v>
       </c>
       <c r="B241" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -3079,10 +3079,10 @@
         <v>528</v>
       </c>
       <c r="B242" t="n">
-        <v>10728.92339674058</v>
+        <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>29591.37924700981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -3090,10 +3090,10 @@
         <v>529</v>
       </c>
       <c r="B243" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -3101,10 +3101,10 @@
         <v>530</v>
       </c>
       <c r="B244" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -3112,10 +3112,10 @@
         <v>531</v>
       </c>
       <c r="B245" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -3123,10 +3123,10 @@
         <v>532</v>
       </c>
       <c r="B246" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -3134,10 +3134,10 @@
         <v>533</v>
       </c>
       <c r="B247" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C247" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -3145,10 +3145,10 @@
         <v>534</v>
       </c>
       <c r="B248" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -3189,10 +3189,10 @@
         <v>538</v>
       </c>
       <c r="B252" t="n">
-        <v>7137.715796175021</v>
+        <v>0</v>
       </c>
       <c r="C252" t="n">
-        <v>19686.49111113555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -3200,10 +3200,10 @@
         <v>539</v>
       </c>
       <c r="B253" t="n">
-        <v>3680.085914273101</v>
+        <v>0</v>
       </c>
       <c r="C253" t="n">
-        <v>10150.02287964115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -3211,10 +3211,10 @@
         <v>540</v>
       </c>
       <c r="B254" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -3222,10 +3222,10 @@
         <v>541</v>
       </c>
       <c r="B255" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -3233,10 +3233,10 @@
         <v>542</v>
       </c>
       <c r="B256" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -3244,10 +3244,10 @@
         <v>543</v>
       </c>
       <c r="B257" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -3255,10 +3255,10 @@
         <v>544</v>
       </c>
       <c r="B258" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -3266,10 +3266,10 @@
         <v>545</v>
       </c>
       <c r="B259" t="n">
-        <v>6958.382315133329</v>
+        <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>19191.87251307534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -3277,10 +3277,10 @@
         <v>546</v>
       </c>
       <c r="B260" t="n">
-        <v>8372.27543650824</v>
+        <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>23091.52264778076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -3288,10 +3288,10 @@
         <v>547</v>
       </c>
       <c r="B261" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -3299,10 +3299,10 @@
         <v>548</v>
       </c>
       <c r="B262" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -3310,10 +3310,10 @@
         <v>549</v>
       </c>
       <c r="B263" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -3321,10 +3321,10 @@
         <v>550</v>
       </c>
       <c r="B264" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -3332,10 +3332,10 @@
         <v>551</v>
       </c>
       <c r="B265" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C265" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -3343,10 +3343,10 @@
         <v>552</v>
       </c>
       <c r="B266" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C266" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -3354,10 +3354,10 @@
         <v>553</v>
       </c>
       <c r="B267" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C267" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -3365,10 +3365,10 @@
         <v>554</v>
       </c>
       <c r="B268" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C268" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -3376,10 +3376,10 @@
         <v>555</v>
       </c>
       <c r="B269" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C269" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -3387,10 +3387,10 @@
         <v>556</v>
       </c>
       <c r="B270" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -3398,10 +3398,10 @@
         <v>557</v>
       </c>
       <c r="B271" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -3409,10 +3409,10 @@
         <v>558</v>
       </c>
       <c r="B272" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C272" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -3420,10 +3420,10 @@
         <v>559</v>
       </c>
       <c r="B273" t="n">
-        <v>9779.305357044783</v>
+        <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>26972.24342943307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -3431,10 +3431,10 @@
         <v>560</v>
       </c>
       <c r="B274" t="n">
-        <v>9996.65096565463</v>
+        <v>0</v>
       </c>
       <c r="C274" t="n">
-        <v>27571.70304846624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -3442,10 +3442,10 @@
         <v>561</v>
       </c>
       <c r="B275" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C275" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -3453,10 +3453,10 @@
         <v>562</v>
       </c>
       <c r="B276" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C276" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -3464,10 +3464,10 @@
         <v>563</v>
       </c>
       <c r="B277" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C277" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -3475,10 +3475,10 @@
         <v>564</v>
       </c>
       <c r="B278" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -3486,10 +3486,10 @@
         <v>565</v>
       </c>
       <c r="B279" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -3497,10 +3497,10 @@
         <v>566</v>
       </c>
       <c r="B280" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C280" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -3508,10 +3508,10 @@
         <v>567</v>
       </c>
       <c r="B281" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -3519,10 +3519,10 @@
         <v>568</v>
       </c>
       <c r="B282" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -3530,10 +3530,10 @@
         <v>569</v>
       </c>
       <c r="B283" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C283" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -3541,10 +3541,10 @@
         <v>570</v>
       </c>
       <c r="B284" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C284" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -3552,10 +3552,10 @@
         <v>571</v>
       </c>
       <c r="B285" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -3563,10 +3563,10 @@
         <v>572</v>
       </c>
       <c r="B286" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C286" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -3574,10 +3574,10 @@
         <v>573</v>
       </c>
       <c r="B287" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C287" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -3585,10 +3585,10 @@
         <v>574</v>
       </c>
       <c r="B288" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -3596,10 +3596,10 @@
         <v>575</v>
       </c>
       <c r="B289" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -3607,10 +3607,10 @@
         <v>576</v>
       </c>
       <c r="B290" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -3618,10 +3618,10 @@
         <v>577</v>
       </c>
       <c r="B291" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -3629,10 +3629,10 @@
         <v>578</v>
       </c>
       <c r="B292" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -3640,10 +3640,10 @@
         <v>579</v>
       </c>
       <c r="B293" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C293" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -3651,10 +3651,10 @@
         <v>580</v>
       </c>
       <c r="B294" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C294" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -3662,10 +3662,10 @@
         <v>581</v>
       </c>
       <c r="B295" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -3673,10 +3673,10 @@
         <v>582</v>
       </c>
       <c r="B296" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -3684,10 +3684,10 @@
         <v>583</v>
       </c>
       <c r="B297" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C297" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -3695,10 +3695,10 @@
         <v>584</v>
       </c>
       <c r="B298" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -3706,10 +3706,10 @@
         <v>585</v>
       </c>
       <c r="B299" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -3717,10 +3717,10 @@
         <v>586</v>
       </c>
       <c r="B300" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -3728,10 +3728,10 @@
         <v>587</v>
       </c>
       <c r="B301" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -3739,10 +3739,10 @@
         <v>588</v>
       </c>
       <c r="B302" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C302" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -3750,10 +3750,10 @@
         <v>589</v>
       </c>
       <c r="B303" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C303" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -3761,10 +3761,10 @@
         <v>590</v>
       </c>
       <c r="B304" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C304" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -3772,10 +3772,10 @@
         <v>591</v>
       </c>
       <c r="B305" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C305" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -3783,10 +3783,10 @@
         <v>592</v>
       </c>
       <c r="B306" t="n">
-        <v>10351.43846863319</v>
+        <v>0</v>
       </c>
       <c r="C306" t="n">
-        <v>28550.2403317064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -3838,10 +3838,10 @@
         <v>597</v>
       </c>
       <c r="B311" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C311" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -3849,10 +3849,10 @@
         <v>598</v>
       </c>
       <c r="B312" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C312" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -3860,10 +3860,10 @@
         <v>599</v>
       </c>
       <c r="B313" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C313" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -3871,10 +3871,10 @@
         <v>600</v>
       </c>
       <c r="B314" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C314" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -3882,10 +3882,10 @@
         <v>601</v>
       </c>
       <c r="B315" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C315" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -3893,10 +3893,10 @@
         <v>602</v>
       </c>
       <c r="B316" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C316" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -3904,10 +3904,10 @@
         <v>603</v>
       </c>
       <c r="B317" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C317" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -3915,10 +3915,10 @@
         <v>604</v>
       </c>
       <c r="B318" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C318" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -3926,10 +3926,10 @@
         <v>605</v>
       </c>
       <c r="B319" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C319" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -3937,10 +3937,10 @@
         <v>606</v>
       </c>
       <c r="B320" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C320" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -3948,10 +3948,10 @@
         <v>607</v>
       </c>
       <c r="B321" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C321" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -3959,10 +3959,10 @@
         <v>608</v>
       </c>
       <c r="B322" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C322" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -3970,10 +3970,10 @@
         <v>609</v>
       </c>
       <c r="B323" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C323" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -3981,10 +3981,10 @@
         <v>610</v>
       </c>
       <c r="B324" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C324" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -3992,10 +3992,10 @@
         <v>611</v>
       </c>
       <c r="B325" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C325" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -4003,10 +4003,10 @@
         <v>612</v>
       </c>
       <c r="B326" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C326" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -4014,10 +4014,10 @@
         <v>613</v>
       </c>
       <c r="B327" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C327" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="328">
@@ -4025,10 +4025,10 @@
         <v>614</v>
       </c>
       <c r="B328" t="n">
-        <v>10816.53264289492</v>
+        <v>16199.51277945756</v>
       </c>
       <c r="C328" t="n">
-        <v>29833.01378317262</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="329">
@@ -4036,10 +4036,10 @@
         <v>615</v>
       </c>
       <c r="B329" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C329" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -4047,10 +4047,10 @@
         <v>616</v>
       </c>
       <c r="B330" t="n">
-        <v>9167.688534285411</v>
+        <v>0</v>
       </c>
       <c r="C330" t="n">
-        <v>25285.34674028138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -4058,10 +4058,10 @@
         <v>617</v>
       </c>
       <c r="B331" t="n">
-        <v>9975.68237012327</v>
+        <v>0</v>
       </c>
       <c r="C331" t="n">
-        <v>27513.86969094277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -4069,10 +4069,10 @@
         <v>618</v>
       </c>
       <c r="B332" t="n">
-        <v>9966.717478079683</v>
+        <v>0</v>
       </c>
       <c r="C332" t="n">
-        <v>27489.14367598671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -4080,10 +4080,10 @@
         <v>619</v>
       </c>
       <c r="B333" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C333" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -4091,10 +4091,10 @@
         <v>620</v>
       </c>
       <c r="B334" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C334" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -4102,10 +4102,10 @@
         <v>621</v>
       </c>
       <c r="B335" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C335" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -4113,10 +4113,10 @@
         <v>622</v>
       </c>
       <c r="B336" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C336" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -4124,10 +4124,10 @@
         <v>623</v>
       </c>
       <c r="B337" t="n">
-        <v>10816.53264289492</v>
+        <v>0</v>
       </c>
       <c r="C337" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4254,7 +4254,7 @@
         <v>5168</v>
       </c>
       <c r="B10" t="n">
-        <v>690.3397879591588</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         <v>5169</v>
       </c>
       <c r="B11" t="n">
-        <v>716.9192426275441</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>5170</v>
       </c>
       <c r="B12" t="n">
-        <v>1088.230744064651</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>5171</v>
       </c>
       <c r="B13" t="n">
-        <v>1844.754962767621</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>5172</v>
       </c>
       <c r="B14" t="n">
-        <v>1490.176574563599</v>
+        <v>8305.802952330294</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>29857.50111376608</v>
       </c>
     </row>
     <row r="15">
@@ -4309,7 +4309,7 @@
         <v>5173</v>
       </c>
       <c r="B15" t="n">
-        <v>1497.163797044169</v>
+        <v>1327.989828441336</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>5174</v>
       </c>
       <c r="B16" t="n">
-        <v>1879.512102603256</v>
+        <v>2000.852027642381</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
         <v>5175</v>
       </c>
       <c r="B17" t="n">
-        <v>1494.335245363373</v>
+        <v>1988.594826220712</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>5176</v>
       </c>
       <c r="B18" t="n">
-        <v>1468.315675708288</v>
+        <v>3261.799678452492</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -4353,7 +4353,7 @@
         <v>5177</v>
       </c>
       <c r="B19" t="n">
-        <v>957.805625470408</v>
+        <v>2324.552178485387</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>5178</v>
       </c>
       <c r="B20" t="n">
-        <v>572.270525798585</v>
+        <v>1517.479418776307</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -4375,7 +4375,7 @@
         <v>5179</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>847.3816435518777</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -4408,10 +4408,10 @@
         <v>5182</v>
       </c>
       <c r="B24" t="n">
-        <v>3757.906203318435</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>13508.83102994023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4419,10 +4419,10 @@
         <v>5183</v>
       </c>
       <c r="B25" t="n">
-        <v>8298.991031199892</v>
+        <v>1918.217499919695</v>
       </c>
       <c r="C25" t="n">
-        <v>29833.01378317262</v>
+        <v>6895.56223149132</v>
       </c>
     </row>
     <row r="26">
@@ -4430,10 +4430,10 @@
         <v>5184</v>
       </c>
       <c r="B26" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4441,10 +4441,10 @@
         <v>5185</v>
       </c>
       <c r="B27" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4452,10 +4452,10 @@
         <v>5186</v>
       </c>
       <c r="B28" t="n">
-        <v>8298.991031199892</v>
+        <v>11945.42514073174</v>
       </c>
       <c r="C28" t="n">
-        <v>29833.01378317262</v>
+        <v>42941.12760569908</v>
       </c>
     </row>
     <row r="29">
@@ -4463,10 +4463,10 @@
         <v>5187</v>
       </c>
       <c r="B29" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -4474,10 +4474,10 @@
         <v>5188</v>
       </c>
       <c r="B30" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4518,10 +4518,10 @@
         <v>5192</v>
       </c>
       <c r="B34" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4529,10 +4529,10 @@
         <v>5193</v>
       </c>
       <c r="B35" t="n">
-        <v>8298.991031199892</v>
+        <v>1916.339354268994</v>
       </c>
       <c r="C35" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4540,10 +4540,10 @@
         <v>5194</v>
       </c>
       <c r="B36" t="n">
-        <v>8298.991031199892</v>
+        <v>3227.117824545722</v>
       </c>
       <c r="C36" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4551,10 +4551,10 @@
         <v>5195</v>
       </c>
       <c r="B37" t="n">
-        <v>8298.991031199892</v>
+        <v>3929.157135457161</v>
       </c>
       <c r="C37" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4562,10 +4562,10 @@
         <v>5196</v>
       </c>
       <c r="B38" t="n">
-        <v>8298.991031199892</v>
+        <v>3964.028805785842</v>
       </c>
       <c r="C38" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4573,10 +4573,10 @@
         <v>5197</v>
       </c>
       <c r="B39" t="n">
-        <v>8298.991031199892</v>
+        <v>3983.964669036627</v>
       </c>
       <c r="C39" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4584,10 +4584,10 @@
         <v>5198</v>
       </c>
       <c r="B40" t="n">
-        <v>8298.991031199892</v>
+        <v>4001.704055284764</v>
       </c>
       <c r="C40" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4595,10 +4595,10 @@
         <v>5199</v>
       </c>
       <c r="B41" t="n">
-        <v>8298.991031199892</v>
+        <v>3314.316683222221</v>
       </c>
       <c r="C41" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4606,10 +4606,10 @@
         <v>5200</v>
       </c>
       <c r="B42" t="n">
-        <v>8298.991031199892</v>
+        <v>4566.527817300436</v>
       </c>
       <c r="C42" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4617,10 +4617,10 @@
         <v>5201</v>
       </c>
       <c r="B43" t="n">
-        <v>8298.991031199892</v>
+        <v>3486.833551854741</v>
       </c>
       <c r="C43" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4628,10 +4628,10 @@
         <v>5202</v>
       </c>
       <c r="B44" t="n">
-        <v>8298.991031199892</v>
+        <v>2023.307809023724</v>
       </c>
       <c r="C44" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4639,7 +4639,7 @@
         <v>5203</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>1271.067649040437</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -4683,10 +4683,10 @@
         <v>5207</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>1918.217499919695</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>6895.56223149132</v>
       </c>
     </row>
     <row r="50">
@@ -4705,10 +4705,10 @@
         <v>5209</v>
       </c>
       <c r="B51" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4716,10 +4716,10 @@
         <v>5210</v>
       </c>
       <c r="B52" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4727,10 +4727,10 @@
         <v>5211</v>
       </c>
       <c r="B53" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4738,10 +4738,10 @@
         <v>5212</v>
       </c>
       <c r="B54" t="n">
-        <v>8180.260414725616</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>29406.20381260569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4793,10 +4793,10 @@
         <v>5217</v>
       </c>
       <c r="B59" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4804,10 +4804,10 @@
         <v>5218</v>
       </c>
       <c r="B60" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4815,10 +4815,10 @@
         <v>5219</v>
       </c>
       <c r="B61" t="n">
-        <v>8298.991031199892</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4826,10 +4826,10 @@
         <v>5220</v>
       </c>
       <c r="B62" t="n">
-        <v>8298.991031199892</v>
+        <v>1376.52520246953</v>
       </c>
       <c r="C62" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4837,10 +4837,10 @@
         <v>5221</v>
       </c>
       <c r="B63" t="n">
-        <v>8298.991031199892</v>
+        <v>1991.984742662004</v>
       </c>
       <c r="C63" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4848,10 +4848,10 @@
         <v>5222</v>
       </c>
       <c r="B64" t="n">
-        <v>8298.991031199892</v>
+        <v>2667.799804557779</v>
       </c>
       <c r="C64" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4859,10 +4859,10 @@
         <v>5223</v>
       </c>
       <c r="B65" t="n">
-        <v>8298.991031199892</v>
+        <v>2054.426363079256</v>
       </c>
       <c r="C65" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4870,10 +4870,10 @@
         <v>5224</v>
       </c>
       <c r="B66" t="n">
-        <v>8298.991031199892</v>
+        <v>2609.440893155184</v>
       </c>
       <c r="C66" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4881,10 +4881,10 @@
         <v>5225</v>
       </c>
       <c r="B67" t="n">
-        <v>8298.991031199892</v>
+        <v>1743.416775927372</v>
       </c>
       <c r="C67" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4892,7 +4892,7 @@
         <v>5226</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1011.655844816268</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -5057,7 +5057,7 @@
         <v>5241</v>
       </c>
       <c r="B83" t="n">
-        <v>1075.375719707645</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
         <v>5242</v>
       </c>
       <c r="B84" t="n">
-        <v>1474.736780830645</v>
+        <v>1936.272246970959</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>5243</v>
       </c>
       <c r="B85" t="n">
-        <v>1475.804549839725</v>
+        <v>3274.289585735333</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>5244</v>
       </c>
       <c r="B86" t="n">
-        <v>1490.176574563599</v>
+        <v>3964.028805785842</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>5245</v>
       </c>
       <c r="B87" t="n">
-        <v>1497.163797044169</v>
+        <v>4647.959583257298</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         <v>5246</v>
       </c>
       <c r="B88" t="n">
-        <v>1127.709109819074</v>
+        <v>4732.546514427365</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>5247</v>
       </c>
       <c r="B89" t="n">
-        <v>1159.230484233877</v>
+        <v>5302.906693155553</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>5248</v>
       </c>
       <c r="B90" t="n">
-        <v>1835.390835249886</v>
+        <v>5218.886602597744</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>5249</v>
       </c>
       <c r="B91" t="n">
-        <v>1277.071086865342</v>
+        <v>4067.968954412758</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
         <v>5250</v>
       </c>
       <c r="B92" t="n">
-        <v>572.270525798585</v>
+        <v>3034.963653839994</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>5251</v>
       </c>
       <c r="B93" t="n">
-        <v>441.9208053756686</v>
+        <v>2118.444476304936</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>5252</v>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>1221.663651469608</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
         <v>5253</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>710.6220486422399</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -5211,10 +5211,10 @@
         <v>5255</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>1918.217499919695</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>6895.56223149132</v>
       </c>
     </row>
     <row r="98">
@@ -5222,10 +5222,10 @@
         <v>5256</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1864.362855986489</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>6701.966849991688</v>
       </c>
     </row>
     <row r="99">
@@ -5233,10 +5233,10 @@
         <v>5257</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="100">
@@ -5244,10 +5244,10 @@
         <v>5258</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>1864.362855986517</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>6701.966849991787</v>
       </c>
     </row>
     <row r="101">
@@ -5255,10 +5255,10 @@
         <v>5259</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>1864.362855986501</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>6701.96684999173</v>
       </c>
     </row>
     <row r="102">
@@ -5277,10 +5277,10 @@
         <v>5261</v>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="104">
@@ -5299,7 +5299,7 @@
         <v>5263</v>
       </c>
       <c r="B105" t="n">
-        <v>656.9809114963647</v>
+        <v>1188.29535412091</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>5264</v>
       </c>
       <c r="B106" t="n">
-        <v>690.3397879591588</v>
+        <v>2475.334940521342</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -5321,7 +5321,7 @@
         <v>5265</v>
       </c>
       <c r="B107" t="n">
-        <v>1075.375719707645</v>
+        <v>3832.674827929175</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
         <v>5266</v>
       </c>
       <c r="B108" t="n">
-        <v>1450.970643549065</v>
+        <v>4558.632946774895</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>5267</v>
       </c>
       <c r="B109" t="n">
-        <v>1844.754962767621</v>
+        <v>5893.755904013819</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
         <v>5268</v>
       </c>
       <c r="B110" t="n">
-        <v>1862.716685368439</v>
+        <v>6606.714988202591</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>5269</v>
       </c>
       <c r="B111" t="n">
-        <v>1871.455470837247</v>
+        <v>7303.93442385259</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>5270</v>
       </c>
       <c r="B112" t="n">
-        <v>1879.512102603256</v>
+        <v>7336.46514994151</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -5387,7 +5387,7 @@
         <v>5271</v>
       </c>
       <c r="B113" t="n">
-        <v>1867.915434044036</v>
+        <v>7357.323423660053</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
         <v>5272</v>
       </c>
       <c r="B114" t="n">
-        <v>1468.315675708288</v>
+        <v>7828.327495752929</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
         <v>5273</v>
       </c>
       <c r="B115" t="n">
-        <v>1277.071086865342</v>
+        <v>5811.404995489645</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>5274</v>
       </c>
       <c r="B116" t="n">
-        <v>804.9293551367629</v>
+        <v>4552.443072616299</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -5431,7 +5431,7 @@
         <v>5275</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>2965.826119856812</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -5442,7 +5442,7 @@
         <v>5276</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>2348.451367717662</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
         <v>5277</v>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>1776.547663254889</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -5464,7 +5464,7 @@
         <v>5278</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>1017.839082958451</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>5279</v>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>915.7336334687392</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
         <v>5280</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>531.9509231328631</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>5285</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>1864.362855986478</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>6701.966849991648</v>
       </c>
     </row>
     <row r="128">
@@ -5552,10 +5552,10 @@
         <v>5286</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="129">
@@ -5563,7 +5563,7 @@
         <v>5287</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>1535.001450798823</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -5574,7 +5574,7 @@
         <v>5288</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>2672.182900350447</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -5585,7 +5585,7 @@
         <v>5289</v>
       </c>
       <c r="B131" t="n">
-        <v>960.499716303184</v>
+        <v>3876.708943975496</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
         <v>5290</v>
       </c>
       <c r="B132" t="n">
-        <v>1298.404483621192</v>
+        <v>5047.89724987357</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>5291</v>
       </c>
       <c r="B133" t="n">
-        <v>1655.295631556161</v>
+        <v>6283.156280782693</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>5292</v>
       </c>
       <c r="B134" t="n">
-        <v>1674.616576256903</v>
+        <v>6932.897048177049</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -5629,7 +5629,7 @@
         <v>5293</v>
       </c>
       <c r="B135" t="n">
-        <v>1683.387241135303</v>
+        <v>7552.574985514701</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>5294</v>
       </c>
       <c r="B136" t="n">
-        <v>1352.735777506381</v>
+        <v>8169.584221112982</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>5295</v>
       </c>
       <c r="B137" t="n">
-        <v>1009.921942040277</v>
+        <v>8133.212161511111</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
         <v>5296</v>
       </c>
       <c r="B138" t="n">
-        <v>995.2646642949775</v>
+        <v>8027.969999425504</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
         <v>5297</v>
       </c>
       <c r="B139" t="n">
-        <v>619.7128942235997</v>
+        <v>6666.308259455172</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
         <v>5298</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>4926.0660631894</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>5299</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>3450.709893829663</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
         <v>5300</v>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>2910.390652124738</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
         <v>5301</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>2390.762180999916</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>5302</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>1649.9029689193</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>5303</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>1498.858027043226</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -5750,7 +5750,7 @@
         <v>5304</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>1059.263761519767</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
         <v>5305</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>731.8419023983838</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         <v>5306</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>504.1155444438644</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -5783,10 +5783,10 @@
         <v>5307</v>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>12429.08570657677</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="150">
@@ -5794,10 +5794,10 @@
         <v>5308</v>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>12429.08570657677</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="151">
@@ -5805,10 +5805,10 @@
         <v>5309</v>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>12429.08570657677</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="152">
@@ -5816,7 +5816,7 @@
         <v>5310</v>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>687.0446550929947</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -5827,7 +5827,7 @@
         <v>5311</v>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>1134.99433511229</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -5838,7 +5838,7 @@
         <v>5312</v>
       </c>
       <c r="B154" t="n">
-        <v>642.022129331799</v>
+        <v>1972.246304425233</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>5313</v>
       </c>
       <c r="B155" t="n">
-        <v>692.7235785653447</v>
+        <v>2458.496529245611</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>5314</v>
       </c>
       <c r="B156" t="n">
-        <v>912.7042013393901</v>
+        <v>3331.587411231836</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
         <v>5315</v>
       </c>
       <c r="B157" t="n">
-        <v>1169.722955275643</v>
+        <v>3832.384905809829</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -5882,7 +5882,7 @@
         <v>5316</v>
       </c>
       <c r="B158" t="n">
-        <v>1191.452244464731</v>
+        <v>4330.922875886352</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -5893,7 +5893,7 @@
         <v>5317</v>
       </c>
       <c r="B159" t="n">
-        <v>1439.334293949124</v>
+        <v>4796.941252195735</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>5318</v>
       </c>
       <c r="B160" t="n">
-        <v>1197.411560566057</v>
+        <v>4794.655036821998</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
         <v>5319</v>
       </c>
       <c r="B161" t="n">
-        <v>1127.884208519988</v>
+        <v>4568.257044403148</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>5320</v>
       </c>
       <c r="B162" t="n">
-        <v>1050.699455014127</v>
+        <v>3992.248631752863</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>5321</v>
       </c>
       <c r="B163" t="n">
-        <v>781.656367405008</v>
+        <v>3331.06299077794</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>5322</v>
       </c>
       <c r="B164" t="n">
-        <v>578.857971071766</v>
+        <v>2926.876029629524</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -5959,7 +5959,7 @@
         <v>5323</v>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>2452.169070888459</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>5324</v>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>1645.560970092511</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
         <v>5325</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>1223.241893982893</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -5992,7 +5992,7 @@
         <v>5326</v>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>1213.878510018219</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>5327</v>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>863.2746313368747</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         <v>5328</v>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>1864.362855986489</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>6701.966849991688</v>
       </c>
     </row>
     <row r="171">
@@ -6025,10 +6025,10 @@
         <v>5329</v>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="172">
@@ -6036,10 +6036,10 @@
         <v>5330</v>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>1864.362855986504</v>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>6701.966849991739</v>
       </c>
     </row>
     <row r="173">
@@ -6047,10 +6047,10 @@
         <v>5331</v>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>9563.101821935843</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>34377.20891505124</v>
       </c>
     </row>
     <row r="174">
@@ -6058,10 +6058,10 @@
         <v>5332</v>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>1864.362855986481</v>
       </c>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>6701.966849991659</v>
       </c>
     </row>
     <row r="175">
@@ -6069,10 +6069,10 @@
         <v>5333</v>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="176">
@@ -6102,7 +6102,7 @@
         <v>5336</v>
       </c>
       <c r="B178" t="n">
-        <v>1380.676677790173</v>
+        <v>1856.503613534696</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>5337</v>
       </c>
       <c r="B179" t="n">
-        <v>1792.292447037863</v>
+        <v>2555.113652987385</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
         <v>5338</v>
       </c>
       <c r="B180" t="n">
-        <v>2539.201387613717</v>
+        <v>3872.550245907864</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>5339</v>
       </c>
       <c r="B181" t="n">
-        <v>2951.606201551307</v>
+        <v>4584.010236316848</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>5340</v>
       </c>
       <c r="B182" t="n">
-        <v>2980.349704097881</v>
+        <v>5946.028759816625</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -6157,7 +6157,7 @@
         <v>5341</v>
       </c>
       <c r="B183" t="n">
-        <v>2994.330492216481</v>
+        <v>6639.949142206677</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
         <v>5342</v>
       </c>
       <c r="B184" t="n">
-        <v>3044.567999579099</v>
+        <v>6669.522189313492</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>5343</v>
       </c>
       <c r="B185" t="n">
-        <v>3362.241985022975</v>
+        <v>6694.464903302984</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -6190,7 +6190,7 @@
         <v>5344</v>
       </c>
       <c r="B186" t="n">
-        <v>2976.238864391453</v>
+        <v>6523.590660008794</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>5345</v>
       </c>
       <c r="B187" t="n">
-        <v>2554.142173730684</v>
+        <v>5230.250327782114</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>5346</v>
       </c>
       <c r="B188" t="n">
-        <v>1609.861608401671</v>
+        <v>4046.609866081502</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>5347</v>
       </c>
       <c r="B189" t="n">
-        <v>1104.797666246954</v>
+        <v>2596.349449865642</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>5348</v>
       </c>
       <c r="B190" t="n">
-        <v>839.6310055495454</v>
+        <v>1957.039907465989</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>5349</v>
       </c>
       <c r="B191" t="n">
-        <v>585.6417030346713</v>
+        <v>1459.963461259691</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>5350</v>
       </c>
       <c r="B192" t="n">
-        <v>563.1645323076219</v>
+        <v>1357.119712956501</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>5351</v>
       </c>
       <c r="B193" t="n">
-        <v>503.2959857066625</v>
+        <v>915.7336334687392</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -6278,7 +6278,7 @@
         <v>5352</v>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>811.8213270037274</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
         <v>5353</v>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>497.999270684367</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -6300,10 +6300,10 @@
         <v>5354</v>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="197">
@@ -6311,10 +6311,10 @@
         <v>5355</v>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>1864.362855986504</v>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>6701.966849991739</v>
       </c>
     </row>
     <row r="198">
@@ -6322,10 +6322,10 @@
         <v>5356</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>1864.362855986481</v>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>6701.966849991659</v>
       </c>
     </row>
     <row r="199">
@@ -6333,10 +6333,10 @@
         <v>5357</v>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>1864.362855986497</v>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>6701.966849991716</v>
       </c>
     </row>
     <row r="200">
@@ -6355,7 +6355,7 @@
         <v>5359</v>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>1782.438214893986</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
         <v>5360</v>
       </c>
       <c r="B202" t="n">
-        <v>1380.676677790173</v>
+        <v>3094.166735347271</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -6377,7 +6377,7 @@
         <v>5361</v>
       </c>
       <c r="B203" t="n">
-        <v>1792.292447037863</v>
+        <v>4471.453007256381</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -6388,7 +6388,7 @@
         <v>5362</v>
       </c>
       <c r="B204" t="n">
-        <v>2539.201387613717</v>
+        <v>5808.83212545358</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>5363</v>
       </c>
       <c r="B205" t="n">
-        <v>3320.565855764806</v>
+        <v>6596.985566397112</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -6410,7 +6410,7 @@
         <v>5364</v>
       </c>
       <c r="B206" t="n">
-        <v>3725.43391763805</v>
+        <v>7928.038346422167</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -6421,7 +6421,7 @@
         <v>5365</v>
       </c>
       <c r="B207" t="n">
-        <v>4117.196819211281</v>
+        <v>8631.904987144411</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>5366</v>
       </c>
       <c r="B208" t="n">
-        <v>4134.936118497692</v>
+        <v>9337.341259020788</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>5367</v>
       </c>
       <c r="B209" t="n">
-        <v>4147.898076832479</v>
+        <v>9942.921289836935</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>5368</v>
       </c>
       <c r="B210" t="n">
-        <v>4404.949925253007</v>
+        <v>9133.067138532761</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
         <v>5369</v>
       </c>
       <c r="B211" t="n">
-        <v>3511.94779920109</v>
+        <v>7554.81695512964</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -6476,7 +6476,7 @@
         <v>5370</v>
       </c>
       <c r="B212" t="n">
-        <v>2683.098998798981</v>
+        <v>6069.927307679985</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -6487,7 +6487,7 @@
         <v>5371</v>
       </c>
       <c r="B213" t="n">
-        <v>1799.365425988101</v>
+        <v>4236.893768897251</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
         <v>5372</v>
       </c>
       <c r="B214" t="n">
-        <v>1469.352537197047</v>
+        <v>3522.67798725506</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>5373</v>
       </c>
       <c r="B215" t="n">
-        <v>1171.283952970514</v>
+        <v>2842.478936265626</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
         <v>5374</v>
       </c>
       <c r="B216" t="n">
-        <v>750.8846578925702</v>
+        <v>2035.683917882848</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -6531,7 +6531,7 @@
         <v>5375</v>
       </c>
       <c r="B217" t="n">
-        <v>671.0582338470149</v>
+        <v>1831.472083224858</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -6542,7 +6542,7 @@
         <v>5376</v>
       </c>
       <c r="B218" t="n">
-        <v>306.3151758225118</v>
+        <v>1353.034251469941</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>5377</v>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>1015.358798552934</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         <v>5378</v>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>993.7423838404452</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>5379</v>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>786.3762244749153</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -6586,7 +6586,7 @@
         <v>5380</v>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>632.572247008873</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
@@ -6597,7 +6597,7 @@
         <v>5381</v>
       </c>
       <c r="B223" t="n">
-        <v>0</v>
+        <v>844.3397324731509</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
         <v>5382</v>
       </c>
       <c r="B224" t="n">
-        <v>842.1372331707084</v>
+        <v>1585.606203008711</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>5383</v>
       </c>
       <c r="B225" t="n">
-        <v>1642.443584356478</v>
+        <v>2970.72393644014</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -6630,7 +6630,7 @@
         <v>5384</v>
       </c>
       <c r="B226" t="n">
-        <v>2761.353355580345</v>
+        <v>4331.834205607942</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -6641,7 +6641,7 @@
         <v>5385</v>
       </c>
       <c r="B227" t="n">
-        <v>3584.595939687137</v>
+        <v>5749.014182198166</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -6652,7 +6652,7 @@
         <v>5386</v>
       </c>
       <c r="B228" t="n">
-        <v>3990.157540522056</v>
+        <v>6454.226016516687</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
         <v>5387</v>
       </c>
       <c r="B229" t="n">
-        <v>3689.50467618012</v>
+        <v>7858.324839167642</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
         <v>5388</v>
       </c>
       <c r="B230" t="n">
-        <v>4470.53787117406</v>
+        <v>8588.72457480813</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
         <v>5389</v>
       </c>
       <c r="B231" t="n">
-        <v>4117.196819211281</v>
+        <v>9355.961275985765</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
         <v>5390</v>
       </c>
       <c r="B232" t="n">
-        <v>4134.936118497692</v>
+        <v>10004.23137838218</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -6707,7 +6707,7 @@
         <v>5391</v>
       </c>
       <c r="B233" t="n">
-        <v>2988.667592598601</v>
+        <v>10008.75563373118</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>5392</v>
       </c>
       <c r="B234" t="n">
-        <v>2936.628453288431</v>
+        <v>9133.067138532761</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
         <v>5393</v>
       </c>
       <c r="B235" t="n">
-        <v>2234.87671233575</v>
+        <v>7554.81695512964</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>5394</v>
       </c>
       <c r="B236" t="n">
-        <v>1609.861608401671</v>
+        <v>5564.103733719947</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
         <v>5395</v>
       </c>
       <c r="B237" t="n">
-        <v>1325.759517998861</v>
+        <v>3813.207763408692</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -6762,7 +6762,7 @@
         <v>5396</v>
       </c>
       <c r="B238" t="n">
-        <v>1049.537034422274</v>
+        <v>3131.265591324821</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -6773,7 +6773,7 @@
         <v>5397</v>
       </c>
       <c r="B239" t="n">
-        <v>780.856934689724</v>
+        <v>2487.169805464986</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -6784,7 +6784,7 @@
         <v>5398</v>
       </c>
       <c r="B240" t="n">
-        <v>563.1645323076219</v>
+        <v>1696.399407275985</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>5399</v>
       </c>
       <c r="B241" t="n">
-        <v>671.0582338470149</v>
+        <v>1220.981076923717</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
         <v>5400</v>
       </c>
       <c r="B242" t="n">
-        <v>600.1805185620557</v>
+        <v>1082.430103812667</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>5401</v>
       </c>
       <c r="B243" t="n">
-        <v>661.63948185294</v>
+        <v>746.998758780038</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         <v>5402</v>
       </c>
       <c r="B244" t="n">
-        <v>791.4783456982442</v>
+        <v>745.3079919521787</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         <v>5403</v>
       </c>
       <c r="B245" t="n">
-        <v>692.2032510547143</v>
+        <v>524.2540895534338</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>5404</v>
       </c>
       <c r="B246" t="n">
-        <v>652.5337281047515</v>
+        <v>1265.134955010845</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
         <v>5405</v>
       </c>
       <c r="B247" t="n">
-        <v>886.006898556305</v>
+        <v>1281.996881384645</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>5406</v>
       </c>
       <c r="B248" t="n">
-        <v>842.1372331707084</v>
+        <v>2092.1977583921</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -6883,7 +6883,7 @@
         <v>5407</v>
       </c>
       <c r="B249" t="n">
-        <v>1642.443584356478</v>
+        <v>2970.72393644014</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>5408</v>
       </c>
       <c r="B250" t="n">
-        <v>2086.860739570775</v>
+        <v>4331.834205607942</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -6905,7 +6905,7 @@
         <v>5409</v>
       </c>
       <c r="B251" t="n">
-        <v>2867.668166745508</v>
+        <v>5145.581536485603</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -6916,7 +6916,7 @@
         <v>5410</v>
       </c>
       <c r="B252" t="n">
-        <v>3627.426882323249</v>
+        <v>5849.492973211798</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -6927,7 +6927,7 @@
         <v>5411</v>
       </c>
       <c r="B253" t="n">
-        <v>4427.411298292202</v>
+        <v>7203.452473158436</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
         <v>5412</v>
       </c>
       <c r="B254" t="n">
-        <v>4470.53787117406</v>
+        <v>7928.038346422167</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>5413</v>
       </c>
       <c r="B255" t="n">
-        <v>2994.330492216481</v>
+        <v>8631.904987144411</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         <v>5414</v>
       </c>
       <c r="B256" t="n">
-        <v>2631.320891643725</v>
+        <v>9337.341259020788</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         <v>5415</v>
       </c>
       <c r="B257" t="n">
-        <v>2615.084505789795</v>
+        <v>9280.114675067925</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -6982,7 +6982,7 @@
         <v>5416</v>
       </c>
       <c r="B258" t="n">
-        <v>2202.475236077089</v>
+        <v>8480.69684930356</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -6993,7 +6993,7 @@
         <v>5417</v>
       </c>
       <c r="B259" t="n">
-        <v>1277.071086865342</v>
+        <v>6392.525949185526</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
         <v>5418</v>
       </c>
       <c r="B260" t="n">
-        <v>1073.240288525456</v>
+        <v>4552.443072616299</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>5419</v>
       </c>
       <c r="B261" t="n">
-        <v>662.8797589994305</v>
+        <v>3389.512125345373</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>5420</v>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>2739.858947360526</v>
       </c>
       <c r="C262" t="n">
         <v>0</v>
@@ -7037,7 +7037,7 @@
         <v>5421</v>
       </c>
       <c r="B263" t="n">
-        <v>0</v>
+        <v>2131.861610342909</v>
       </c>
       <c r="C263" t="n">
         <v>0</v>
@@ -7048,7 +7048,7 @@
         <v>5422</v>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>1696.399407275985</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
@@ -7059,7 +7059,7 @@
         <v>5423</v>
       </c>
       <c r="B265" t="n">
-        <v>0</v>
+        <v>1220.981076923717</v>
       </c>
       <c r="C265" t="n">
         <v>0</v>
@@ -7070,7 +7070,7 @@
         <v>5424</v>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>1082.430103812667</v>
       </c>
       <c r="C266" t="n">
         <v>0</v>
@@ -7081,7 +7081,7 @@
         <v>5425</v>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>746.998758780038</v>
       </c>
       <c r="C267" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>5426</v>
       </c>
       <c r="B268" t="n">
-        <v>0</v>
+        <v>745.3079919521787</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
@@ -7103,7 +7103,7 @@
         <v>5427</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>524.2540895534338</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>5428</v>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>632.572247008873</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -7125,7 +7125,7 @@
         <v>5429</v>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>844.3397324731509</v>
       </c>
       <c r="C271" t="n">
         <v>0</v>
@@ -7136,7 +7136,7 @@
         <v>5430</v>
       </c>
       <c r="B272" t="n">
-        <v>0</v>
+        <v>1569.148272010146</v>
       </c>
       <c r="C272" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
         <v>5431</v>
       </c>
       <c r="B273" t="n">
-        <v>1313.95602673644</v>
+        <v>2398.847605634659</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>5432</v>
       </c>
       <c r="B274" t="n">
-        <v>2071.016465749331</v>
+        <v>3713.002410782014</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
         <v>5433</v>
       </c>
       <c r="B275" t="n">
-        <v>2509.211525595056</v>
+        <v>5110.24563544572</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -7180,7 +7180,7 @@
         <v>5434</v>
       </c>
       <c r="B276" t="n">
-        <v>2901.941287098131</v>
+        <v>5808.83212545358</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>5435</v>
       </c>
       <c r="B277" t="n">
-        <v>2951.606201551307</v>
+        <v>6548.580107149232</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
         <v>5436</v>
       </c>
       <c r="B278" t="n">
-        <v>2980.349704097881</v>
+        <v>7267.353053714765</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>5437</v>
       </c>
       <c r="B279" t="n">
-        <v>3029.413655426994</v>
+        <v>7967.919705498499</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
@@ -7224,7 +7224,7 @@
         <v>5438</v>
       </c>
       <c r="B280" t="n">
-        <v>3383.124431329076</v>
+        <v>8003.408110569526</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
@@ -7235,7 +7235,7 @@
         <v>5439</v>
       </c>
       <c r="B281" t="n">
-        <v>2988.667592598601</v>
+        <v>7291.491886801509</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
@@ -7246,7 +7246,7 @@
         <v>5440</v>
       </c>
       <c r="B282" t="n">
-        <v>2202.475236077089</v>
+        <v>5218.886602597744</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
@@ -7257,7 +7257,7 @@
         <v>5441</v>
       </c>
       <c r="B283" t="n">
-        <v>1277.071086865342</v>
+        <v>4067.968954412758</v>
       </c>
       <c r="C283" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>5442</v>
       </c>
       <c r="B284" t="n">
-        <v>536.621319876215</v>
+        <v>3540.787227800031</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
         <v>5443</v>
       </c>
       <c r="B285" t="n">
-        <v>0</v>
+        <v>2542.135298080876</v>
       </c>
       <c r="C285" t="n">
         <v>0</v>
@@ -7290,7 +7290,7 @@
         <v>5444</v>
       </c>
       <c r="B286" t="n">
-        <v>0</v>
+        <v>1957.039907465989</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>5445</v>
       </c>
       <c r="B287" t="n">
-        <v>0</v>
+        <v>1776.547663254889</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
         <v>5446</v>
       </c>
       <c r="B288" t="n">
-        <v>0</v>
+        <v>1357.119712956501</v>
       </c>
       <c r="C288" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
         <v>5447</v>
       </c>
       <c r="B289" t="n">
-        <v>0</v>
+        <v>915.7336334687392</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
@@ -7334,7 +7334,7 @@
         <v>5448</v>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>797.926337915366</v>
       </c>
       <c r="C290" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
         <v>5449</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>509.3212378009041</v>
       </c>
       <c r="C291" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         <v>5450</v>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>488.7701965487762</v>
       </c>
       <c r="C292" t="n">
         <v>0</v>
@@ -7367,10 +7367,10 @@
         <v>5451</v>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>6222.996085221091</v>
       </c>
       <c r="C293" t="n">
-        <v>0</v>
+        <v>22370.27697524673</v>
       </c>
     </row>
     <row r="294">
@@ -7378,10 +7378,10 @@
         <v>5452</v>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C294" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="295">
@@ -7389,10 +7389,10 @@
         <v>5453</v>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C295" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="296">
@@ -7400,7 +7400,7 @@
         <v>5454</v>
       </c>
       <c r="B296" t="n">
-        <v>0</v>
+        <v>902.6553921878502</v>
       </c>
       <c r="C296" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
         <v>5455</v>
       </c>
       <c r="B297" t="n">
-        <v>0</v>
+        <v>1535.001450798823</v>
       </c>
       <c r="C297" t="n">
         <v>0</v>
@@ -7422,7 +7422,7 @@
         <v>5456</v>
       </c>
       <c r="B298" t="n">
-        <v>0</v>
+        <v>2137.746909266406</v>
       </c>
       <c r="C298" t="n">
         <v>0</v>
@@ -7433,7 +7433,7 @@
         <v>5457</v>
       </c>
       <c r="B299" t="n">
-        <v>0</v>
+        <v>2769.076020338925</v>
       </c>
       <c r="C299" t="n">
         <v>0</v>
@@ -7444,10 +7444,10 @@
         <v>5458</v>
       </c>
       <c r="B300" t="n">
-        <v>8298.991031199892</v>
+        <v>3926.141889600081</v>
       </c>
       <c r="C300" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -7455,10 +7455,10 @@
         <v>5459</v>
       </c>
       <c r="B301" t="n">
-        <v>8298.991031199892</v>
+        <v>4569.577594131159</v>
       </c>
       <c r="C301" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -7466,7 +7466,7 @@
         <v>5460</v>
       </c>
       <c r="B302" t="n">
-        <v>1004.771214385633</v>
+        <v>4621.947107849776</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>5461</v>
       </c>
       <c r="B303" t="n">
-        <v>1010.033503932439</v>
+        <v>4647.749937617412</v>
       </c>
       <c r="C303" t="n">
         <v>0</v>
@@ -7488,7 +7488,7 @@
         <v>5462</v>
       </c>
       <c r="B304" t="n">
-        <v>1352.735777506381</v>
+        <v>4668.335771090785</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -7499,7 +7499,7 @@
         <v>5463</v>
       </c>
       <c r="B305" t="n">
-        <v>1048.400267719588</v>
+        <v>4066.606548594838</v>
       </c>
       <c r="C305" t="n">
         <v>0</v>
@@ -7510,7 +7510,7 @@
         <v>5464</v>
       </c>
       <c r="B306" t="n">
-        <v>995.2646642949775</v>
+        <v>4081.751519845503</v>
       </c>
       <c r="C306" t="n">
         <v>0</v>
@@ -7521,10 +7521,10 @@
         <v>5465</v>
       </c>
       <c r="B307" t="n">
-        <v>8298.991031199892</v>
+        <v>2563.962358929924</v>
       </c>
       <c r="C307" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -7532,7 +7532,7 @@
         <v>5466</v>
       </c>
       <c r="B308" t="n">
-        <v>0</v>
+        <v>1404.463043698418</v>
       </c>
       <c r="C308" t="n">
         <v>0</v>
@@ -7543,7 +7543,7 @@
         <v>5467</v>
       </c>
       <c r="B309" t="n">
-        <v>0</v>
+        <v>766.8244208510366</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
         <v>5470</v>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>989.9431464593922</v>
       </c>
       <c r="C312" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>5471</v>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>599.5481206725257</v>
       </c>
       <c r="C313" t="n">
         <v>0</v>
@@ -7598,10 +7598,10 @@
         <v>5472</v>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>1864.362855986485</v>
       </c>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>6701.966849991672</v>
       </c>
     </row>
     <row r="315">
@@ -7609,10 +7609,10 @@
         <v>5473</v>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C315" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="316">
@@ -7620,10 +7620,10 @@
         <v>5474</v>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>12429.08570657677</v>
       </c>
       <c r="C316" t="n">
-        <v>0</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="317">
@@ -7631,10 +7631,10 @@
         <v>5475</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>12429.08570657677</v>
       </c>
       <c r="C317" t="n">
-        <v>0</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="318">
@@ -7642,10 +7642,10 @@
         <v>5476</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>12429.08570657677</v>
       </c>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="319">
@@ -7653,10 +7653,10 @@
         <v>5477</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C319" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
     <row r="320">
@@ -7664,10 +7664,10 @@
         <v>5478</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>1864.362855986486</v>
       </c>
       <c r="C320" t="n">
-        <v>0</v>
+        <v>6701.966849991673</v>
       </c>
     </row>
     <row r="321">
@@ -7675,10 +7675,10 @@
         <v>5479</v>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>12429.08570657677</v>
       </c>
       <c r="C321" t="n">
-        <v>0</v>
+        <v>44679.77899994522</v>
       </c>
     </row>
     <row r="322">
@@ -7697,10 +7697,10 @@
         <v>5481</v>
       </c>
       <c r="B323" t="n">
-        <v>8298.991031199892</v>
+        <v>854.8344322288972</v>
       </c>
       <c r="C323" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -7708,10 +7708,10 @@
         <v>5482</v>
       </c>
       <c r="B324" t="n">
-        <v>8298.991031199892</v>
+        <v>1290.005291014592</v>
       </c>
       <c r="C324" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -7719,10 +7719,10 @@
         <v>5483</v>
       </c>
       <c r="B325" t="n">
-        <v>8298.991031199892</v>
+        <v>1703.277483358446</v>
       </c>
       <c r="C325" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -7730,10 +7730,10 @@
         <v>5484</v>
       </c>
       <c r="B326" t="n">
-        <v>8298.991031199892</v>
+        <v>2165.460970103893</v>
       </c>
       <c r="C326" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -7741,10 +7741,10 @@
         <v>5485</v>
       </c>
       <c r="B327" t="n">
-        <v>8298.991031199892</v>
+        <v>2616.514723821504</v>
       </c>
       <c r="C327" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -7752,10 +7752,10 @@
         <v>5486</v>
       </c>
       <c r="B328" t="n">
-        <v>8298.991031199892</v>
+        <v>2615.268305221695</v>
       </c>
       <c r="C328" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -7763,10 +7763,10 @@
         <v>5487</v>
       </c>
       <c r="B329" t="n">
-        <v>8298.991031199892</v>
+        <v>2557.610733598832</v>
       </c>
       <c r="C329" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -7774,10 +7774,10 @@
         <v>5488</v>
       </c>
       <c r="B330" t="n">
-        <v>8298.991031199892</v>
+        <v>2354.688892700638</v>
       </c>
       <c r="C330" t="n">
-        <v>29833.01378317262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -7785,7 +7785,7 @@
         <v>5489</v>
       </c>
       <c r="B331" t="n">
-        <v>0</v>
+        <v>1915.452366438793</v>
       </c>
       <c r="C331" t="n">
         <v>0</v>
@@ -7796,7 +7796,7 @@
         <v>5490</v>
       </c>
       <c r="B332" t="n">
-        <v>0</v>
+        <v>1463.438482654044</v>
       </c>
       <c r="C332" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
         <v>5491</v>
       </c>
       <c r="B333" t="n">
-        <v>0</v>
+        <v>1050.92960180934</v>
       </c>
       <c r="C333" t="n">
         <v>0</v>
@@ -7818,7 +7818,7 @@
         <v>5492</v>
       </c>
       <c r="B334" t="n">
-        <v>0</v>
+        <v>658.2265016876692</v>
       </c>
       <c r="C334" t="n">
         <v>0</v>
@@ -7851,10 +7851,10 @@
         <v>5495</v>
       </c>
       <c r="B337" t="n">
-        <v>0</v>
+        <v>1864.3628559865</v>
       </c>
       <c r="C337" t="n">
-        <v>0</v>
+        <v>6701.966849991724</v>
       </c>
     </row>
   </sheetData>

--- a/first_stage_optimization/lshp_operation.xlsx
+++ b/first_stage_optimization/lshp_operation.xlsx
@@ -439,10 +439,10 @@
         <v>288</v>
       </c>
       <c r="B2" t="n">
-        <v>13118.95506015835</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C2" t="n">
-        <v>36183.3112376924</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="3">
@@ -450,10 +450,10 @@
         <v>289</v>
       </c>
       <c r="B3" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C3" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>290</v>
       </c>
       <c r="B4" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C4" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="5">
@@ -472,10 +472,10 @@
         <v>291</v>
       </c>
       <c r="B5" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C5" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="6">
@@ -483,10 +483,10 @@
         <v>292</v>
       </c>
       <c r="B6" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C6" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="7">
@@ -494,10 +494,10 @@
         <v>293</v>
       </c>
       <c r="B7" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C7" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="8">
@@ -505,10 +505,10 @@
         <v>294</v>
       </c>
       <c r="B8" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C8" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="9">
@@ -516,10 +516,10 @@
         <v>295</v>
       </c>
       <c r="B9" t="n">
-        <v>2429.926916918618</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>6701.966849991739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>297</v>
       </c>
       <c r="B11" t="n">
-        <v>8695.088195568311</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23981.87058166778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -549,10 +549,10 @@
         <v>298</v>
       </c>
       <c r="B12" t="n">
-        <v>4801.571070258774</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>13243.1843594543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -560,10 +560,10 @@
         <v>299</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="14">
@@ -571,10 +571,10 @@
         <v>300</v>
       </c>
       <c r="B14" t="n">
-        <v>2429.926916918618</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C14" t="n">
-        <v>6701.966849991739</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="15">
@@ -582,10 +582,10 @@
         <v>301</v>
       </c>
       <c r="B15" t="n">
-        <v>2429.926916918618</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C15" t="n">
-        <v>6701.966849991739</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="16">
@@ -593,10 +593,10 @@
         <v>302</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="17">
@@ -648,10 +648,10 @@
         <v>307</v>
       </c>
       <c r="B21" t="n">
-        <v>2429.926916918602</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C21" t="n">
-        <v>6701.966849991695</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="22">
@@ -659,10 +659,10 @@
         <v>308</v>
       </c>
       <c r="B22" t="n">
-        <v>5537.230684303509</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C22" t="n">
-        <v>15272.2027269934</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="23">
@@ -670,10 +670,10 @@
         <v>309</v>
       </c>
       <c r="B23" t="n">
-        <v>10202.12806732262</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C23" t="n">
-        <v>28138.42820971411</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="24">
@@ -681,10 +681,10 @@
         <v>310</v>
       </c>
       <c r="B24" t="n">
-        <v>14160.70821029218</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C24" t="n">
-        <v>39056.5643505576</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="25">
@@ -692,10 +692,10 @@
         <v>311</v>
       </c>
       <c r="B25" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C25" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="26">
@@ -703,10 +703,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="n">
-        <v>15961.39403155136</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C26" t="n">
-        <v>44023.02511005761</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="27">
@@ -714,10 +714,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C27" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="28">
@@ -725,10 +725,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C28" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="29">
@@ -736,10 +736,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C29" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="30">
@@ -747,10 +747,10 @@
         <v>316</v>
       </c>
       <c r="B30" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C30" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="31">
@@ -758,10 +758,10 @@
         <v>317</v>
       </c>
       <c r="B31" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C31" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="32">
@@ -769,10 +769,10 @@
         <v>318</v>
       </c>
       <c r="B32" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C32" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="33">
@@ -780,10 +780,10 @@
         <v>319</v>
       </c>
       <c r="B33" t="n">
-        <v>2429.926916918618</v>
+        <v>3223.09421407784</v>
       </c>
       <c r="C33" t="n">
-        <v>6701.966849991739</v>
+        <v>8889.596813282806</v>
       </c>
     </row>
     <row r="34">
@@ -813,10 +813,10 @@
         <v>322</v>
       </c>
       <c r="B36" t="n">
-        <v>7056.137241076699</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C36" t="n">
-        <v>19461.4897877902</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="37">
@@ -824,10 +824,10 @@
         <v>323</v>
       </c>
       <c r="B37" t="n">
-        <v>2898.191571504383</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C37" t="n">
-        <v>7993.484784216809</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="38">
@@ -835,10 +835,10 @@
         <v>324</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="39">
@@ -846,10 +846,10 @@
         <v>325</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="40">
@@ -857,10 +857,10 @@
         <v>326</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="41">
@@ -912,10 +912,10 @@
         <v>331</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>2915.747720849548</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>8041.906294388813</v>
       </c>
     </row>
     <row r="46">
@@ -923,10 +923,10 @@
         <v>332</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="47">
@@ -934,10 +934,10 @@
         <v>333</v>
       </c>
       <c r="B47" t="n">
-        <v>7705.537650202712</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C47" t="n">
-        <v>21252.5971597982</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="48">
@@ -945,10 +945,10 @@
         <v>334</v>
       </c>
       <c r="B48" t="n">
-        <v>14160.70821029218</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C48" t="n">
-        <v>39056.5643505576</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="49">
@@ -956,10 +956,10 @@
         <v>335</v>
       </c>
       <c r="B49" t="n">
-        <v>15127.20991356922</v>
+        <v>2822.756190901325</v>
       </c>
       <c r="C49" t="n">
-        <v>41722.26689935577</v>
+        <v>7785.426913587798</v>
       </c>
     </row>
     <row r="50">
@@ -967,10 +967,10 @@
         <v>336</v>
       </c>
       <c r="B50" t="n">
-        <v>13118.95506015835</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C50" t="n">
-        <v>36183.3112376924</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="51">
@@ -978,10 +978,10 @@
         <v>337</v>
       </c>
       <c r="B51" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C51" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="52">
@@ -989,10 +989,10 @@
         <v>338</v>
       </c>
       <c r="B52" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C52" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="53">
@@ -1000,10 +1000,10 @@
         <v>339</v>
       </c>
       <c r="B53" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C53" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="54">
@@ -1011,10 +1011,10 @@
         <v>340</v>
       </c>
       <c r="B54" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C54" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="55">
@@ -1022,10 +1022,10 @@
         <v>341</v>
       </c>
       <c r="B55" t="n">
-        <v>14698.92106657426</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C55" t="n">
-        <v>40541.00600019208</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="56">
@@ -1033,10 +1033,10 @@
         <v>342</v>
       </c>
       <c r="B56" t="n">
-        <v>12360.75770685234</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>34092.1316667232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1220,10 +1220,10 @@
         <v>359</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>7785.058501106087</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>21471.92314154969</v>
       </c>
     </row>
     <row r="74">
@@ -1231,10 +1231,10 @@
         <v>360</v>
       </c>
       <c r="B74" t="n">
-        <v>2638.281499484566</v>
+        <v>7921.8076075279</v>
       </c>
       <c r="C74" t="n">
-        <v>7276.628374039385</v>
+        <v>21849.09003147706</v>
       </c>
     </row>
     <row r="75">
@@ -1242,10 +1242,10 @@
         <v>361</v>
       </c>
       <c r="B75" t="n">
-        <v>2843.180045531988</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C75" t="n">
-        <v>7841.757824501503</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="76">
@@ -1253,10 +1253,10 @@
         <v>362</v>
       </c>
       <c r="B76" t="n">
-        <v>3081.266129689524</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C76" t="n">
-        <v>8498.421624699899</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="77">
@@ -1264,10 +1264,10 @@
         <v>363</v>
       </c>
       <c r="B77" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C77" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="78">
@@ -1275,10 +1275,10 @@
         <v>364</v>
       </c>
       <c r="B78" t="n">
-        <v>6877.03455153217</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C78" t="n">
-        <v>18967.50773437357</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="79">
@@ -1286,10 +1286,10 @@
         <v>365</v>
       </c>
       <c r="B79" t="n">
-        <v>4173.492512380869</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C79" t="n">
-        <v>11510.8846574426</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="80">
@@ -1297,10 +1297,10 @@
         <v>366</v>
       </c>
       <c r="B80" t="n">
-        <v>4917.184139769854</v>
+        <v>10077.01547937512</v>
       </c>
       <c r="C80" t="n">
-        <v>13562.0560727944</v>
+        <v>27793.35593157163</v>
       </c>
     </row>
     <row r="81">
@@ -1374,10 +1374,10 @@
         <v>373</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>7468.834858130776</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>20599.74860920134</v>
       </c>
     </row>
     <row r="88">
@@ -1473,10 +1473,10 @@
         <v>382</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>3424.946608583287</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>9446.324691453912</v>
       </c>
     </row>
     <row r="97">
@@ -1484,10 +1484,10 @@
         <v>383</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="98">
@@ -1495,10 +1495,10 @@
         <v>384</v>
       </c>
       <c r="B98" t="n">
-        <v>5064.45420342849</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C98" t="n">
-        <v>13968.2407517509</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="99">
@@ -1506,10 +1506,10 @@
         <v>385</v>
       </c>
       <c r="B99" t="n">
-        <v>5315.822562258178</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C99" t="n">
-        <v>14661.53831402891</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="100">
@@ -1517,10 +1517,10 @@
         <v>386</v>
       </c>
       <c r="B100" t="n">
-        <v>5568.829288862742</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C100" t="n">
-        <v>15359.3546486366</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="101">
@@ -1528,10 +1528,10 @@
         <v>387</v>
       </c>
       <c r="B101" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C101" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="102">
@@ -1539,10 +1539,10 @@
         <v>388</v>
       </c>
       <c r="B102" t="n">
-        <v>10731.33559033422</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C102" t="n">
-        <v>29598.03230368727</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="103">
@@ -1550,10 +1550,10 @@
         <v>389</v>
       </c>
       <c r="B103" t="n">
-        <v>4173.492512380869</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C103" t="n">
-        <v>11510.8846574426</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="104">
@@ -1561,10 +1561,10 @@
         <v>390</v>
       </c>
       <c r="B104" t="n">
-        <v>7258.852022223756</v>
+        <v>6829.30336611773</v>
       </c>
       <c r="C104" t="n">
-        <v>20020.59620938321</v>
+        <v>18835.86063826911</v>
       </c>
     </row>
     <row r="105">
@@ -1605,10 +1605,10 @@
         <v>394</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>2264.450114450163</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>6245.566273964308</v>
       </c>
     </row>
     <row r="109">
@@ -1627,10 +1627,10 @@
         <v>396</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="111">
@@ -1638,10 +1638,10 @@
         <v>397</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="112">
@@ -1715,10 +1715,10 @@
         <v>404</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>2927.085533910706</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>8073.177048565914</v>
       </c>
     </row>
     <row r="119">
@@ -1726,10 +1726,10 @@
         <v>405</v>
       </c>
       <c r="B119" t="n">
-        <v>3052.562834927492</v>
+        <v>5120.850451717535</v>
       </c>
       <c r="C119" t="n">
-        <v>8419.255239636506</v>
+        <v>14123.78690577942</v>
       </c>
     </row>
     <row r="120">
@@ -1737,10 +1737,10 @@
         <v>406</v>
       </c>
       <c r="B120" t="n">
-        <v>6394.335385638709</v>
+        <v>6401.987222217381</v>
       </c>
       <c r="C120" t="n">
-        <v>17636.17806111781</v>
+        <v>17657.28254567442</v>
       </c>
     </row>
     <row r="121">
@@ -1748,10 +1748,10 @@
         <v>407</v>
       </c>
       <c r="B121" t="n">
-        <v>7081.874035517784</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C121" t="n">
-        <v>19532.47428611739</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="122">
@@ -1759,10 +1759,10 @@
         <v>408</v>
       </c>
       <c r="B122" t="n">
-        <v>9022.237545176489</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C122" t="n">
-        <v>24884.179239926</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="123">
@@ -1770,10 +1770,10 @@
         <v>409</v>
       </c>
       <c r="B123" t="n">
-        <v>9162.386086882425</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C123" t="n">
-        <v>25270.72209191389</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="124">
@@ -1781,10 +1781,10 @@
         <v>410</v>
       </c>
       <c r="B124" t="n">
-        <v>9416.796369629241</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C124" t="n">
-        <v>25972.40956629619</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="125">
@@ -1792,10 +1792,10 @@
         <v>411</v>
       </c>
       <c r="B125" t="n">
-        <v>11667.69471951104</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C125" t="n">
-        <v>32180.5987997151</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="126">
@@ -1803,10 +1803,10 @@
         <v>412</v>
       </c>
       <c r="B126" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C126" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="127">
@@ -1814,10 +1814,10 @@
         <v>413</v>
       </c>
       <c r="B127" t="n">
-        <v>6370.840815083351</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C127" t="n">
-        <v>17571.3778270365</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="128">
@@ -1825,10 +1825,10 @@
         <v>414</v>
       </c>
       <c r="B128" t="n">
-        <v>5351.549131298641</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C128" t="n">
-        <v>14760.07554974</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="129">
@@ -1836,10 +1836,10 @@
         <v>415</v>
       </c>
       <c r="B129" t="n">
-        <v>5056.985611796154</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C129" t="n">
-        <v>13947.6416739813</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="130">
@@ -1847,10 +1847,10 @@
         <v>416</v>
       </c>
       <c r="B130" t="n">
-        <v>5287.524291730701</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C130" t="n">
-        <v>14583.4890238767</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="131">
@@ -1858,10 +1858,10 @@
         <v>417</v>
       </c>
       <c r="B131" t="n">
-        <v>5383.29470299504</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C131" t="n">
-        <v>14847.6328205624</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="132">
@@ -1869,10 +1869,10 @@
         <v>418</v>
       </c>
       <c r="B132" t="n">
-        <v>3762.636051725938</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C132" t="n">
-        <v>10377.703918449</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="133">
@@ -1880,10 +1880,10 @@
         <v>419</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="134">
@@ -1891,10 +1891,10 @@
         <v>420</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="135">
@@ -1902,10 +1902,10 @@
         <v>421</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="136">
@@ -1913,10 +1913,10 @@
         <v>422</v>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="137">
@@ -1924,10 +1924,10 @@
         <v>423</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>2320.557769345792</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>6400.316460286012</v>
       </c>
     </row>
     <row r="138">
@@ -1935,10 +1935,10 @@
         <v>424</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>3106.571651286182</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>8568.216631982512</v>
       </c>
     </row>
     <row r="139">
@@ -1946,10 +1946,10 @@
         <v>425</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>4204.723158340804</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>11597.02171468082</v>
       </c>
     </row>
     <row r="140">
@@ -1979,10 +1979,10 @@
         <v>428</v>
       </c>
       <c r="B142" t="n">
-        <v>4315.482029573499</v>
+        <v>6550.057076146253</v>
       </c>
       <c r="C142" t="n">
-        <v>11902.50509287449</v>
+        <v>18065.67312137652</v>
       </c>
     </row>
     <row r="143">
@@ -1990,10 +1990,10 @@
         <v>429</v>
       </c>
       <c r="B143" t="n">
-        <v>4810.551126905028</v>
+        <v>7641.828945744639</v>
       </c>
       <c r="C143" t="n">
-        <v>13267.95219981</v>
+        <v>21076.88256428461</v>
       </c>
     </row>
     <row r="144">
@@ -2001,10 +2001,10 @@
         <v>430</v>
       </c>
       <c r="B144" t="n">
-        <v>6123.780274270564</v>
+        <v>6285.017751154897</v>
       </c>
       <c r="C144" t="n">
-        <v>16889.961631784</v>
+        <v>17334.66974935382</v>
       </c>
     </row>
     <row r="145">
@@ -2012,10 +2012,10 @@
         <v>431</v>
       </c>
       <c r="B145" t="n">
-        <v>7456.161935427655</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C145" t="n">
-        <v>20564.7954971314</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="146">
@@ -2023,10 +2023,10 @@
         <v>432</v>
       </c>
       <c r="B146" t="n">
-        <v>9238.733826220248</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C146" t="n">
-        <v>25481.29633369511</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="147">
@@ -2034,10 +2034,10 @@
         <v>433</v>
       </c>
       <c r="B147" t="n">
-        <v>10011.22412247041</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C147" t="n">
-        <v>27611.8971848409</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="148">
@@ -2045,10 +2045,10 @@
         <v>434</v>
       </c>
       <c r="B148" t="n">
-        <v>10253.18297777342</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C148" t="n">
-        <v>28279.242451899</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="149">
@@ -2056,10 +2056,10 @@
         <v>435</v>
       </c>
       <c r="B149" t="n">
-        <v>10313.70327275604</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C149" t="n">
-        <v>28446.1631143688</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="150">
@@ -2067,10 +2067,10 @@
         <v>436</v>
       </c>
       <c r="B150" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C150" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="151">
@@ -2078,10 +2078,10 @@
         <v>437</v>
       </c>
       <c r="B151" t="n">
-        <v>11841.81921428548</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C151" t="n">
-        <v>32660.85052400551</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="152">
@@ -2089,10 +2089,10 @@
         <v>438</v>
       </c>
       <c r="B152" t="n">
-        <v>7927.511444964237</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C152" t="n">
-        <v>21864.82175128719</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="153">
@@ -2100,10 +2100,10 @@
         <v>439</v>
       </c>
       <c r="B153" t="n">
-        <v>7662.983402361594</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C153" t="n">
-        <v>21135.2285441531</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="154">
@@ -2111,10 +2111,10 @@
         <v>440</v>
       </c>
       <c r="B154" t="n">
-        <v>7873.063988659377</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C154" t="n">
-        <v>21714.6505487375</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="155">
@@ -2122,10 +2122,10 @@
         <v>441</v>
       </c>
       <c r="B155" t="n">
-        <v>6572.88908759745</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C155" t="n">
-        <v>18128.645955168</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="156">
@@ -2133,10 +2133,10 @@
         <v>442</v>
       </c>
       <c r="B156" t="n">
-        <v>5550.704995034321</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C156" t="n">
-        <v>15309.36614257419</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="157">
@@ -2144,10 +2144,10 @@
         <v>443</v>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="158">
@@ -2155,10 +2155,10 @@
         <v>444</v>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="159">
@@ -2166,10 +2166,10 @@
         <v>445</v>
       </c>
       <c r="B159" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C159" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="160">
@@ -2177,10 +2177,10 @@
         <v>446</v>
       </c>
       <c r="B160" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C160" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="161">
@@ -2188,10 +2188,10 @@
         <v>447</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="162">
@@ -2221,10 +2221,10 @@
         <v>450</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>2276.598239046935</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>6279.071943525916</v>
       </c>
     </row>
     <row r="165">
@@ -2232,10 +2232,10 @@
         <v>451</v>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>4048.996121715179</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>11167.51190932591</v>
       </c>
     </row>
     <row r="166">
@@ -2243,10 +2243,10 @@
         <v>452</v>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>5905.338808472769</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>16287.47953561589</v>
       </c>
     </row>
     <row r="167">
@@ -2254,10 +2254,10 @@
         <v>453</v>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>8110.341523189127</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>22369.08429305879</v>
       </c>
     </row>
     <row r="168">
@@ -2265,10 +2265,10 @@
         <v>454</v>
       </c>
       <c r="B168" t="n">
-        <v>4590.808653745414</v>
+        <v>9876.209333476605</v>
       </c>
       <c r="C168" t="n">
-        <v>12661.8818030433</v>
+        <v>27239.51370540582</v>
       </c>
     </row>
     <row r="169">
@@ -2276,10 +2276,10 @@
         <v>455</v>
       </c>
       <c r="B169" t="n">
-        <v>5388.367454674169</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C169" t="n">
-        <v>14861.6239465321</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="170">
@@ -2287,10 +2287,10 @@
         <v>456</v>
       </c>
       <c r="B170" t="n">
-        <v>5064.45420342849</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C170" t="n">
-        <v>13968.2407517509</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="171">
@@ -2298,10 +2298,10 @@
         <v>457</v>
       </c>
       <c r="B171" t="n">
-        <v>5315.822562258178</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C171" t="n">
-        <v>14661.53831402891</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="172">
@@ -2309,10 +2309,10 @@
         <v>458</v>
       </c>
       <c r="B172" t="n">
-        <v>5568.829288862742</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C172" t="n">
-        <v>15359.3546486366</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="173">
@@ -2320,10 +2320,10 @@
         <v>459</v>
       </c>
       <c r="B173" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C173" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="174">
@@ -2331,10 +2331,10 @@
         <v>460</v>
       </c>
       <c r="B174" t="n">
-        <v>14337.74605321794</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C174" t="n">
-        <v>39544.85136290408</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="175">
@@ -2342,10 +2342,10 @@
         <v>461</v>
       </c>
       <c r="B175" t="n">
-        <v>11845.17922815347</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C175" t="n">
-        <v>32670.11775809471</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="176">
@@ -2353,10 +2353,10 @@
         <v>462</v>
       </c>
       <c r="B176" t="n">
-        <v>12360.75770685234</v>
+        <v>9808.95195246167</v>
       </c>
       <c r="C176" t="n">
-        <v>34092.1316667232</v>
+        <v>27054.01152637281</v>
       </c>
     </row>
     <row r="177">
@@ -2518,10 +2518,10 @@
         <v>477</v>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>2289.434984626635</v>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>6314.476894488813</v>
       </c>
     </row>
     <row r="192">
@@ -2529,10 +2529,10 @@
         <v>478</v>
       </c>
       <c r="B192" t="n">
-        <v>4079.838630950432</v>
+        <v>3424.946608583287</v>
       </c>
       <c r="C192" t="n">
-        <v>11252.5784489926</v>
+        <v>9446.324691453912</v>
       </c>
     </row>
     <row r="193">
@@ -2540,10 +2540,10 @@
         <v>479</v>
       </c>
       <c r="B193" t="n">
-        <v>4635.133747201618</v>
+        <v>3836.83402470794</v>
       </c>
       <c r="C193" t="n">
-        <v>12784.1345773543</v>
+        <v>10582.34890254282</v>
       </c>
     </row>
     <row r="194">
@@ -2551,10 +2551,10 @@
         <v>480</v>
       </c>
       <c r="B194" t="n">
-        <v>5064.45420342849</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C194" t="n">
-        <v>13968.2407517509</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="195">
@@ -2562,10 +2562,10 @@
         <v>481</v>
       </c>
       <c r="B195" t="n">
-        <v>5315.822562258178</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C195" t="n">
-        <v>14661.53831402891</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="196">
@@ -2573,10 +2573,10 @@
         <v>482</v>
       </c>
       <c r="B196" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C196" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="197">
@@ -2584,10 +2584,10 @@
         <v>483</v>
       </c>
       <c r="B197" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C197" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="198">
@@ -2595,10 +2595,10 @@
         <v>484</v>
       </c>
       <c r="B198" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C198" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="199">
@@ -2606,10 +2606,10 @@
         <v>485</v>
       </c>
       <c r="B199" t="n">
-        <v>9084.662055747518</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C199" t="n">
-        <v>25056.35190798489</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="200">
@@ -2617,10 +2617,10 @@
         <v>486</v>
       </c>
       <c r="B200" t="n">
-        <v>9670.207921098548</v>
+        <v>9808.95195246167</v>
       </c>
       <c r="C200" t="n">
-        <v>26671.34244593438</v>
+        <v>27054.01152637281</v>
       </c>
     </row>
     <row r="201">
@@ -2628,10 +2628,10 @@
         <v>487</v>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>9322.006597581485</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>25710.97046474991</v>
       </c>
     </row>
     <row r="202">
@@ -2771,10 +2771,10 @@
         <v>500</v>
       </c>
       <c r="B214" t="n">
-        <v>0</v>
+        <v>2927.085533910706</v>
       </c>
       <c r="C214" t="n">
-        <v>0</v>
+        <v>8073.177048565914</v>
       </c>
     </row>
     <row r="215">
@@ -2782,10 +2782,10 @@
         <v>501</v>
       </c>
       <c r="B215" t="n">
-        <v>3052.562834927492</v>
+        <v>5120.850451717535</v>
       </c>
       <c r="C215" t="n">
-        <v>8419.255239636506</v>
+        <v>14123.78690577942</v>
       </c>
     </row>
     <row r="216">
@@ -2793,10 +2793,10 @@
         <v>502</v>
       </c>
       <c r="B216" t="n">
-        <v>4079.838630950432</v>
+        <v>6401.987222217381</v>
       </c>
       <c r="C216" t="n">
-        <v>11252.5784489926</v>
+        <v>17657.28254567442</v>
       </c>
     </row>
     <row r="217">
@@ -2804,10 +2804,10 @@
         <v>503</v>
       </c>
       <c r="B217" t="n">
-        <v>4635.133747201618</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C217" t="n">
-        <v>12784.1345773543</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="218">
@@ -2815,10 +2815,10 @@
         <v>504</v>
       </c>
       <c r="B218" t="n">
-        <v>5064.45420342849</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C218" t="n">
-        <v>13968.2407517509</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="219">
@@ -2826,10 +2826,10 @@
         <v>505</v>
       </c>
       <c r="B219" t="n">
-        <v>5315.822562258178</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C219" t="n">
-        <v>14661.53831402891</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="220">
@@ -2837,10 +2837,10 @@
         <v>506</v>
       </c>
       <c r="B220" t="n">
-        <v>8143.049025518385</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C220" t="n">
-        <v>22459.2946589881</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="221">
@@ -2848,10 +2848,10 @@
         <v>507</v>
       </c>
       <c r="B221" t="n">
-        <v>8648.041618868174</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C221" t="n">
-        <v>23852.1117007506</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="222">
@@ -2859,10 +2859,10 @@
         <v>508</v>
       </c>
       <c r="B222" t="n">
-        <v>8725.29299097402</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C222" t="n">
-        <v>24065.1782466475</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="223">
@@ -2870,10 +2870,10 @@
         <v>509</v>
       </c>
       <c r="B223" t="n">
-        <v>9084.662055747518</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C223" t="n">
-        <v>25056.35190798489</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="224">
@@ -2881,10 +2881,10 @@
         <v>510</v>
       </c>
       <c r="B224" t="n">
-        <v>7258.852022223756</v>
+        <v>9808.95195246167</v>
       </c>
       <c r="C224" t="n">
-        <v>20020.59620938321</v>
+        <v>27054.01152637281</v>
       </c>
     </row>
     <row r="225">
@@ -3046,10 +3046,10 @@
         <v>525</v>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C239" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="240">
@@ -3057,10 +3057,10 @@
         <v>526</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C240" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="241">
@@ -3068,10 +3068,10 @@
         <v>527</v>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C241" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="242">
@@ -3079,10 +3079,10 @@
         <v>528</v>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>10576.92396349697</v>
       </c>
       <c r="C242" t="n">
-        <v>0</v>
+        <v>29172.15052217722</v>
       </c>
     </row>
     <row r="243">
@@ -3090,10 +3090,10 @@
         <v>529</v>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>9010.631191404405</v>
       </c>
       <c r="C243" t="n">
-        <v>0</v>
+        <v>24852.16782522534</v>
       </c>
     </row>
     <row r="244">
@@ -3101,10 +3101,10 @@
         <v>530</v>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C244" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="245">
@@ -3112,10 +3112,10 @@
         <v>531</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C245" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="246">
@@ -3123,10 +3123,10 @@
         <v>532</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C246" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="247">
@@ -3134,10 +3134,10 @@
         <v>533</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C247" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="248">
@@ -3145,10 +3145,10 @@
         <v>534</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C248" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="249">
@@ -3189,10 +3189,10 @@
         <v>538</v>
       </c>
       <c r="B252" t="n">
-        <v>0</v>
+        <v>2793.359913950261</v>
       </c>
       <c r="C252" t="n">
-        <v>0</v>
+        <v>7704.34921850673</v>
       </c>
     </row>
     <row r="253">
@@ -3211,10 +3211,10 @@
         <v>540</v>
       </c>
       <c r="B254" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C254" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="255">
@@ -3222,10 +3222,10 @@
         <v>541</v>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C255" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="256">
@@ -3233,10 +3233,10 @@
         <v>542</v>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C256" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="257">
@@ -3244,10 +3244,10 @@
         <v>543</v>
       </c>
       <c r="B257" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C257" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="258">
@@ -3255,10 +3255,10 @@
         <v>544</v>
       </c>
       <c r="B258" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C258" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="259">
@@ -3266,10 +3266,10 @@
         <v>545</v>
       </c>
       <c r="B259" t="n">
-        <v>0</v>
+        <v>3903.516373553333</v>
       </c>
       <c r="C259" t="n">
-        <v>0</v>
+        <v>10766.26508879921</v>
       </c>
     </row>
     <row r="260">
@@ -3277,10 +3277,10 @@
         <v>546</v>
       </c>
       <c r="B260" t="n">
-        <v>0</v>
+        <v>5380.7035609299</v>
       </c>
       <c r="C260" t="n">
-        <v>0</v>
+        <v>14840.48620717939</v>
       </c>
     </row>
     <row r="261">
@@ -3288,10 +3288,10 @@
         <v>547</v>
       </c>
       <c r="B261" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C261" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="262">
@@ -3299,10 +3299,10 @@
         <v>548</v>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C262" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="263">
@@ -3310,10 +3310,10 @@
         <v>549</v>
       </c>
       <c r="B263" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C263" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="264">
@@ -3321,10 +3321,10 @@
         <v>550</v>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C264" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="265">
@@ -3332,10 +3332,10 @@
         <v>551</v>
       </c>
       <c r="B265" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C265" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="266">
@@ -3343,10 +3343,10 @@
         <v>552</v>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C266" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="267">
@@ -3354,10 +3354,10 @@
         <v>553</v>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C267" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="268">
@@ -3365,10 +3365,10 @@
         <v>554</v>
       </c>
       <c r="B268" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C268" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="269">
@@ -3376,10 +3376,10 @@
         <v>555</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C269" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="270">
@@ -3387,10 +3387,10 @@
         <v>556</v>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C270" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="271">
@@ -3398,10 +3398,10 @@
         <v>557</v>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C271" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="272">
@@ -3409,10 +3409,10 @@
         <v>558</v>
       </c>
       <c r="B272" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C272" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="273">
@@ -3420,10 +3420,10 @@
         <v>559</v>
       </c>
       <c r="B273" t="n">
-        <v>0</v>
+        <v>6858.099304179449</v>
       </c>
       <c r="C273" t="n">
-        <v>0</v>
+        <v>18915.28254226151</v>
       </c>
     </row>
     <row r="274">
@@ -3431,10 +3431,10 @@
         <v>560</v>
       </c>
       <c r="B274" t="n">
-        <v>0</v>
+        <v>5013.591876888828</v>
       </c>
       <c r="C274" t="n">
-        <v>0</v>
+        <v>13827.95767409581</v>
       </c>
     </row>
     <row r="275">
@@ -3442,10 +3442,10 @@
         <v>561</v>
       </c>
       <c r="B275" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C275" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="276">
@@ -3453,10 +3453,10 @@
         <v>562</v>
       </c>
       <c r="B276" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C276" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="277">
@@ -3464,10 +3464,10 @@
         <v>563</v>
       </c>
       <c r="B277" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C277" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="278">
@@ -3475,10 +3475,10 @@
         <v>564</v>
       </c>
       <c r="B278" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C278" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="279">
@@ -3486,10 +3486,10 @@
         <v>565</v>
       </c>
       <c r="B279" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C279" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="280">
@@ -3497,10 +3497,10 @@
         <v>566</v>
       </c>
       <c r="B280" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C280" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="281">
@@ -3508,10 +3508,10 @@
         <v>567</v>
       </c>
       <c r="B281" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C281" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="282">
@@ -3519,10 +3519,10 @@
         <v>568</v>
       </c>
       <c r="B282" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C282" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="283">
@@ -3530,10 +3530,10 @@
         <v>569</v>
       </c>
       <c r="B283" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C283" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="284">
@@ -3541,10 +3541,10 @@
         <v>570</v>
       </c>
       <c r="B284" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C284" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="285">
@@ -3552,10 +3552,10 @@
         <v>571</v>
       </c>
       <c r="B285" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C285" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="286">
@@ -3563,10 +3563,10 @@
         <v>572</v>
       </c>
       <c r="B286" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C286" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="287">
@@ -3574,10 +3574,10 @@
         <v>573</v>
       </c>
       <c r="B287" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C287" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="288">
@@ -3585,10 +3585,10 @@
         <v>574</v>
       </c>
       <c r="B288" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C288" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="289">
@@ -3596,10 +3596,10 @@
         <v>575</v>
       </c>
       <c r="B289" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C289" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="290">
@@ -3607,10 +3607,10 @@
         <v>576</v>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C290" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="291">
@@ -3618,10 +3618,10 @@
         <v>577</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C291" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="292">
@@ -3629,10 +3629,10 @@
         <v>578</v>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C292" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="293">
@@ -3640,10 +3640,10 @@
         <v>579</v>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C293" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="294">
@@ -3651,10 +3651,10 @@
         <v>580</v>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C294" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="295">
@@ -3662,10 +3662,10 @@
         <v>581</v>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C295" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="296">
@@ -3673,10 +3673,10 @@
         <v>582</v>
       </c>
       <c r="B296" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C296" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="297">
@@ -3684,10 +3684,10 @@
         <v>583</v>
       </c>
       <c r="B297" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C297" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="298">
@@ -3695,10 +3695,10 @@
         <v>584</v>
       </c>
       <c r="B298" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C298" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="299">
@@ -3706,10 +3706,10 @@
         <v>585</v>
       </c>
       <c r="B299" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C299" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="300">
@@ -3717,10 +3717,10 @@
         <v>586</v>
       </c>
       <c r="B300" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C300" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="301">
@@ -3728,10 +3728,10 @@
         <v>587</v>
       </c>
       <c r="B301" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="302">
@@ -3739,10 +3739,10 @@
         <v>588</v>
       </c>
       <c r="B302" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C302" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="303">
@@ -3750,10 +3750,10 @@
         <v>589</v>
       </c>
       <c r="B303" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C303" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="304">
@@ -3761,10 +3761,10 @@
         <v>590</v>
       </c>
       <c r="B304" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C304" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="305">
@@ -3772,10 +3772,10 @@
         <v>591</v>
       </c>
       <c r="B305" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C305" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="306">
@@ -3783,10 +3783,10 @@
         <v>592</v>
       </c>
       <c r="B306" t="n">
-        <v>0</v>
+        <v>5659.777218754313</v>
       </c>
       <c r="C306" t="n">
-        <v>0</v>
+        <v>15610.19758838296</v>
       </c>
     </row>
     <row r="307">
@@ -3838,10 +3838,10 @@
         <v>597</v>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C311" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="312">
@@ -3849,10 +3849,10 @@
         <v>598</v>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C312" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="313">
@@ -3860,10 +3860,10 @@
         <v>599</v>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C313" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="314">
@@ -3871,10 +3871,10 @@
         <v>600</v>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="315">
@@ -3882,10 +3882,10 @@
         <v>601</v>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C315" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="316">
@@ -3893,10 +3893,10 @@
         <v>602</v>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C316" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="317">
@@ -3904,10 +3904,10 @@
         <v>603</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C317" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="318">
@@ -3915,10 +3915,10 @@
         <v>604</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="319">
@@ -3926,10 +3926,10 @@
         <v>605</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C319" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="320">
@@ -3937,10 +3937,10 @@
         <v>606</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C320" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="321">
@@ -3948,10 +3948,10 @@
         <v>607</v>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C321" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="322">
@@ -3959,10 +3959,10 @@
         <v>608</v>
       </c>
       <c r="B322" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C322" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="323">
@@ -3970,10 +3970,10 @@
         <v>609</v>
       </c>
       <c r="B323" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C323" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="324">
@@ -3981,10 +3981,10 @@
         <v>610</v>
       </c>
       <c r="B324" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C324" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="325">
@@ -3992,10 +3992,10 @@
         <v>611</v>
       </c>
       <c r="B325" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C325" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="326">
@@ -4003,10 +4003,10 @@
         <v>612</v>
       </c>
       <c r="B326" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C326" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="327">
@@ -4014,10 +4014,10 @@
         <v>613</v>
       </c>
       <c r="B327" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C327" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="328">
@@ -4025,10 +4025,10 @@
         <v>614</v>
       </c>
       <c r="B328" t="n">
-        <v>16199.51277945756</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C328" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="329">
@@ -4036,10 +4036,10 @@
         <v>615</v>
       </c>
       <c r="B329" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C329" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="330">
@@ -4047,10 +4047,10 @@
         <v>616</v>
       </c>
       <c r="B330" t="n">
-        <v>0</v>
+        <v>7526.226465563411</v>
       </c>
       <c r="C330" t="n">
-        <v>0</v>
+        <v>20758.04005731165</v>
       </c>
     </row>
     <row r="331">
@@ -4058,10 +4058,10 @@
         <v>617</v>
       </c>
       <c r="B331" t="n">
-        <v>0</v>
+        <v>8262.238613153166</v>
       </c>
       <c r="C331" t="n">
-        <v>0</v>
+        <v>22788.03074550607</v>
       </c>
     </row>
     <row r="332">
@@ -4069,10 +4069,10 @@
         <v>618</v>
       </c>
       <c r="B332" t="n">
-        <v>0</v>
+        <v>7594.491250292505</v>
       </c>
       <c r="C332" t="n">
-        <v>0</v>
+        <v>20946.32075048426</v>
       </c>
     </row>
     <row r="333">
@@ -4080,10 +4080,10 @@
         <v>619</v>
       </c>
       <c r="B333" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C333" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="334">
@@ -4091,10 +4091,10 @@
         <v>620</v>
       </c>
       <c r="B334" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C334" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="335">
@@ -4102,10 +4102,10 @@
         <v>621</v>
       </c>
       <c r="B335" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C335" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="336">
@@ -4113,10 +4113,10 @@
         <v>622</v>
       </c>
       <c r="B336" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C336" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="337">
@@ -4124,10 +4124,10 @@
         <v>623</v>
       </c>
       <c r="B337" t="n">
-        <v>0</v>
+        <v>10651.48526512742</v>
       </c>
       <c r="C337" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
   </sheetData>
@@ -4199,10 +4199,10 @@
         <v>5163</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2687.381128205926</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>9660.533182527583</v>
       </c>
     </row>
     <row r="6">
@@ -4254,7 +4254,7 @@
         <v>5168</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>690.3397879591588</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         <v>5169</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>716.9192426275441</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>5170</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1088.230744064651</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>5171</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1844.754962767621</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>5172</v>
       </c>
       <c r="B14" t="n">
-        <v>8305.802952330294</v>
+        <v>1490.176574563599</v>
       </c>
       <c r="C14" t="n">
-        <v>29857.50111376608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4309,7 +4309,7 @@
         <v>5173</v>
       </c>
       <c r="B15" t="n">
-        <v>1327.989828441336</v>
+        <v>1497.163797044169</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>5174</v>
       </c>
       <c r="B16" t="n">
-        <v>2000.852027642381</v>
+        <v>1879.512102603256</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
         <v>5175</v>
       </c>
       <c r="B17" t="n">
-        <v>1988.594826220712</v>
+        <v>1494.335245363373</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>5176</v>
       </c>
       <c r="B18" t="n">
-        <v>3261.799678452492</v>
+        <v>1468.315675708288</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -4353,7 +4353,7 @@
         <v>5177</v>
       </c>
       <c r="B19" t="n">
-        <v>2324.552178485387</v>
+        <v>957.805625470408</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>5178</v>
       </c>
       <c r="B20" t="n">
-        <v>1517.479418776307</v>
+        <v>572.270525798585</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -4375,10 +4375,10 @@
         <v>5179</v>
       </c>
       <c r="B21" t="n">
-        <v>847.3816435518777</v>
+        <v>2269.559322750585</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>8158.557384000055</v>
       </c>
     </row>
     <row r="22">
@@ -4386,10 +4386,10 @@
         <v>5180</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>2347.394234261428</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>8438.356455861358</v>
       </c>
     </row>
     <row r="23">
@@ -4397,10 +4397,10 @@
         <v>5181</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2158.475785200996</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>7759.236949221693</v>
       </c>
     </row>
     <row r="24">
@@ -4408,10 +4408,10 @@
         <v>5182</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1875.771080859399</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>6742.976862967427</v>
       </c>
     </row>
     <row r="25">
@@ -4419,10 +4419,10 @@
         <v>5183</v>
       </c>
       <c r="B25" t="n">
-        <v>1918.217499919695</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C25" t="n">
-        <v>6895.56223149132</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="26">
@@ -4430,10 +4430,10 @@
         <v>5184</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>8172.358333547438</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>29377.79760083632</v>
       </c>
     </row>
     <row r="27">
@@ -4441,10 +4441,10 @@
         <v>5185</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="28">
@@ -4452,10 +4452,10 @@
         <v>5186</v>
       </c>
       <c r="B28" t="n">
-        <v>11945.42514073174</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C28" t="n">
-        <v>42941.12760569908</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="29">
@@ -4463,10 +4463,10 @@
         <v>5187</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="30">
@@ -4474,10 +4474,10 @@
         <v>5188</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="31">
@@ -4485,10 +4485,10 @@
         <v>5189</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>5893.627185623548</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>21186.26955982707</v>
       </c>
     </row>
     <row r="32">
@@ -4518,10 +4518,10 @@
         <v>5192</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>3620.761535666179</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>13015.82667013592</v>
       </c>
     </row>
     <row r="35">
@@ -4529,10 +4529,10 @@
         <v>5193</v>
       </c>
       <c r="B35" t="n">
-        <v>1916.339354268994</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="36">
@@ -4540,10 +4540,10 @@
         <v>5194</v>
       </c>
       <c r="B36" t="n">
-        <v>3227.117824545722</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="37">
@@ -4551,10 +4551,10 @@
         <v>5195</v>
       </c>
       <c r="B37" t="n">
-        <v>3929.157135457161</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="38">
@@ -4562,10 +4562,10 @@
         <v>5196</v>
       </c>
       <c r="B38" t="n">
-        <v>3964.028805785842</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="39">
@@ -4573,10 +4573,10 @@
         <v>5197</v>
       </c>
       <c r="B39" t="n">
-        <v>3983.964669036627</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="40">
@@ -4584,10 +4584,10 @@
         <v>5198</v>
       </c>
       <c r="B40" t="n">
-        <v>4001.704055284764</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="41">
@@ -4595,10 +4595,10 @@
         <v>5199</v>
       </c>
       <c r="B41" t="n">
-        <v>3314.316683222221</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="42">
@@ -4606,10 +4606,10 @@
         <v>5200</v>
       </c>
       <c r="B42" t="n">
-        <v>4566.527817300436</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="43">
@@ -4617,10 +4617,10 @@
         <v>5201</v>
       </c>
       <c r="B43" t="n">
-        <v>3486.833551854741</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="44">
@@ -4628,10 +4628,10 @@
         <v>5202</v>
       </c>
       <c r="B44" t="n">
-        <v>2023.307809023724</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="45">
@@ -4639,10 +4639,10 @@
         <v>5203</v>
       </c>
       <c r="B45" t="n">
-        <v>1271.067649040437</v>
+        <v>2269.559322750585</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>8158.557384000055</v>
       </c>
     </row>
     <row r="46">
@@ -4683,10 +4683,10 @@
         <v>5207</v>
       </c>
       <c r="B49" t="n">
-        <v>1918.217499919695</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>6895.56223149132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4705,10 +4705,10 @@
         <v>5209</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="52">
@@ -4716,10 +4716,10 @@
         <v>5210</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>8172.358333547444</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="53">
@@ -4727,10 +4727,10 @@
         <v>5211</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="54">
@@ -4738,10 +4738,10 @@
         <v>5212</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="55">
@@ -4793,10 +4793,10 @@
         <v>5217</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="60">
@@ -4804,10 +4804,10 @@
         <v>5218</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="61">
@@ -4815,10 +4815,10 @@
         <v>5219</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="62">
@@ -4826,10 +4826,10 @@
         <v>5220</v>
       </c>
       <c r="B62" t="n">
-        <v>1376.52520246953</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="63">
@@ -4837,10 +4837,10 @@
         <v>5221</v>
       </c>
       <c r="B63" t="n">
-        <v>1991.984742662004</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="64">
@@ -4848,10 +4848,10 @@
         <v>5222</v>
       </c>
       <c r="B64" t="n">
-        <v>2667.799804557779</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="65">
@@ -4859,10 +4859,10 @@
         <v>5223</v>
       </c>
       <c r="B65" t="n">
-        <v>2054.426363079256</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="66">
@@ -4870,10 +4870,10 @@
         <v>5224</v>
       </c>
       <c r="B66" t="n">
-        <v>2609.440893155184</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="67">
@@ -4881,10 +4881,10 @@
         <v>5225</v>
       </c>
       <c r="B67" t="n">
-        <v>1743.416775927372</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="68">
@@ -4892,10 +4892,10 @@
         <v>5226</v>
       </c>
       <c r="B68" t="n">
-        <v>1011.655844816268</v>
+        <v>2114.307417088083</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>7600.46155957023</v>
       </c>
     </row>
     <row r="69">
@@ -5002,10 +5002,10 @@
         <v>5236</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>3407.121799670613</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>12247.83967453272</v>
       </c>
     </row>
     <row r="79">
@@ -5035,10 +5035,10 @@
         <v>5239</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>2631.044817889538</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>9458.016766273679</v>
       </c>
     </row>
     <row r="82">
@@ -5057,7 +5057,7 @@
         <v>5241</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>1075.375719707645</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -5068,7 +5068,7 @@
         <v>5242</v>
       </c>
       <c r="B84" t="n">
-        <v>1936.272246970959</v>
+        <v>1474.736780830645</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>5243</v>
       </c>
       <c r="B85" t="n">
-        <v>3274.289585735333</v>
+        <v>1475.804549839725</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>5244</v>
       </c>
       <c r="B86" t="n">
-        <v>3964.028805785842</v>
+        <v>1490.176574563599</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>5245</v>
       </c>
       <c r="B87" t="n">
-        <v>4647.959583257298</v>
+        <v>1497.163797044169</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         <v>5246</v>
       </c>
       <c r="B88" t="n">
-        <v>4732.546514427365</v>
+        <v>1127.709109819074</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>5247</v>
       </c>
       <c r="B89" t="n">
-        <v>5302.906693155553</v>
+        <v>1159.230484233877</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>5248</v>
       </c>
       <c r="B90" t="n">
-        <v>5218.886602597744</v>
+        <v>1835.390835249886</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>5249</v>
       </c>
       <c r="B91" t="n">
-        <v>4067.968954412758</v>
+        <v>1277.071086865342</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
         <v>5250</v>
       </c>
       <c r="B92" t="n">
-        <v>3034.963653839994</v>
+        <v>572.270525798585</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>5251</v>
       </c>
       <c r="B93" t="n">
-        <v>2118.444476304936</v>
+        <v>441.9208053756686</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -5178,10 +5178,10 @@
         <v>5252</v>
       </c>
       <c r="B94" t="n">
-        <v>1221.663651469608</v>
+        <v>2347.394234261428</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>8438.356455861358</v>
       </c>
     </row>
     <row r="95">
@@ -5189,7 +5189,7 @@
         <v>5253</v>
       </c>
       <c r="B95" t="n">
-        <v>710.6220486422399</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -5200,10 +5200,10 @@
         <v>5254</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>1875.771080859399</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>6742.976862967427</v>
       </c>
     </row>
     <row r="97">
@@ -5211,10 +5211,10 @@
         <v>5255</v>
       </c>
       <c r="B97" t="n">
-        <v>1918.217499919695</v>
+        <v>1419.616534635928</v>
       </c>
       <c r="C97" t="n">
-        <v>6895.56223149132</v>
+        <v>5103.203447912404</v>
       </c>
     </row>
     <row r="98">
@@ -5222,10 +5222,10 @@
         <v>5256</v>
       </c>
       <c r="B98" t="n">
-        <v>1864.362855986489</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>6701.966849991688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5233,10 +5233,10 @@
         <v>5257</v>
       </c>
       <c r="B99" t="n">
-        <v>1864.3628559865</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>6701.966849991724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5244,10 +5244,10 @@
         <v>5258</v>
       </c>
       <c r="B100" t="n">
-        <v>1864.362855986517</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>6701.966849991787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5255,10 +5255,10 @@
         <v>5259</v>
       </c>
       <c r="B101" t="n">
-        <v>1864.362855986501</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>6701.96684999173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -5277,10 +5277,10 @@
         <v>5261</v>
       </c>
       <c r="B103" t="n">
-        <v>1864.3628559865</v>
+        <v>1264.498084981877</v>
       </c>
       <c r="C103" t="n">
-        <v>6701.966849991724</v>
+        <v>4545.587367938811</v>
       </c>
     </row>
     <row r="104">
@@ -5288,10 +5288,10 @@
         <v>5262</v>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>2071.806406992595</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>7447.679948503212</v>
       </c>
     </row>
     <row r="105">
@@ -5299,7 +5299,7 @@
         <v>5263</v>
       </c>
       <c r="B105" t="n">
-        <v>1188.29535412091</v>
+        <v>656.9809114963647</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>5264</v>
       </c>
       <c r="B106" t="n">
-        <v>2475.334940521342</v>
+        <v>690.3397879591588</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -5321,7 +5321,7 @@
         <v>5265</v>
       </c>
       <c r="B107" t="n">
-        <v>3832.674827929175</v>
+        <v>1075.375719707645</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
         <v>5266</v>
       </c>
       <c r="B108" t="n">
-        <v>4558.632946774895</v>
+        <v>1450.970643549065</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>5267</v>
       </c>
       <c r="B109" t="n">
-        <v>5893.755904013819</v>
+        <v>1844.754962767621</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
         <v>5268</v>
       </c>
       <c r="B110" t="n">
-        <v>6606.714988202591</v>
+        <v>1862.716685368439</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>5269</v>
       </c>
       <c r="B111" t="n">
-        <v>7303.93442385259</v>
+        <v>1871.455470837247</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>5270</v>
       </c>
       <c r="B112" t="n">
-        <v>7336.46514994151</v>
+        <v>1879.512102603256</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -5387,7 +5387,7 @@
         <v>5271</v>
       </c>
       <c r="B113" t="n">
-        <v>7357.323423660053</v>
+        <v>1867.915434044036</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
         <v>5272</v>
       </c>
       <c r="B114" t="n">
-        <v>7828.327495752929</v>
+        <v>1468.315675708288</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
         <v>5273</v>
       </c>
       <c r="B115" t="n">
-        <v>5811.404995489645</v>
+        <v>1277.071086865342</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>5274</v>
       </c>
       <c r="B116" t="n">
-        <v>4552.443072616299</v>
+        <v>804.9293551367629</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -5431,10 +5431,10 @@
         <v>5275</v>
       </c>
       <c r="B117" t="n">
-        <v>2965.826119856812</v>
+        <v>2269.559322750585</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>8158.557384000055</v>
       </c>
     </row>
     <row r="118">
@@ -5442,7 +5442,7 @@
         <v>5276</v>
       </c>
       <c r="B118" t="n">
-        <v>2348.451367717662</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
         <v>5277</v>
       </c>
       <c r="B119" t="n">
-        <v>1776.547663254889</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -5464,7 +5464,7 @@
         <v>5278</v>
       </c>
       <c r="B120" t="n">
-        <v>1017.839082958451</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>5279</v>
       </c>
       <c r="B121" t="n">
-        <v>915.7336334687392</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
         <v>5280</v>
       </c>
       <c r="B122" t="n">
-        <v>531.9509231328631</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>5285</v>
       </c>
       <c r="B127" t="n">
-        <v>1864.362855986478</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>6701.966849991648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -5552,10 +5552,10 @@
         <v>5286</v>
       </c>
       <c r="B128" t="n">
-        <v>1864.3628559865</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>6701.966849991724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5563,10 +5563,10 @@
         <v>5287</v>
       </c>
       <c r="B129" t="n">
-        <v>1535.001450798823</v>
+        <v>1932.317511575456</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>6946.248614991171</v>
       </c>
     </row>
     <row r="130">
@@ -5574,10 +5574,10 @@
         <v>5288</v>
       </c>
       <c r="B130" t="n">
-        <v>2672.182900350447</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="131">
@@ -5585,7 +5585,7 @@
         <v>5289</v>
       </c>
       <c r="B131" t="n">
-        <v>3876.708943975496</v>
+        <v>960.499716303184</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
         <v>5290</v>
       </c>
       <c r="B132" t="n">
-        <v>5047.89724987357</v>
+        <v>1298.404483621192</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>5291</v>
       </c>
       <c r="B133" t="n">
-        <v>6283.156280782693</v>
+        <v>1655.295631556161</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>5292</v>
       </c>
       <c r="B134" t="n">
-        <v>6932.897048177049</v>
+        <v>1674.616576256903</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -5629,7 +5629,7 @@
         <v>5293</v>
       </c>
       <c r="B135" t="n">
-        <v>7552.574985514701</v>
+        <v>1683.387241135303</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>5294</v>
       </c>
       <c r="B136" t="n">
-        <v>8169.584221112982</v>
+        <v>1352.735777506381</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>5295</v>
       </c>
       <c r="B137" t="n">
-        <v>8133.212161511111</v>
+        <v>1009.921942040277</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
         <v>5296</v>
       </c>
       <c r="B138" t="n">
-        <v>8027.969999425504</v>
+        <v>995.2646642949775</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
         <v>5297</v>
       </c>
       <c r="B139" t="n">
-        <v>6666.308259455172</v>
+        <v>619.7128942235997</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -5684,10 +5684,10 @@
         <v>5298</v>
       </c>
       <c r="B140" t="n">
-        <v>4926.0660631894</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="141">
@@ -5695,7 +5695,7 @@
         <v>5299</v>
       </c>
       <c r="B141" t="n">
-        <v>3450.709893829663</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
         <v>5300</v>
       </c>
       <c r="B142" t="n">
-        <v>2910.390652124738</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -5717,10 +5717,10 @@
         <v>5301</v>
       </c>
       <c r="B143" t="n">
-        <v>2390.762180999916</v>
+        <v>2328.607533719675</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>8370.822475634677</v>
       </c>
     </row>
     <row r="144">
@@ -5728,7 +5728,7 @@
         <v>5302</v>
       </c>
       <c r="B144" t="n">
-        <v>1649.9029689193</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>5303</v>
       </c>
       <c r="B145" t="n">
-        <v>1498.858027043226</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -5750,10 +5750,10 @@
         <v>5304</v>
       </c>
       <c r="B146" t="n">
-        <v>1059.263761519767</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="147">
@@ -5761,10 +5761,10 @@
         <v>5305</v>
       </c>
       <c r="B147" t="n">
-        <v>731.8419023983838</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="148">
@@ -5772,10 +5772,10 @@
         <v>5306</v>
       </c>
       <c r="B148" t="n">
-        <v>504.1155444438644</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="149">
@@ -5783,10 +5783,10 @@
         <v>5307</v>
       </c>
       <c r="B149" t="n">
-        <v>12429.08570657677</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C149" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="150">
@@ -5794,10 +5794,10 @@
         <v>5308</v>
       </c>
       <c r="B150" t="n">
-        <v>12429.08570657677</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C150" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="151">
@@ -5805,10 +5805,10 @@
         <v>5309</v>
       </c>
       <c r="B151" t="n">
-        <v>12429.08570657677</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C151" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="152">
@@ -5816,10 +5816,10 @@
         <v>5310</v>
       </c>
       <c r="B152" t="n">
-        <v>687.0446550929947</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="153">
@@ -5827,10 +5827,10 @@
         <v>5311</v>
       </c>
       <c r="B153" t="n">
-        <v>1134.99433511229</v>
+        <v>1449.576525810038</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>5210.902905145304</v>
       </c>
     </row>
     <row r="154">
@@ -5838,7 +5838,7 @@
         <v>5312</v>
       </c>
       <c r="B154" t="n">
-        <v>1972.246304425233</v>
+        <v>642.022129331799</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>5313</v>
       </c>
       <c r="B155" t="n">
-        <v>2458.496529245611</v>
+        <v>692.7235785653447</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>5314</v>
       </c>
       <c r="B156" t="n">
-        <v>3331.587411231836</v>
+        <v>912.7042013393901</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
         <v>5315</v>
       </c>
       <c r="B157" t="n">
-        <v>3832.384905809829</v>
+        <v>1169.722955275643</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -5882,7 +5882,7 @@
         <v>5316</v>
       </c>
       <c r="B158" t="n">
-        <v>4330.922875886352</v>
+        <v>1191.452244464731</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -5893,7 +5893,7 @@
         <v>5317</v>
       </c>
       <c r="B159" t="n">
-        <v>4796.941252195735</v>
+        <v>1439.334293949124</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>5318</v>
       </c>
       <c r="B160" t="n">
-        <v>4794.655036821998</v>
+        <v>1197.411560566057</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
         <v>5319</v>
       </c>
       <c r="B161" t="n">
-        <v>4568.257044403148</v>
+        <v>1127.884208519988</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>5320</v>
       </c>
       <c r="B162" t="n">
-        <v>3992.248631752863</v>
+        <v>1050.699455014127</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>5321</v>
       </c>
       <c r="B163" t="n">
-        <v>3331.06299077794</v>
+        <v>781.656367405008</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>5322</v>
       </c>
       <c r="B164" t="n">
-        <v>2926.876029629524</v>
+        <v>578.857971071766</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -5959,10 +5959,10 @@
         <v>5323</v>
       </c>
       <c r="B165" t="n">
-        <v>2452.169070888459</v>
+        <v>2059.940996370286</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>7405.02645516799</v>
       </c>
     </row>
     <row r="166">
@@ -5970,10 +5970,10 @@
         <v>5324</v>
       </c>
       <c r="B166" t="n">
-        <v>1645.560970092511</v>
+        <v>1943.017407301031</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>6984.712343347969</v>
       </c>
     </row>
     <row r="167">
@@ -5981,10 +5981,10 @@
         <v>5325</v>
       </c>
       <c r="B167" t="n">
-        <v>1223.241893982893</v>
+        <v>1891.679605926428</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>6800.164447073782</v>
       </c>
     </row>
     <row r="168">
@@ -5992,7 +5992,7 @@
         <v>5326</v>
       </c>
       <c r="B168" t="n">
-        <v>1213.878510018219</v>
+        <v>0</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>5327</v>
       </c>
       <c r="B169" t="n">
-        <v>863.2746313368747</v>
+        <v>0</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         <v>5328</v>
       </c>
       <c r="B170" t="n">
-        <v>1864.362855986489</v>
+        <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>6701.966849991688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -6025,10 +6025,10 @@
         <v>5329</v>
       </c>
       <c r="B171" t="n">
-        <v>1864.3628559865</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C171" t="n">
-        <v>6701.966849991724</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="172">
@@ -6036,10 +6036,10 @@
         <v>5330</v>
       </c>
       <c r="B172" t="n">
-        <v>1864.362855986504</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C172" t="n">
-        <v>6701.966849991739</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="173">
@@ -6047,10 +6047,10 @@
         <v>5331</v>
       </c>
       <c r="B173" t="n">
-        <v>9563.101821935843</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C173" t="n">
-        <v>34377.20891505124</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="174">
@@ -6058,10 +6058,10 @@
         <v>5332</v>
       </c>
       <c r="B174" t="n">
-        <v>1864.362855986481</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C174" t="n">
-        <v>6701.966849991659</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="175">
@@ -6069,10 +6069,10 @@
         <v>5333</v>
       </c>
       <c r="B175" t="n">
-        <v>1864.3628559865</v>
+        <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>6701.966849991724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -6091,10 +6091,10 @@
         <v>5335</v>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>2631.044817889538</v>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>9458.016766273679</v>
       </c>
     </row>
     <row r="178">
@@ -6102,7 +6102,7 @@
         <v>5336</v>
       </c>
       <c r="B178" t="n">
-        <v>1856.503613534696</v>
+        <v>1380.676677790173</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>5337</v>
       </c>
       <c r="B179" t="n">
-        <v>2555.113652987385</v>
+        <v>1792.292447037863</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
         <v>5338</v>
       </c>
       <c r="B180" t="n">
-        <v>3872.550245907864</v>
+        <v>2539.201387613717</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>5339</v>
       </c>
       <c r="B181" t="n">
-        <v>4584.010236316848</v>
+        <v>2951.606201551307</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>5340</v>
       </c>
       <c r="B182" t="n">
-        <v>5946.028759816625</v>
+        <v>2980.349704097881</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -6157,7 +6157,7 @@
         <v>5341</v>
       </c>
       <c r="B183" t="n">
-        <v>6639.949142206677</v>
+        <v>2994.330492216481</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
         <v>5342</v>
       </c>
       <c r="B184" t="n">
-        <v>6669.522189313492</v>
+        <v>3044.567999579099</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>5343</v>
       </c>
       <c r="B185" t="n">
-        <v>6694.464903302984</v>
+        <v>3362.241985022975</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -6190,7 +6190,7 @@
         <v>5344</v>
       </c>
       <c r="B186" t="n">
-        <v>6523.590660008794</v>
+        <v>2976.238864391453</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>5345</v>
       </c>
       <c r="B187" t="n">
-        <v>5230.250327782114</v>
+        <v>2554.142173730684</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>5346</v>
       </c>
       <c r="B188" t="n">
-        <v>4046.609866081502</v>
+        <v>1609.861608401671</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>5347</v>
       </c>
       <c r="B189" t="n">
-        <v>2596.349449865642</v>
+        <v>1104.797666246954</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>5348</v>
       </c>
       <c r="B190" t="n">
-        <v>1957.039907465989</v>
+        <v>839.6310055495454</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>5349</v>
       </c>
       <c r="B191" t="n">
-        <v>1459.963461259691</v>
+        <v>585.6417030346713</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>5350</v>
       </c>
       <c r="B192" t="n">
-        <v>1357.119712956501</v>
+        <v>563.1645323076219</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>5351</v>
       </c>
       <c r="B193" t="n">
-        <v>915.7336334687392</v>
+        <v>503.2959857066625</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -6278,7 +6278,7 @@
         <v>5352</v>
       </c>
       <c r="B194" t="n">
-        <v>811.8213270037274</v>
+        <v>0</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
         <v>5353</v>
       </c>
       <c r="B195" t="n">
-        <v>497.999270684367</v>
+        <v>0</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -6300,10 +6300,10 @@
         <v>5354</v>
       </c>
       <c r="B196" t="n">
-        <v>1864.3628559865</v>
+        <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>6701.966849991724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -6311,10 +6311,10 @@
         <v>5355</v>
       </c>
       <c r="B197" t="n">
-        <v>1864.362855986504</v>
+        <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>6701.966849991739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -6322,10 +6322,10 @@
         <v>5356</v>
       </c>
       <c r="B198" t="n">
-        <v>1864.362855986481</v>
+        <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>6701.966849991659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -6333,10 +6333,10 @@
         <v>5357</v>
       </c>
       <c r="B199" t="n">
-        <v>1864.362855986497</v>
+        <v>1264.498084981877</v>
       </c>
       <c r="C199" t="n">
-        <v>6701.966849991716</v>
+        <v>4545.587367938811</v>
       </c>
     </row>
     <row r="200">
@@ -6344,10 +6344,10 @@
         <v>5358</v>
       </c>
       <c r="B200" t="n">
-        <v>0</v>
+        <v>2071.806406992595</v>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>7447.679948503212</v>
       </c>
     </row>
     <row r="201">
@@ -6355,10 +6355,10 @@
         <v>5359</v>
       </c>
       <c r="B201" t="n">
-        <v>1782.438214893986</v>
+        <v>2631.044817889538</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>9458.016766273679</v>
       </c>
     </row>
     <row r="202">
@@ -6366,7 +6366,7 @@
         <v>5360</v>
       </c>
       <c r="B202" t="n">
-        <v>3094.166735347271</v>
+        <v>1380.676677790173</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -6377,7 +6377,7 @@
         <v>5361</v>
       </c>
       <c r="B203" t="n">
-        <v>4471.453007256381</v>
+        <v>1792.292447037863</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -6388,7 +6388,7 @@
         <v>5362</v>
       </c>
       <c r="B204" t="n">
-        <v>5808.83212545358</v>
+        <v>2539.201387613717</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>5363</v>
       </c>
       <c r="B205" t="n">
-        <v>6596.985566397112</v>
+        <v>3320.565855764806</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -6410,7 +6410,7 @@
         <v>5364</v>
       </c>
       <c r="B206" t="n">
-        <v>7928.038346422167</v>
+        <v>3725.43391763805</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -6421,7 +6421,7 @@
         <v>5365</v>
       </c>
       <c r="B207" t="n">
-        <v>8631.904987144411</v>
+        <v>4117.196819211281</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>5366</v>
       </c>
       <c r="B208" t="n">
-        <v>9337.341259020788</v>
+        <v>4134.936118497692</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>5367</v>
       </c>
       <c r="B209" t="n">
-        <v>9942.921289836935</v>
+        <v>4147.898076832479</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>5368</v>
       </c>
       <c r="B210" t="n">
-        <v>9133.067138532761</v>
+        <v>4404.949925253007</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
         <v>5369</v>
       </c>
       <c r="B211" t="n">
-        <v>7554.81695512964</v>
+        <v>3511.94779920109</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -6476,7 +6476,7 @@
         <v>5370</v>
       </c>
       <c r="B212" t="n">
-        <v>6069.927307679985</v>
+        <v>2683.098998798981</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -6487,7 +6487,7 @@
         <v>5371</v>
       </c>
       <c r="B213" t="n">
-        <v>4236.893768897251</v>
+        <v>1799.365425988101</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
         <v>5372</v>
       </c>
       <c r="B214" t="n">
-        <v>3522.67798725506</v>
+        <v>1469.352537197047</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>5373</v>
       </c>
       <c r="B215" t="n">
-        <v>2842.478936265626</v>
+        <v>1171.283952970514</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
         <v>5374</v>
       </c>
       <c r="B216" t="n">
-        <v>2035.683917882848</v>
+        <v>750.8846578925702</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -6531,7 +6531,7 @@
         <v>5375</v>
       </c>
       <c r="B217" t="n">
-        <v>1831.472083224858</v>
+        <v>671.0582338470149</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -6542,7 +6542,7 @@
         <v>5376</v>
       </c>
       <c r="B218" t="n">
-        <v>1353.034251469941</v>
+        <v>306.3151758225118</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>5377</v>
       </c>
       <c r="B219" t="n">
-        <v>1015.358798552934</v>
+        <v>0</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         <v>5378</v>
       </c>
       <c r="B220" t="n">
-        <v>993.7423838404452</v>
+        <v>0</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>5379</v>
       </c>
       <c r="B221" t="n">
-        <v>786.3762244749153</v>
+        <v>0</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -6586,7 +6586,7 @@
         <v>5380</v>
       </c>
       <c r="B222" t="n">
-        <v>632.572247008873</v>
+        <v>0</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
@@ -6597,10 +6597,10 @@
         <v>5381</v>
       </c>
       <c r="B223" t="n">
-        <v>844.3397324731509</v>
+        <v>1264.498084981877</v>
       </c>
       <c r="C223" t="n">
-        <v>0</v>
+        <v>4545.587367938811</v>
       </c>
     </row>
     <row r="224">
@@ -6608,7 +6608,7 @@
         <v>5382</v>
       </c>
       <c r="B224" t="n">
-        <v>1585.606203008711</v>
+        <v>842.1372331707084</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>5383</v>
       </c>
       <c r="B225" t="n">
-        <v>2970.72393644014</v>
+        <v>1642.443584356478</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -6630,7 +6630,7 @@
         <v>5384</v>
       </c>
       <c r="B226" t="n">
-        <v>4331.834205607942</v>
+        <v>2761.353355580345</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -6641,7 +6641,7 @@
         <v>5385</v>
       </c>
       <c r="B227" t="n">
-        <v>5749.014182198166</v>
+        <v>3584.595939687137</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -6652,7 +6652,7 @@
         <v>5386</v>
       </c>
       <c r="B228" t="n">
-        <v>6454.226016516687</v>
+        <v>3990.157540522056</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
         <v>5387</v>
       </c>
       <c r="B229" t="n">
-        <v>7858.324839167642</v>
+        <v>3689.50467618012</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
         <v>5388</v>
       </c>
       <c r="B230" t="n">
-        <v>8588.72457480813</v>
+        <v>4470.53787117406</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
         <v>5389</v>
       </c>
       <c r="B231" t="n">
-        <v>9355.961275985765</v>
+        <v>4117.196819211281</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
         <v>5390</v>
       </c>
       <c r="B232" t="n">
-        <v>10004.23137838218</v>
+        <v>4134.936118497692</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -6707,7 +6707,7 @@
         <v>5391</v>
       </c>
       <c r="B233" t="n">
-        <v>10008.75563373118</v>
+        <v>2988.667592598601</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>5392</v>
       </c>
       <c r="B234" t="n">
-        <v>9133.067138532761</v>
+        <v>2936.628453288431</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
         <v>5393</v>
       </c>
       <c r="B235" t="n">
-        <v>7554.81695512964</v>
+        <v>2234.87671233575</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>5394</v>
       </c>
       <c r="B236" t="n">
-        <v>5564.103733719947</v>
+        <v>1609.861608401671</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
         <v>5395</v>
       </c>
       <c r="B237" t="n">
-        <v>3813.207763408692</v>
+        <v>1325.759517998861</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -6762,7 +6762,7 @@
         <v>5396</v>
       </c>
       <c r="B238" t="n">
-        <v>3131.265591324821</v>
+        <v>1049.537034422274</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -6773,7 +6773,7 @@
         <v>5397</v>
       </c>
       <c r="B239" t="n">
-        <v>2487.169805464986</v>
+        <v>780.856934689724</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -6784,7 +6784,7 @@
         <v>5398</v>
       </c>
       <c r="B240" t="n">
-        <v>1696.399407275985</v>
+        <v>563.1645323076219</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>5399</v>
       </c>
       <c r="B241" t="n">
-        <v>1220.981076923717</v>
+        <v>671.0582338470149</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
         <v>5400</v>
       </c>
       <c r="B242" t="n">
-        <v>1082.430103812667</v>
+        <v>600.1805185620557</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>5401</v>
       </c>
       <c r="B243" t="n">
-        <v>746.998758780038</v>
+        <v>661.63948185294</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         <v>5402</v>
       </c>
       <c r="B244" t="n">
-        <v>745.3079919521787</v>
+        <v>791.4783456982442</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         <v>5403</v>
       </c>
       <c r="B245" t="n">
-        <v>524.2540895534338</v>
+        <v>692.2032510547143</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>5404</v>
       </c>
       <c r="B246" t="n">
-        <v>1265.134955010845</v>
+        <v>652.5337281047515</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
         <v>5405</v>
       </c>
       <c r="B247" t="n">
-        <v>1281.996881384645</v>
+        <v>886.006898556305</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>5406</v>
       </c>
       <c r="B248" t="n">
-        <v>2092.1977583921</v>
+        <v>842.1372331707084</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -6883,7 +6883,7 @@
         <v>5407</v>
       </c>
       <c r="B249" t="n">
-        <v>2970.72393644014</v>
+        <v>1642.443584356478</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>5408</v>
       </c>
       <c r="B250" t="n">
-        <v>4331.834205607942</v>
+        <v>2086.860739570775</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -6905,7 +6905,7 @@
         <v>5409</v>
       </c>
       <c r="B251" t="n">
-        <v>5145.581536485603</v>
+        <v>2867.668166745508</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -6916,7 +6916,7 @@
         <v>5410</v>
       </c>
       <c r="B252" t="n">
-        <v>5849.492973211798</v>
+        <v>3627.426882323249</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -6927,7 +6927,7 @@
         <v>5411</v>
       </c>
       <c r="B253" t="n">
-        <v>7203.452473158436</v>
+        <v>4427.411298292202</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
         <v>5412</v>
       </c>
       <c r="B254" t="n">
-        <v>7928.038346422167</v>
+        <v>4470.53787117406</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>5413</v>
       </c>
       <c r="B255" t="n">
-        <v>8631.904987144411</v>
+        <v>2994.330492216481</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         <v>5414</v>
       </c>
       <c r="B256" t="n">
-        <v>9337.341259020788</v>
+        <v>2631.320891643725</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         <v>5415</v>
       </c>
       <c r="B257" t="n">
-        <v>9280.114675067925</v>
+        <v>2615.084505789795</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -6982,7 +6982,7 @@
         <v>5416</v>
       </c>
       <c r="B258" t="n">
-        <v>8480.69684930356</v>
+        <v>2202.475236077089</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -6993,7 +6993,7 @@
         <v>5417</v>
       </c>
       <c r="B259" t="n">
-        <v>6392.525949185526</v>
+        <v>1277.071086865342</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
         <v>5418</v>
       </c>
       <c r="B260" t="n">
-        <v>4552.443072616299</v>
+        <v>1073.240288525456</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>5419</v>
       </c>
       <c r="B261" t="n">
-        <v>3389.512125345373</v>
+        <v>662.8797589994305</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>5420</v>
       </c>
       <c r="B262" t="n">
-        <v>2739.858947360526</v>
+        <v>0</v>
       </c>
       <c r="C262" t="n">
         <v>0</v>
@@ -7037,10 +7037,10 @@
         <v>5421</v>
       </c>
       <c r="B263" t="n">
-        <v>2131.861610342909</v>
+        <v>2158.475785200996</v>
       </c>
       <c r="C263" t="n">
-        <v>0</v>
+        <v>7759.236949221693</v>
       </c>
     </row>
     <row r="264">
@@ -7048,10 +7048,10 @@
         <v>5422</v>
       </c>
       <c r="B264" t="n">
-        <v>1696.399407275985</v>
+        <v>1875.771080859399</v>
       </c>
       <c r="C264" t="n">
-        <v>0</v>
+        <v>6742.976862967427</v>
       </c>
     </row>
     <row r="265">
@@ -7059,10 +7059,10 @@
         <v>5423</v>
       </c>
       <c r="B265" t="n">
-        <v>1220.981076923717</v>
+        <v>1419.616534635928</v>
       </c>
       <c r="C265" t="n">
-        <v>0</v>
+        <v>5103.203447912404</v>
       </c>
     </row>
     <row r="266">
@@ -7070,7 +7070,7 @@
         <v>5424</v>
       </c>
       <c r="B266" t="n">
-        <v>1082.430103812667</v>
+        <v>0</v>
       </c>
       <c r="C266" t="n">
         <v>0</v>
@@ -7081,7 +7081,7 @@
         <v>5425</v>
       </c>
       <c r="B267" t="n">
-        <v>746.998758780038</v>
+        <v>0</v>
       </c>
       <c r="C267" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>5426</v>
       </c>
       <c r="B268" t="n">
-        <v>745.3079919521787</v>
+        <v>0</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
@@ -7103,7 +7103,7 @@
         <v>5427</v>
       </c>
       <c r="B269" t="n">
-        <v>524.2540895534338</v>
+        <v>0</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>5428</v>
       </c>
       <c r="B270" t="n">
-        <v>632.572247008873</v>
+        <v>0</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -7125,10 +7125,10 @@
         <v>5429</v>
       </c>
       <c r="B271" t="n">
-        <v>844.3397324731509</v>
+        <v>1264.498084981872</v>
       </c>
       <c r="C271" t="n">
-        <v>0</v>
+        <v>4545.587367938794</v>
       </c>
     </row>
     <row r="272">
@@ -7136,10 +7136,10 @@
         <v>5430</v>
       </c>
       <c r="B272" t="n">
-        <v>1569.148272010146</v>
+        <v>2071.806406992595</v>
       </c>
       <c r="C272" t="n">
-        <v>0</v>
+        <v>7447.679948503212</v>
       </c>
     </row>
     <row r="273">
@@ -7147,7 +7147,7 @@
         <v>5431</v>
       </c>
       <c r="B273" t="n">
-        <v>2398.847605634659</v>
+        <v>1313.95602673644</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>5432</v>
       </c>
       <c r="B274" t="n">
-        <v>3713.002410782014</v>
+        <v>2071.016465749331</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
         <v>5433</v>
       </c>
       <c r="B275" t="n">
-        <v>5110.24563544572</v>
+        <v>2509.211525595056</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -7180,7 +7180,7 @@
         <v>5434</v>
       </c>
       <c r="B276" t="n">
-        <v>5808.83212545358</v>
+        <v>2901.941287098131</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>5435</v>
       </c>
       <c r="B277" t="n">
-        <v>6548.580107149232</v>
+        <v>2951.606201551307</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
         <v>5436</v>
       </c>
       <c r="B278" t="n">
-        <v>7267.353053714765</v>
+        <v>2980.349704097881</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>5437</v>
       </c>
       <c r="B279" t="n">
-        <v>7967.919705498499</v>
+        <v>3029.413655426994</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
@@ -7224,7 +7224,7 @@
         <v>5438</v>
       </c>
       <c r="B280" t="n">
-        <v>8003.408110569526</v>
+        <v>3383.124431329076</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
@@ -7235,7 +7235,7 @@
         <v>5439</v>
       </c>
       <c r="B281" t="n">
-        <v>7291.491886801509</v>
+        <v>2988.667592598601</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
@@ -7246,7 +7246,7 @@
         <v>5440</v>
       </c>
       <c r="B282" t="n">
-        <v>5218.886602597744</v>
+        <v>2202.475236077089</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
@@ -7257,7 +7257,7 @@
         <v>5441</v>
       </c>
       <c r="B283" t="n">
-        <v>4067.968954412758</v>
+        <v>1277.071086865342</v>
       </c>
       <c r="C283" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>5442</v>
       </c>
       <c r="B284" t="n">
-        <v>3540.787227800031</v>
+        <v>536.621319876215</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
@@ -7279,10 +7279,10 @@
         <v>5443</v>
       </c>
       <c r="B285" t="n">
-        <v>2542.135298080876</v>
+        <v>2269.559322750585</v>
       </c>
       <c r="C285" t="n">
-        <v>0</v>
+        <v>8158.557384000055</v>
       </c>
     </row>
     <row r="286">
@@ -7290,10 +7290,10 @@
         <v>5444</v>
       </c>
       <c r="B286" t="n">
-        <v>1957.039907465989</v>
+        <v>2347.394234261428</v>
       </c>
       <c r="C286" t="n">
-        <v>0</v>
+        <v>8438.356455861358</v>
       </c>
     </row>
     <row r="287">
@@ -7301,10 +7301,10 @@
         <v>5445</v>
       </c>
       <c r="B287" t="n">
-        <v>1776.547663254889</v>
+        <v>2158.475785200996</v>
       </c>
       <c r="C287" t="n">
-        <v>0</v>
+        <v>7759.236949221693</v>
       </c>
     </row>
     <row r="288">
@@ -7312,10 +7312,10 @@
         <v>5446</v>
       </c>
       <c r="B288" t="n">
-        <v>1357.119712956501</v>
+        <v>1875.771080859399</v>
       </c>
       <c r="C288" t="n">
-        <v>0</v>
+        <v>6742.976862967427</v>
       </c>
     </row>
     <row r="289">
@@ -7323,10 +7323,10 @@
         <v>5447</v>
       </c>
       <c r="B289" t="n">
-        <v>915.7336334687392</v>
+        <v>1419.616534635928</v>
       </c>
       <c r="C289" t="n">
-        <v>0</v>
+        <v>5103.203447912404</v>
       </c>
     </row>
     <row r="290">
@@ -7334,7 +7334,7 @@
         <v>5448</v>
       </c>
       <c r="B290" t="n">
-        <v>797.926337915366</v>
+        <v>0</v>
       </c>
       <c r="C290" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
         <v>5449</v>
       </c>
       <c r="B291" t="n">
-        <v>509.3212378009041</v>
+        <v>0</v>
       </c>
       <c r="C291" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         <v>5450</v>
       </c>
       <c r="B292" t="n">
-        <v>488.7701965487762</v>
+        <v>0</v>
       </c>
       <c r="C292" t="n">
         <v>0</v>
@@ -7367,10 +7367,10 @@
         <v>5451</v>
       </c>
       <c r="B293" t="n">
-        <v>6222.996085221091</v>
+        <v>0</v>
       </c>
       <c r="C293" t="n">
-        <v>22370.27697524673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -7378,10 +7378,10 @@
         <v>5452</v>
       </c>
       <c r="B294" t="n">
-        <v>1864.3628559865</v>
+        <v>0</v>
       </c>
       <c r="C294" t="n">
-        <v>6701.966849991724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -7389,10 +7389,10 @@
         <v>5453</v>
       </c>
       <c r="B295" t="n">
-        <v>1864.3628559865</v>
+        <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>6701.966849991724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -7400,10 +7400,10 @@
         <v>5454</v>
       </c>
       <c r="B296" t="n">
-        <v>902.6553921878502</v>
+        <v>1227.423328951206</v>
       </c>
       <c r="C296" t="n">
-        <v>0</v>
+        <v>4412.311924753902</v>
       </c>
     </row>
     <row r="297">
@@ -7411,10 +7411,10 @@
         <v>5455</v>
       </c>
       <c r="B297" t="n">
-        <v>1535.001450798823</v>
+        <v>1932.317511575456</v>
       </c>
       <c r="C297" t="n">
-        <v>0</v>
+        <v>6946.248614991171</v>
       </c>
     </row>
     <row r="298">
@@ -7422,10 +7422,10 @@
         <v>5456</v>
       </c>
       <c r="B298" t="n">
-        <v>2137.746909266406</v>
+        <v>2709.037134108128</v>
       </c>
       <c r="C298" t="n">
-        <v>0</v>
+        <v>9738.381672800679</v>
       </c>
     </row>
     <row r="299">
@@ -7433,10 +7433,10 @@
         <v>5457</v>
       </c>
       <c r="B299" t="n">
-        <v>2769.076020338925</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C299" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="300">
@@ -7444,10 +7444,10 @@
         <v>5458</v>
       </c>
       <c r="B300" t="n">
-        <v>3926.141889600081</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C300" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="301">
@@ -7455,10 +7455,10 @@
         <v>5459</v>
       </c>
       <c r="B301" t="n">
-        <v>4569.577594131159</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="302">
@@ -7466,7 +7466,7 @@
         <v>5460</v>
       </c>
       <c r="B302" t="n">
-        <v>4621.947107849776</v>
+        <v>1004.771214385633</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>5461</v>
       </c>
       <c r="B303" t="n">
-        <v>4647.749937617412</v>
+        <v>1010.033503932439</v>
       </c>
       <c r="C303" t="n">
         <v>0</v>
@@ -7488,7 +7488,7 @@
         <v>5462</v>
       </c>
       <c r="B304" t="n">
-        <v>4668.335771090785</v>
+        <v>1352.735777506381</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -7499,7 +7499,7 @@
         <v>5463</v>
       </c>
       <c r="B305" t="n">
-        <v>4066.606548594838</v>
+        <v>1048.400267719588</v>
       </c>
       <c r="C305" t="n">
         <v>0</v>
@@ -7510,7 +7510,7 @@
         <v>5464</v>
       </c>
       <c r="B306" t="n">
-        <v>4081.751519845503</v>
+        <v>995.2646642949775</v>
       </c>
       <c r="C306" t="n">
         <v>0</v>
@@ -7521,10 +7521,10 @@
         <v>5465</v>
       </c>
       <c r="B307" t="n">
-        <v>2563.962358929924</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C307" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="308">
@@ -7532,10 +7532,10 @@
         <v>5466</v>
       </c>
       <c r="B308" t="n">
-        <v>1404.463043698418</v>
+        <v>3394.461673839469</v>
       </c>
       <c r="C308" t="n">
-        <v>0</v>
+        <v>12202.32935803795</v>
       </c>
     </row>
     <row r="309">
@@ -7543,7 +7543,7 @@
         <v>5467</v>
       </c>
       <c r="B309" t="n">
-        <v>766.8244208510366</v>
+        <v>0</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
         <v>5470</v>
       </c>
       <c r="B312" t="n">
-        <v>989.9431464593922</v>
+        <v>0</v>
       </c>
       <c r="C312" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>5471</v>
       </c>
       <c r="B313" t="n">
-        <v>599.5481206725257</v>
+        <v>0</v>
       </c>
       <c r="C313" t="n">
         <v>0</v>
@@ -7598,10 +7598,10 @@
         <v>5472</v>
       </c>
       <c r="B314" t="n">
-        <v>1864.362855986485</v>
+        <v>0</v>
       </c>
       <c r="C314" t="n">
-        <v>6701.966849991672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -7609,10 +7609,10 @@
         <v>5473</v>
       </c>
       <c r="B315" t="n">
-        <v>1864.3628559865</v>
+        <v>0</v>
       </c>
       <c r="C315" t="n">
-        <v>6701.966849991724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -7620,10 +7620,10 @@
         <v>5474</v>
       </c>
       <c r="B316" t="n">
-        <v>12429.08570657677</v>
+        <v>0</v>
       </c>
       <c r="C316" t="n">
-        <v>44679.77899994522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -7631,10 +7631,10 @@
         <v>5475</v>
       </c>
       <c r="B317" t="n">
-        <v>12429.08570657677</v>
+        <v>6223.9768355225</v>
       </c>
       <c r="C317" t="n">
-        <v>44679.77899994522</v>
+        <v>22373.80255289223</v>
       </c>
     </row>
     <row r="318">
@@ -7642,10 +7642,10 @@
         <v>5476</v>
       </c>
       <c r="B318" t="n">
-        <v>12429.08570657677</v>
+        <v>0</v>
       </c>
       <c r="C318" t="n">
-        <v>44679.77899994522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -7653,10 +7653,10 @@
         <v>5477</v>
       </c>
       <c r="B319" t="n">
-        <v>1864.3628559865</v>
+        <v>0</v>
       </c>
       <c r="C319" t="n">
-        <v>6701.966849991724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -7664,10 +7664,10 @@
         <v>5478</v>
       </c>
       <c r="B320" t="n">
-        <v>1864.362855986486</v>
+        <v>0</v>
       </c>
       <c r="C320" t="n">
-        <v>6701.966849991673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -7675,10 +7675,10 @@
         <v>5479</v>
       </c>
       <c r="B321" t="n">
-        <v>12429.08570657677</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C321" t="n">
-        <v>44679.77899994522</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="322">
@@ -7686,10 +7686,10 @@
         <v>5480</v>
       </c>
       <c r="B322" t="n">
-        <v>0</v>
+        <v>2441.081073598025</v>
       </c>
       <c r="C322" t="n">
-        <v>0</v>
+        <v>8775.139657424412</v>
       </c>
     </row>
     <row r="323">
@@ -7697,10 +7697,10 @@
         <v>5481</v>
       </c>
       <c r="B323" t="n">
-        <v>854.8344322288972</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C323" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="324">
@@ -7708,10 +7708,10 @@
         <v>5482</v>
       </c>
       <c r="B324" t="n">
-        <v>1290.005291014592</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C324" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="325">
@@ -7719,10 +7719,10 @@
         <v>5483</v>
       </c>
       <c r="B325" t="n">
-        <v>1703.277483358446</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C325" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="326">
@@ -7730,10 +7730,10 @@
         <v>5484</v>
       </c>
       <c r="B326" t="n">
-        <v>2165.460970103893</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C326" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="327">
@@ -7741,10 +7741,10 @@
         <v>5485</v>
       </c>
       <c r="B327" t="n">
-        <v>2616.514723821504</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C327" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="328">
@@ -7752,10 +7752,10 @@
         <v>5486</v>
       </c>
       <c r="B328" t="n">
-        <v>2615.268305221695</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C328" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="329">
@@ -7763,10 +7763,10 @@
         <v>5487</v>
       </c>
       <c r="B329" t="n">
-        <v>2557.610733598832</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C329" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="330">
@@ -7774,10 +7774,10 @@
         <v>5488</v>
       </c>
       <c r="B330" t="n">
-        <v>2354.688892700638</v>
+        <v>8172.358333547443</v>
       </c>
       <c r="C330" t="n">
-        <v>0</v>
+        <v>29377.79760083634</v>
       </c>
     </row>
     <row r="331">
@@ -7785,10 +7785,10 @@
         <v>5489</v>
       </c>
       <c r="B331" t="n">
-        <v>1915.452366438793</v>
+        <v>1656.991126763742</v>
       </c>
       <c r="C331" t="n">
-        <v>0</v>
+        <v>5956.511934703258</v>
       </c>
     </row>
     <row r="332">
@@ -7796,10 +7796,10 @@
         <v>5490</v>
       </c>
       <c r="B332" t="n">
-        <v>1463.438482654044</v>
+        <v>1896.868533533586</v>
       </c>
       <c r="C332" t="n">
-        <v>0</v>
+        <v>6818.81747950173</v>
       </c>
     </row>
     <row r="333">
@@ -7807,10 +7807,10 @@
         <v>5491</v>
       </c>
       <c r="B333" t="n">
-        <v>1050.92960180934</v>
+        <v>2059.940996370286</v>
       </c>
       <c r="C333" t="n">
-        <v>0</v>
+        <v>7405.02645516799</v>
       </c>
     </row>
     <row r="334">
@@ -7818,10 +7818,10 @@
         <v>5492</v>
       </c>
       <c r="B334" t="n">
-        <v>658.2265016876692</v>
+        <v>1943.017407301031</v>
       </c>
       <c r="C334" t="n">
-        <v>0</v>
+        <v>6984.712343347969</v>
       </c>
     </row>
     <row r="335">
@@ -7829,10 +7829,10 @@
         <v>5493</v>
       </c>
       <c r="B335" t="n">
-        <v>0</v>
+        <v>1891.679605926428</v>
       </c>
       <c r="C335" t="n">
-        <v>0</v>
+        <v>6800.164447073782</v>
       </c>
     </row>
     <row r="336">
@@ -7840,10 +7840,10 @@
         <v>5494</v>
       </c>
       <c r="B336" t="n">
-        <v>0</v>
+        <v>1557.950230140451</v>
       </c>
       <c r="C336" t="n">
-        <v>0</v>
+        <v>5600.482096503369</v>
       </c>
     </row>
     <row r="337">
@@ -7851,10 +7851,10 @@
         <v>5495</v>
       </c>
       <c r="B337" t="n">
-        <v>1864.3628559865</v>
+        <v>3227.007384090737</v>
       </c>
       <c r="C337" t="n">
-        <v>6701.966849991724</v>
+        <v>11600.36869615216</v>
       </c>
     </row>
   </sheetData>

--- a/first_stage_optimization/lshp_operation.xlsx
+++ b/first_stage_optimization/lshp_operation.xlsx
@@ -439,10 +439,10 @@
         <v>288</v>
       </c>
       <c r="B2" t="n">
-        <v>10651.48526512742</v>
+        <v>14661.83753471311</v>
       </c>
       <c r="C2" t="n">
-        <v>29377.79760083634</v>
+        <v>40438.72613346702</v>
       </c>
     </row>
     <row r="3">
@@ -450,10 +450,10 @@
         <v>289</v>
       </c>
       <c r="B3" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C3" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>290</v>
       </c>
       <c r="B4" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C4" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="5">
@@ -472,10 +472,10 @@
         <v>291</v>
       </c>
       <c r="B5" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C5" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="6">
@@ -483,10 +483,10 @@
         <v>292</v>
       </c>
       <c r="B6" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C6" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="7">
@@ -494,10 +494,10 @@
         <v>293</v>
       </c>
       <c r="B7" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C7" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="8">
@@ -505,10 +505,10 @@
         <v>294</v>
       </c>
       <c r="B8" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C8" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="9">
@@ -538,10 +538,10 @@
         <v>297</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>10892.0487091489</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>30041.29419241133</v>
       </c>
     </row>
     <row r="12">
@@ -549,10 +549,10 @@
         <v>298</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>13613.69344088266</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>37547.84619713782</v>
       </c>
     </row>
     <row r="13">
@@ -560,10 +560,10 @@
         <v>299</v>
       </c>
       <c r="B13" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -571,10 +571,10 @@
         <v>300</v>
       </c>
       <c r="B14" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C14" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="15">
@@ -582,10 +582,10 @@
         <v>301</v>
       </c>
       <c r="B15" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C15" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="16">
@@ -593,10 +593,10 @@
         <v>302</v>
       </c>
       <c r="B16" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C16" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="17">
@@ -648,10 +648,10 @@
         <v>307</v>
       </c>
       <c r="B21" t="n">
-        <v>10651.48526512742</v>
+        <v>5628.311937815829</v>
       </c>
       <c r="C21" t="n">
-        <v>29377.79760083634</v>
+        <v>15523.41338581821</v>
       </c>
     </row>
     <row r="22">
@@ -659,10 +659,10 @@
         <v>308</v>
       </c>
       <c r="B22" t="n">
-        <v>10651.48526512742</v>
+        <v>6906.990958459112</v>
       </c>
       <c r="C22" t="n">
-        <v>29377.79760083634</v>
+        <v>19050.13032058033</v>
       </c>
     </row>
     <row r="23">
@@ -670,10 +670,10 @@
         <v>309</v>
       </c>
       <c r="B23" t="n">
-        <v>10651.48526512742</v>
+        <v>11687.76275546055</v>
       </c>
       <c r="C23" t="n">
-        <v>29377.79760083634</v>
+        <v>32235.9483292592</v>
       </c>
     </row>
     <row r="24">
@@ -681,10 +681,10 @@
         <v>310</v>
       </c>
       <c r="B24" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C24" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="25">
@@ -692,10 +692,10 @@
         <v>311</v>
       </c>
       <c r="B25" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C25" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="26">
@@ -703,10 +703,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C26" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="27">
@@ -714,10 +714,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C27" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="28">
@@ -725,10 +725,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C28" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="29">
@@ -736,10 +736,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C29" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="30">
@@ -747,10 +747,10 @@
         <v>316</v>
       </c>
       <c r="B30" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C30" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="31">
@@ -758,10 +758,10 @@
         <v>317</v>
       </c>
       <c r="B31" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C31" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="32">
@@ -769,10 +769,10 @@
         <v>318</v>
       </c>
       <c r="B32" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C32" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="33">
@@ -780,10 +780,10 @@
         <v>319</v>
       </c>
       <c r="B33" t="n">
-        <v>3223.09421407784</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C33" t="n">
-        <v>8889.596813282806</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="34">
@@ -802,10 +802,10 @@
         <v>321</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>10892.0487091489</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>30041.29419241133</v>
       </c>
     </row>
     <row r="36">
@@ -813,10 +813,10 @@
         <v>322</v>
       </c>
       <c r="B36" t="n">
-        <v>10651.48526512742</v>
+        <v>8570.769153159979</v>
       </c>
       <c r="C36" t="n">
-        <v>29377.79760083634</v>
+        <v>23638.98697671562</v>
       </c>
     </row>
     <row r="37">
@@ -824,10 +824,10 @@
         <v>323</v>
       </c>
       <c r="B37" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C37" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="38">
@@ -835,10 +835,10 @@
         <v>324</v>
       </c>
       <c r="B38" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -846,10 +846,10 @@
         <v>325</v>
       </c>
       <c r="B39" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -857,10 +857,10 @@
         <v>326</v>
       </c>
       <c r="B40" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -912,10 +912,10 @@
         <v>331</v>
       </c>
       <c r="B45" t="n">
-        <v>2915.747720849548</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>8041.906294388813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -923,10 +923,10 @@
         <v>332</v>
       </c>
       <c r="B46" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -934,10 +934,10 @@
         <v>333</v>
       </c>
       <c r="B47" t="n">
-        <v>10651.48526512742</v>
+        <v>9011.154174682662</v>
       </c>
       <c r="C47" t="n">
-        <v>29377.79760083634</v>
+        <v>24853.6102622672</v>
       </c>
     </row>
     <row r="48">
@@ -945,10 +945,10 @@
         <v>334</v>
       </c>
       <c r="B48" t="n">
-        <v>10651.48526512742</v>
+        <v>15797.05665565501</v>
       </c>
       <c r="C48" t="n">
-        <v>29377.79760083634</v>
+        <v>43569.76717962214</v>
       </c>
     </row>
     <row r="49">
@@ -956,10 +956,10 @@
         <v>335</v>
       </c>
       <c r="B49" t="n">
-        <v>2822.756190901325</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C49" t="n">
-        <v>7785.426913587798</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="50">
@@ -967,10 +967,10 @@
         <v>336</v>
       </c>
       <c r="B50" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C50" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="51">
@@ -978,10 +978,10 @@
         <v>337</v>
       </c>
       <c r="B51" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C51" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="52">
@@ -989,10 +989,10 @@
         <v>338</v>
       </c>
       <c r="B52" t="n">
-        <v>10651.48526512742</v>
+        <v>15400.42560310273</v>
       </c>
       <c r="C52" t="n">
-        <v>29377.79760083634</v>
+        <v>42475.82145336401</v>
       </c>
     </row>
     <row r="53">
@@ -1000,10 +1000,10 @@
         <v>339</v>
       </c>
       <c r="B53" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C53" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="54">
@@ -1011,10 +1011,10 @@
         <v>340</v>
       </c>
       <c r="B54" t="n">
-        <v>10651.48526512742</v>
+        <v>15967.42976796647</v>
       </c>
       <c r="C54" t="n">
-        <v>29377.79760083634</v>
+        <v>44039.67223844971</v>
       </c>
     </row>
     <row r="55">
@@ -1022,10 +1022,10 @@
         <v>341</v>
       </c>
       <c r="B55" t="n">
-        <v>10651.48526512742</v>
+        <v>16079.27149234439</v>
       </c>
       <c r="C55" t="n">
-        <v>29377.79760083634</v>
+        <v>44348.14222740612</v>
       </c>
     </row>
     <row r="56">
@@ -1033,10 +1033,10 @@
         <v>342</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>13356.16694275438</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>36837.56390780921</v>
       </c>
     </row>
     <row r="57">
@@ -1220,10 +1220,10 @@
         <v>359</v>
       </c>
       <c r="B73" t="n">
-        <v>7785.058501106087</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>21471.92314154969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1231,10 +1231,10 @@
         <v>360</v>
       </c>
       <c r="B74" t="n">
-        <v>7921.8076075279</v>
+        <v>3622.480496173405</v>
       </c>
       <c r="C74" t="n">
-        <v>21849.09003147706</v>
+        <v>9991.14172161289</v>
       </c>
     </row>
     <row r="75">
@@ -1242,10 +1242,10 @@
         <v>361</v>
       </c>
       <c r="B75" t="n">
-        <v>10651.48526512742</v>
+        <v>3851.506422101356</v>
       </c>
       <c r="C75" t="n">
-        <v>29377.79760083634</v>
+        <v>10622.81675375922</v>
       </c>
     </row>
     <row r="76">
@@ -1253,10 +1253,10 @@
         <v>362</v>
       </c>
       <c r="B76" t="n">
-        <v>10651.48526512742</v>
+        <v>4117.917007473863</v>
       </c>
       <c r="C76" t="n">
-        <v>29377.79760083634</v>
+        <v>11357.60219081162</v>
       </c>
     </row>
     <row r="77">
@@ -1264,10 +1264,10 @@
         <v>363</v>
       </c>
       <c r="B77" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C77" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="78">
@@ -1275,10 +1275,10 @@
         <v>364</v>
       </c>
       <c r="B78" t="n">
-        <v>10651.48526512742</v>
+        <v>13113.2559399548</v>
       </c>
       <c r="C78" t="n">
-        <v>29377.79760083634</v>
+        <v>36167.5925284537</v>
       </c>
     </row>
     <row r="79">
@@ -1286,10 +1286,10 @@
         <v>365</v>
       </c>
       <c r="B79" t="n">
-        <v>10651.48526512742</v>
+        <v>4994.891653253849</v>
       </c>
       <c r="C79" t="n">
-        <v>29377.79760083634</v>
+        <v>13776.38069948952</v>
       </c>
     </row>
     <row r="80">
@@ -1297,10 +1297,10 @@
         <v>366</v>
       </c>
       <c r="B80" t="n">
-        <v>10077.01547937512</v>
+        <v>5468.613123466752</v>
       </c>
       <c r="C80" t="n">
-        <v>27793.35593157163</v>
+        <v>15082.94904415491</v>
       </c>
     </row>
     <row r="81">
@@ -1374,10 +1374,10 @@
         <v>373</v>
       </c>
       <c r="B87" t="n">
-        <v>7468.834858130776</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>20599.74860920134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -1473,10 +1473,10 @@
         <v>382</v>
       </c>
       <c r="B96" t="n">
-        <v>3424.946608583287</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>9446.324691453912</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1484,10 +1484,10 @@
         <v>383</v>
       </c>
       <c r="B97" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1495,10 +1495,10 @@
         <v>384</v>
       </c>
       <c r="B98" t="n">
-        <v>10651.48526512742</v>
+        <v>6183.793196442298</v>
       </c>
       <c r="C98" t="n">
-        <v>29377.79760083634</v>
+        <v>17055.48291234832</v>
       </c>
     </row>
     <row r="99">
@@ -1506,10 +1506,10 @@
         <v>385</v>
       </c>
       <c r="B99" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C99" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="100">
@@ -1517,10 +1517,10 @@
         <v>386</v>
       </c>
       <c r="B100" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C100" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="101">
@@ -1528,10 +1528,10 @@
         <v>387</v>
       </c>
       <c r="B101" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C101" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="102">
@@ -1539,10 +1539,10 @@
         <v>388</v>
       </c>
       <c r="B102" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C102" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="103">
@@ -1550,10 +1550,10 @@
         <v>389</v>
       </c>
       <c r="B103" t="n">
-        <v>10651.48526512742</v>
+        <v>4994.891653253849</v>
       </c>
       <c r="C103" t="n">
-        <v>29377.79760083634</v>
+        <v>13776.38069948952</v>
       </c>
     </row>
     <row r="104">
@@ -1561,10 +1561,10 @@
         <v>390</v>
       </c>
       <c r="B104" t="n">
-        <v>6829.30336611773</v>
+        <v>7952.96607559232</v>
       </c>
       <c r="C104" t="n">
-        <v>18835.86063826911</v>
+        <v>21935.02801529472</v>
       </c>
     </row>
     <row r="105">
@@ -1605,10 +1605,10 @@
         <v>394</v>
       </c>
       <c r="B108" t="n">
-        <v>2264.450114450163</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>6245.566273964308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1627,10 +1627,10 @@
         <v>396</v>
       </c>
       <c r="B110" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -1638,10 +1638,10 @@
         <v>397</v>
       </c>
       <c r="B111" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1715,10 +1715,10 @@
         <v>404</v>
       </c>
       <c r="B118" t="n">
-        <v>2927.085533910706</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>8073.177048565914</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -1726,10 +1726,10 @@
         <v>405</v>
       </c>
       <c r="B119" t="n">
-        <v>5120.850451717535</v>
+        <v>4018.932957836866</v>
       </c>
       <c r="C119" t="n">
-        <v>14123.78690577942</v>
+        <v>11084.59487741211</v>
       </c>
     </row>
     <row r="120">
@@ -1737,10 +1737,10 @@
         <v>406</v>
       </c>
       <c r="B120" t="n">
-        <v>6401.987222217381</v>
+        <v>7538.776746350087</v>
       </c>
       <c r="C120" t="n">
-        <v>17657.28254567442</v>
+        <v>20792.65491144769</v>
       </c>
     </row>
     <row r="121">
@@ -1748,10 +1748,10 @@
         <v>407</v>
       </c>
       <c r="B121" t="n">
-        <v>10651.48526512742</v>
+        <v>8152.132178745583</v>
       </c>
       <c r="C121" t="n">
-        <v>29377.79760083634</v>
+        <v>22484.34684940512</v>
       </c>
     </row>
     <row r="122">
@@ -1759,10 +1759,10 @@
         <v>408</v>
       </c>
       <c r="B122" t="n">
-        <v>10651.48526512742</v>
+        <v>10086.38505501611</v>
       </c>
       <c r="C122" t="n">
-        <v>29377.79760083634</v>
+        <v>27819.19810192959</v>
       </c>
     </row>
     <row r="123">
@@ -1770,10 +1770,10 @@
         <v>409</v>
       </c>
       <c r="B123" t="n">
-        <v>10651.48526512742</v>
+        <v>10284.60671765093</v>
       </c>
       <c r="C123" t="n">
-        <v>29377.79760083634</v>
+        <v>28365.91208031273</v>
       </c>
     </row>
     <row r="124">
@@ -1781,10 +1781,10 @@
         <v>410</v>
       </c>
       <c r="B124" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C124" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="125">
@@ -1792,10 +1792,10 @@
         <v>411</v>
       </c>
       <c r="B125" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C125" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="126">
@@ -1803,10 +1803,10 @@
         <v>412</v>
       </c>
       <c r="B126" t="n">
-        <v>10651.48526512742</v>
+        <v>8089.609984129404</v>
       </c>
       <c r="C126" t="n">
-        <v>29377.79760083634</v>
+        <v>22311.90475956741</v>
       </c>
     </row>
     <row r="127">
@@ -1814,10 +1814,10 @@
         <v>413</v>
       </c>
       <c r="B127" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C127" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="128">
@@ -1825,10 +1825,10 @@
         <v>414</v>
       </c>
       <c r="B128" t="n">
-        <v>10651.48526512742</v>
+        <v>6535.69842051366</v>
       </c>
       <c r="C128" t="n">
-        <v>29377.79760083634</v>
+        <v>18026.0705994282</v>
       </c>
     </row>
     <row r="129">
@@ -1836,10 +1836,10 @@
         <v>415</v>
       </c>
       <c r="B129" t="n">
-        <v>10651.48526512742</v>
+        <v>6150.872376992415</v>
       </c>
       <c r="C129" t="n">
-        <v>29377.79760083634</v>
+        <v>16964.68419774852</v>
       </c>
     </row>
     <row r="130">
@@ -1847,10 +1847,10 @@
         <v>416</v>
       </c>
       <c r="B130" t="n">
-        <v>10651.48526512742</v>
+        <v>6038.775086831522</v>
       </c>
       <c r="C130" t="n">
-        <v>29377.79760083634</v>
+        <v>16655.5093343395</v>
       </c>
     </row>
     <row r="131">
@@ -1858,10 +1858,10 @@
         <v>417</v>
       </c>
       <c r="B131" t="n">
-        <v>10651.48526512742</v>
+        <v>5855.842708277934</v>
       </c>
       <c r="C131" t="n">
-        <v>29377.79760083634</v>
+        <v>16150.96463864512</v>
       </c>
     </row>
     <row r="132">
@@ -1869,10 +1869,10 @@
         <v>418</v>
       </c>
       <c r="B132" t="n">
-        <v>10651.48526512742</v>
+        <v>4200.058406524801</v>
       </c>
       <c r="C132" t="n">
-        <v>29377.79760083634</v>
+        <v>11584.15589068562</v>
       </c>
     </row>
     <row r="133">
@@ -1880,10 +1880,10 @@
         <v>419</v>
       </c>
       <c r="B133" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -1891,10 +1891,10 @@
         <v>420</v>
       </c>
       <c r="B134" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -1902,10 +1902,10 @@
         <v>421</v>
       </c>
       <c r="B135" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -1913,10 +1913,10 @@
         <v>422</v>
       </c>
       <c r="B136" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -1924,10 +1924,10 @@
         <v>423</v>
       </c>
       <c r="B137" t="n">
-        <v>2320.557769345792</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>6400.316460286012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -1935,10 +1935,10 @@
         <v>424</v>
       </c>
       <c r="B138" t="n">
-        <v>3106.571651286182</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>8568.216631982512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -1946,10 +1946,10 @@
         <v>425</v>
       </c>
       <c r="B139" t="n">
-        <v>4204.723158340804</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>11597.02171468082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -1979,10 +1979,10 @@
         <v>428</v>
       </c>
       <c r="B142" t="n">
-        <v>6550.057076146253</v>
+        <v>5349.056572928629</v>
       </c>
       <c r="C142" t="n">
-        <v>18065.67312137652</v>
+        <v>14753.20083945501</v>
       </c>
     </row>
     <row r="143">
@@ -1990,10 +1990,10 @@
         <v>429</v>
       </c>
       <c r="B143" t="n">
-        <v>7641.828945744639</v>
+        <v>6072.162767063096</v>
       </c>
       <c r="C143" t="n">
-        <v>21076.88256428461</v>
+        <v>16747.59569486012</v>
       </c>
     </row>
     <row r="144">
@@ -2001,10 +2001,10 @@
         <v>430</v>
       </c>
       <c r="B144" t="n">
-        <v>6285.017751154897</v>
+        <v>7392.41216357169</v>
       </c>
       <c r="C144" t="n">
-        <v>17334.66974935382</v>
+        <v>20388.9676338741</v>
       </c>
     </row>
     <row r="145">
@@ -2012,10 +2012,10 @@
         <v>431</v>
       </c>
       <c r="B145" t="n">
-        <v>10651.48526512742</v>
+        <v>8541.22723488989</v>
       </c>
       <c r="C145" t="n">
-        <v>29377.79760083634</v>
+        <v>23557.5075891864</v>
       </c>
     </row>
     <row r="146">
@@ -2023,10 +2023,10 @@
         <v>432</v>
       </c>
       <c r="B146" t="n">
-        <v>10651.48526512742</v>
+        <v>10291.95742004125</v>
       </c>
       <c r="C146" t="n">
-        <v>29377.79760083634</v>
+        <v>28386.18600847124</v>
       </c>
     </row>
     <row r="147">
@@ -2034,10 +2034,10 @@
         <v>433</v>
       </c>
       <c r="B147" t="n">
-        <v>10651.48526512742</v>
+        <v>11026.63922527536</v>
       </c>
       <c r="C147" t="n">
-        <v>29377.79760083634</v>
+        <v>30412.50748739662</v>
       </c>
     </row>
     <row r="148">
@@ -2045,10 +2045,10 @@
         <v>434</v>
       </c>
       <c r="B148" t="n">
-        <v>10651.48526512742</v>
+        <v>11475.17202671491</v>
       </c>
       <c r="C148" t="n">
-        <v>29377.79760083634</v>
+        <v>31649.60311585024</v>
       </c>
     </row>
     <row r="149">
@@ -2056,10 +2056,10 @@
         <v>435</v>
       </c>
       <c r="B149" t="n">
-        <v>10651.48526512742</v>
+        <v>11447.5183340251</v>
       </c>
       <c r="C149" t="n">
-        <v>29377.79760083634</v>
+        <v>31573.33163196463</v>
       </c>
     </row>
     <row r="150">
@@ -2067,10 +2067,10 @@
         <v>436</v>
       </c>
       <c r="B150" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C150" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="151">
@@ -2078,10 +2078,10 @@
         <v>437</v>
       </c>
       <c r="B151" t="n">
-        <v>10651.48526512742</v>
+        <v>13245.85570408344</v>
       </c>
       <c r="C151" t="n">
-        <v>29377.79760083634</v>
+        <v>36533.31514229832</v>
       </c>
     </row>
     <row r="152">
@@ -2089,10 +2089,10 @@
         <v>438</v>
       </c>
       <c r="B152" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C152" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="153">
@@ -2100,10 +2100,10 @@
         <v>439</v>
       </c>
       <c r="B153" t="n">
-        <v>10651.48526512742</v>
+        <v>8903.385898554039</v>
       </c>
       <c r="C153" t="n">
-        <v>29377.79760083634</v>
+        <v>24556.3752264865</v>
       </c>
     </row>
     <row r="154">
@@ -2111,10 +2111,10 @@
         <v>440</v>
       </c>
       <c r="B154" t="n">
-        <v>10651.48526512742</v>
+        <v>8782.912519094494</v>
       </c>
       <c r="C154" t="n">
-        <v>29377.79760083634</v>
+        <v>24224.09832143941</v>
       </c>
     </row>
     <row r="155">
@@ -2122,10 +2122,10 @@
         <v>441</v>
       </c>
       <c r="B155" t="n">
-        <v>10651.48526512742</v>
+        <v>6895.755311556394</v>
       </c>
       <c r="C155" t="n">
-        <v>29377.79760083634</v>
+        <v>19019.14135027182</v>
       </c>
     </row>
     <row r="156">
@@ -2133,10 +2133,10 @@
         <v>442</v>
       </c>
       <c r="B156" t="n">
-        <v>10651.48526512742</v>
+        <v>5736.285052507169</v>
       </c>
       <c r="C156" t="n">
-        <v>29377.79760083634</v>
+        <v>15821.21338560971</v>
       </c>
     </row>
     <row r="157">
@@ -2144,10 +2144,10 @@
         <v>443</v>
       </c>
       <c r="B157" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -2155,10 +2155,10 @@
         <v>444</v>
       </c>
       <c r="B158" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C158" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="159">
@@ -2166,10 +2166,10 @@
         <v>445</v>
       </c>
       <c r="B159" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C159" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="160">
@@ -2177,10 +2177,10 @@
         <v>446</v>
       </c>
       <c r="B160" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C160" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="161">
@@ -2188,10 +2188,10 @@
         <v>447</v>
       </c>
       <c r="B161" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -2221,10 +2221,10 @@
         <v>450</v>
       </c>
       <c r="B164" t="n">
-        <v>2276.598239046935</v>
+        <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>6279.071943525916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -2232,10 +2232,10 @@
         <v>451</v>
       </c>
       <c r="B165" t="n">
-        <v>4048.996121715179</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>11167.51190932591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -2243,10 +2243,10 @@
         <v>452</v>
       </c>
       <c r="B166" t="n">
-        <v>5905.338808472769</v>
+        <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>16287.47953561589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -2254,10 +2254,10 @@
         <v>453</v>
       </c>
       <c r="B167" t="n">
-        <v>8110.341523189127</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>22369.08429305879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -2265,10 +2265,10 @@
         <v>454</v>
       </c>
       <c r="B168" t="n">
-        <v>9876.209333476605</v>
+        <v>5546.557472199574</v>
       </c>
       <c r="C168" t="n">
-        <v>27239.51370540582</v>
+        <v>15297.92688472881</v>
       </c>
     </row>
     <row r="169">
@@ -2276,10 +2276,10 @@
         <v>455</v>
       </c>
       <c r="B169" t="n">
-        <v>10651.48526512742</v>
+        <v>6253.125660203575</v>
       </c>
       <c r="C169" t="n">
-        <v>29377.79760083634</v>
+        <v>17246.70836465352</v>
       </c>
     </row>
     <row r="170">
@@ -2287,10 +2287,10 @@
         <v>456</v>
       </c>
       <c r="B170" t="n">
-        <v>10651.48526512742</v>
+        <v>6183.793196442298</v>
       </c>
       <c r="C170" t="n">
-        <v>29377.79760083634</v>
+        <v>17055.48291234832</v>
       </c>
     </row>
     <row r="171">
@@ -2298,10 +2298,10 @@
         <v>457</v>
       </c>
       <c r="B171" t="n">
-        <v>10651.48526512742</v>
+        <v>6455.139844724877</v>
       </c>
       <c r="C171" t="n">
-        <v>29377.79760083634</v>
+        <v>17803.88247489661</v>
       </c>
     </row>
     <row r="172">
@@ -2309,10 +2309,10 @@
         <v>458</v>
       </c>
       <c r="B172" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C172" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="173">
@@ -2320,10 +2320,10 @@
         <v>459</v>
       </c>
       <c r="B173" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C173" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="174">
@@ -2331,10 +2331,10 @@
         <v>460</v>
       </c>
       <c r="B174" t="n">
-        <v>10651.48526512742</v>
+        <v>12942.558574349</v>
       </c>
       <c r="C174" t="n">
-        <v>29377.79760083634</v>
+        <v>35696.79314856054</v>
       </c>
     </row>
     <row r="175">
@@ -2342,10 +2342,10 @@
         <v>461</v>
       </c>
       <c r="B175" t="n">
-        <v>10651.48526512742</v>
+        <v>13075.26811572656</v>
       </c>
       <c r="C175" t="n">
-        <v>29377.79760083634</v>
+        <v>36062.81853837674</v>
       </c>
     </row>
     <row r="176">
@@ -2353,10 +2353,10 @@
         <v>462</v>
       </c>
       <c r="B176" t="n">
-        <v>9808.95195246167</v>
+        <v>13356.16694275438</v>
       </c>
       <c r="C176" t="n">
-        <v>27054.01152637281</v>
+        <v>36837.56390780921</v>
       </c>
     </row>
     <row r="177">
@@ -2518,10 +2518,10 @@
         <v>477</v>
       </c>
       <c r="B191" t="n">
-        <v>2289.434984626635</v>
+        <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>6314.476894488813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -2529,10 +2529,10 @@
         <v>478</v>
       </c>
       <c r="B192" t="n">
-        <v>3424.946608583287</v>
+        <v>5072.773245545554</v>
       </c>
       <c r="C192" t="n">
-        <v>9446.324691453912</v>
+        <v>13991.18545189972</v>
       </c>
     </row>
     <row r="193">
@@ -2540,10 +2540,10 @@
         <v>479</v>
       </c>
       <c r="B193" t="n">
-        <v>3836.83402470794</v>
+        <v>5559.296919778698</v>
       </c>
       <c r="C193" t="n">
-        <v>10582.34890254282</v>
+        <v>15333.06347866011</v>
       </c>
     </row>
     <row r="194">
@@ -2551,10 +2551,10 @@
         <v>480</v>
       </c>
       <c r="B194" t="n">
-        <v>10651.48526512742</v>
+        <v>6183.793196442298</v>
       </c>
       <c r="C194" t="n">
-        <v>29377.79760083634</v>
+        <v>17055.48291234832</v>
       </c>
     </row>
     <row r="195">
@@ -2562,10 +2562,10 @@
         <v>481</v>
       </c>
       <c r="B195" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C195" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="196">
@@ -2573,10 +2573,10 @@
         <v>482</v>
       </c>
       <c r="B196" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C196" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="197">
@@ -2584,10 +2584,10 @@
         <v>483</v>
       </c>
       <c r="B197" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C197" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="198">
@@ -2595,10 +2595,10 @@
         <v>484</v>
       </c>
       <c r="B198" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C198" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="199">
@@ -2606,10 +2606,10 @@
         <v>485</v>
       </c>
       <c r="B199" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C199" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="200">
@@ -2617,10 +2617,10 @@
         <v>486</v>
       </c>
       <c r="B200" t="n">
-        <v>9808.95195246167</v>
+        <v>10507.18058270959</v>
       </c>
       <c r="C200" t="n">
-        <v>27054.01152637281</v>
+        <v>28979.79172208783</v>
       </c>
     </row>
     <row r="201">
@@ -2628,10 +2628,10 @@
         <v>487</v>
       </c>
       <c r="B201" t="n">
-        <v>9322.006597581485</v>
+        <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>25710.97046474991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -2771,10 +2771,10 @@
         <v>500</v>
       </c>
       <c r="B214" t="n">
-        <v>2927.085533910706</v>
+        <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>8073.177048565914</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -2782,10 +2782,10 @@
         <v>501</v>
       </c>
       <c r="B215" t="n">
-        <v>5120.850451717535</v>
+        <v>4018.932957836866</v>
       </c>
       <c r="C215" t="n">
-        <v>14123.78690577942</v>
+        <v>11084.59487741211</v>
       </c>
     </row>
     <row r="216">
@@ -2793,10 +2793,10 @@
         <v>502</v>
       </c>
       <c r="B216" t="n">
-        <v>6401.987222217381</v>
+        <v>5072.773245545554</v>
       </c>
       <c r="C216" t="n">
-        <v>17657.28254567442</v>
+        <v>13991.18545189972</v>
       </c>
     </row>
     <row r="217">
@@ -2804,10 +2804,10 @@
         <v>503</v>
       </c>
       <c r="B217" t="n">
-        <v>10651.48526512742</v>
+        <v>5559.296919778698</v>
       </c>
       <c r="C217" t="n">
-        <v>29377.79760083634</v>
+        <v>15333.06347866011</v>
       </c>
     </row>
     <row r="218">
@@ -2815,10 +2815,10 @@
         <v>504</v>
       </c>
       <c r="B218" t="n">
-        <v>10651.48526512742</v>
+        <v>6183.793196442298</v>
       </c>
       <c r="C218" t="n">
-        <v>29377.79760083634</v>
+        <v>17055.48291234832</v>
       </c>
     </row>
     <row r="219">
@@ -2826,10 +2826,10 @@
         <v>505</v>
       </c>
       <c r="B219" t="n">
-        <v>10651.48526512742</v>
+        <v>6455.139844724877</v>
       </c>
       <c r="C219" t="n">
-        <v>29377.79760083634</v>
+        <v>17803.88247489661</v>
       </c>
     </row>
     <row r="220">
@@ -2837,10 +2837,10 @@
         <v>506</v>
       </c>
       <c r="B220" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C220" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="221">
@@ -2848,10 +2848,10 @@
         <v>507</v>
       </c>
       <c r="B221" t="n">
-        <v>10651.48526512742</v>
+        <v>9945.630804522254</v>
       </c>
       <c r="C221" t="n">
-        <v>29377.79760083634</v>
+        <v>27430.984648168</v>
       </c>
     </row>
     <row r="222">
@@ -2859,10 +2859,10 @@
         <v>508</v>
       </c>
       <c r="B222" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C222" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="223">
@@ -2870,10 +2870,10 @@
         <v>509</v>
       </c>
       <c r="B223" t="n">
-        <v>10651.48526512742</v>
+        <v>10171.08903431566</v>
       </c>
       <c r="C223" t="n">
-        <v>29377.79760083634</v>
+        <v>28052.81963901181</v>
       </c>
     </row>
     <row r="224">
@@ -2881,10 +2881,10 @@
         <v>510</v>
       </c>
       <c r="B224" t="n">
-        <v>9808.95195246167</v>
+        <v>7952.96607559232</v>
       </c>
       <c r="C224" t="n">
-        <v>27054.01152637281</v>
+        <v>21935.02801529472</v>
       </c>
     </row>
     <row r="225">
@@ -3046,10 +3046,10 @@
         <v>525</v>
       </c>
       <c r="B239" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -3057,10 +3057,10 @@
         <v>526</v>
       </c>
       <c r="B240" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -3068,10 +3068,10 @@
         <v>527</v>
       </c>
       <c r="B241" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -3079,10 +3079,10 @@
         <v>528</v>
       </c>
       <c r="B242" t="n">
-        <v>10576.92396349697</v>
+        <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>29172.15052217722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -3090,10 +3090,10 @@
         <v>529</v>
       </c>
       <c r="B243" t="n">
-        <v>9010.631191404405</v>
+        <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>24852.16782522534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -3101,10 +3101,10 @@
         <v>530</v>
       </c>
       <c r="B244" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -3112,10 +3112,10 @@
         <v>531</v>
       </c>
       <c r="B245" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -3123,10 +3123,10 @@
         <v>532</v>
       </c>
       <c r="B246" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -3134,10 +3134,10 @@
         <v>533</v>
       </c>
       <c r="B247" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C247" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -3145,10 +3145,10 @@
         <v>534</v>
       </c>
       <c r="B248" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -3189,10 +3189,10 @@
         <v>538</v>
       </c>
       <c r="B252" t="n">
-        <v>2793.359913950261</v>
+        <v>0</v>
       </c>
       <c r="C252" t="n">
-        <v>7704.34921850673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -3211,10 +3211,10 @@
         <v>540</v>
       </c>
       <c r="B254" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -3222,10 +3222,10 @@
         <v>541</v>
       </c>
       <c r="B255" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -3233,10 +3233,10 @@
         <v>542</v>
       </c>
       <c r="B256" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -3244,10 +3244,10 @@
         <v>543</v>
       </c>
       <c r="B257" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -3255,10 +3255,10 @@
         <v>544</v>
       </c>
       <c r="B258" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -3266,10 +3266,10 @@
         <v>545</v>
       </c>
       <c r="B259" t="n">
-        <v>3903.516373553333</v>
+        <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>10766.26508879921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -3277,10 +3277,10 @@
         <v>546</v>
       </c>
       <c r="B260" t="n">
-        <v>5380.7035609299</v>
+        <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>14840.48620717939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -3288,10 +3288,10 @@
         <v>547</v>
       </c>
       <c r="B261" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -3299,10 +3299,10 @@
         <v>548</v>
       </c>
       <c r="B262" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -3310,10 +3310,10 @@
         <v>549</v>
       </c>
       <c r="B263" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -3321,10 +3321,10 @@
         <v>550</v>
       </c>
       <c r="B264" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -3332,10 +3332,10 @@
         <v>551</v>
       </c>
       <c r="B265" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C265" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -3343,10 +3343,10 @@
         <v>552</v>
       </c>
       <c r="B266" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C266" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -3354,10 +3354,10 @@
         <v>553</v>
       </c>
       <c r="B267" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C267" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -3365,10 +3365,10 @@
         <v>554</v>
       </c>
       <c r="B268" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C268" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -3376,10 +3376,10 @@
         <v>555</v>
       </c>
       <c r="B269" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C269" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -3387,10 +3387,10 @@
         <v>556</v>
       </c>
       <c r="B270" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -3398,10 +3398,10 @@
         <v>557</v>
       </c>
       <c r="B271" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -3409,10 +3409,10 @@
         <v>558</v>
       </c>
       <c r="B272" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C272" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -3420,10 +3420,10 @@
         <v>559</v>
       </c>
       <c r="B273" t="n">
-        <v>6858.099304179449</v>
+        <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>18915.28254226151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -3431,10 +3431,10 @@
         <v>560</v>
       </c>
       <c r="B274" t="n">
-        <v>5013.591876888828</v>
+        <v>0</v>
       </c>
       <c r="C274" t="n">
-        <v>13827.95767409581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -3442,10 +3442,10 @@
         <v>561</v>
       </c>
       <c r="B275" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C275" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -3453,10 +3453,10 @@
         <v>562</v>
       </c>
       <c r="B276" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C276" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -3464,10 +3464,10 @@
         <v>563</v>
       </c>
       <c r="B277" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C277" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -3475,10 +3475,10 @@
         <v>564</v>
       </c>
       <c r="B278" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -3486,10 +3486,10 @@
         <v>565</v>
       </c>
       <c r="B279" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -3497,10 +3497,10 @@
         <v>566</v>
       </c>
       <c r="B280" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C280" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -3508,10 +3508,10 @@
         <v>567</v>
       </c>
       <c r="B281" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -3519,10 +3519,10 @@
         <v>568</v>
       </c>
       <c r="B282" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -3530,10 +3530,10 @@
         <v>569</v>
       </c>
       <c r="B283" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C283" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -3541,10 +3541,10 @@
         <v>570</v>
       </c>
       <c r="B284" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C284" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -3552,10 +3552,10 @@
         <v>571</v>
       </c>
       <c r="B285" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -3563,10 +3563,10 @@
         <v>572</v>
       </c>
       <c r="B286" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C286" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -3574,10 +3574,10 @@
         <v>573</v>
       </c>
       <c r="B287" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C287" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -3585,10 +3585,10 @@
         <v>574</v>
       </c>
       <c r="B288" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -3596,10 +3596,10 @@
         <v>575</v>
       </c>
       <c r="B289" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -3607,10 +3607,10 @@
         <v>576</v>
       </c>
       <c r="B290" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -3618,10 +3618,10 @@
         <v>577</v>
       </c>
       <c r="B291" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -3629,10 +3629,10 @@
         <v>578</v>
       </c>
       <c r="B292" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -3640,10 +3640,10 @@
         <v>579</v>
       </c>
       <c r="B293" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C293" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -3651,10 +3651,10 @@
         <v>580</v>
       </c>
       <c r="B294" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C294" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -3662,10 +3662,10 @@
         <v>581</v>
       </c>
       <c r="B295" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -3673,10 +3673,10 @@
         <v>582</v>
       </c>
       <c r="B296" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -3684,10 +3684,10 @@
         <v>583</v>
       </c>
       <c r="B297" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C297" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -3695,10 +3695,10 @@
         <v>584</v>
       </c>
       <c r="B298" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -3706,10 +3706,10 @@
         <v>585</v>
       </c>
       <c r="B299" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -3717,10 +3717,10 @@
         <v>586</v>
       </c>
       <c r="B300" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -3728,10 +3728,10 @@
         <v>587</v>
       </c>
       <c r="B301" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -3739,10 +3739,10 @@
         <v>588</v>
       </c>
       <c r="B302" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C302" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -3750,10 +3750,10 @@
         <v>589</v>
       </c>
       <c r="B303" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C303" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -3761,10 +3761,10 @@
         <v>590</v>
       </c>
       <c r="B304" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C304" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -3772,10 +3772,10 @@
         <v>591</v>
       </c>
       <c r="B305" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C305" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -3783,10 +3783,10 @@
         <v>592</v>
       </c>
       <c r="B306" t="n">
-        <v>5659.777218754313</v>
+        <v>0</v>
       </c>
       <c r="C306" t="n">
-        <v>15610.19758838296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -3838,10 +3838,10 @@
         <v>597</v>
       </c>
       <c r="B311" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C311" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -3849,10 +3849,10 @@
         <v>598</v>
       </c>
       <c r="B312" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C312" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -3860,10 +3860,10 @@
         <v>599</v>
       </c>
       <c r="B313" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C313" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -3871,10 +3871,10 @@
         <v>600</v>
       </c>
       <c r="B314" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C314" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -3882,10 +3882,10 @@
         <v>601</v>
       </c>
       <c r="B315" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C315" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -3893,10 +3893,10 @@
         <v>602</v>
       </c>
       <c r="B316" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C316" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -3904,10 +3904,10 @@
         <v>603</v>
       </c>
       <c r="B317" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C317" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -3915,10 +3915,10 @@
         <v>604</v>
       </c>
       <c r="B318" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C318" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -3926,10 +3926,10 @@
         <v>605</v>
       </c>
       <c r="B319" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C319" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -3937,10 +3937,10 @@
         <v>606</v>
       </c>
       <c r="B320" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C320" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -3948,10 +3948,10 @@
         <v>607</v>
       </c>
       <c r="B321" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C321" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -3959,10 +3959,10 @@
         <v>608</v>
       </c>
       <c r="B322" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C322" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -3970,10 +3970,10 @@
         <v>609</v>
       </c>
       <c r="B323" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C323" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -3981,10 +3981,10 @@
         <v>610</v>
       </c>
       <c r="B324" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C324" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -3992,10 +3992,10 @@
         <v>611</v>
       </c>
       <c r="B325" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C325" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -4003,10 +4003,10 @@
         <v>612</v>
       </c>
       <c r="B326" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C326" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="327">
@@ -4014,10 +4014,10 @@
         <v>613</v>
       </c>
       <c r="B327" t="n">
-        <v>10651.48526512742</v>
+        <v>16227.52394141103</v>
       </c>
       <c r="C327" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="328">
@@ -4025,10 +4025,10 @@
         <v>614</v>
       </c>
       <c r="B328" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C328" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -4036,10 +4036,10 @@
         <v>615</v>
       </c>
       <c r="B329" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C329" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -4047,10 +4047,10 @@
         <v>616</v>
       </c>
       <c r="B330" t="n">
-        <v>7526.226465563411</v>
+        <v>0</v>
       </c>
       <c r="C330" t="n">
-        <v>20758.04005731165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -4058,10 +4058,10 @@
         <v>617</v>
       </c>
       <c r="B331" t="n">
-        <v>8262.238613153166</v>
+        <v>0</v>
       </c>
       <c r="C331" t="n">
-        <v>22788.03074550607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -4069,10 +4069,10 @@
         <v>618</v>
       </c>
       <c r="B332" t="n">
-        <v>7594.491250292505</v>
+        <v>0</v>
       </c>
       <c r="C332" t="n">
-        <v>20946.32075048426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -4080,10 +4080,10 @@
         <v>619</v>
       </c>
       <c r="B333" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C333" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -4091,10 +4091,10 @@
         <v>620</v>
       </c>
       <c r="B334" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C334" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -4102,10 +4102,10 @@
         <v>621</v>
       </c>
       <c r="B335" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C335" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -4113,10 +4113,10 @@
         <v>622</v>
       </c>
       <c r="B336" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C336" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -4124,10 +4124,10 @@
         <v>623</v>
       </c>
       <c r="B337" t="n">
-        <v>10651.48526512742</v>
+        <v>0</v>
       </c>
       <c r="C337" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4199,10 +4199,10 @@
         <v>5163</v>
       </c>
       <c r="B5" t="n">
-        <v>2687.381128205926</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>9660.533182527583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4254,7 +4254,7 @@
         <v>5168</v>
       </c>
       <c r="B10" t="n">
-        <v>690.3397879591588</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         <v>5169</v>
       </c>
       <c r="B11" t="n">
-        <v>716.9192426275441</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>5170</v>
       </c>
       <c r="B12" t="n">
-        <v>1088.230744064651</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>5171</v>
       </c>
       <c r="B13" t="n">
-        <v>1844.754962767621</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>5172</v>
       </c>
       <c r="B14" t="n">
-        <v>1490.176574563599</v>
+        <v>5309.422455413364</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>19086.18441658103</v>
       </c>
     </row>
     <row r="15">
@@ -4309,7 +4309,7 @@
         <v>5173</v>
       </c>
       <c r="B15" t="n">
-        <v>1497.163797044169</v>
+        <v>1327.989828441336</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>5174</v>
       </c>
       <c r="B16" t="n">
-        <v>1879.512102603256</v>
+        <v>2000.852027642381</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
         <v>5175</v>
       </c>
       <c r="B17" t="n">
-        <v>1494.335245363373</v>
+        <v>1988.594826220712</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>5176</v>
       </c>
       <c r="B18" t="n">
-        <v>1468.315675708288</v>
+        <v>3261.799678452492</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -4353,7 +4353,7 @@
         <v>5177</v>
       </c>
       <c r="B19" t="n">
-        <v>957.805625470408</v>
+        <v>2324.552178485387</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
         <v>5178</v>
       </c>
       <c r="B20" t="n">
-        <v>572.270525798585</v>
+        <v>1517.479418776307</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -4375,10 +4375,10 @@
         <v>5179</v>
       </c>
       <c r="B21" t="n">
-        <v>2269.559322750585</v>
+        <v>847.3816435518777</v>
       </c>
       <c r="C21" t="n">
-        <v>8158.557384000055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -4386,10 +4386,10 @@
         <v>5180</v>
       </c>
       <c r="B22" t="n">
-        <v>2347.394234261428</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>8438.356455861358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4397,10 +4397,10 @@
         <v>5181</v>
       </c>
       <c r="B23" t="n">
-        <v>2158.475785200996</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>7759.236949221693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4408,10 +4408,10 @@
         <v>5182</v>
       </c>
       <c r="B24" t="n">
-        <v>1875.771080859399</v>
+        <v>1874.820568382635</v>
       </c>
       <c r="C24" t="n">
-        <v>6742.976862967427</v>
+        <v>6739.559983528256</v>
       </c>
     </row>
     <row r="25">
@@ -4419,10 +4419,10 @@
         <v>5183</v>
       </c>
       <c r="B25" t="n">
-        <v>8172.358333547443</v>
+        <v>2686.906972228544</v>
       </c>
       <c r="C25" t="n">
-        <v>29377.79760083634</v>
+        <v>9658.828697999836</v>
       </c>
     </row>
     <row r="26">
@@ -4430,10 +4430,10 @@
         <v>5184</v>
       </c>
       <c r="B26" t="n">
-        <v>8172.358333547438</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>29377.79760083632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4441,10 +4441,10 @@
         <v>5185</v>
       </c>
       <c r="B27" t="n">
-        <v>8172.358333547443</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4452,10 +4452,10 @@
         <v>5186</v>
       </c>
       <c r="B28" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C28" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="29">
@@ -4463,10 +4463,10 @@
         <v>5187</v>
       </c>
       <c r="B29" t="n">
-        <v>8172.358333547443</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -4474,10 +4474,10 @@
         <v>5188</v>
       </c>
       <c r="B30" t="n">
-        <v>8172.358333547443</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4485,10 +4485,10 @@
         <v>5189</v>
       </c>
       <c r="B31" t="n">
-        <v>5893.627185623548</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>21186.26955982707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4496,10 +4496,10 @@
         <v>5190</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2070.628765404916</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>7443.446590787222</v>
       </c>
     </row>
     <row r="33">
@@ -4518,10 +4518,10 @@
         <v>5192</v>
       </c>
       <c r="B34" t="n">
-        <v>3620.761535666179</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>13015.82667013592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4529,10 +4529,10 @@
         <v>5193</v>
       </c>
       <c r="B35" t="n">
-        <v>8172.358333547443</v>
+        <v>1916.339354268994</v>
       </c>
       <c r="C35" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4540,10 +4540,10 @@
         <v>5194</v>
       </c>
       <c r="B36" t="n">
-        <v>8172.358333547443</v>
+        <v>3227.117824545722</v>
       </c>
       <c r="C36" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4551,10 +4551,10 @@
         <v>5195</v>
       </c>
       <c r="B37" t="n">
-        <v>8172.358333547443</v>
+        <v>3929.157135457161</v>
       </c>
       <c r="C37" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4562,10 +4562,10 @@
         <v>5196</v>
       </c>
       <c r="B38" t="n">
-        <v>8172.358333547443</v>
+        <v>3964.028805785842</v>
       </c>
       <c r="C38" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4573,10 +4573,10 @@
         <v>5197</v>
       </c>
       <c r="B39" t="n">
-        <v>8172.358333547443</v>
+        <v>3983.964669036627</v>
       </c>
       <c r="C39" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4584,10 +4584,10 @@
         <v>5198</v>
       </c>
       <c r="B40" t="n">
-        <v>8172.358333547443</v>
+        <v>4001.704055284764</v>
       </c>
       <c r="C40" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4595,10 +4595,10 @@
         <v>5199</v>
       </c>
       <c r="B41" t="n">
-        <v>8172.358333547443</v>
+        <v>3314.316683222221</v>
       </c>
       <c r="C41" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4606,10 +4606,10 @@
         <v>5200</v>
       </c>
       <c r="B42" t="n">
-        <v>8172.358333547443</v>
+        <v>4566.527817300436</v>
       </c>
       <c r="C42" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4617,10 +4617,10 @@
         <v>5201</v>
       </c>
       <c r="B43" t="n">
-        <v>8172.358333547443</v>
+        <v>3486.833551854741</v>
       </c>
       <c r="C43" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4628,10 +4628,10 @@
         <v>5202</v>
       </c>
       <c r="B44" t="n">
-        <v>8172.358333547443</v>
+        <v>2023.307809023724</v>
       </c>
       <c r="C44" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4639,10 +4639,10 @@
         <v>5203</v>
       </c>
       <c r="B45" t="n">
-        <v>2269.559322750585</v>
+        <v>1271.067649040437</v>
       </c>
       <c r="C45" t="n">
-        <v>8158.557384000055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4661,10 +4661,10 @@
         <v>5205</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>2157.297466391308</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>7755.00115704428</v>
       </c>
     </row>
     <row r="48">
@@ -4672,10 +4672,10 @@
         <v>5206</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1874.820568382635</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>6739.559983528256</v>
       </c>
     </row>
     <row r="49">
@@ -4683,10 +4683,10 @@
         <v>5207</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="50">
@@ -4705,10 +4705,10 @@
         <v>5209</v>
       </c>
       <c r="B51" t="n">
-        <v>8172.358333547443</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4716,10 +4716,10 @@
         <v>5210</v>
       </c>
       <c r="B52" t="n">
-        <v>8172.358333547444</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4727,10 +4727,10 @@
         <v>5211</v>
       </c>
       <c r="B53" t="n">
-        <v>8172.358333547443</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4738,10 +4738,10 @@
         <v>5212</v>
       </c>
       <c r="B54" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C54" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="55">
@@ -4793,10 +4793,10 @@
         <v>5217</v>
       </c>
       <c r="B59" t="n">
-        <v>8172.358333547443</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4804,10 +4804,10 @@
         <v>5218</v>
       </c>
       <c r="B60" t="n">
-        <v>8172.358333547443</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4815,10 +4815,10 @@
         <v>5219</v>
       </c>
       <c r="B61" t="n">
-        <v>8172.358333547443</v>
+        <v>2288.64786677666</v>
       </c>
       <c r="C61" t="n">
-        <v>29377.79760083634</v>
+        <v>8227.176423939933</v>
       </c>
     </row>
     <row r="62">
@@ -4826,10 +4826,10 @@
         <v>5220</v>
       </c>
       <c r="B62" t="n">
-        <v>8172.358333547443</v>
+        <v>1376.52520246953</v>
       </c>
       <c r="C62" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4837,10 +4837,10 @@
         <v>5221</v>
       </c>
       <c r="B63" t="n">
-        <v>8172.358333547443</v>
+        <v>1991.984742662004</v>
       </c>
       <c r="C63" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4848,10 +4848,10 @@
         <v>5222</v>
       </c>
       <c r="B64" t="n">
-        <v>8172.358333547443</v>
+        <v>2667.799804557779</v>
       </c>
       <c r="C64" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4859,10 +4859,10 @@
         <v>5223</v>
       </c>
       <c r="B65" t="n">
-        <v>8172.358333547443</v>
+        <v>2054.426363079256</v>
       </c>
       <c r="C65" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4870,10 +4870,10 @@
         <v>5224</v>
       </c>
       <c r="B66" t="n">
-        <v>8172.358333547443</v>
+        <v>2609.440893155184</v>
       </c>
       <c r="C66" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4881,10 +4881,10 @@
         <v>5225</v>
       </c>
       <c r="B67" t="n">
-        <v>8172.358333547443</v>
+        <v>1743.416775927372</v>
       </c>
       <c r="C67" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4892,10 +4892,10 @@
         <v>5226</v>
       </c>
       <c r="B68" t="n">
-        <v>2114.307417088083</v>
+        <v>1011.655844816268</v>
       </c>
       <c r="C68" t="n">
-        <v>7600.46155957023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5002,10 +5002,10 @@
         <v>5236</v>
       </c>
       <c r="B78" t="n">
-        <v>3407.121799670613</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>12247.83967453272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -5035,10 +5035,10 @@
         <v>5239</v>
       </c>
       <c r="B81" t="n">
-        <v>2631.044817889538</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>9458.016766273679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5057,10 +5057,10 @@
         <v>5241</v>
       </c>
       <c r="B83" t="n">
-        <v>1075.375719707645</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="84">
@@ -5068,7 +5068,7 @@
         <v>5242</v>
       </c>
       <c r="B84" t="n">
-        <v>1474.736780830645</v>
+        <v>1936.272246970959</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>5243</v>
       </c>
       <c r="B85" t="n">
-        <v>1475.804549839725</v>
+        <v>3274.289585735333</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>5244</v>
       </c>
       <c r="B86" t="n">
-        <v>1490.176574563599</v>
+        <v>3964.028805785842</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>5245</v>
       </c>
       <c r="B87" t="n">
-        <v>1497.163797044169</v>
+        <v>4647.959583257298</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         <v>5246</v>
       </c>
       <c r="B88" t="n">
-        <v>1127.709109819074</v>
+        <v>4732.546514427365</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
         <v>5247</v>
       </c>
       <c r="B89" t="n">
-        <v>1159.230484233877</v>
+        <v>5302.906693155553</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>5248</v>
       </c>
       <c r="B90" t="n">
-        <v>1835.390835249886</v>
+        <v>5218.886602597744</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>5249</v>
       </c>
       <c r="B91" t="n">
-        <v>1277.071086865342</v>
+        <v>4067.968954412758</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
         <v>5250</v>
       </c>
       <c r="B92" t="n">
-        <v>572.270525798585</v>
+        <v>3034.963653839994</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>5251</v>
       </c>
       <c r="B93" t="n">
-        <v>441.9208053756686</v>
+        <v>2118.444476304936</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -5178,10 +5178,10 @@
         <v>5252</v>
       </c>
       <c r="B94" t="n">
-        <v>2347.394234261428</v>
+        <v>1221.663651469608</v>
       </c>
       <c r="C94" t="n">
-        <v>8438.356455861358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5189,7 +5189,7 @@
         <v>5253</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>710.6220486422399</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -5200,10 +5200,10 @@
         <v>5254</v>
       </c>
       <c r="B96" t="n">
-        <v>1875.771080859399</v>
+        <v>1874.820568382665</v>
       </c>
       <c r="C96" t="n">
-        <v>6742.976862967427</v>
+        <v>6739.55998352836</v>
       </c>
     </row>
     <row r="97">
@@ -5211,10 +5211,10 @@
         <v>5255</v>
       </c>
       <c r="B97" t="n">
-        <v>1419.616534635928</v>
+        <v>1867.586593058722</v>
       </c>
       <c r="C97" t="n">
-        <v>5103.203447912404</v>
+        <v>6713.555462649259</v>
       </c>
     </row>
     <row r="98">
@@ -5266,10 +5266,10 @@
         <v>5260</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>12388.0429580152</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>44532.23951244205</v>
       </c>
     </row>
     <row r="103">
@@ -5277,10 +5277,10 @@
         <v>5261</v>
       </c>
       <c r="B103" t="n">
-        <v>1264.498084981877</v>
+        <v>1867.586593058722</v>
       </c>
       <c r="C103" t="n">
-        <v>4545.587367938811</v>
+        <v>6713.555462649259</v>
       </c>
     </row>
     <row r="104">
@@ -5288,10 +5288,10 @@
         <v>5262</v>
       </c>
       <c r="B104" t="n">
-        <v>2071.806406992595</v>
+        <v>2070.628765404916</v>
       </c>
       <c r="C104" t="n">
-        <v>7447.679948503212</v>
+        <v>7443.446590787222</v>
       </c>
     </row>
     <row r="105">
@@ -5299,7 +5299,7 @@
         <v>5263</v>
       </c>
       <c r="B105" t="n">
-        <v>656.9809114963647</v>
+        <v>1188.29535412091</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>5264</v>
       </c>
       <c r="B106" t="n">
-        <v>690.3397879591588</v>
+        <v>2475.334940521342</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -5321,7 +5321,7 @@
         <v>5265</v>
       </c>
       <c r="B107" t="n">
-        <v>1075.375719707645</v>
+        <v>3832.674827929175</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
         <v>5266</v>
       </c>
       <c r="B108" t="n">
-        <v>1450.970643549065</v>
+        <v>4558.632946774895</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>5267</v>
       </c>
       <c r="B109" t="n">
-        <v>1844.754962767621</v>
+        <v>5893.755904013819</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
         <v>5268</v>
       </c>
       <c r="B110" t="n">
-        <v>1862.716685368439</v>
+        <v>6606.714988202591</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>5269</v>
       </c>
       <c r="B111" t="n">
-        <v>1871.455470837247</v>
+        <v>7303.93442385259</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>5270</v>
       </c>
       <c r="B112" t="n">
-        <v>1879.512102603256</v>
+        <v>7336.46514994151</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -5387,7 +5387,7 @@
         <v>5271</v>
       </c>
       <c r="B113" t="n">
-        <v>1867.915434044036</v>
+        <v>7357.323423660053</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
         <v>5272</v>
       </c>
       <c r="B114" t="n">
-        <v>1468.315675708288</v>
+        <v>7828.327495752929</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -5409,7 +5409,7 @@
         <v>5273</v>
       </c>
       <c r="B115" t="n">
-        <v>1277.071086865342</v>
+        <v>5811.404995489645</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>5274</v>
       </c>
       <c r="B116" t="n">
-        <v>804.9293551367629</v>
+        <v>4552.443072616299</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -5431,10 +5431,10 @@
         <v>5275</v>
       </c>
       <c r="B117" t="n">
-        <v>2269.559322750585</v>
+        <v>2965.826119856812</v>
       </c>
       <c r="C117" t="n">
-        <v>8158.557384000055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5442,7 +5442,7 @@
         <v>5276</v>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>2348.451367717662</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
         <v>5277</v>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>1776.547663254889</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -5464,7 +5464,7 @@
         <v>5278</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>1017.839082958451</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>5279</v>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>915.7336334687392</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
         <v>5280</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>531.9509231328631</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -5563,10 +5563,10 @@
         <v>5287</v>
       </c>
       <c r="B129" t="n">
-        <v>1932.317511575456</v>
+        <v>1535.001450798823</v>
       </c>
       <c r="C129" t="n">
-        <v>6946.248614991171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5574,10 +5574,10 @@
         <v>5288</v>
       </c>
       <c r="B130" t="n">
-        <v>8172.358333547443</v>
+        <v>2672.182900350447</v>
       </c>
       <c r="C130" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5585,7 +5585,7 @@
         <v>5289</v>
       </c>
       <c r="B131" t="n">
-        <v>960.499716303184</v>
+        <v>3876.708943975496</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
         <v>5290</v>
       </c>
       <c r="B132" t="n">
-        <v>1298.404483621192</v>
+        <v>5047.89724987357</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>5291</v>
       </c>
       <c r="B133" t="n">
-        <v>1655.295631556161</v>
+        <v>6283.156280782693</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>5292</v>
       </c>
       <c r="B134" t="n">
-        <v>1674.616576256903</v>
+        <v>6932.897048177049</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -5629,7 +5629,7 @@
         <v>5293</v>
       </c>
       <c r="B135" t="n">
-        <v>1683.387241135303</v>
+        <v>7552.574985514701</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>5294</v>
       </c>
       <c r="B136" t="n">
-        <v>1352.735777506381</v>
+        <v>8169.584221112982</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>5295</v>
       </c>
       <c r="B137" t="n">
-        <v>1009.921942040277</v>
+        <v>8133.212161511111</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -5662,7 +5662,7 @@
         <v>5296</v>
       </c>
       <c r="B138" t="n">
-        <v>995.2646642949775</v>
+        <v>8027.969999425504</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
         <v>5297</v>
       </c>
       <c r="B139" t="n">
-        <v>619.7128942235997</v>
+        <v>6666.308259455172</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -5684,10 +5684,10 @@
         <v>5298</v>
       </c>
       <c r="B140" t="n">
-        <v>8172.358333547443</v>
+        <v>4926.0660631894</v>
       </c>
       <c r="C140" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -5695,7 +5695,7 @@
         <v>5299</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>3450.709893829663</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -5706,7 +5706,7 @@
         <v>5300</v>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>2910.390652124738</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -5717,10 +5717,10 @@
         <v>5301</v>
       </c>
       <c r="B143" t="n">
-        <v>2328.607533719675</v>
+        <v>2390.762180999916</v>
       </c>
       <c r="C143" t="n">
-        <v>8370.822475634677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -5728,7 +5728,7 @@
         <v>5302</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>1649.9029689193</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>5303</v>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>1498.858027043226</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -5750,10 +5750,10 @@
         <v>5304</v>
       </c>
       <c r="B146" t="n">
-        <v>8172.358333547443</v>
+        <v>1059.263761519767</v>
       </c>
       <c r="C146" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -5761,10 +5761,10 @@
         <v>5305</v>
       </c>
       <c r="B147" t="n">
-        <v>8172.358333547443</v>
+        <v>731.8419023983838</v>
       </c>
       <c r="C147" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -5772,10 +5772,10 @@
         <v>5306</v>
       </c>
       <c r="B148" t="n">
-        <v>8172.358333547443</v>
+        <v>504.1155444438644</v>
       </c>
       <c r="C148" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -5783,10 +5783,10 @@
         <v>5307</v>
       </c>
       <c r="B149" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C149" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="150">
@@ -5794,10 +5794,10 @@
         <v>5308</v>
       </c>
       <c r="B150" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C150" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.03641766209</v>
       </c>
     </row>
     <row r="151">
@@ -5805,10 +5805,10 @@
         <v>5309</v>
       </c>
       <c r="B151" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C151" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="152">
@@ -5816,10 +5816,10 @@
         <v>5310</v>
       </c>
       <c r="B152" t="n">
-        <v>8172.358333547443</v>
+        <v>687.0446550929947</v>
       </c>
       <c r="C152" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -5827,10 +5827,10 @@
         <v>5311</v>
       </c>
       <c r="B153" t="n">
-        <v>1449.576525810038</v>
+        <v>1134.99433511229</v>
       </c>
       <c r="C153" t="n">
-        <v>5210.902905145304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -5838,7 +5838,7 @@
         <v>5312</v>
       </c>
       <c r="B154" t="n">
-        <v>642.022129331799</v>
+        <v>1972.246304425233</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>5313</v>
       </c>
       <c r="B155" t="n">
-        <v>692.7235785653447</v>
+        <v>2458.496529245611</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>5314</v>
       </c>
       <c r="B156" t="n">
-        <v>912.7042013393901</v>
+        <v>3331.587411231836</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
         <v>5315</v>
       </c>
       <c r="B157" t="n">
-        <v>1169.722955275643</v>
+        <v>3832.384905809829</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -5882,7 +5882,7 @@
         <v>5316</v>
       </c>
       <c r="B158" t="n">
-        <v>1191.452244464731</v>
+        <v>4330.922875886352</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -5893,7 +5893,7 @@
         <v>5317</v>
       </c>
       <c r="B159" t="n">
-        <v>1439.334293949124</v>
+        <v>4796.941252195735</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>5318</v>
       </c>
       <c r="B160" t="n">
-        <v>1197.411560566057</v>
+        <v>4794.655036821998</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -5915,7 +5915,7 @@
         <v>5319</v>
       </c>
       <c r="B161" t="n">
-        <v>1127.884208519988</v>
+        <v>4568.257044403148</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>5320</v>
       </c>
       <c r="B162" t="n">
-        <v>1050.699455014127</v>
+        <v>3992.248631752863</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>5321</v>
       </c>
       <c r="B163" t="n">
-        <v>781.656367405008</v>
+        <v>3331.06299077794</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>5322</v>
       </c>
       <c r="B164" t="n">
-        <v>578.857971071766</v>
+        <v>2926.876029629524</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -5959,10 +5959,10 @@
         <v>5323</v>
       </c>
       <c r="B165" t="n">
-        <v>2059.940996370286</v>
+        <v>2452.169070888459</v>
       </c>
       <c r="C165" t="n">
-        <v>7405.02645516799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -5970,10 +5970,10 @@
         <v>5324</v>
       </c>
       <c r="B166" t="n">
-        <v>1943.017407301031</v>
+        <v>1645.560970092511</v>
       </c>
       <c r="C166" t="n">
-        <v>6984.712343347969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -5981,10 +5981,10 @@
         <v>5325</v>
       </c>
       <c r="B167" t="n">
-        <v>1891.679605926428</v>
+        <v>1223.241893982893</v>
       </c>
       <c r="C167" t="n">
-        <v>6800.164447073782</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -5992,7 +5992,7 @@
         <v>5326</v>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>1213.878510018219</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>5327</v>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>863.2746313368747</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         <v>5328</v>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>1867.586593058724</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>6713.555462649267</v>
       </c>
     </row>
     <row r="171">
@@ -6025,10 +6025,10 @@
         <v>5329</v>
       </c>
       <c r="B171" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C171" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="172">
@@ -6036,10 +6036,10 @@
         <v>5330</v>
       </c>
       <c r="B172" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C172" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="173">
@@ -6047,10 +6047,10 @@
         <v>5331</v>
       </c>
       <c r="B173" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C173" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="174">
@@ -6058,10 +6058,10 @@
         <v>5332</v>
       </c>
       <c r="B174" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C174" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="175">
@@ -6069,10 +6069,10 @@
         <v>5333</v>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>1867.586593058722</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>6713.555462649259</v>
       </c>
     </row>
     <row r="176">
@@ -6080,10 +6080,10 @@
         <v>5334</v>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>2070.628765404916</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>7443.446590787222</v>
       </c>
     </row>
     <row r="177">
@@ -6091,10 +6091,10 @@
         <v>5335</v>
       </c>
       <c r="B177" t="n">
-        <v>2631.044817889538</v>
+        <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>9458.016766273679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -6102,7 +6102,7 @@
         <v>5336</v>
       </c>
       <c r="B178" t="n">
-        <v>1380.676677790173</v>
+        <v>1856.503613534696</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>5337</v>
       </c>
       <c r="B179" t="n">
-        <v>1792.292447037863</v>
+        <v>2555.113652987385</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
         <v>5338</v>
       </c>
       <c r="B180" t="n">
-        <v>2539.201387613717</v>
+        <v>3872.550245907864</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>5339</v>
       </c>
       <c r="B181" t="n">
-        <v>2951.606201551307</v>
+        <v>4584.010236316848</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>5340</v>
       </c>
       <c r="B182" t="n">
-        <v>2980.349704097881</v>
+        <v>5946.028759816625</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -6157,7 +6157,7 @@
         <v>5341</v>
       </c>
       <c r="B183" t="n">
-        <v>2994.330492216481</v>
+        <v>6639.949142206677</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
         <v>5342</v>
       </c>
       <c r="B184" t="n">
-        <v>3044.567999579099</v>
+        <v>6669.522189313492</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>5343</v>
       </c>
       <c r="B185" t="n">
-        <v>3362.241985022975</v>
+        <v>6694.464903302984</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -6190,7 +6190,7 @@
         <v>5344</v>
       </c>
       <c r="B186" t="n">
-        <v>2976.238864391453</v>
+        <v>6523.590660008794</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>5345</v>
       </c>
       <c r="B187" t="n">
-        <v>2554.142173730684</v>
+        <v>5230.250327782114</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>5346</v>
       </c>
       <c r="B188" t="n">
-        <v>1609.861608401671</v>
+        <v>4046.609866081502</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>5347</v>
       </c>
       <c r="B189" t="n">
-        <v>1104.797666246954</v>
+        <v>2596.349449865642</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>5348</v>
       </c>
       <c r="B190" t="n">
-        <v>839.6310055495454</v>
+        <v>1957.039907465989</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>5349</v>
       </c>
       <c r="B191" t="n">
-        <v>585.6417030346713</v>
+        <v>1459.963461259691</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>5350</v>
       </c>
       <c r="B192" t="n">
-        <v>563.1645323076219</v>
+        <v>1357.119712956501</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -6267,7 +6267,7 @@
         <v>5351</v>
       </c>
       <c r="B193" t="n">
-        <v>503.2959857066625</v>
+        <v>915.7336334687392</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -6278,7 +6278,7 @@
         <v>5352</v>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>811.8213270037274</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
         <v>5353</v>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>497.999270684367</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -6322,10 +6322,10 @@
         <v>5356</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>11521.83592488392</v>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>41418.4192587105</v>
       </c>
     </row>
     <row r="199">
@@ -6333,10 +6333,10 @@
         <v>5357</v>
       </c>
       <c r="B199" t="n">
-        <v>1264.498084981877</v>
+        <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>4545.587367938811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -6344,10 +6344,10 @@
         <v>5358</v>
       </c>
       <c r="B200" t="n">
-        <v>2071.806406992595</v>
+        <v>2070.628765404943</v>
       </c>
       <c r="C200" t="n">
-        <v>7447.679948503212</v>
+        <v>7443.44659078732</v>
       </c>
     </row>
     <row r="201">
@@ -6355,10 +6355,10 @@
         <v>5359</v>
       </c>
       <c r="B201" t="n">
-        <v>2631.044817889538</v>
+        <v>1782.438214893986</v>
       </c>
       <c r="C201" t="n">
-        <v>9458.016766273679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -6366,7 +6366,7 @@
         <v>5360</v>
       </c>
       <c r="B202" t="n">
-        <v>1380.676677790173</v>
+        <v>3094.166735347271</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -6377,7 +6377,7 @@
         <v>5361</v>
       </c>
       <c r="B203" t="n">
-        <v>1792.292447037863</v>
+        <v>4471.453007256381</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -6388,7 +6388,7 @@
         <v>5362</v>
       </c>
       <c r="B204" t="n">
-        <v>2539.201387613717</v>
+        <v>5808.83212545358</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -6399,7 +6399,7 @@
         <v>5363</v>
       </c>
       <c r="B205" t="n">
-        <v>3320.565855764806</v>
+        <v>6596.985566397112</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -6410,7 +6410,7 @@
         <v>5364</v>
       </c>
       <c r="B206" t="n">
-        <v>3725.43391763805</v>
+        <v>7928.038346422167</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -6421,7 +6421,7 @@
         <v>5365</v>
       </c>
       <c r="B207" t="n">
-        <v>4117.196819211281</v>
+        <v>8631.904987144411</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>5366</v>
       </c>
       <c r="B208" t="n">
-        <v>4134.936118497692</v>
+        <v>9337.341259020788</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>5367</v>
       </c>
       <c r="B209" t="n">
-        <v>4147.898076832479</v>
+        <v>9942.921289836935</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>5368</v>
       </c>
       <c r="B210" t="n">
-        <v>4404.949925253007</v>
+        <v>9133.067138532761</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
         <v>5369</v>
       </c>
       <c r="B211" t="n">
-        <v>3511.94779920109</v>
+        <v>7554.81695512964</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -6476,7 +6476,7 @@
         <v>5370</v>
       </c>
       <c r="B212" t="n">
-        <v>2683.098998798981</v>
+        <v>6069.927307679985</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -6487,7 +6487,7 @@
         <v>5371</v>
       </c>
       <c r="B213" t="n">
-        <v>1799.365425988101</v>
+        <v>4236.893768897251</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
         <v>5372</v>
       </c>
       <c r="B214" t="n">
-        <v>1469.352537197047</v>
+        <v>3522.67798725506</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>5373</v>
       </c>
       <c r="B215" t="n">
-        <v>1171.283952970514</v>
+        <v>2842.478936265626</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
         <v>5374</v>
       </c>
       <c r="B216" t="n">
-        <v>750.8846578925702</v>
+        <v>2035.683917882848</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -6531,7 +6531,7 @@
         <v>5375</v>
       </c>
       <c r="B217" t="n">
-        <v>671.0582338470149</v>
+        <v>1831.472083224858</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
@@ -6542,7 +6542,7 @@
         <v>5376</v>
       </c>
       <c r="B218" t="n">
-        <v>306.3151758225118</v>
+        <v>1353.034251469941</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>5377</v>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>1015.358798552934</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         <v>5378</v>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>993.7423838404452</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>5379</v>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>786.3762244749153</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -6586,7 +6586,7 @@
         <v>5380</v>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>632.572247008873</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
@@ -6597,10 +6597,10 @@
         <v>5381</v>
       </c>
       <c r="B223" t="n">
-        <v>1264.498084981877</v>
+        <v>844.3397324731509</v>
       </c>
       <c r="C223" t="n">
-        <v>4545.587367938811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -6608,7 +6608,7 @@
         <v>5382</v>
       </c>
       <c r="B224" t="n">
-        <v>842.1372331707084</v>
+        <v>1585.606203008711</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>5383</v>
       </c>
       <c r="B225" t="n">
-        <v>1642.443584356478</v>
+        <v>2970.72393644014</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -6630,7 +6630,7 @@
         <v>5384</v>
       </c>
       <c r="B226" t="n">
-        <v>2761.353355580345</v>
+        <v>4331.834205607942</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
@@ -6641,7 +6641,7 @@
         <v>5385</v>
       </c>
       <c r="B227" t="n">
-        <v>3584.595939687137</v>
+        <v>5749.014182198166</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -6652,7 +6652,7 @@
         <v>5386</v>
       </c>
       <c r="B228" t="n">
-        <v>3990.157540522056</v>
+        <v>6454.226016516687</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
         <v>5387</v>
       </c>
       <c r="B229" t="n">
-        <v>3689.50467618012</v>
+        <v>7858.324839167642</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
         <v>5388</v>
       </c>
       <c r="B230" t="n">
-        <v>4470.53787117406</v>
+        <v>8588.72457480813</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
         <v>5389</v>
       </c>
       <c r="B231" t="n">
-        <v>4117.196819211281</v>
+        <v>9355.961275985765</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
         <v>5390</v>
       </c>
       <c r="B232" t="n">
-        <v>4134.936118497692</v>
+        <v>10004.23137838218</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -6707,7 +6707,7 @@
         <v>5391</v>
       </c>
       <c r="B233" t="n">
-        <v>2988.667592598601</v>
+        <v>10008.75563373118</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>5392</v>
       </c>
       <c r="B234" t="n">
-        <v>2936.628453288431</v>
+        <v>9133.067138532761</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
         <v>5393</v>
       </c>
       <c r="B235" t="n">
-        <v>2234.87671233575</v>
+        <v>7554.81695512964</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>5394</v>
       </c>
       <c r="B236" t="n">
-        <v>1609.861608401671</v>
+        <v>5564.103733719947</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
         <v>5395</v>
       </c>
       <c r="B237" t="n">
-        <v>1325.759517998861</v>
+        <v>3813.207763408692</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -6762,7 +6762,7 @@
         <v>5396</v>
       </c>
       <c r="B238" t="n">
-        <v>1049.537034422274</v>
+        <v>3131.265591324821</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -6773,7 +6773,7 @@
         <v>5397</v>
       </c>
       <c r="B239" t="n">
-        <v>780.856934689724</v>
+        <v>2487.169805464986</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -6784,7 +6784,7 @@
         <v>5398</v>
       </c>
       <c r="B240" t="n">
-        <v>563.1645323076219</v>
+        <v>1696.399407275985</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>5399</v>
       </c>
       <c r="B241" t="n">
-        <v>671.0582338470149</v>
+        <v>1220.981076923717</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -6806,7 +6806,7 @@
         <v>5400</v>
       </c>
       <c r="B242" t="n">
-        <v>600.1805185620557</v>
+        <v>1082.430103812667</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
         <v>5401</v>
       </c>
       <c r="B243" t="n">
-        <v>661.63948185294</v>
+        <v>746.998758780038</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         <v>5402</v>
       </c>
       <c r="B244" t="n">
-        <v>791.4783456982442</v>
+        <v>745.3079919521787</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         <v>5403</v>
       </c>
       <c r="B245" t="n">
-        <v>692.2032510547143</v>
+        <v>524.2540895534338</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>5404</v>
       </c>
       <c r="B246" t="n">
-        <v>652.5337281047515</v>
+        <v>1265.134955010845</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
         <v>5405</v>
       </c>
       <c r="B247" t="n">
-        <v>886.006898556305</v>
+        <v>1281.996881384645</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>5406</v>
       </c>
       <c r="B248" t="n">
-        <v>842.1372331707084</v>
+        <v>2092.1977583921</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -6883,7 +6883,7 @@
         <v>5407</v>
       </c>
       <c r="B249" t="n">
-        <v>1642.443584356478</v>
+        <v>2970.72393644014</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>5408</v>
       </c>
       <c r="B250" t="n">
-        <v>2086.860739570775</v>
+        <v>4331.834205607942</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -6905,7 +6905,7 @@
         <v>5409</v>
       </c>
       <c r="B251" t="n">
-        <v>2867.668166745508</v>
+        <v>5145.581536485603</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -6916,7 +6916,7 @@
         <v>5410</v>
       </c>
       <c r="B252" t="n">
-        <v>3627.426882323249</v>
+        <v>5849.492973211798</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -6927,7 +6927,7 @@
         <v>5411</v>
       </c>
       <c r="B253" t="n">
-        <v>4427.411298292202</v>
+        <v>7203.452473158436</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
         <v>5412</v>
       </c>
       <c r="B254" t="n">
-        <v>4470.53787117406</v>
+        <v>7928.038346422167</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>5413</v>
       </c>
       <c r="B255" t="n">
-        <v>2994.330492216481</v>
+        <v>8631.904987144411</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         <v>5414</v>
       </c>
       <c r="B256" t="n">
-        <v>2631.320891643725</v>
+        <v>9337.341259020788</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         <v>5415</v>
       </c>
       <c r="B257" t="n">
-        <v>2615.084505789795</v>
+        <v>9280.114675067925</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -6982,7 +6982,7 @@
         <v>5416</v>
       </c>
       <c r="B258" t="n">
-        <v>2202.475236077089</v>
+        <v>8480.69684930356</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -6993,7 +6993,7 @@
         <v>5417</v>
       </c>
       <c r="B259" t="n">
-        <v>1277.071086865342</v>
+        <v>6392.525949185526</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
         <v>5418</v>
       </c>
       <c r="B260" t="n">
-        <v>1073.240288525456</v>
+        <v>4552.443072616299</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>5419</v>
       </c>
       <c r="B261" t="n">
-        <v>662.8797589994305</v>
+        <v>3389.512125345373</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>5420</v>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>2739.858947360526</v>
       </c>
       <c r="C262" t="n">
         <v>0</v>
@@ -7037,10 +7037,10 @@
         <v>5421</v>
       </c>
       <c r="B263" t="n">
-        <v>2158.475785200996</v>
+        <v>2131.861610342909</v>
       </c>
       <c r="C263" t="n">
-        <v>7759.236949221693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -7048,10 +7048,10 @@
         <v>5422</v>
       </c>
       <c r="B264" t="n">
-        <v>1875.771080859399</v>
+        <v>1696.399407275985</v>
       </c>
       <c r="C264" t="n">
-        <v>6742.976862967427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -7059,10 +7059,10 @@
         <v>5423</v>
       </c>
       <c r="B265" t="n">
-        <v>1419.616534635928</v>
+        <v>1220.981076923717</v>
       </c>
       <c r="C265" t="n">
-        <v>5103.203447912404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -7070,7 +7070,7 @@
         <v>5424</v>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>1082.430103812667</v>
       </c>
       <c r="C266" t="n">
         <v>0</v>
@@ -7081,7 +7081,7 @@
         <v>5425</v>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>746.998758780038</v>
       </c>
       <c r="C267" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>5426</v>
       </c>
       <c r="B268" t="n">
-        <v>0</v>
+        <v>745.3079919521787</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
@@ -7103,7 +7103,7 @@
         <v>5427</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>524.2540895534338</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>5428</v>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>632.572247008873</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -7125,10 +7125,10 @@
         <v>5429</v>
       </c>
       <c r="B271" t="n">
-        <v>1264.498084981872</v>
+        <v>844.3397324731509</v>
       </c>
       <c r="C271" t="n">
-        <v>4545.587367938794</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -7136,10 +7136,10 @@
         <v>5430</v>
       </c>
       <c r="B272" t="n">
-        <v>2071.806406992595</v>
+        <v>1569.148272010146</v>
       </c>
       <c r="C272" t="n">
-        <v>7447.679948503212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -7147,7 +7147,7 @@
         <v>5431</v>
       </c>
       <c r="B273" t="n">
-        <v>1313.95602673644</v>
+        <v>2398.847605634659</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>5432</v>
       </c>
       <c r="B274" t="n">
-        <v>2071.016465749331</v>
+        <v>3713.002410782014</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
@@ -7169,7 +7169,7 @@
         <v>5433</v>
       </c>
       <c r="B275" t="n">
-        <v>2509.211525595056</v>
+        <v>5110.24563544572</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -7180,7 +7180,7 @@
         <v>5434</v>
       </c>
       <c r="B276" t="n">
-        <v>2901.941287098131</v>
+        <v>5808.83212545358</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>5435</v>
       </c>
       <c r="B277" t="n">
-        <v>2951.606201551307</v>
+        <v>6548.580107149232</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
         <v>5436</v>
       </c>
       <c r="B278" t="n">
-        <v>2980.349704097881</v>
+        <v>7267.353053714765</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>5437</v>
       </c>
       <c r="B279" t="n">
-        <v>3029.413655426994</v>
+        <v>7967.919705498499</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
@@ -7224,7 +7224,7 @@
         <v>5438</v>
       </c>
       <c r="B280" t="n">
-        <v>3383.124431329076</v>
+        <v>8003.408110569526</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
@@ -7235,7 +7235,7 @@
         <v>5439</v>
       </c>
       <c r="B281" t="n">
-        <v>2988.667592598601</v>
+        <v>7291.491886801509</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
@@ -7246,7 +7246,7 @@
         <v>5440</v>
       </c>
       <c r="B282" t="n">
-        <v>2202.475236077089</v>
+        <v>5218.886602597744</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
@@ -7257,7 +7257,7 @@
         <v>5441</v>
       </c>
       <c r="B283" t="n">
-        <v>1277.071086865342</v>
+        <v>4067.968954412758</v>
       </c>
       <c r="C283" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>5442</v>
       </c>
       <c r="B284" t="n">
-        <v>536.621319876215</v>
+        <v>3540.787227800031</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
@@ -7279,10 +7279,10 @@
         <v>5443</v>
       </c>
       <c r="B285" t="n">
-        <v>2269.559322750585</v>
+        <v>2542.135298080876</v>
       </c>
       <c r="C285" t="n">
-        <v>8158.557384000055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -7290,10 +7290,10 @@
         <v>5444</v>
       </c>
       <c r="B286" t="n">
-        <v>2347.394234261428</v>
+        <v>1957.039907465989</v>
       </c>
       <c r="C286" t="n">
-        <v>8438.356455861358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -7301,10 +7301,10 @@
         <v>5445</v>
       </c>
       <c r="B287" t="n">
-        <v>2158.475785200996</v>
+        <v>1776.547663254889</v>
       </c>
       <c r="C287" t="n">
-        <v>7759.236949221693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -7312,10 +7312,10 @@
         <v>5446</v>
       </c>
       <c r="B288" t="n">
-        <v>1875.771080859399</v>
+        <v>1357.119712956501</v>
       </c>
       <c r="C288" t="n">
-        <v>6742.976862967427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -7323,10 +7323,10 @@
         <v>5447</v>
       </c>
       <c r="B289" t="n">
-        <v>1419.616534635928</v>
+        <v>915.7336334687392</v>
       </c>
       <c r="C289" t="n">
-        <v>5103.203447912404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -7334,7 +7334,7 @@
         <v>5448</v>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>797.926337915366</v>
       </c>
       <c r="C290" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
         <v>5449</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>509.3212378009041</v>
       </c>
       <c r="C291" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         <v>5450</v>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>488.7701965487762</v>
       </c>
       <c r="C292" t="n">
         <v>0</v>
@@ -7367,10 +7367,10 @@
         <v>5451</v>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>5818.181396072483</v>
       </c>
       <c r="C293" t="n">
-        <v>0</v>
+        <v>20915.05884624785</v>
       </c>
     </row>
     <row r="294">
@@ -7378,10 +7378,10 @@
         <v>5452</v>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>1867.586593058724</v>
       </c>
       <c r="C294" t="n">
-        <v>0</v>
+        <v>6713.555462649267</v>
       </c>
     </row>
     <row r="295">
@@ -7389,10 +7389,10 @@
         <v>5453</v>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>1867.586593058722</v>
       </c>
       <c r="C295" t="n">
-        <v>0</v>
+        <v>6713.555462649259</v>
       </c>
     </row>
     <row r="296">
@@ -7400,10 +7400,10 @@
         <v>5454</v>
       </c>
       <c r="B296" t="n">
-        <v>1227.423328951206</v>
+        <v>902.6553921878502</v>
       </c>
       <c r="C296" t="n">
-        <v>4412.311924753902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -7411,10 +7411,10 @@
         <v>5455</v>
       </c>
       <c r="B297" t="n">
-        <v>1932.317511575456</v>
+        <v>1535.001450798823</v>
       </c>
       <c r="C297" t="n">
-        <v>6946.248614991171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -7422,10 +7422,10 @@
         <v>5456</v>
       </c>
       <c r="B298" t="n">
-        <v>2709.037134108128</v>
+        <v>2137.746909266406</v>
       </c>
       <c r="C298" t="n">
-        <v>9738.381672800679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -7433,10 +7433,10 @@
         <v>5457</v>
       </c>
       <c r="B299" t="n">
-        <v>8172.358333547443</v>
+        <v>2769.076020338925</v>
       </c>
       <c r="C299" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -7444,10 +7444,10 @@
         <v>5458</v>
       </c>
       <c r="B300" t="n">
-        <v>8172.358333547443</v>
+        <v>3926.141889600081</v>
       </c>
       <c r="C300" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -7455,10 +7455,10 @@
         <v>5459</v>
       </c>
       <c r="B301" t="n">
-        <v>8172.358333547443</v>
+        <v>4569.577594131159</v>
       </c>
       <c r="C301" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -7466,7 +7466,7 @@
         <v>5460</v>
       </c>
       <c r="B302" t="n">
-        <v>1004.771214385633</v>
+        <v>4621.947107849776</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -7477,7 +7477,7 @@
         <v>5461</v>
       </c>
       <c r="B303" t="n">
-        <v>1010.033503932439</v>
+        <v>4647.749937617412</v>
       </c>
       <c r="C303" t="n">
         <v>0</v>
@@ -7488,7 +7488,7 @@
         <v>5462</v>
       </c>
       <c r="B304" t="n">
-        <v>1352.735777506381</v>
+        <v>4668.335771090785</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -7499,7 +7499,7 @@
         <v>5463</v>
       </c>
       <c r="B305" t="n">
-        <v>1048.400267719588</v>
+        <v>4066.606548594838</v>
       </c>
       <c r="C305" t="n">
         <v>0</v>
@@ -7510,7 +7510,7 @@
         <v>5464</v>
       </c>
       <c r="B306" t="n">
-        <v>995.2646642949775</v>
+        <v>4081.751519845503</v>
       </c>
       <c r="C306" t="n">
         <v>0</v>
@@ -7521,10 +7521,10 @@
         <v>5465</v>
       </c>
       <c r="B307" t="n">
-        <v>8172.358333547443</v>
+        <v>2563.962358929924</v>
       </c>
       <c r="C307" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -7532,10 +7532,10 @@
         <v>5466</v>
       </c>
       <c r="B308" t="n">
-        <v>3394.461673839469</v>
+        <v>1404.463043698418</v>
       </c>
       <c r="C308" t="n">
-        <v>12202.32935803795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -7543,7 +7543,7 @@
         <v>5467</v>
       </c>
       <c r="B309" t="n">
-        <v>0</v>
+        <v>766.8244208510366</v>
       </c>
       <c r="C309" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
         <v>5470</v>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>989.9431464593922</v>
       </c>
       <c r="C312" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>5471</v>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>599.5481206725257</v>
       </c>
       <c r="C313" t="n">
         <v>0</v>
@@ -7598,10 +7598,10 @@
         <v>5472</v>
       </c>
       <c r="B314" t="n">
-        <v>0</v>
+        <v>1867.586593058722</v>
       </c>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>6713.555462649259</v>
       </c>
     </row>
     <row r="315">
@@ -7609,10 +7609,10 @@
         <v>5473</v>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>3866.5968391644</v>
       </c>
       <c r="C315" t="n">
-        <v>0</v>
+        <v>13899.54951910404</v>
       </c>
     </row>
     <row r="316">
@@ -7620,10 +7620,10 @@
         <v>5474</v>
       </c>
       <c r="B316" t="n">
-        <v>0</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C316" t="n">
-        <v>0</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="317">
@@ -7631,10 +7631,10 @@
         <v>5475</v>
       </c>
       <c r="B317" t="n">
-        <v>6223.9768355225</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C317" t="n">
-        <v>22373.80255289223</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="318">
@@ -7642,10 +7642,10 @@
         <v>5476</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="319">
@@ -7653,10 +7653,10 @@
         <v>5477</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>1867.586593058724</v>
       </c>
       <c r="C319" t="n">
-        <v>0</v>
+        <v>6713.555462649267</v>
       </c>
     </row>
     <row r="320">
@@ -7664,10 +7664,10 @@
         <v>5478</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>1867.586593058722</v>
       </c>
       <c r="C320" t="n">
-        <v>0</v>
+        <v>6713.555462649259</v>
       </c>
     </row>
     <row r="321">
@@ -7675,10 +7675,10 @@
         <v>5479</v>
       </c>
       <c r="B321" t="n">
-        <v>8172.358333547443</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C321" t="n">
-        <v>29377.79760083634</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="322">
@@ -7686,10 +7686,10 @@
         <v>5480</v>
       </c>
       <c r="B322" t="n">
-        <v>2441.081073598025</v>
+        <v>12450.57728705825</v>
       </c>
       <c r="C322" t="n">
-        <v>8775.139657424412</v>
+        <v>44757.0364176621</v>
       </c>
     </row>
     <row r="323">
@@ -7697,10 +7697,10 @@
         <v>5481</v>
       </c>
       <c r="B323" t="n">
-        <v>8172.358333547443</v>
+        <v>854.8344322288972</v>
       </c>
       <c r="C323" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -7708,10 +7708,10 @@
         <v>5482</v>
       </c>
       <c r="B324" t="n">
-        <v>8172.358333547443</v>
+        <v>1290.005291014592</v>
       </c>
       <c r="C324" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -7719,10 +7719,10 @@
         <v>5483</v>
       </c>
       <c r="B325" t="n">
-        <v>8172.358333547443</v>
+        <v>1703.277483358446</v>
       </c>
       <c r="C325" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -7730,10 +7730,10 @@
         <v>5484</v>
       </c>
       <c r="B326" t="n">
-        <v>8172.358333547443</v>
+        <v>2165.460970103893</v>
       </c>
       <c r="C326" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -7741,10 +7741,10 @@
         <v>5485</v>
       </c>
       <c r="B327" t="n">
-        <v>8172.358333547443</v>
+        <v>2616.514723821504</v>
       </c>
       <c r="C327" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -7752,10 +7752,10 @@
         <v>5486</v>
       </c>
       <c r="B328" t="n">
-        <v>8172.358333547443</v>
+        <v>2615.268305221695</v>
       </c>
       <c r="C328" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -7763,10 +7763,10 @@
         <v>5487</v>
       </c>
       <c r="B329" t="n">
-        <v>8172.358333547443</v>
+        <v>2557.610733598832</v>
       </c>
       <c r="C329" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -7774,10 +7774,10 @@
         <v>5488</v>
       </c>
       <c r="B330" t="n">
-        <v>8172.358333547443</v>
+        <v>2354.688892700638</v>
       </c>
       <c r="C330" t="n">
-        <v>29377.79760083634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -7785,10 +7785,10 @@
         <v>5489</v>
       </c>
       <c r="B331" t="n">
-        <v>1656.991126763742</v>
+        <v>1915.452366438793</v>
       </c>
       <c r="C331" t="n">
-        <v>5956.511934703258</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -7796,10 +7796,10 @@
         <v>5490</v>
       </c>
       <c r="B332" t="n">
-        <v>1896.868533533586</v>
+        <v>1463.438482654044</v>
       </c>
       <c r="C332" t="n">
-        <v>6818.81747950173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -7807,10 +7807,10 @@
         <v>5491</v>
       </c>
       <c r="B333" t="n">
-        <v>2059.940996370286</v>
+        <v>1050.92960180934</v>
       </c>
       <c r="C333" t="n">
-        <v>7405.02645516799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -7818,10 +7818,10 @@
         <v>5492</v>
       </c>
       <c r="B334" t="n">
-        <v>1943.017407301031</v>
+        <v>658.2265016876692</v>
       </c>
       <c r="C334" t="n">
-        <v>6984.712343347969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -7829,10 +7829,10 @@
         <v>5493</v>
       </c>
       <c r="B335" t="n">
-        <v>1891.679605926428</v>
+        <v>1890.661705562889</v>
       </c>
       <c r="C335" t="n">
-        <v>6800.164447073782</v>
+        <v>6796.505323276539</v>
       </c>
     </row>
     <row r="336">
@@ -7840,10 +7840,10 @@
         <v>5494</v>
       </c>
       <c r="B336" t="n">
-        <v>1557.950230140451</v>
+        <v>0</v>
       </c>
       <c r="C336" t="n">
-        <v>5600.482096503369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -7851,10 +7851,10 @@
         <v>5495</v>
       </c>
       <c r="B337" t="n">
-        <v>3227.007384090737</v>
+        <v>0</v>
       </c>
       <c r="C337" t="n">
-        <v>11600.36869615216</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/first_stage_optimization/lshp_operation.xlsx
+++ b/first_stage_optimization/lshp_operation.xlsx
@@ -439,10 +439,10 @@
         <v>288</v>
       </c>
       <c r="B2" t="n">
-        <v>14661.83753471311</v>
+        <v>11197.08202174817</v>
       </c>
       <c r="C2" t="n">
-        <v>40438.72613346702</v>
+        <v>30882.6047416915</v>
       </c>
     </row>
     <row r="3">
@@ -450,10 +450,10 @@
         <v>289</v>
       </c>
       <c r="B3" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C3" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>290</v>
       </c>
       <c r="B4" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C4" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="5">
@@ -472,10 +472,10 @@
         <v>291</v>
       </c>
       <c r="B5" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C5" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="6">
@@ -483,10 +483,10 @@
         <v>292</v>
       </c>
       <c r="B6" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C6" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="7">
@@ -494,10 +494,10 @@
         <v>293</v>
       </c>
       <c r="B7" t="n">
-        <v>16227.52394141103</v>
+        <v>15640.50738895312</v>
       </c>
       <c r="C7" t="n">
-        <v>44757.0364176621</v>
+        <v>43137.98958642726</v>
       </c>
     </row>
     <row r="8">
@@ -505,10 +505,10 @@
         <v>294</v>
       </c>
       <c r="B8" t="n">
-        <v>16227.52394141103</v>
+        <v>15771.71513208502</v>
       </c>
       <c r="C8" t="n">
-        <v>44757.0364176621</v>
+        <v>43499.8728755129</v>
       </c>
     </row>
     <row r="9">
@@ -538,10 +538,10 @@
         <v>297</v>
       </c>
       <c r="B11" t="n">
-        <v>10892.0487091489</v>
+        <v>7427.29319618396</v>
       </c>
       <c r="C11" t="n">
-        <v>30041.29419241133</v>
+        <v>20485.1728006358</v>
       </c>
     </row>
     <row r="12">
@@ -549,10 +549,10 @@
         <v>298</v>
       </c>
       <c r="B12" t="n">
-        <v>13613.69344088266</v>
+        <v>2671.138940993995</v>
       </c>
       <c r="C12" t="n">
-        <v>37547.84619713782</v>
+        <v>7367.252286321891</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +571,10 @@
         <v>300</v>
       </c>
       <c r="B14" t="n">
-        <v>16227.52394141103</v>
+        <v>11725.51941396181</v>
       </c>
       <c r="C14" t="n">
-        <v>44757.0364176621</v>
+        <v>32340.08474253159</v>
       </c>
     </row>
     <row r="15">
@@ -582,10 +582,10 @@
         <v>301</v>
       </c>
       <c r="B15" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C15" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="16">
@@ -593,10 +593,10 @@
         <v>302</v>
       </c>
       <c r="B16" t="n">
-        <v>16227.52394141103</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>44757.0364176621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -648,10 +648,10 @@
         <v>307</v>
       </c>
       <c r="B21" t="n">
-        <v>5628.311937815829</v>
+        <v>2420.200107322064</v>
       </c>
       <c r="C21" t="n">
-        <v>15523.41338581821</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="22">
@@ -659,10 +659,10 @@
         <v>308</v>
       </c>
       <c r="B22" t="n">
-        <v>6906.990958459112</v>
+        <v>3442.235445494172</v>
       </c>
       <c r="C22" t="n">
-        <v>19050.13032058033</v>
+        <v>9494.008928804804</v>
       </c>
     </row>
     <row r="23">
@@ -670,10 +670,10 @@
         <v>309</v>
       </c>
       <c r="B23" t="n">
-        <v>11687.76275546055</v>
+        <v>8223.007242495609</v>
       </c>
       <c r="C23" t="n">
-        <v>32235.9483292592</v>
+        <v>22679.82693748368</v>
       </c>
     </row>
     <row r="24">
@@ -681,10 +681,10 @@
         <v>310</v>
       </c>
       <c r="B24" t="n">
-        <v>16227.52394141103</v>
+        <v>12332.30114269007</v>
       </c>
       <c r="C24" t="n">
-        <v>44757.0364176621</v>
+        <v>34013.64578784662</v>
       </c>
     </row>
     <row r="25">
@@ -692,10 +692,10 @@
         <v>311</v>
       </c>
       <c r="B25" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C25" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="26">
@@ -703,10 +703,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="n">
-        <v>16227.52394141103</v>
+        <v>14184.39603300014</v>
       </c>
       <c r="C26" t="n">
-        <v>44757.0364176621</v>
+        <v>39121.8975922415</v>
       </c>
     </row>
     <row r="27">
@@ -714,10 +714,10 @@
         <v>313</v>
       </c>
       <c r="B27" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C27" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="28">
@@ -725,10 +725,10 @@
         <v>314</v>
       </c>
       <c r="B28" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C28" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="29">
@@ -736,10 +736,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="n">
-        <v>16227.52394141103</v>
+        <v>15700.36452466098</v>
       </c>
       <c r="C29" t="n">
-        <v>44757.0364176621</v>
+        <v>43303.08119328029</v>
       </c>
     </row>
     <row r="30">
@@ -747,10 +747,10 @@
         <v>316</v>
       </c>
       <c r="B30" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C30" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="31">
@@ -758,10 +758,10 @@
         <v>317</v>
       </c>
       <c r="B31" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C31" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="32">
@@ -769,10 +769,10 @@
         <v>318</v>
       </c>
       <c r="B32" t="n">
-        <v>16227.52394141103</v>
+        <v>15771.71513208502</v>
       </c>
       <c r="C32" t="n">
-        <v>44757.0364176621</v>
+        <v>43499.8728755129</v>
       </c>
     </row>
     <row r="33">
@@ -780,10 +780,10 @@
         <v>319</v>
       </c>
       <c r="B33" t="n">
-        <v>16227.52394141103</v>
+        <v>4574.87140815473</v>
       </c>
       <c r="C33" t="n">
-        <v>44757.0364176621</v>
+        <v>12617.92538160311</v>
       </c>
     </row>
     <row r="34">
@@ -802,10 +802,10 @@
         <v>321</v>
       </c>
       <c r="B35" t="n">
-        <v>10892.0487091489</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>30041.29419241133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -813,10 +813,10 @@
         <v>322</v>
       </c>
       <c r="B36" t="n">
-        <v>8570.769153159979</v>
+        <v>5106.013640195039</v>
       </c>
       <c r="C36" t="n">
-        <v>23638.98697671562</v>
+        <v>14082.8655849401</v>
       </c>
     </row>
     <row r="37">
@@ -824,10 +824,10 @@
         <v>323</v>
       </c>
       <c r="B37" t="n">
-        <v>16227.52394141103</v>
+        <v>2420.200107322064</v>
       </c>
       <c r="C37" t="n">
-        <v>44757.0364176621</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="38">
@@ -934,10 +934,10 @@
         <v>333</v>
       </c>
       <c r="B47" t="n">
-        <v>9011.154174682662</v>
+        <v>5546.398661717728</v>
       </c>
       <c r="C47" t="n">
-        <v>24853.6102622672</v>
+        <v>15297.4888704917</v>
       </c>
     </row>
     <row r="48">
@@ -945,10 +945,10 @@
         <v>334</v>
       </c>
       <c r="B48" t="n">
-        <v>15797.05665565501</v>
+        <v>12332.30114269007</v>
       </c>
       <c r="C48" t="n">
-        <v>43569.76717962214</v>
+        <v>34013.64578784662</v>
       </c>
     </row>
     <row r="49">
@@ -956,10 +956,10 @@
         <v>335</v>
       </c>
       <c r="B49" t="n">
-        <v>16227.52394141103</v>
+        <v>13180.5251643192</v>
       </c>
       <c r="C49" t="n">
-        <v>44757.0364176621</v>
+        <v>36353.12737255779</v>
       </c>
     </row>
     <row r="50">
@@ -967,10 +967,10 @@
         <v>336</v>
       </c>
       <c r="B50" t="n">
-        <v>16227.52394141103</v>
+        <v>11197.08202174817</v>
       </c>
       <c r="C50" t="n">
-        <v>44757.0364176621</v>
+        <v>30882.6047416915</v>
       </c>
     </row>
     <row r="51">
@@ -978,10 +978,10 @@
         <v>337</v>
       </c>
       <c r="B51" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C51" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="52">
@@ -989,10 +989,10 @@
         <v>338</v>
       </c>
       <c r="B52" t="n">
-        <v>15400.42560310273</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C52" t="n">
-        <v>42475.82145336401</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="53">
@@ -1000,10 +1000,10 @@
         <v>339</v>
       </c>
       <c r="B53" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C53" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="54">
@@ -1011,10 +1011,10 @@
         <v>340</v>
       </c>
       <c r="B54" t="n">
-        <v>15967.42976796647</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C54" t="n">
-        <v>44039.67223844971</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="55">
@@ -1022,10 +1022,10 @@
         <v>341</v>
       </c>
       <c r="B55" t="n">
-        <v>16079.27149234439</v>
+        <v>13873.55516262652</v>
       </c>
       <c r="C55" t="n">
-        <v>44348.14222740612</v>
+        <v>38264.56925270922</v>
       </c>
     </row>
     <row r="56">
@@ -1033,10 +1033,10 @@
         <v>342</v>
       </c>
       <c r="B56" t="n">
-        <v>13356.16694275438</v>
+        <v>9891.411429789443</v>
       </c>
       <c r="C56" t="n">
-        <v>36837.56390780921</v>
+        <v>27281.44251603368</v>
       </c>
     </row>
     <row r="57">
@@ -1231,10 +1231,10 @@
         <v>360</v>
       </c>
       <c r="B74" t="n">
-        <v>3622.480496173405</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>9991.14172161289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1242,10 +1242,10 @@
         <v>361</v>
       </c>
       <c r="B75" t="n">
-        <v>3851.506422101356</v>
+        <v>2420.200107322062</v>
       </c>
       <c r="C75" t="n">
-        <v>10622.81675375922</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="76">
@@ -1253,10 +1253,10 @@
         <v>362</v>
       </c>
       <c r="B76" t="n">
-        <v>4117.917007473863</v>
+        <v>2420.200107322062</v>
       </c>
       <c r="C76" t="n">
-        <v>11357.60219081162</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="77">
@@ -1264,10 +1264,10 @@
         <v>363</v>
       </c>
       <c r="B77" t="n">
-        <v>16227.52394141103</v>
+        <v>2420.200107322064</v>
       </c>
       <c r="C77" t="n">
-        <v>44757.0364176621</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="78">
@@ -1275,10 +1275,10 @@
         <v>364</v>
       </c>
       <c r="B78" t="n">
-        <v>13113.2559399548</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>36167.5925284537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1286,10 +1286,10 @@
         <v>365</v>
       </c>
       <c r="B79" t="n">
-        <v>4994.891653253849</v>
+        <v>2420.200107322062</v>
       </c>
       <c r="C79" t="n">
-        <v>13776.38069948952</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="80">
@@ -1297,10 +1297,10 @@
         <v>366</v>
       </c>
       <c r="B80" t="n">
-        <v>5468.613123466752</v>
+        <v>2420.200107322062</v>
       </c>
       <c r="C80" t="n">
-        <v>15082.94904415491</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="81">
@@ -1495,10 +1495,10 @@
         <v>384</v>
       </c>
       <c r="B98" t="n">
-        <v>6183.793196442298</v>
+        <v>2719.037683477357</v>
       </c>
       <c r="C98" t="n">
-        <v>17055.48291234832</v>
+        <v>7499.361520572798</v>
       </c>
     </row>
     <row r="99">
@@ -1506,10 +1506,10 @@
         <v>385</v>
       </c>
       <c r="B99" t="n">
-        <v>16227.52394141103</v>
+        <v>2990.384331759942</v>
       </c>
       <c r="C99" t="n">
-        <v>44757.0364176621</v>
+        <v>8247.761083121106</v>
       </c>
     </row>
     <row r="100">
@@ -1517,10 +1517,10 @@
         <v>386</v>
       </c>
       <c r="B100" t="n">
-        <v>16227.52394141103</v>
+        <v>3268.251465062969</v>
       </c>
       <c r="C100" t="n">
-        <v>44757.0364176621</v>
+        <v>9014.144756281385</v>
       </c>
     </row>
     <row r="101">
@@ -1528,10 +1528,10 @@
         <v>387</v>
       </c>
       <c r="B101" t="n">
-        <v>16227.52394141103</v>
+        <v>6948.505853923947</v>
       </c>
       <c r="C101" t="n">
-        <v>44757.0364176621</v>
+        <v>19164.63230467252</v>
       </c>
     </row>
     <row r="102">
@@ -1539,10 +1539,10 @@
         <v>388</v>
       </c>
       <c r="B102" t="n">
-        <v>16227.52394141103</v>
+        <v>2420.200107322062</v>
       </c>
       <c r="C102" t="n">
-        <v>44757.0364176621</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="103">
@@ -1550,10 +1550,10 @@
         <v>389</v>
       </c>
       <c r="B103" t="n">
-        <v>4994.891653253849</v>
+        <v>2420.200107322062</v>
       </c>
       <c r="C103" t="n">
-        <v>13776.38069948952</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="104">
@@ -1561,10 +1561,10 @@
         <v>390</v>
       </c>
       <c r="B104" t="n">
-        <v>7952.96607559232</v>
+        <v>4488.21056262738</v>
       </c>
       <c r="C104" t="n">
-        <v>21935.02801529472</v>
+        <v>12378.9066235192</v>
       </c>
     </row>
     <row r="105">
@@ -1726,10 +1726,10 @@
         <v>405</v>
       </c>
       <c r="B119" t="n">
-        <v>4018.932957836866</v>
+        <v>2420.200107322062</v>
       </c>
       <c r="C119" t="n">
-        <v>11084.59487741211</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="120">
@@ -1737,10 +1737,10 @@
         <v>406</v>
       </c>
       <c r="B120" t="n">
-        <v>7538.776746350087</v>
+        <v>4074.021233385152</v>
       </c>
       <c r="C120" t="n">
-        <v>20792.65491144769</v>
+        <v>11236.53351967219</v>
       </c>
     </row>
     <row r="121">
@@ -1748,10 +1748,10 @@
         <v>407</v>
       </c>
       <c r="B121" t="n">
-        <v>8152.132178745583</v>
+        <v>4687.376665780643</v>
       </c>
       <c r="C121" t="n">
-        <v>22484.34684940512</v>
+        <v>12928.2254576296</v>
       </c>
     </row>
     <row r="122">
@@ -1759,10 +1759,10 @@
         <v>408</v>
       </c>
       <c r="B122" t="n">
-        <v>10086.38505501611</v>
+        <v>6621.629542051171</v>
       </c>
       <c r="C122" t="n">
-        <v>27819.19810192959</v>
+        <v>18263.07671015408</v>
       </c>
     </row>
     <row r="123">
@@ -1770,10 +1770,10 @@
         <v>409</v>
       </c>
       <c r="B123" t="n">
-        <v>10284.60671765093</v>
+        <v>6819.851204685992</v>
       </c>
       <c r="C123" t="n">
-        <v>28365.91208031273</v>
+        <v>18809.79068853721</v>
       </c>
     </row>
     <row r="124">
@@ -1781,10 +1781,10 @@
         <v>410</v>
       </c>
       <c r="B124" t="n">
-        <v>16227.52394141103</v>
+        <v>7099.280057115846</v>
       </c>
       <c r="C124" t="n">
-        <v>44757.0364176621</v>
+        <v>19580.48172985087</v>
       </c>
     </row>
     <row r="125">
@@ -1792,10 +1792,10 @@
         <v>411</v>
       </c>
       <c r="B125" t="n">
-        <v>16227.52394141103</v>
+        <v>7496.823652848921</v>
       </c>
       <c r="C125" t="n">
-        <v>44757.0364176621</v>
+        <v>20676.94433598069</v>
       </c>
     </row>
     <row r="126">
@@ -1803,10 +1803,10 @@
         <v>412</v>
       </c>
       <c r="B126" t="n">
-        <v>8089.609984129404</v>
+        <v>5654.012943367195</v>
       </c>
       <c r="C126" t="n">
-        <v>22311.90475956741</v>
+        <v>15594.2991750234</v>
       </c>
     </row>
     <row r="127">
@@ -1814,10 +1814,10 @@
         <v>413</v>
       </c>
       <c r="B127" t="n">
-        <v>16227.52394141103</v>
+        <v>4015.178821929269</v>
       </c>
       <c r="C127" t="n">
-        <v>44757.0364176621</v>
+        <v>11074.24061769019</v>
       </c>
     </row>
     <row r="128">
@@ -1825,10 +1825,10 @@
         <v>414</v>
       </c>
       <c r="B128" t="n">
-        <v>6535.69842051366</v>
+        <v>3070.942907548726</v>
       </c>
       <c r="C128" t="n">
-        <v>18026.0705994282</v>
+        <v>8469.949207652695</v>
       </c>
     </row>
     <row r="129">
@@ -1836,10 +1836,10 @@
         <v>415</v>
       </c>
       <c r="B129" t="n">
-        <v>6150.872376992415</v>
+        <v>2686.116864027475</v>
       </c>
       <c r="C129" t="n">
-        <v>16964.68419774852</v>
+        <v>7408.562805972993</v>
       </c>
     </row>
     <row r="130">
@@ -1847,10 +1847,10 @@
         <v>416</v>
       </c>
       <c r="B130" t="n">
-        <v>6038.775086831522</v>
+        <v>2574.019573866587</v>
       </c>
       <c r="C130" t="n">
-        <v>16655.5093343395</v>
+        <v>7099.38794256399</v>
       </c>
     </row>
     <row r="131">
@@ -1858,10 +1858,10 @@
         <v>417</v>
       </c>
       <c r="B131" t="n">
-        <v>5855.842708277934</v>
+        <v>2420.200107322064</v>
       </c>
       <c r="C131" t="n">
-        <v>16150.96463864512</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="132">
@@ -1869,10 +1869,10 @@
         <v>418</v>
       </c>
       <c r="B132" t="n">
-        <v>4200.058406524801</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>11584.15589068562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -1979,10 +1979,10 @@
         <v>428</v>
       </c>
       <c r="B142" t="n">
-        <v>5349.056572928629</v>
+        <v>2420.200107322062</v>
       </c>
       <c r="C142" t="n">
-        <v>14753.20083945501</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="143">
@@ -1990,10 +1990,10 @@
         <v>429</v>
       </c>
       <c r="B143" t="n">
-        <v>6072.162767063096</v>
+        <v>2607.407254098156</v>
       </c>
       <c r="C143" t="n">
-        <v>16747.59569486012</v>
+        <v>7191.4743030846</v>
       </c>
     </row>
     <row r="144">
@@ -2001,10 +2001,10 @@
         <v>430</v>
       </c>
       <c r="B144" t="n">
-        <v>7392.41216357169</v>
+        <v>3927.656650606756</v>
       </c>
       <c r="C144" t="n">
-        <v>20388.9676338741</v>
+        <v>10832.84624209859</v>
       </c>
     </row>
     <row r="145">
@@ -2012,10 +2012,10 @@
         <v>431</v>
       </c>
       <c r="B145" t="n">
-        <v>8541.22723488989</v>
+        <v>5076.471721924955</v>
       </c>
       <c r="C145" t="n">
-        <v>23557.5075891864</v>
+        <v>14001.38619741089</v>
       </c>
     </row>
     <row r="146">
@@ -2023,10 +2023,10 @@
         <v>432</v>
       </c>
       <c r="B146" t="n">
-        <v>10291.95742004125</v>
+        <v>6827.201907076305</v>
       </c>
       <c r="C146" t="n">
-        <v>28386.18600847124</v>
+        <v>18830.06461669572</v>
       </c>
     </row>
     <row r="147">
@@ -2034,10 +2034,10 @@
         <v>433</v>
       </c>
       <c r="B147" t="n">
-        <v>11026.63922527536</v>
+        <v>7561.883712310421</v>
       </c>
       <c r="C147" t="n">
-        <v>30412.50748739662</v>
+        <v>20856.3860956211</v>
       </c>
     </row>
     <row r="148">
@@ -2045,10 +2045,10 @@
         <v>434</v>
       </c>
       <c r="B148" t="n">
-        <v>11475.17202671491</v>
+        <v>7829.974092509725</v>
       </c>
       <c r="C148" t="n">
-        <v>31649.60311585024</v>
+        <v>21595.80456470652</v>
       </c>
     </row>
     <row r="149">
@@ -2056,10 +2056,10 @@
         <v>435</v>
       </c>
       <c r="B149" t="n">
-        <v>11447.5183340251</v>
+        <v>7982.762821060161</v>
       </c>
       <c r="C149" t="n">
-        <v>31573.33163196463</v>
+        <v>22017.2102401891</v>
       </c>
     </row>
     <row r="150">
@@ -2067,10 +2067,10 @@
         <v>436</v>
       </c>
       <c r="B150" t="n">
-        <v>16227.52394141103</v>
+        <v>7680.581968994567</v>
       </c>
       <c r="C150" t="n">
-        <v>44757.0364176621</v>
+        <v>21183.7670451921</v>
       </c>
     </row>
     <row r="151">
@@ -2078,10 +2078,10 @@
         <v>437</v>
       </c>
       <c r="B151" t="n">
-        <v>13245.85570408344</v>
+        <v>9781.100191118503</v>
       </c>
       <c r="C151" t="n">
-        <v>36533.31514229832</v>
+        <v>26977.1937505228</v>
       </c>
     </row>
     <row r="152">
@@ -2089,10 +2089,10 @@
         <v>438</v>
       </c>
       <c r="B152" t="n">
-        <v>16227.52394141103</v>
+        <v>5809.303108874029</v>
       </c>
       <c r="C152" t="n">
-        <v>44757.0364176621</v>
+        <v>16022.60404876681</v>
       </c>
     </row>
     <row r="153">
@@ -2100,10 +2100,10 @@
         <v>439</v>
       </c>
       <c r="B153" t="n">
-        <v>8903.385898554039</v>
+        <v>5438.630385589105</v>
       </c>
       <c r="C153" t="n">
-        <v>24556.3752264865</v>
+        <v>15000.25383471099</v>
       </c>
     </row>
     <row r="154">
@@ -2111,10 +2111,10 @@
         <v>440</v>
       </c>
       <c r="B154" t="n">
-        <v>8782.912519094494</v>
+        <v>5318.157006129553</v>
       </c>
       <c r="C154" t="n">
-        <v>24224.09832143941</v>
+        <v>14667.97692966388</v>
       </c>
     </row>
     <row r="155">
@@ -2122,10 +2122,10 @@
         <v>441</v>
       </c>
       <c r="B155" t="n">
-        <v>6895.755311556394</v>
+        <v>3430.999798591454</v>
       </c>
       <c r="C155" t="n">
-        <v>19019.14135027182</v>
+        <v>9463.019958496297</v>
       </c>
     </row>
     <row r="156">
@@ -2133,10 +2133,10 @@
         <v>442</v>
       </c>
       <c r="B156" t="n">
-        <v>5736.285052507169</v>
+        <v>2420.200107322064</v>
       </c>
       <c r="C156" t="n">
-        <v>15821.21338560971</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="157">
@@ -2155,10 +2155,10 @@
         <v>444</v>
       </c>
       <c r="B158" t="n">
-        <v>16227.52394141103</v>
+        <v>7731.830712880651</v>
       </c>
       <c r="C158" t="n">
-        <v>44757.0364176621</v>
+        <v>21325.11589821185</v>
       </c>
     </row>
     <row r="159">
@@ -2166,10 +2166,10 @@
         <v>445</v>
       </c>
       <c r="B159" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C159" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="160">
@@ -2177,10 +2177,10 @@
         <v>446</v>
       </c>
       <c r="B160" t="n">
-        <v>16227.52394141103</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C160" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="161">
@@ -2265,10 +2265,10 @@
         <v>454</v>
       </c>
       <c r="B168" t="n">
-        <v>5546.557472199574</v>
+        <v>2420.200107322064</v>
       </c>
       <c r="C168" t="n">
-        <v>15297.92688472881</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="169">
@@ -2276,10 +2276,10 @@
         <v>455</v>
       </c>
       <c r="B169" t="n">
-        <v>6253.125660203575</v>
+        <v>2788.370147238635</v>
       </c>
       <c r="C169" t="n">
-        <v>17246.70836465352</v>
+        <v>7690.586972877994</v>
       </c>
     </row>
     <row r="170">
@@ -2287,10 +2287,10 @@
         <v>456</v>
       </c>
       <c r="B170" t="n">
-        <v>6183.793196442298</v>
+        <v>2719.037683477357</v>
       </c>
       <c r="C170" t="n">
-        <v>17055.48291234832</v>
+        <v>7499.361520572798</v>
       </c>
     </row>
     <row r="171">
@@ -2298,10 +2298,10 @@
         <v>457</v>
       </c>
       <c r="B171" t="n">
-        <v>6455.139844724877</v>
+        <v>2990.384331759942</v>
       </c>
       <c r="C171" t="n">
-        <v>17803.88247489661</v>
+        <v>8247.761083121106</v>
       </c>
     </row>
     <row r="172">
@@ -2309,10 +2309,10 @@
         <v>458</v>
       </c>
       <c r="B172" t="n">
-        <v>16227.52394141103</v>
+        <v>3268.251465062969</v>
       </c>
       <c r="C172" t="n">
-        <v>44757.0364176621</v>
+        <v>9014.144756281385</v>
       </c>
     </row>
     <row r="173">
@@ -2320,10 +2320,10 @@
         <v>459</v>
       </c>
       <c r="B173" t="n">
-        <v>16227.52394141103</v>
+        <v>3800.567685719266</v>
       </c>
       <c r="C173" t="n">
-        <v>44757.0364176621</v>
+        <v>10482.32293057619</v>
       </c>
     </row>
     <row r="174">
@@ -2331,10 +2331,10 @@
         <v>460</v>
       </c>
       <c r="B174" t="n">
-        <v>12942.558574349</v>
+        <v>9477.803061384062</v>
       </c>
       <c r="C174" t="n">
-        <v>35696.79314856054</v>
+        <v>26140.67175678501</v>
       </c>
     </row>
     <row r="175">
@@ -2342,10 +2342,10 @@
         <v>461</v>
       </c>
       <c r="B175" t="n">
-        <v>13075.26811572656</v>
+        <v>9610.512602761624</v>
       </c>
       <c r="C175" t="n">
-        <v>36062.81853837674</v>
+        <v>26506.69714660122</v>
       </c>
     </row>
     <row r="176">
@@ -2353,10 +2353,10 @@
         <v>462</v>
       </c>
       <c r="B176" t="n">
-        <v>13356.16694275438</v>
+        <v>9891.411429789443</v>
       </c>
       <c r="C176" t="n">
-        <v>36837.56390780921</v>
+        <v>27281.44251603368</v>
       </c>
     </row>
     <row r="177">
@@ -2529,10 +2529,10 @@
         <v>478</v>
       </c>
       <c r="B192" t="n">
-        <v>5072.773245545554</v>
+        <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>13991.18545189972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -2540,10 +2540,10 @@
         <v>479</v>
       </c>
       <c r="B193" t="n">
-        <v>5559.296919778698</v>
+        <v>2420.200107322064</v>
       </c>
       <c r="C193" t="n">
-        <v>15333.06347866011</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="194">
@@ -2551,10 +2551,10 @@
         <v>480</v>
       </c>
       <c r="B194" t="n">
-        <v>6183.793196442298</v>
+        <v>2719.037683477357</v>
       </c>
       <c r="C194" t="n">
-        <v>17055.48291234832</v>
+        <v>7499.361520572798</v>
       </c>
     </row>
     <row r="195">
@@ -2562,10 +2562,10 @@
         <v>481</v>
       </c>
       <c r="B195" t="n">
-        <v>16227.52394141103</v>
+        <v>2990.384331759942</v>
       </c>
       <c r="C195" t="n">
-        <v>44757.0364176621</v>
+        <v>8247.761083121106</v>
       </c>
     </row>
     <row r="196">
@@ -2573,10 +2573,10 @@
         <v>482</v>
       </c>
       <c r="B196" t="n">
-        <v>16227.52394141103</v>
+        <v>3268.251465062969</v>
       </c>
       <c r="C196" t="n">
-        <v>44757.0364176621</v>
+        <v>9014.144756281385</v>
       </c>
     </row>
     <row r="197">
@@ -2584,10 +2584,10 @@
         <v>483</v>
       </c>
       <c r="B197" t="n">
-        <v>16227.52394141103</v>
+        <v>3800.567685719266</v>
       </c>
       <c r="C197" t="n">
-        <v>44757.0364176621</v>
+        <v>10482.32293057619</v>
       </c>
     </row>
     <row r="198">
@@ -2595,10 +2595,10 @@
         <v>484</v>
       </c>
       <c r="B198" t="n">
-        <v>16227.52394141103</v>
+        <v>6512.570198329713</v>
       </c>
       <c r="C198" t="n">
-        <v>44757.0364176621</v>
+        <v>17962.28078859199</v>
       </c>
     </row>
     <row r="199">
@@ -2606,10 +2606,10 @@
         <v>485</v>
       </c>
       <c r="B199" t="n">
-        <v>16227.52394141103</v>
+        <v>6706.333521350718</v>
       </c>
       <c r="C199" t="n">
-        <v>44757.0364176621</v>
+        <v>18496.69824723629</v>
       </c>
     </row>
     <row r="200">
@@ -2617,10 +2617,10 @@
         <v>486</v>
       </c>
       <c r="B200" t="n">
-        <v>10507.18058270959</v>
+        <v>7042.425069744652</v>
       </c>
       <c r="C200" t="n">
-        <v>28979.79172208783</v>
+        <v>19423.67033031231</v>
       </c>
     </row>
     <row r="201">
@@ -2782,10 +2782,10 @@
         <v>501</v>
       </c>
       <c r="B215" t="n">
-        <v>4018.932957836866</v>
+        <v>2420.200107322062</v>
       </c>
       <c r="C215" t="n">
-        <v>11084.59487741211</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="216">
@@ -2793,10 +2793,10 @@
         <v>502</v>
       </c>
       <c r="B216" t="n">
-        <v>5072.773245545554</v>
+        <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>13991.18545189972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -2804,10 +2804,10 @@
         <v>503</v>
       </c>
       <c r="B217" t="n">
-        <v>5559.296919778698</v>
+        <v>2420.200107322064</v>
       </c>
       <c r="C217" t="n">
-        <v>15333.06347866011</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="218">
@@ -2815,10 +2815,10 @@
         <v>504</v>
       </c>
       <c r="B218" t="n">
-        <v>6183.793196442298</v>
+        <v>2719.037683477357</v>
       </c>
       <c r="C218" t="n">
-        <v>17055.48291234832</v>
+        <v>7499.361520572798</v>
       </c>
     </row>
     <row r="219">
@@ -2826,10 +2826,10 @@
         <v>505</v>
       </c>
       <c r="B219" t="n">
-        <v>6455.139844724877</v>
+        <v>2990.384331759942</v>
       </c>
       <c r="C219" t="n">
-        <v>17803.88247489661</v>
+        <v>8247.761083121106</v>
       </c>
     </row>
     <row r="220">
@@ -2837,10 +2837,10 @@
         <v>506</v>
       </c>
       <c r="B220" t="n">
-        <v>16227.52394141103</v>
+        <v>5970.788395873496</v>
       </c>
       <c r="C220" t="n">
-        <v>44757.0364176621</v>
+        <v>16467.99564992831</v>
       </c>
     </row>
     <row r="221">
@@ -2848,10 +2848,10 @@
         <v>507</v>
       </c>
       <c r="B221" t="n">
-        <v>9945.630804522254</v>
+        <v>6480.875291557313</v>
       </c>
       <c r="C221" t="n">
-        <v>27430.984648168</v>
+        <v>17874.86325639248</v>
       </c>
     </row>
     <row r="222">
@@ -2859,10 +2859,10 @@
         <v>508</v>
       </c>
       <c r="B222" t="n">
-        <v>16227.52394141103</v>
+        <v>6512.570198329713</v>
       </c>
       <c r="C222" t="n">
-        <v>44757.0364176621</v>
+        <v>17962.28078859199</v>
       </c>
     </row>
     <row r="223">
@@ -2870,10 +2870,10 @@
         <v>509</v>
       </c>
       <c r="B223" t="n">
-        <v>10171.08903431566</v>
+        <v>6706.333521350718</v>
       </c>
       <c r="C223" t="n">
-        <v>28052.81963901181</v>
+        <v>18496.69824723629</v>
       </c>
     </row>
     <row r="224">
@@ -2881,10 +2881,10 @@
         <v>510</v>
       </c>
       <c r="B224" t="n">
-        <v>7952.96607559232</v>
+        <v>4488.21056262738</v>
       </c>
       <c r="C224" t="n">
-        <v>21935.02801529472</v>
+        <v>12378.9066235192</v>
       </c>
     </row>
     <row r="225">
@@ -4003,10 +4003,10 @@
         <v>612</v>
       </c>
       <c r="B326" t="n">
-        <v>16227.52394141103</v>
+        <v>0</v>
       </c>
       <c r="C326" t="n">
-        <v>44757.0364176621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -4014,10 +4014,10 @@
         <v>613</v>
       </c>
       <c r="B327" t="n">
-        <v>16227.52394141103</v>
+        <v>2420.200107322064</v>
       </c>
       <c r="C327" t="n">
-        <v>44757.0364176621</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="328">
@@ -4298,10 +4298,10 @@
         <v>5172</v>
       </c>
       <c r="B14" t="n">
-        <v>5309.422455413364</v>
+        <v>7563.007057174681</v>
       </c>
       <c r="C14" t="n">
-        <v>19086.18441658103</v>
+        <v>27187.31625696217</v>
       </c>
     </row>
     <row r="15">
@@ -4408,10 +4408,10 @@
         <v>5182</v>
       </c>
       <c r="B24" t="n">
-        <v>1874.820568382635</v>
+        <v>1874.820568382665</v>
       </c>
       <c r="C24" t="n">
-        <v>6739.559983528256</v>
+        <v>6739.55998352836</v>
       </c>
     </row>
     <row r="25">
@@ -4419,10 +4419,10 @@
         <v>5183</v>
       </c>
       <c r="B25" t="n">
-        <v>2686.906972228544</v>
+        <v>1856.899955603442</v>
       </c>
       <c r="C25" t="n">
-        <v>9658.828697999836</v>
+        <v>6675.139394804318</v>
       </c>
     </row>
     <row r="26">
@@ -4441,10 +4441,10 @@
         <v>5185</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2284.204171165625</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>8211.202333606079</v>
       </c>
     </row>
     <row r="28">
@@ -4452,10 +4452,10 @@
         <v>5186</v>
       </c>
       <c r="B28" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C28" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="29">
@@ -4463,10 +4463,10 @@
         <v>5187</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>2299.850630719266</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>8267.447850894478</v>
       </c>
     </row>
     <row r="30">
@@ -4474,10 +4474,10 @@
         <v>5188</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>9272.421191446763</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>33332.27716090422</v>
       </c>
     </row>
     <row r="31">
@@ -4485,10 +4485,10 @@
         <v>5189</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="32">
@@ -4496,10 +4496,10 @@
         <v>5190</v>
       </c>
       <c r="B32" t="n">
-        <v>2070.628765404916</v>
+        <v>2070.628765404943</v>
       </c>
       <c r="C32" t="n">
-        <v>7443.446590787222</v>
+        <v>7443.44659078732</v>
       </c>
     </row>
     <row r="33">
@@ -4650,10 +4650,10 @@
         <v>5204</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2346.064435599156</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>8433.57612754539</v>
       </c>
     </row>
     <row r="47">
@@ -4661,10 +4661,10 @@
         <v>5205</v>
       </c>
       <c r="B47" t="n">
-        <v>2157.297466391308</v>
+        <v>2157.297466391335</v>
       </c>
       <c r="C47" t="n">
-        <v>7755.00115704428</v>
+        <v>7755.001157044377</v>
       </c>
     </row>
     <row r="48">
@@ -4672,10 +4672,10 @@
         <v>5206</v>
       </c>
       <c r="B48" t="n">
-        <v>1874.820568382635</v>
+        <v>1874.820568382665</v>
       </c>
       <c r="C48" t="n">
-        <v>6739.559983528256</v>
+        <v>6739.55998352836</v>
       </c>
     </row>
     <row r="49">
@@ -4683,10 +4683,10 @@
         <v>5207</v>
       </c>
       <c r="B49" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C49" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="50">
@@ -4694,10 +4694,10 @@
         <v>5208</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>2552.756939774566</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>9176.589380935055</v>
       </c>
     </row>
     <row r="51">
@@ -4705,10 +4705,10 @@
         <v>5209</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>2518.087048222285</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>9051.958886860313</v>
       </c>
     </row>
     <row r="52">
@@ -4738,10 +4738,10 @@
         <v>5212</v>
       </c>
       <c r="B54" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C54" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="55">
@@ -4749,10 +4749,10 @@
         <v>5213</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="56">
@@ -4793,10 +4793,10 @@
         <v>5217</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="60">
@@ -4804,10 +4804,10 @@
         <v>5218</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>2205.349870521857</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>7927.738786155077</v>
       </c>
     </row>
     <row r="61">
@@ -4815,10 +4815,10 @@
         <v>5219</v>
       </c>
       <c r="B61" t="n">
-        <v>2288.64786677666</v>
+        <v>2033.817988805349</v>
       </c>
       <c r="C61" t="n">
-        <v>8227.176423939933</v>
+        <v>7311.120094525737</v>
       </c>
     </row>
     <row r="62">
@@ -4903,10 +4903,10 @@
         <v>5227</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>2268.320949722101</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>8154.105710358214</v>
       </c>
     </row>
     <row r="70">
@@ -4914,10 +4914,10 @@
         <v>5228</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>2346.064435599156</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>8433.57612754539</v>
       </c>
     </row>
     <row r="71">
@@ -4925,10 +4925,10 @@
         <v>5229</v>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>2157.297466391335</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>7755.001157044377</v>
       </c>
     </row>
     <row r="72">
@@ -5002,10 +5002,10 @@
         <v>5236</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>8662.985600275406</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>31141.49272421562</v>
       </c>
     </row>
     <row r="79">
@@ -5057,10 +5057,10 @@
         <v>5241</v>
       </c>
       <c r="B83" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C83" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="84">
@@ -5211,10 +5211,10 @@
         <v>5255</v>
       </c>
       <c r="B97" t="n">
-        <v>1867.586593058722</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>6713.555462649259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5266,10 +5266,10 @@
         <v>5260</v>
       </c>
       <c r="B102" t="n">
-        <v>12388.0429580152</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C102" t="n">
-        <v>44532.23951244205</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="103">
@@ -5277,10 +5277,10 @@
         <v>5261</v>
       </c>
       <c r="B103" t="n">
-        <v>1867.586593058722</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C103" t="n">
-        <v>6713.555462649259</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="104">
@@ -5288,10 +5288,10 @@
         <v>5262</v>
       </c>
       <c r="B104" t="n">
-        <v>2070.628765404916</v>
+        <v>2070.628765404943</v>
       </c>
       <c r="C104" t="n">
-        <v>7443.446590787222</v>
+        <v>7443.44659078732</v>
       </c>
     </row>
     <row r="105">
@@ -5783,10 +5783,10 @@
         <v>5307</v>
       </c>
       <c r="B149" t="n">
-        <v>12450.57728705825</v>
+        <v>9800.278967776228</v>
       </c>
       <c r="C149" t="n">
-        <v>44757.0364176621</v>
+        <v>35229.80762666676</v>
       </c>
     </row>
     <row r="150">
@@ -5794,10 +5794,10 @@
         <v>5308</v>
       </c>
       <c r="B150" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C150" t="n">
-        <v>44757.03641766209</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="151">
@@ -5805,10 +5805,10 @@
         <v>5309</v>
       </c>
       <c r="B151" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C151" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="152">
@@ -6014,10 +6014,10 @@
         <v>5328</v>
       </c>
       <c r="B170" t="n">
-        <v>1867.586593058724</v>
+        <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>6713.555462649267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -6025,10 +6025,10 @@
         <v>5329</v>
       </c>
       <c r="B171" t="n">
-        <v>12450.57728705825</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>44757.0364176621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -6036,10 +6036,10 @@
         <v>5330</v>
       </c>
       <c r="B172" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C172" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="173">
@@ -6047,10 +6047,10 @@
         <v>5331</v>
       </c>
       <c r="B173" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C173" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869556</v>
       </c>
     </row>
     <row r="174">
@@ -6058,10 +6058,10 @@
         <v>5332</v>
       </c>
       <c r="B174" t="n">
-        <v>12450.57728705825</v>
+        <v>5422.989787194354</v>
       </c>
       <c r="C174" t="n">
-        <v>44757.0364176621</v>
+        <v>19494.43353525137</v>
       </c>
     </row>
     <row r="175">
@@ -6069,10 +6069,10 @@
         <v>5333</v>
       </c>
       <c r="B175" t="n">
-        <v>1867.586593058722</v>
+        <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>6713.555462649259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -6080,10 +6080,10 @@
         <v>5334</v>
       </c>
       <c r="B176" t="n">
-        <v>2070.628765404916</v>
+        <v>2070.628765404943</v>
       </c>
       <c r="C176" t="n">
-        <v>7443.446590787222</v>
+        <v>7443.44659078732</v>
       </c>
     </row>
     <row r="177">
@@ -6091,10 +6091,10 @@
         <v>5335</v>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="178">
@@ -6300,10 +6300,10 @@
         <v>5354</v>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="197">
@@ -6311,10 +6311,10 @@
         <v>5355</v>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="198">
@@ -6322,10 +6322,10 @@
         <v>5356</v>
       </c>
       <c r="B198" t="n">
-        <v>11521.83592488392</v>
+        <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>41418.4192587105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -7367,10 +7367,10 @@
         <v>5451</v>
       </c>
       <c r="B293" t="n">
-        <v>5818.181396072483</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C293" t="n">
-        <v>20915.05884624785</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="294">
@@ -7378,10 +7378,10 @@
         <v>5452</v>
       </c>
       <c r="B294" t="n">
-        <v>1867.586593058724</v>
+        <v>2364.6056215037</v>
       </c>
       <c r="C294" t="n">
-        <v>6713.555462649267</v>
+        <v>8500.227537646582</v>
       </c>
     </row>
     <row r="295">
@@ -7389,10 +7389,10 @@
         <v>5453</v>
       </c>
       <c r="B295" t="n">
-        <v>1867.586593058722</v>
+        <v>1856.899955603448</v>
       </c>
       <c r="C295" t="n">
-        <v>6713.555462649259</v>
+        <v>6675.139394804341</v>
       </c>
     </row>
     <row r="296">
@@ -7565,10 +7565,10 @@
         <v>5469</v>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>2327.1776631764</v>
       </c>
       <c r="C311" t="n">
-        <v>0</v>
+        <v>8365.682411322605</v>
       </c>
     </row>
     <row r="312">
@@ -7598,10 +7598,10 @@
         <v>5472</v>
       </c>
       <c r="B314" t="n">
-        <v>1867.586593058722</v>
+        <v>1856.899955603442</v>
       </c>
       <c r="C314" t="n">
-        <v>6713.555462649259</v>
+        <v>6675.139394804317</v>
       </c>
     </row>
     <row r="315">
@@ -7609,10 +7609,10 @@
         <v>5473</v>
       </c>
       <c r="B315" t="n">
-        <v>3866.5968391644</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C315" t="n">
-        <v>13899.54951910404</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="316">
@@ -7620,10 +7620,10 @@
         <v>5474</v>
       </c>
       <c r="B316" t="n">
-        <v>12450.57728705825</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C316" t="n">
-        <v>44757.0364176621</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="317">
@@ -7631,10 +7631,10 @@
         <v>5475</v>
       </c>
       <c r="B317" t="n">
-        <v>12450.57728705825</v>
+        <v>7707.830164704253</v>
       </c>
       <c r="C317" t="n">
-        <v>44757.0364176621</v>
+        <v>27707.92288815489</v>
       </c>
     </row>
     <row r="318">
@@ -7642,10 +7642,10 @@
         <v>5476</v>
       </c>
       <c r="B318" t="n">
-        <v>12450.57728705825</v>
+        <v>1856.89995560341</v>
       </c>
       <c r="C318" t="n">
-        <v>44757.0364176621</v>
+        <v>6675.139394804203</v>
       </c>
     </row>
     <row r="319">
@@ -7653,10 +7653,10 @@
         <v>5477</v>
       </c>
       <c r="B319" t="n">
-        <v>1867.586593058724</v>
+        <v>0</v>
       </c>
       <c r="C319" t="n">
-        <v>6713.555462649267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -7664,10 +7664,10 @@
         <v>5478</v>
       </c>
       <c r="B320" t="n">
-        <v>1867.586593058722</v>
+        <v>1856.89995560344</v>
       </c>
       <c r="C320" t="n">
-        <v>6713.555462649259</v>
+        <v>6675.13939480431</v>
       </c>
     </row>
     <row r="321">
@@ -7675,10 +7675,10 @@
         <v>5479</v>
       </c>
       <c r="B321" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C321" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="322">
@@ -7686,10 +7686,10 @@
         <v>5480</v>
       </c>
       <c r="B322" t="n">
-        <v>12450.57728705825</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C322" t="n">
-        <v>44757.0364176621</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="323">
@@ -7829,10 +7829,10 @@
         <v>5493</v>
       </c>
       <c r="B335" t="n">
-        <v>1890.661705562889</v>
+        <v>1890.661705562905</v>
       </c>
       <c r="C335" t="n">
-        <v>6796.505323276539</v>
+        <v>6796.505323276597</v>
       </c>
     </row>
     <row r="336">
@@ -7851,10 +7851,10 @@
         <v>5495</v>
       </c>
       <c r="B337" t="n">
-        <v>0</v>
+        <v>1856.899955603446</v>
       </c>
       <c r="C337" t="n">
-        <v>0</v>
+        <v>6675.139394804332</v>
       </c>
     </row>
   </sheetData>

--- a/first_stage_optimization/lshp_operation.xlsx
+++ b/first_stage_optimization/lshp_operation.xlsx
@@ -439,10 +439,10 @@
         <v>288</v>
       </c>
       <c r="B2" t="n">
-        <v>11197.08202174817</v>
+        <v>12937.01956816348</v>
       </c>
       <c r="C2" t="n">
-        <v>30882.6047416915</v>
+        <v>35681.5160488343</v>
       </c>
     </row>
     <row r="3">
@@ -450,10 +450,10 @@
         <v>289</v>
       </c>
       <c r="B3" t="n">
-        <v>16134.66738214708</v>
+        <v>16134.66738214692</v>
       </c>
       <c r="C3" t="n">
-        <v>44500.92929869557</v>
+        <v>44500.92929869513</v>
       </c>
     </row>
     <row r="4">
@@ -494,10 +494,10 @@
         <v>293</v>
       </c>
       <c r="B7" t="n">
-        <v>15640.50738895312</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C7" t="n">
-        <v>43137.98958642726</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="8">
@@ -505,10 +505,10 @@
         <v>294</v>
       </c>
       <c r="B8" t="n">
-        <v>15771.71513208502</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C8" t="n">
-        <v>43499.8728755129</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="9">
@@ -538,10 +538,10 @@
         <v>297</v>
       </c>
       <c r="B11" t="n">
-        <v>7427.29319618396</v>
+        <v>9167.230742599275</v>
       </c>
       <c r="C11" t="n">
-        <v>20485.1728006358</v>
+        <v>25284.0841077786</v>
       </c>
     </row>
     <row r="12">
@@ -549,10 +549,10 @@
         <v>298</v>
       </c>
       <c r="B12" t="n">
-        <v>2671.138940993995</v>
+        <v>4411.076487409309</v>
       </c>
       <c r="C12" t="n">
-        <v>7367.252286321891</v>
+        <v>12166.16359346469</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +571,10 @@
         <v>300</v>
       </c>
       <c r="B14" t="n">
-        <v>11725.51941396181</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C14" t="n">
-        <v>32340.08474253159</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="15">
@@ -582,10 +582,10 @@
         <v>301</v>
       </c>
       <c r="B15" t="n">
-        <v>16134.66738214708</v>
+        <v>16031.5577692864</v>
       </c>
       <c r="C15" t="n">
-        <v>44500.92929869557</v>
+        <v>44216.5432941222</v>
       </c>
     </row>
     <row r="16">
@@ -648,10 +648,10 @@
         <v>307</v>
       </c>
       <c r="B21" t="n">
-        <v>2420.200107322064</v>
+        <v>3903.493971266206</v>
       </c>
       <c r="C21" t="n">
-        <v>6675.139394804341</v>
+        <v>10766.20330118549</v>
       </c>
     </row>
     <row r="22">
@@ -659,10 +659,10 @@
         <v>308</v>
       </c>
       <c r="B22" t="n">
-        <v>3442.235445494172</v>
+        <v>5182.172991909332</v>
       </c>
       <c r="C22" t="n">
-        <v>9494.008928804804</v>
+        <v>14292.92023594718</v>
       </c>
     </row>
     <row r="23">
@@ -670,10 +670,10 @@
         <v>309</v>
       </c>
       <c r="B23" t="n">
-        <v>8223.007242495609</v>
+        <v>16134.66738214692</v>
       </c>
       <c r="C23" t="n">
-        <v>22679.82693748368</v>
+        <v>44500.92929869513</v>
       </c>
     </row>
     <row r="24">
@@ -681,10 +681,10 @@
         <v>310</v>
       </c>
       <c r="B24" t="n">
-        <v>12332.30114269007</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C24" t="n">
-        <v>34013.64578784662</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="25">
@@ -703,10 +703,10 @@
         <v>312</v>
       </c>
       <c r="B26" t="n">
-        <v>14184.39603300014</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C26" t="n">
-        <v>39121.8975922415</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="27">
@@ -736,10 +736,10 @@
         <v>315</v>
       </c>
       <c r="B29" t="n">
-        <v>15700.36452466098</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C29" t="n">
-        <v>43303.08119328029</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="30">
@@ -769,10 +769,10 @@
         <v>318</v>
       </c>
       <c r="B32" t="n">
-        <v>15771.71513208502</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C32" t="n">
-        <v>43499.8728755129</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="33">
@@ -780,10 +780,10 @@
         <v>319</v>
       </c>
       <c r="B33" t="n">
-        <v>4574.87140815473</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C33" t="n">
-        <v>12617.92538160311</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="34">
@@ -813,10 +813,10 @@
         <v>322</v>
       </c>
       <c r="B36" t="n">
-        <v>5106.013640195039</v>
+        <v>6845.951186610199</v>
       </c>
       <c r="C36" t="n">
-        <v>14082.8655849401</v>
+        <v>18881.77689208247</v>
       </c>
     </row>
     <row r="37">
@@ -824,10 +824,10 @@
         <v>323</v>
       </c>
       <c r="B37" t="n">
-        <v>2420.200107322064</v>
+        <v>13751.78979370113</v>
       </c>
       <c r="C37" t="n">
-        <v>6675.139394804341</v>
+        <v>37928.72891926834</v>
       </c>
     </row>
     <row r="38">
@@ -934,10 +934,10 @@
         <v>333</v>
       </c>
       <c r="B47" t="n">
-        <v>5546.398661717728</v>
+        <v>7286.336208132883</v>
       </c>
       <c r="C47" t="n">
-        <v>15297.4888704917</v>
+        <v>20096.40017763406</v>
       </c>
     </row>
     <row r="48">
@@ -945,10 +945,10 @@
         <v>334</v>
       </c>
       <c r="B48" t="n">
-        <v>12332.30114269007</v>
+        <v>14072.23868910538</v>
       </c>
       <c r="C48" t="n">
-        <v>34013.64578784662</v>
+        <v>38812.55709498942</v>
       </c>
     </row>
     <row r="49">
@@ -956,10 +956,10 @@
         <v>335</v>
       </c>
       <c r="B49" t="n">
-        <v>13180.5251643192</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C49" t="n">
-        <v>36353.12737255779</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="50">
@@ -967,10 +967,10 @@
         <v>336</v>
       </c>
       <c r="B50" t="n">
-        <v>11197.08202174817</v>
+        <v>16134.66738214188</v>
       </c>
       <c r="C50" t="n">
-        <v>30882.6047416915</v>
+        <v>44500.92929868122</v>
       </c>
     </row>
     <row r="51">
@@ -1011,10 +1011,10 @@
         <v>340</v>
       </c>
       <c r="B54" t="n">
-        <v>16134.66738214708</v>
+        <v>16134.66738214695</v>
       </c>
       <c r="C54" t="n">
-        <v>44500.92929869557</v>
+        <v>44500.92929869522</v>
       </c>
     </row>
     <row r="55">
@@ -1022,10 +1022,10 @@
         <v>341</v>
       </c>
       <c r="B55" t="n">
-        <v>13873.55516262652</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C55" t="n">
-        <v>38264.56925270922</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="56">
@@ -1033,10 +1033,10 @@
         <v>342</v>
       </c>
       <c r="B56" t="n">
-        <v>9891.411429789443</v>
+        <v>11631.34897620476</v>
       </c>
       <c r="C56" t="n">
-        <v>27281.44251603368</v>
+        <v>32080.35382317648</v>
       </c>
     </row>
     <row r="57">
@@ -1231,10 +1231,10 @@
         <v>360</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>2420.200107322061</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>6675.139394804333</v>
       </c>
     </row>
     <row r="75">
@@ -1242,10 +1242,10 @@
         <v>361</v>
       </c>
       <c r="B75" t="n">
-        <v>2420.200107322062</v>
+        <v>2420.200107322061</v>
       </c>
       <c r="C75" t="n">
-        <v>6675.139394804335</v>
+        <v>6675.139394804333</v>
       </c>
     </row>
     <row r="76">
@@ -1253,10 +1253,10 @@
         <v>362</v>
       </c>
       <c r="B76" t="n">
-        <v>2420.200107322062</v>
+        <v>2420.200107322061</v>
       </c>
       <c r="C76" t="n">
-        <v>6675.139394804335</v>
+        <v>6675.139394804333</v>
       </c>
     </row>
     <row r="77">
@@ -1264,10 +1264,10 @@
         <v>363</v>
       </c>
       <c r="B77" t="n">
-        <v>2420.200107322064</v>
+        <v>12239.10204538795</v>
       </c>
       <c r="C77" t="n">
-        <v>6675.139394804341</v>
+        <v>33756.59391677224</v>
       </c>
     </row>
     <row r="78">
@@ -1275,10 +1275,10 @@
         <v>364</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>2938.65569474311</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>8105.088639736801</v>
       </c>
     </row>
     <row r="79">
@@ -1286,10 +1286,10 @@
         <v>365</v>
       </c>
       <c r="B79" t="n">
-        <v>2420.200107322062</v>
+        <v>3270.073686704226</v>
       </c>
       <c r="C79" t="n">
-        <v>6675.139394804335</v>
+        <v>9019.170614856805</v>
       </c>
     </row>
     <row r="80">
@@ -1297,10 +1297,10 @@
         <v>366</v>
       </c>
       <c r="B80" t="n">
-        <v>2420.200107322062</v>
+        <v>3743.795156917129</v>
       </c>
       <c r="C80" t="n">
-        <v>6675.139394804335</v>
+        <v>10325.73895952219</v>
       </c>
     </row>
     <row r="81">
@@ -1495,10 +1495,10 @@
         <v>384</v>
       </c>
       <c r="B98" t="n">
-        <v>2719.037683477357</v>
+        <v>4458.975229892671</v>
       </c>
       <c r="C98" t="n">
-        <v>7499.361520572798</v>
+        <v>12298.2728277156</v>
       </c>
     </row>
     <row r="99">
@@ -1506,10 +1506,10 @@
         <v>385</v>
       </c>
       <c r="B99" t="n">
-        <v>2990.384331759942</v>
+        <v>4730.321878175111</v>
       </c>
       <c r="C99" t="n">
-        <v>8247.761083121106</v>
+        <v>13046.67239026351</v>
       </c>
     </row>
     <row r="100">
@@ -1517,10 +1517,10 @@
         <v>386</v>
       </c>
       <c r="B100" t="n">
-        <v>3268.251465062969</v>
+        <v>4924.58664359358</v>
       </c>
       <c r="C100" t="n">
-        <v>9014.144756281385</v>
+        <v>13582.47287417559</v>
       </c>
     </row>
     <row r="101">
@@ -1528,10 +1528,10 @@
         <v>387</v>
       </c>
       <c r="B101" t="n">
-        <v>6948.505853923947</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C101" t="n">
-        <v>19164.63230467252</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="102">
@@ -1539,10 +1539,10 @@
         <v>388</v>
       </c>
       <c r="B102" t="n">
-        <v>2420.200107322062</v>
+        <v>5048.578090239315</v>
       </c>
       <c r="C102" t="n">
-        <v>6675.139394804335</v>
+        <v>13924.45293922051</v>
       </c>
     </row>
     <row r="103">
@@ -1550,10 +1550,10 @@
         <v>389</v>
       </c>
       <c r="B103" t="n">
-        <v>2420.200107322062</v>
+        <v>3270.073686704226</v>
       </c>
       <c r="C103" t="n">
-        <v>6675.139394804335</v>
+        <v>9019.170614856805</v>
       </c>
     </row>
     <row r="104">
@@ -1561,10 +1561,10 @@
         <v>390</v>
       </c>
       <c r="B104" t="n">
-        <v>4488.21056262738</v>
+        <v>6228.148109042694</v>
       </c>
       <c r="C104" t="n">
-        <v>12378.9066235192</v>
+        <v>17177.817930662</v>
       </c>
     </row>
     <row r="105">
@@ -1726,10 +1726,10 @@
         <v>405</v>
       </c>
       <c r="B119" t="n">
-        <v>2420.200107322062</v>
+        <v>2420.200107322061</v>
       </c>
       <c r="C119" t="n">
-        <v>6675.139394804335</v>
+        <v>6675.139394804333</v>
       </c>
     </row>
     <row r="120">
@@ -1737,10 +1737,10 @@
         <v>406</v>
       </c>
       <c r="B120" t="n">
-        <v>4074.021233385152</v>
+        <v>5813.958779800466</v>
       </c>
       <c r="C120" t="n">
-        <v>11236.53351967219</v>
+        <v>16035.44482681499</v>
       </c>
     </row>
     <row r="121">
@@ -1748,10 +1748,10 @@
         <v>407</v>
       </c>
       <c r="B121" t="n">
-        <v>4687.376665780643</v>
+        <v>6427.314212195957</v>
       </c>
       <c r="C121" t="n">
-        <v>12928.2254576296</v>
+        <v>17727.1367647724</v>
       </c>
     </row>
     <row r="122">
@@ -1759,10 +1759,10 @@
         <v>408</v>
       </c>
       <c r="B122" t="n">
-        <v>6621.629542051171</v>
+        <v>8361.567088466487</v>
       </c>
       <c r="C122" t="n">
-        <v>18263.07671015408</v>
+        <v>23061.98801729688</v>
       </c>
     </row>
     <row r="123">
@@ -1770,10 +1770,10 @@
         <v>409</v>
       </c>
       <c r="B123" t="n">
-        <v>6819.851204685992</v>
+        <v>8559.788751101307</v>
       </c>
       <c r="C123" t="n">
-        <v>18809.79068853721</v>
+        <v>23608.70199568001</v>
       </c>
     </row>
     <row r="124">
@@ -1781,10 +1781,10 @@
         <v>410</v>
       </c>
       <c r="B124" t="n">
-        <v>7099.280057115846</v>
+        <v>8839.21760353116</v>
       </c>
       <c r="C124" t="n">
-        <v>19580.48172985087</v>
+        <v>24379.39303699367</v>
       </c>
     </row>
     <row r="125">
@@ -1792,10 +1792,10 @@
         <v>411</v>
       </c>
       <c r="B125" t="n">
-        <v>7496.823652848921</v>
+        <v>9236.761199264234</v>
       </c>
       <c r="C125" t="n">
-        <v>20676.94433598069</v>
+        <v>25475.85564312349</v>
       </c>
     </row>
     <row r="126">
@@ -1803,10 +1803,10 @@
         <v>412</v>
       </c>
       <c r="B126" t="n">
-        <v>5654.012943367195</v>
+        <v>11339.74663090383</v>
       </c>
       <c r="C126" t="n">
-        <v>15594.2991750234</v>
+        <v>31276.08714421606</v>
       </c>
     </row>
     <row r="127">
@@ -1814,10 +1814,10 @@
         <v>413</v>
       </c>
       <c r="B127" t="n">
-        <v>4015.178821929269</v>
+        <v>5755.116368344424</v>
       </c>
       <c r="C127" t="n">
-        <v>11074.24061769019</v>
+        <v>15873.15192483255</v>
       </c>
     </row>
     <row r="128">
@@ -1825,10 +1825,10 @@
         <v>414</v>
       </c>
       <c r="B128" t="n">
-        <v>3070.942907548726</v>
+        <v>4810.88045396404</v>
       </c>
       <c r="C128" t="n">
-        <v>8469.949207652695</v>
+        <v>13268.86051479549</v>
       </c>
     </row>
     <row r="129">
@@ -1836,10 +1836,10 @@
         <v>415</v>
       </c>
       <c r="B129" t="n">
-        <v>2686.116864027475</v>
+        <v>4426.054410442789</v>
       </c>
       <c r="C129" t="n">
-        <v>7408.562805972993</v>
+        <v>12207.47411311579</v>
       </c>
     </row>
     <row r="130">
@@ -1847,10 +1847,10 @@
         <v>416</v>
       </c>
       <c r="B130" t="n">
-        <v>2574.019573866587</v>
+        <v>4313.957120281902</v>
       </c>
       <c r="C130" t="n">
-        <v>7099.38794256399</v>
+        <v>11898.29924970679</v>
       </c>
     </row>
     <row r="131">
@@ -1858,10 +1858,10 @@
         <v>417</v>
       </c>
       <c r="B131" t="n">
-        <v>2420.200107322064</v>
+        <v>4131.024741728158</v>
       </c>
       <c r="C131" t="n">
-        <v>6675.139394804341</v>
+        <v>11393.75455401198</v>
       </c>
     </row>
     <row r="132">
@@ -1869,10 +1869,10 @@
         <v>418</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>2475.240439975179</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>6826.9458060529</v>
       </c>
     </row>
     <row r="133">
@@ -1979,10 +1979,10 @@
         <v>428</v>
       </c>
       <c r="B142" t="n">
-        <v>2420.200107322062</v>
+        <v>3540.636238494415</v>
       </c>
       <c r="C142" t="n">
-        <v>6675.139394804335</v>
+        <v>9765.407565574016</v>
       </c>
     </row>
     <row r="143">
@@ -1990,10 +1990,10 @@
         <v>429</v>
       </c>
       <c r="B143" t="n">
-        <v>2607.407254098156</v>
+        <v>4347.344800513471</v>
       </c>
       <c r="C143" t="n">
-        <v>7191.4743030846</v>
+        <v>11990.3856102274</v>
       </c>
     </row>
     <row r="144">
@@ -2001,10 +2001,10 @@
         <v>430</v>
       </c>
       <c r="B144" t="n">
-        <v>3927.656650606756</v>
+        <v>5667.59419702207</v>
       </c>
       <c r="C144" t="n">
-        <v>10832.84624209859</v>
+        <v>15631.75754924139</v>
       </c>
     </row>
     <row r="145">
@@ -2012,10 +2012,10 @@
         <v>431</v>
       </c>
       <c r="B145" t="n">
-        <v>5076.471721924955</v>
+        <v>6816.40926834027</v>
       </c>
       <c r="C145" t="n">
-        <v>14001.38619741089</v>
+        <v>18800.29750455369</v>
       </c>
     </row>
     <row r="146">
@@ -2023,10 +2023,10 @@
         <v>432</v>
       </c>
       <c r="B146" t="n">
-        <v>6827.201907076305</v>
+        <v>8567.13945349162</v>
       </c>
       <c r="C146" t="n">
-        <v>18830.06461669572</v>
+        <v>23628.97592383852</v>
       </c>
     </row>
     <row r="147">
@@ -2034,10 +2034,10 @@
         <v>433</v>
       </c>
       <c r="B147" t="n">
-        <v>7561.883712310421</v>
+        <v>9301.821258725737</v>
       </c>
       <c r="C147" t="n">
-        <v>20856.3860956211</v>
+        <v>25655.2974027639</v>
       </c>
     </row>
     <row r="148">
@@ -2045,10 +2045,10 @@
         <v>434</v>
       </c>
       <c r="B148" t="n">
-        <v>7829.974092509725</v>
+        <v>9569.911638925039</v>
       </c>
       <c r="C148" t="n">
-        <v>21595.80456470652</v>
+        <v>26394.71587184932</v>
       </c>
     </row>
     <row r="149">
@@ -2056,10 +2056,10 @@
         <v>435</v>
       </c>
       <c r="B149" t="n">
-        <v>7982.762821060161</v>
+        <v>9722.700367475476</v>
       </c>
       <c r="C149" t="n">
-        <v>22017.2102401891</v>
+        <v>26816.1215473319</v>
       </c>
     </row>
     <row r="150">
@@ -2067,10 +2067,10 @@
         <v>436</v>
       </c>
       <c r="B150" t="n">
-        <v>7680.581968994567</v>
+        <v>9420.519515409724</v>
       </c>
       <c r="C150" t="n">
-        <v>21183.7670451921</v>
+        <v>25982.67835233447</v>
       </c>
     </row>
     <row r="151">
@@ -2078,10 +2078,10 @@
         <v>437</v>
       </c>
       <c r="B151" t="n">
-        <v>9781.100191118503</v>
+        <v>11521.03773753382</v>
       </c>
       <c r="C151" t="n">
-        <v>26977.1937505228</v>
+        <v>31776.1050576656</v>
       </c>
     </row>
     <row r="152">
@@ -2089,10 +2089,10 @@
         <v>438</v>
       </c>
       <c r="B152" t="n">
-        <v>5809.303108874029</v>
+        <v>7549.240655289194</v>
       </c>
       <c r="C152" t="n">
-        <v>16022.60404876681</v>
+        <v>20821.5153559092</v>
       </c>
     </row>
     <row r="153">
@@ -2100,10 +2100,10 @@
         <v>439</v>
       </c>
       <c r="B153" t="n">
-        <v>5438.630385589105</v>
+        <v>7178.567932004261</v>
       </c>
       <c r="C153" t="n">
-        <v>15000.25383471099</v>
+        <v>19799.16514185336</v>
       </c>
     </row>
     <row r="154">
@@ -2111,10 +2111,10 @@
         <v>440</v>
       </c>
       <c r="B154" t="n">
-        <v>5318.157006129553</v>
+        <v>6974.492184660128</v>
       </c>
       <c r="C154" t="n">
-        <v>14667.97692966388</v>
+        <v>19236.30504755799</v>
       </c>
     </row>
     <row r="155">
@@ -2122,10 +2122,10 @@
         <v>441</v>
       </c>
       <c r="B155" t="n">
-        <v>3430.999798591454</v>
+        <v>5087.334977122176</v>
       </c>
       <c r="C155" t="n">
-        <v>9463.019958496297</v>
+        <v>14031.34807639081</v>
       </c>
     </row>
     <row r="156">
@@ -2133,10 +2133,10 @@
         <v>442</v>
       </c>
       <c r="B156" t="n">
-        <v>2420.200107322064</v>
+        <v>4011.467085957548</v>
       </c>
       <c r="C156" t="n">
-        <v>6675.139394804341</v>
+        <v>11064.003300977</v>
       </c>
     </row>
     <row r="157">
@@ -2155,10 +2155,10 @@
         <v>444</v>
       </c>
       <c r="B158" t="n">
-        <v>7731.830712880651</v>
+        <v>16134.66738214707</v>
       </c>
       <c r="C158" t="n">
-        <v>21325.11589821185</v>
+        <v>44500.92929869554</v>
       </c>
     </row>
     <row r="159">
@@ -2265,10 +2265,10 @@
         <v>454</v>
       </c>
       <c r="B168" t="n">
-        <v>2420.200107322064</v>
+        <v>3821.739505649951</v>
       </c>
       <c r="C168" t="n">
-        <v>6675.139394804341</v>
+        <v>10540.7168000961</v>
       </c>
     </row>
     <row r="169">
@@ -2276,10 +2276,10 @@
         <v>455</v>
       </c>
       <c r="B169" t="n">
-        <v>2788.370147238635</v>
+        <v>4528.307693653949</v>
       </c>
       <c r="C169" t="n">
-        <v>7690.586972877994</v>
+        <v>12489.49828002079</v>
       </c>
     </row>
     <row r="170">
@@ -2287,10 +2287,10 @@
         <v>456</v>
       </c>
       <c r="B170" t="n">
-        <v>2719.037683477357</v>
+        <v>4458.975229892671</v>
       </c>
       <c r="C170" t="n">
-        <v>7499.361520572798</v>
+        <v>12298.2728277156</v>
       </c>
     </row>
     <row r="171">
@@ -2298,10 +2298,10 @@
         <v>457</v>
       </c>
       <c r="B171" t="n">
-        <v>2990.384331759942</v>
+        <v>4730.321878175097</v>
       </c>
       <c r="C171" t="n">
-        <v>8247.761083121106</v>
+        <v>13046.67239026347</v>
       </c>
     </row>
     <row r="172">
@@ -2309,10 +2309,10 @@
         <v>458</v>
       </c>
       <c r="B172" t="n">
-        <v>3268.251465062969</v>
+        <v>5008.189011478284</v>
       </c>
       <c r="C172" t="n">
-        <v>9014.144756281385</v>
+        <v>13813.05606342418</v>
       </c>
     </row>
     <row r="173">
@@ -2320,10 +2320,10 @@
         <v>459</v>
       </c>
       <c r="B173" t="n">
-        <v>3800.567685719266</v>
+        <v>5540.50523213458</v>
       </c>
       <c r="C173" t="n">
-        <v>10482.32293057619</v>
+        <v>15281.23423771899</v>
       </c>
     </row>
     <row r="174">
@@ -2331,10 +2331,10 @@
         <v>460</v>
       </c>
       <c r="B174" t="n">
-        <v>9477.803061384062</v>
+        <v>11217.74060779926</v>
       </c>
       <c r="C174" t="n">
-        <v>26140.67175678501</v>
+        <v>30939.58306392749</v>
       </c>
     </row>
     <row r="175">
@@ -2342,10 +2342,10 @@
         <v>461</v>
       </c>
       <c r="B175" t="n">
-        <v>9610.512602761624</v>
+        <v>11350.45014917682</v>
       </c>
       <c r="C175" t="n">
-        <v>26506.69714660122</v>
+        <v>31305.60845374369</v>
       </c>
     </row>
     <row r="176">
@@ -2353,10 +2353,10 @@
         <v>462</v>
       </c>
       <c r="B176" t="n">
-        <v>9891.411429789443</v>
+        <v>11631.34897620476</v>
       </c>
       <c r="C176" t="n">
-        <v>27281.44251603368</v>
+        <v>32080.35382317648</v>
       </c>
     </row>
     <row r="177">
@@ -2529,10 +2529,10 @@
         <v>478</v>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>3347.955278995932</v>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>9233.975367267005</v>
       </c>
     </row>
     <row r="193">
@@ -2540,10 +2540,10 @@
         <v>479</v>
       </c>
       <c r="B193" t="n">
-        <v>2420.200107322064</v>
+        <v>3834.478953229075</v>
       </c>
       <c r="C193" t="n">
-        <v>6675.139394804341</v>
+        <v>10575.85339402739</v>
       </c>
     </row>
     <row r="194">
@@ -2551,10 +2551,10 @@
         <v>480</v>
       </c>
       <c r="B194" t="n">
-        <v>2719.037683477357</v>
+        <v>4458.975229892671</v>
       </c>
       <c r="C194" t="n">
-        <v>7499.361520572798</v>
+        <v>12298.2728277156</v>
       </c>
     </row>
     <row r="195">
@@ -2562,10 +2562,10 @@
         <v>481</v>
       </c>
       <c r="B195" t="n">
-        <v>2990.384331759942</v>
+        <v>4646.71951029074</v>
       </c>
       <c r="C195" t="n">
-        <v>8247.761083121106</v>
+        <v>12816.08920101583</v>
       </c>
     </row>
     <row r="196">
@@ -2573,10 +2573,10 @@
         <v>482</v>
       </c>
       <c r="B196" t="n">
-        <v>3268.251465062969</v>
+        <v>9167.273969977028</v>
       </c>
       <c r="C196" t="n">
-        <v>9014.144756281385</v>
+        <v>25284.20333294982</v>
       </c>
     </row>
     <row r="197">
@@ -2584,10 +2584,10 @@
         <v>483</v>
       </c>
       <c r="B197" t="n">
-        <v>3800.567685719266</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C197" t="n">
-        <v>10482.32293057619</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="198">
@@ -2595,10 +2595,10 @@
         <v>484</v>
       </c>
       <c r="B198" t="n">
-        <v>6512.570198329713</v>
+        <v>16134.66738214708</v>
       </c>
       <c r="C198" t="n">
-        <v>17962.28078859199</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="199">
@@ -2606,10 +2606,10 @@
         <v>485</v>
       </c>
       <c r="B199" t="n">
-        <v>6706.333521350718</v>
+        <v>8446.271067766033</v>
       </c>
       <c r="C199" t="n">
-        <v>18496.69824723629</v>
+        <v>23295.60955437909</v>
       </c>
     </row>
     <row r="200">
@@ -2617,10 +2617,10 @@
         <v>486</v>
       </c>
       <c r="B200" t="n">
-        <v>7042.425069744652</v>
+        <v>8782.362616159966</v>
       </c>
       <c r="C200" t="n">
-        <v>19423.67033031231</v>
+        <v>24222.58163745511</v>
       </c>
     </row>
     <row r="201">
@@ -2782,10 +2782,10 @@
         <v>501</v>
       </c>
       <c r="B215" t="n">
-        <v>2420.200107322062</v>
+        <v>2420.200107322061</v>
       </c>
       <c r="C215" t="n">
-        <v>6675.139394804335</v>
+        <v>6675.139394804333</v>
       </c>
     </row>
     <row r="216">
@@ -2793,10 +2793,10 @@
         <v>502</v>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>3347.955278995932</v>
       </c>
       <c r="C216" t="n">
-        <v>0</v>
+        <v>9233.975367267005</v>
       </c>
     </row>
     <row r="217">
@@ -2804,10 +2804,10 @@
         <v>503</v>
       </c>
       <c r="B217" t="n">
-        <v>2420.200107322064</v>
+        <v>3834.478953229075</v>
       </c>
       <c r="C217" t="n">
-        <v>6675.139394804341</v>
+        <v>10575.85339402739</v>
       </c>
     </row>
     <row r="218">
@@ -2815,10 +2815,10 @@
         <v>504</v>
       </c>
       <c r="B218" t="n">
-        <v>2719.037683477357</v>
+        <v>4458.97522989251</v>
       </c>
       <c r="C218" t="n">
-        <v>7499.361520572798</v>
+        <v>12298.27282771515</v>
       </c>
     </row>
     <row r="219">
@@ -2826,10 +2826,10 @@
         <v>505</v>
       </c>
       <c r="B219" t="n">
-        <v>2990.384331759942</v>
+        <v>4730.321878175257</v>
       </c>
       <c r="C219" t="n">
-        <v>8247.761083121106</v>
+        <v>13046.67239026391</v>
       </c>
     </row>
     <row r="220">
@@ -2837,10 +2837,10 @@
         <v>506</v>
       </c>
       <c r="B220" t="n">
-        <v>5970.788395873496</v>
+        <v>7710.725942288811</v>
       </c>
       <c r="C220" t="n">
-        <v>16467.99564992831</v>
+        <v>21266.90695707111</v>
       </c>
     </row>
     <row r="221">
@@ -2848,10 +2848,10 @@
         <v>507</v>
       </c>
       <c r="B221" t="n">
-        <v>6480.875291557313</v>
+        <v>8220.812837972628</v>
       </c>
       <c r="C221" t="n">
-        <v>17874.86325639248</v>
+        <v>22673.77456353528</v>
       </c>
     </row>
     <row r="222">
@@ -2859,10 +2859,10 @@
         <v>508</v>
       </c>
       <c r="B222" t="n">
-        <v>6512.570198329713</v>
+        <v>8252.507744745028</v>
       </c>
       <c r="C222" t="n">
-        <v>17962.28078859199</v>
+        <v>22761.19209573479</v>
       </c>
     </row>
     <row r="223">
@@ -2870,10 +2870,10 @@
         <v>509</v>
       </c>
       <c r="B223" t="n">
-        <v>6706.333521350718</v>
+        <v>8446.271067766033</v>
       </c>
       <c r="C223" t="n">
-        <v>18496.69824723629</v>
+        <v>23295.60955437909</v>
       </c>
     </row>
     <row r="224">
@@ -2881,10 +2881,10 @@
         <v>510</v>
       </c>
       <c r="B224" t="n">
-        <v>4488.21056262738</v>
+        <v>6228.148109042542</v>
       </c>
       <c r="C224" t="n">
-        <v>12378.9066235192</v>
+        <v>17177.81793066158</v>
       </c>
     </row>
     <row r="225">
@@ -4014,10 +4014,10 @@
         <v>613</v>
       </c>
       <c r="B327" t="n">
-        <v>2420.200107322064</v>
+        <v>0</v>
       </c>
       <c r="C327" t="n">
-        <v>6675.139394804341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -4298,10 +4298,10 @@
         <v>5172</v>
       </c>
       <c r="B14" t="n">
-        <v>7563.007057174681</v>
+        <v>12379.33303735647</v>
       </c>
       <c r="C14" t="n">
-        <v>27187.31625696217</v>
+        <v>44500.92929869613</v>
       </c>
     </row>
     <row r="15">
@@ -4408,10 +4408,10 @@
         <v>5182</v>
       </c>
       <c r="B24" t="n">
-        <v>1874.820568382665</v>
+        <v>8915.784984633759</v>
       </c>
       <c r="C24" t="n">
-        <v>6739.55998352836</v>
+        <v>32050.2498839218</v>
       </c>
     </row>
     <row r="25">
@@ -4419,10 +4419,10 @@
         <v>5183</v>
       </c>
       <c r="B25" t="n">
-        <v>1856.899955603442</v>
+        <v>1856.899955603446</v>
       </c>
       <c r="C25" t="n">
-        <v>6675.139394804318</v>
+        <v>6675.139394804333</v>
       </c>
     </row>
     <row r="26">
@@ -4441,10 +4441,10 @@
         <v>5185</v>
       </c>
       <c r="B27" t="n">
-        <v>2284.204171165625</v>
+        <v>2284.204171165599</v>
       </c>
       <c r="C27" t="n">
-        <v>8211.202333606079</v>
+        <v>8211.202333605986</v>
       </c>
     </row>
     <row r="28">
@@ -4463,10 +4463,10 @@
         <v>5187</v>
       </c>
       <c r="B29" t="n">
-        <v>2299.850630719266</v>
+        <v>2299.85063071924</v>
       </c>
       <c r="C29" t="n">
-        <v>8267.447850894478</v>
+        <v>8267.447850894387</v>
       </c>
     </row>
     <row r="30">
@@ -4474,10 +4474,10 @@
         <v>5188</v>
       </c>
       <c r="B30" t="n">
-        <v>9272.421191446763</v>
+        <v>12379.33303735646</v>
       </c>
       <c r="C30" t="n">
-        <v>33332.27716090422</v>
+        <v>44500.92929869612</v>
       </c>
     </row>
     <row r="31">
@@ -4485,10 +4485,10 @@
         <v>5189</v>
       </c>
       <c r="B31" t="n">
-        <v>1856.899955603447</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>6675.139394804335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4496,10 +4496,10 @@
         <v>5190</v>
       </c>
       <c r="B32" t="n">
-        <v>2070.628765404943</v>
+        <v>2070.62876540492</v>
       </c>
       <c r="C32" t="n">
-        <v>7443.44659078732</v>
+        <v>7443.446590787236</v>
       </c>
     </row>
     <row r="33">
@@ -4650,10 +4650,10 @@
         <v>5204</v>
       </c>
       <c r="B46" t="n">
-        <v>2346.064435599156</v>
+        <v>2346.06443559913</v>
       </c>
       <c r="C46" t="n">
-        <v>8433.57612754539</v>
+        <v>8433.576127545297</v>
       </c>
     </row>
     <row r="47">
@@ -4661,10 +4661,10 @@
         <v>5205</v>
       </c>
       <c r="B47" t="n">
-        <v>2157.297466391335</v>
+        <v>12379.33303735643</v>
       </c>
       <c r="C47" t="n">
-        <v>7755.001157044377</v>
+        <v>44500.92929869599</v>
       </c>
     </row>
     <row r="48">
@@ -4672,10 +4672,10 @@
         <v>5206</v>
       </c>
       <c r="B48" t="n">
-        <v>1874.820568382665</v>
+        <v>1874.82056838264</v>
       </c>
       <c r="C48" t="n">
-        <v>6739.55998352836</v>
+        <v>6739.55998352827</v>
       </c>
     </row>
     <row r="49">
@@ -4694,10 +4694,10 @@
         <v>5208</v>
       </c>
       <c r="B50" t="n">
-        <v>2552.756939774566</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9176.589380935055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4705,10 +4705,10 @@
         <v>5209</v>
       </c>
       <c r="B51" t="n">
-        <v>2518.087048222285</v>
+        <v>2284.204171165599</v>
       </c>
       <c r="C51" t="n">
-        <v>9051.958886860313</v>
+        <v>8211.202333605986</v>
       </c>
     </row>
     <row r="52">
@@ -4738,10 +4738,10 @@
         <v>5212</v>
       </c>
       <c r="B54" t="n">
-        <v>12379.33303735631</v>
+        <v>4470.603618251954</v>
       </c>
       <c r="C54" t="n">
-        <v>44500.92929869557</v>
+        <v>16070.81859240528</v>
       </c>
     </row>
     <row r="55">
@@ -4749,10 +4749,10 @@
         <v>5213</v>
       </c>
       <c r="B55" t="n">
-        <v>1856.899955603447</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>6675.139394804335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4793,10 +4793,10 @@
         <v>5217</v>
       </c>
       <c r="B59" t="n">
-        <v>1856.899955603447</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>6675.139394804335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4804,10 +4804,10 @@
         <v>5218</v>
       </c>
       <c r="B60" t="n">
-        <v>2205.349870521857</v>
+        <v>2205.349870521832</v>
       </c>
       <c r="C60" t="n">
-        <v>7927.738786155077</v>
+        <v>7927.738786154987</v>
       </c>
     </row>
     <row r="61">
@@ -4815,10 +4815,10 @@
         <v>5219</v>
       </c>
       <c r="B61" t="n">
-        <v>2033.817988805349</v>
+        <v>2132.385027743748</v>
       </c>
       <c r="C61" t="n">
-        <v>7311.120094525737</v>
+        <v>7665.446520492558</v>
       </c>
     </row>
     <row r="62">
@@ -4903,10 +4903,10 @@
         <v>5227</v>
       </c>
       <c r="B69" t="n">
-        <v>2268.320949722101</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C69" t="n">
-        <v>8154.105710358214</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="70">
@@ -4914,10 +4914,10 @@
         <v>5228</v>
       </c>
       <c r="B70" t="n">
-        <v>2346.064435599156</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>8433.57612754539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4925,10 +4925,10 @@
         <v>5229</v>
       </c>
       <c r="B71" t="n">
-        <v>2157.297466391335</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>7755.001157044377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -5002,10 +5002,10 @@
         <v>5236</v>
       </c>
       <c r="B78" t="n">
-        <v>8662.985600275406</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>31141.49272421562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -5200,10 +5200,10 @@
         <v>5254</v>
       </c>
       <c r="B96" t="n">
-        <v>1874.820568382665</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C96" t="n">
-        <v>6739.55998352836</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="97">
@@ -5222,10 +5222,10 @@
         <v>5256</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>6675.139394804337</v>
       </c>
     </row>
     <row r="99">
@@ -5233,10 +5233,10 @@
         <v>5257</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1856.899955603445</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>6675.139394804329</v>
       </c>
     </row>
     <row r="100">
@@ -5244,10 +5244,10 @@
         <v>5258</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>9120.569383798414</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>32786.40392721332</v>
       </c>
     </row>
     <row r="101">
@@ -5255,10 +5255,10 @@
         <v>5259</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>1856.899955603445</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>6675.13939480433</v>
       </c>
     </row>
     <row r="102">
@@ -5266,10 +5266,10 @@
         <v>5260</v>
       </c>
       <c r="B102" t="n">
-        <v>12379.33303735631</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>44500.92929869557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5277,10 +5277,10 @@
         <v>5261</v>
       </c>
       <c r="B103" t="n">
-        <v>12379.33303735631</v>
+        <v>3147.954604277232</v>
       </c>
       <c r="C103" t="n">
-        <v>44500.92929869557</v>
+        <v>11316.19166054529</v>
       </c>
     </row>
     <row r="104">
@@ -5288,10 +5288,10 @@
         <v>5262</v>
       </c>
       <c r="B104" t="n">
-        <v>2070.628765404943</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C104" t="n">
-        <v>7443.44659078732</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="105">
@@ -5519,10 +5519,10 @@
         <v>5283</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>1856.899955603445</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>6675.13939480433</v>
       </c>
     </row>
     <row r="126">
@@ -5530,10 +5530,10 @@
         <v>5284</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>6709.015463848392</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>24117.40777307106</v>
       </c>
     </row>
     <row r="127">
@@ -5541,10 +5541,10 @@
         <v>5285</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>6675.139394804337</v>
       </c>
     </row>
     <row r="128">
@@ -5552,10 +5552,10 @@
         <v>5286</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>7516.445331520613</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>27019.93728306234</v>
       </c>
     </row>
     <row r="129">
@@ -5783,10 +5783,10 @@
         <v>5307</v>
       </c>
       <c r="B149" t="n">
-        <v>9800.278967776228</v>
+        <v>12379.33303735647</v>
       </c>
       <c r="C149" t="n">
-        <v>35229.80762666676</v>
+        <v>44500.92929869614</v>
       </c>
     </row>
     <row r="150">
@@ -5805,10 +5805,10 @@
         <v>5309</v>
       </c>
       <c r="B151" t="n">
-        <v>12379.33303735631</v>
+        <v>12379.33303735647</v>
       </c>
       <c r="C151" t="n">
-        <v>44500.92929869557</v>
+        <v>44500.92929869614</v>
       </c>
     </row>
     <row r="152">
@@ -6014,10 +6014,10 @@
         <v>5328</v>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>12379.33303735629</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>44500.9292986955</v>
       </c>
     </row>
     <row r="171">
@@ -6025,10 +6025,10 @@
         <v>5329</v>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>1856.899955603445</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>6675.139394804329</v>
       </c>
     </row>
     <row r="172">
@@ -6036,10 +6036,10 @@
         <v>5330</v>
       </c>
       <c r="B172" t="n">
-        <v>12379.33303735631</v>
+        <v>12379.33303735629</v>
       </c>
       <c r="C172" t="n">
-        <v>44500.92929869557</v>
+        <v>44500.92929869548</v>
       </c>
     </row>
     <row r="173">
@@ -6050,7 +6050,7 @@
         <v>12379.33303735631</v>
       </c>
       <c r="C173" t="n">
-        <v>44500.92929869556</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="174">
@@ -6058,10 +6058,10 @@
         <v>5332</v>
       </c>
       <c r="B174" t="n">
-        <v>5422.989787194354</v>
+        <v>12379.33303735619</v>
       </c>
       <c r="C174" t="n">
-        <v>19494.43353525137</v>
+        <v>44500.92929869511</v>
       </c>
     </row>
     <row r="175">
@@ -6069,10 +6069,10 @@
         <v>5333</v>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>1856.899955603446</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>6675.139394804333</v>
       </c>
     </row>
     <row r="176">
@@ -6080,10 +6080,10 @@
         <v>5334</v>
       </c>
       <c r="B176" t="n">
-        <v>2070.628765404943</v>
+        <v>2070.628765404715</v>
       </c>
       <c r="C176" t="n">
-        <v>7443.44659078732</v>
+        <v>7443.446590786497</v>
       </c>
     </row>
     <row r="177">
@@ -6091,10 +6091,10 @@
         <v>5335</v>
       </c>
       <c r="B177" t="n">
-        <v>1856.899955603447</v>
+        <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>6675.139394804335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -6300,10 +6300,10 @@
         <v>5354</v>
       </c>
       <c r="B196" t="n">
-        <v>12379.33303735631</v>
+        <v>12379.33303735647</v>
       </c>
       <c r="C196" t="n">
-        <v>44500.92929869557</v>
+        <v>44500.92929869613</v>
       </c>
     </row>
     <row r="197">
@@ -6322,10 +6322,10 @@
         <v>5356</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>1856.899955603444</v>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>6675.139394804326</v>
       </c>
     </row>
     <row r="199">
@@ -6333,10 +6333,10 @@
         <v>5357</v>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>12379.33303735647</v>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>44500.92929869614</v>
       </c>
     </row>
     <row r="200">
@@ -6344,10 +6344,10 @@
         <v>5358</v>
       </c>
       <c r="B200" t="n">
-        <v>2070.628765404943</v>
+        <v>4659.605940207125</v>
       </c>
       <c r="C200" t="n">
-        <v>7443.44659078732</v>
+        <v>16750.23960331401</v>
       </c>
     </row>
     <row r="201">
@@ -7367,10 +7367,10 @@
         <v>5451</v>
       </c>
       <c r="B293" t="n">
-        <v>12379.33303735631</v>
+        <v>8794.585734492903</v>
       </c>
       <c r="C293" t="n">
-        <v>44500.92929869557</v>
+        <v>31614.56572829746</v>
       </c>
     </row>
     <row r="294">
@@ -7378,10 +7378,10 @@
         <v>5452</v>
       </c>
       <c r="B294" t="n">
-        <v>2364.6056215037</v>
+        <v>1856.899955603448</v>
       </c>
       <c r="C294" t="n">
-        <v>8500.227537646582</v>
+        <v>6675.139394804339</v>
       </c>
     </row>
     <row r="295">
@@ -7389,10 +7389,10 @@
         <v>5453</v>
       </c>
       <c r="B295" t="n">
-        <v>1856.899955603448</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C295" t="n">
-        <v>6675.139394804341</v>
+        <v>6675.139394804337</v>
       </c>
     </row>
     <row r="296">
@@ -7565,10 +7565,10 @@
         <v>5469</v>
       </c>
       <c r="B311" t="n">
-        <v>2327.1776631764</v>
+        <v>2327.177663176375</v>
       </c>
       <c r="C311" t="n">
-        <v>8365.682411322605</v>
+        <v>8365.682411322516</v>
       </c>
     </row>
     <row r="312">
@@ -7598,10 +7598,10 @@
         <v>5472</v>
       </c>
       <c r="B314" t="n">
-        <v>1856.899955603442</v>
+        <v>1856.899955603446</v>
       </c>
       <c r="C314" t="n">
-        <v>6675.139394804317</v>
+        <v>6675.139394804331</v>
       </c>
     </row>
     <row r="315">
@@ -7620,10 +7620,10 @@
         <v>5474</v>
       </c>
       <c r="B316" t="n">
-        <v>1856.899955603447</v>
+        <v>1856.899955603445</v>
       </c>
       <c r="C316" t="n">
-        <v>6675.139394804335</v>
+        <v>6675.139394804328</v>
       </c>
     </row>
     <row r="317">
@@ -7631,10 +7631,10 @@
         <v>5475</v>
       </c>
       <c r="B317" t="n">
-        <v>7707.830164704253</v>
+        <v>12379.33303735631</v>
       </c>
       <c r="C317" t="n">
-        <v>27707.92288815489</v>
+        <v>44500.92929869557</v>
       </c>
     </row>
     <row r="318">
@@ -7642,10 +7642,10 @@
         <v>5476</v>
       </c>
       <c r="B318" t="n">
-        <v>1856.89995560341</v>
+        <v>8969.238617531319</v>
       </c>
       <c r="C318" t="n">
-        <v>6675.139394804203</v>
+        <v>32242.40372057476</v>
       </c>
     </row>
     <row r="319">
@@ -7653,10 +7653,10 @@
         <v>5477</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>1856.899955603446</v>
       </c>
       <c r="C319" t="n">
-        <v>0</v>
+        <v>6675.139394804331</v>
       </c>
     </row>
     <row r="320">
@@ -7664,10 +7664,10 @@
         <v>5478</v>
       </c>
       <c r="B320" t="n">
-        <v>1856.89995560344</v>
+        <v>1856.899955603444</v>
       </c>
       <c r="C320" t="n">
-        <v>6675.13939480431</v>
+        <v>6675.139394804326</v>
       </c>
     </row>
     <row r="321">
@@ -7675,10 +7675,10 @@
         <v>5479</v>
       </c>
       <c r="B321" t="n">
-        <v>12379.33303735631</v>
+        <v>12379.33303735647</v>
       </c>
       <c r="C321" t="n">
-        <v>44500.92929869557</v>
+        <v>44500.92929869613</v>
       </c>
     </row>
     <row r="322">
@@ -7829,10 +7829,10 @@
         <v>5493</v>
       </c>
       <c r="B335" t="n">
-        <v>1890.661705562905</v>
+        <v>1856.899955603447</v>
       </c>
       <c r="C335" t="n">
-        <v>6796.505323276597</v>
+        <v>6675.139394804335</v>
       </c>
     </row>
     <row r="336">
@@ -7840,10 +7840,10 @@
         <v>5494</v>
       </c>
       <c r="B336" t="n">
-        <v>0</v>
+        <v>1856.899955603429</v>
       </c>
       <c r="C336" t="n">
-        <v>0</v>
+        <v>6675.139394804271</v>
       </c>
     </row>
     <row r="337">
@@ -7854,7 +7854,7 @@
         <v>1856.899955603446</v>
       </c>
       <c r="C337" t="n">
-        <v>6675.139394804332</v>
+        <v>6675.139394804333</v>
       </c>
     </row>
   </sheetData>
